--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -35182,35 +35182,35 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="D669" t="n">
-        <v>361.43</v>
+        <v>471.66</v>
       </c>
       <c r="E669" t="n">
-        <v>-37.93</v>
+        <v>18.14</v>
       </c>
       <c r="F669" t="n">
-        <v>324.8</v>
+        <v>511.95</v>
       </c>
       <c r="G669" t="n">
-        <v>361.43</v>
+        <v>501.29</v>
       </c>
       <c r="H669" t="n">
-        <v>-36.63</v>
+        <v>10.66</v>
       </c>
       <c r="I669" t="n">
-        <v>316.05</v>
+        <v>485.4</v>
       </c>
       <c r="J669" t="n">
-        <v>318.96</v>
+        <v>480.38</v>
       </c>
       <c r="K669" t="n">
-        <v>-2.91</v>
+        <v>5.02</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         </is>
       </c>
       <c r="N669" t="n">
-        <v>10.49</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="670">
@@ -35234,35 +35234,35 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="D670" t="n">
-        <v>512.71</v>
+        <v>291.87</v>
       </c>
       <c r="E670" t="n">
-        <v>-22.91</v>
+        <v>31.63</v>
       </c>
       <c r="F670" t="n">
-        <v>511.95</v>
+        <v>324.8</v>
       </c>
       <c r="G670" t="n">
-        <v>512.71</v>
+        <v>327.66</v>
       </c>
       <c r="H670" t="n">
-        <v>-0.76</v>
+        <v>-2.86</v>
       </c>
       <c r="I670" t="n">
-        <v>485.4</v>
+        <v>316.05</v>
       </c>
       <c r="J670" t="n">
-        <v>483.68</v>
+        <v>313.87</v>
       </c>
       <c r="K670" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         </is>
       </c>
       <c r="N670" t="n">
-        <v>4.47</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="671">
@@ -35293,28 +35293,28 @@
         <v>3276</v>
       </c>
       <c r="D671" t="n">
-        <v>2650.75</v>
+        <v>4081.14</v>
       </c>
       <c r="E671" t="n">
-        <v>625.25</v>
+        <v>-805.14</v>
       </c>
       <c r="F671" t="n">
         <v>3389</v>
       </c>
       <c r="G671" t="n">
-        <v>3293.11</v>
+        <v>4081.14</v>
       </c>
       <c r="H671" t="n">
-        <v>95.89</v>
+        <v>-692.14</v>
       </c>
       <c r="I671" t="n">
         <v>3247.2</v>
       </c>
       <c r="J671" t="n">
-        <v>3254.88</v>
+        <v>3222.36</v>
       </c>
       <c r="K671" t="n">
-        <v>-7.68</v>
+        <v>24.84</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -35323,11 +35323,11 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N671" t="n">
-        <v>23.59</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="672">
@@ -35338,48 +35338,48 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1026.5</v>
+        <v>431</v>
       </c>
       <c r="D672" t="n">
-        <v>957.6</v>
+        <v>433.19</v>
       </c>
       <c r="E672" t="n">
-        <v>68.90000000000001</v>
+        <v>-2.19</v>
       </c>
       <c r="F672" t="n">
-        <v>1030.7</v>
+        <v>433</v>
       </c>
       <c r="G672" t="n">
-        <v>1021.74</v>
+        <v>443.36</v>
       </c>
       <c r="H672" t="n">
-        <v>8.960000000000001</v>
+        <v>-10.36</v>
       </c>
       <c r="I672" t="n">
-        <v>988</v>
+        <v>418.2</v>
       </c>
       <c r="J672" t="n">
-        <v>1009.53</v>
+        <v>424.93</v>
       </c>
       <c r="K672" t="n">
-        <v>-21.53</v>
+        <v>-6.73</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.2</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="673">
@@ -35397,28 +35397,28 @@
         <v>2153.5</v>
       </c>
       <c r="D673" t="n">
-        <v>2159.29</v>
+        <v>2164.91</v>
       </c>
       <c r="E673" t="n">
-        <v>-5.79</v>
+        <v>-11.41</v>
       </c>
       <c r="F673" t="n">
         <v>2176.2</v>
       </c>
       <c r="G673" t="n">
-        <v>2162.34</v>
+        <v>2209.5</v>
       </c>
       <c r="H673" t="n">
-        <v>13.86</v>
+        <v>-33.3</v>
       </c>
       <c r="I673" t="n">
         <v>2109.8</v>
       </c>
       <c r="J673" t="n">
-        <v>2137.15</v>
+        <v>2117.49</v>
       </c>
       <c r="K673" t="n">
-        <v>-27.35</v>
+        <v>-7.69</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         </is>
       </c>
       <c r="N673" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="674">
@@ -35442,35 +35442,35 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D674" t="n">
-        <v>432.25</v>
+        <v>413.48</v>
       </c>
       <c r="E674" t="n">
-        <v>-1.25</v>
+        <v>5.52</v>
       </c>
       <c r="F674" t="n">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="G674" t="n">
-        <v>434.29</v>
+        <v>427.84</v>
       </c>
       <c r="H674" t="n">
-        <v>-1.29</v>
+        <v>-7.84</v>
       </c>
       <c r="I674" t="n">
-        <v>418.2</v>
+        <v>409.25</v>
       </c>
       <c r="J674" t="n">
-        <v>429.28</v>
+        <v>409.96</v>
       </c>
       <c r="K674" t="n">
-        <v>-11.08</v>
+        <v>-0.71</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         </is>
       </c>
       <c r="N674" t="n">
-        <v>0.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="675">
@@ -35494,35 +35494,35 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>116.75</v>
+        <v>562.9</v>
       </c>
       <c r="D675" t="n">
-        <v>118.63</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="E675" t="n">
-        <v>-1.88</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="F675" t="n">
-        <v>117.79</v>
+        <v>572.35</v>
       </c>
       <c r="G675" t="n">
-        <v>118.63</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="H675" t="n">
-        <v>-0.84</v>
+        <v>0.16</v>
       </c>
       <c r="I675" t="n">
-        <v>114.52</v>
+        <v>546</v>
       </c>
       <c r="J675" t="n">
-        <v>115.96</v>
+        <v>542.64</v>
       </c>
       <c r="K675" t="n">
-        <v>-1.44</v>
+        <v>3.36</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         </is>
       </c>
       <c r="N675" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="676">
@@ -35546,35 +35546,35 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>419</v>
+        <v>287.2</v>
       </c>
       <c r="D676" t="n">
-        <v>427.99</v>
+        <v>296.54</v>
       </c>
       <c r="E676" t="n">
-        <v>-8.99</v>
+        <v>-9.34</v>
       </c>
       <c r="F676" t="n">
-        <v>420</v>
+        <v>287.2</v>
       </c>
       <c r="G676" t="n">
-        <v>427.99</v>
+        <v>296.54</v>
       </c>
       <c r="H676" t="n">
-        <v>-7.99</v>
+        <v>-9.34</v>
       </c>
       <c r="I676" t="n">
-        <v>409.25</v>
+        <v>283.85</v>
       </c>
       <c r="J676" t="n">
-        <v>413.81</v>
+        <v>280.56</v>
       </c>
       <c r="K676" t="n">
-        <v>-4.56</v>
+        <v>3.29</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="N676" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="677">
@@ -35598,35 +35598,35 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>287.2</v>
+        <v>116.75</v>
       </c>
       <c r="D677" t="n">
-        <v>280.38</v>
+        <v>115.81</v>
       </c>
       <c r="E677" t="n">
-        <v>6.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F677" t="n">
-        <v>287.2</v>
+        <v>117.79</v>
       </c>
       <c r="G677" t="n">
-        <v>286.38</v>
+        <v>120.07</v>
       </c>
       <c r="H677" t="n">
-        <v>0.82</v>
+        <v>-2.28</v>
       </c>
       <c r="I677" t="n">
-        <v>283.85</v>
+        <v>114.52</v>
       </c>
       <c r="J677" t="n">
-        <v>282.97</v>
+        <v>115.23</v>
       </c>
       <c r="K677" t="n">
-        <v>0.88</v>
+        <v>-0.71</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         </is>
       </c>
       <c r="N677" t="n">
-        <v>2.43</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="678">
@@ -35650,35 +35650,35 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>1797.3</v>
+        <v>1026.5</v>
       </c>
       <c r="D678" t="n">
-        <v>1820.18</v>
+        <v>1109.16</v>
       </c>
       <c r="E678" t="n">
-        <v>-22.88</v>
+        <v>-82.66</v>
       </c>
       <c r="F678" t="n">
-        <v>1813.3</v>
+        <v>1030.7</v>
       </c>
       <c r="G678" t="n">
-        <v>1820.18</v>
+        <v>1109.16</v>
       </c>
       <c r="H678" t="n">
-        <v>-6.88</v>
+        <v>-78.45999999999999</v>
       </c>
       <c r="I678" t="n">
-        <v>1757.3</v>
+        <v>988</v>
       </c>
       <c r="J678" t="n">
-        <v>1783.33</v>
+        <v>1002.1</v>
       </c>
       <c r="K678" t="n">
-        <v>-26.03</v>
+        <v>-14.1</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         </is>
       </c>
       <c r="N678" t="n">
-        <v>1.26</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="679">
@@ -35702,35 +35702,35 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>562.9</v>
+        <v>1797.3</v>
       </c>
       <c r="D679" t="n">
-        <v>558.1900000000001</v>
+        <v>1788.91</v>
       </c>
       <c r="E679" t="n">
-        <v>4.71</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F679" t="n">
-        <v>572.35</v>
+        <v>1813.3</v>
       </c>
       <c r="G679" t="n">
-        <v>558.1900000000001</v>
+        <v>1845.46</v>
       </c>
       <c r="H679" t="n">
-        <v>14.16</v>
+        <v>-32.16</v>
       </c>
       <c r="I679" t="n">
-        <v>546</v>
+        <v>1757.3</v>
       </c>
       <c r="J679" t="n">
-        <v>547.52</v>
+        <v>1768.66</v>
       </c>
       <c r="K679" t="n">
-        <v>-1.52</v>
+        <v>-11.36</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         </is>
       </c>
       <c r="N679" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -73522,35 +73522,35 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>ETERNAL (SEP-2026 FUT)</t>
+          <t>OIL (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="D669" t="n">
-        <v>368.75</v>
+        <v>483.54</v>
       </c>
       <c r="E669" t="n">
-        <v>-45.25</v>
+        <v>6.26</v>
       </c>
       <c r="F669" t="n">
-        <v>324.8</v>
+        <v>511.95</v>
       </c>
       <c r="G669" t="n">
-        <v>325.59</v>
+        <v>506.38</v>
       </c>
       <c r="H669" t="n">
-        <v>-0.79</v>
+        <v>5.57</v>
       </c>
       <c r="I669" t="n">
-        <v>316.05</v>
+        <v>485.4</v>
       </c>
       <c r="J669" t="n">
-        <v>318.67</v>
+        <v>476.25</v>
       </c>
       <c r="K669" t="n">
-        <v>-2.62</v>
+        <v>9.15</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -73559,11 +73559,11 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N669" t="n">
-        <v>12.27</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="670">
@@ -73574,35 +73574,35 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>OIL (SEP-2026 FUT)</t>
+          <t>ETERNAL (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="D670" t="n">
-        <v>525.87</v>
+        <v>297.65</v>
       </c>
       <c r="E670" t="n">
-        <v>-36.07</v>
+        <v>25.85</v>
       </c>
       <c r="F670" t="n">
-        <v>511.95</v>
+        <v>324.8</v>
       </c>
       <c r="G670" t="n">
-        <v>495.46</v>
+        <v>332.77</v>
       </c>
       <c r="H670" t="n">
-        <v>16.49</v>
+        <v>-7.97</v>
       </c>
       <c r="I670" t="n">
-        <v>485.4</v>
+        <v>316.05</v>
       </c>
       <c r="J670" t="n">
-        <v>480.57</v>
+        <v>315.81</v>
       </c>
       <c r="K670" t="n">
-        <v>4.83</v>
+        <v>0.24</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -73611,11 +73611,11 @@
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N670" t="n">
-        <v>6.86</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="671">
@@ -73633,28 +73633,28 @@
         <v>3276</v>
       </c>
       <c r="D671" t="n">
-        <v>2734.05</v>
+        <v>4207.55</v>
       </c>
       <c r="E671" t="n">
-        <v>541.95</v>
+        <v>-931.55</v>
       </c>
       <c r="F671" t="n">
         <v>3389</v>
       </c>
       <c r="G671" t="n">
-        <v>3331.78</v>
+        <v>3405.25</v>
       </c>
       <c r="H671" t="n">
-        <v>57.22</v>
+        <v>-16.25</v>
       </c>
       <c r="I671" t="n">
         <v>3247.2</v>
       </c>
       <c r="J671" t="n">
-        <v>3200.46</v>
+        <v>3171.76</v>
       </c>
       <c r="K671" t="n">
-        <v>46.74</v>
+        <v>75.44</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -73663,11 +73663,11 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N671" t="n">
-        <v>19.82</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="672">
@@ -73685,28 +73685,28 @@
         <v>1026.5</v>
       </c>
       <c r="D672" t="n">
-        <v>984.3200000000001</v>
+        <v>1139.61</v>
       </c>
       <c r="E672" t="n">
-        <v>42.18</v>
+        <v>-113.11</v>
       </c>
       <c r="F672" t="n">
         <v>1030.7</v>
       </c>
       <c r="G672" t="n">
-        <v>1040.55</v>
+        <v>1063.49</v>
       </c>
       <c r="H672" t="n">
-        <v>-9.85</v>
+        <v>-32.79</v>
       </c>
       <c r="I672" t="n">
         <v>988</v>
       </c>
       <c r="J672" t="n">
-        <v>1005.47</v>
+        <v>996.4400000000001</v>
       </c>
       <c r="K672" t="n">
-        <v>-17.47</v>
+        <v>-8.44</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -73715,11 +73715,11 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N672" t="n">
-        <v>4.29</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="673">
@@ -73730,35 +73730,35 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>APLAPOLLO (SEP-2026 FUT)</t>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>2153.5</v>
+        <v>419</v>
       </c>
       <c r="D673" t="n">
-        <v>2219.05</v>
+        <v>419.36</v>
       </c>
       <c r="E673" t="n">
-        <v>-65.55</v>
+        <v>-0.36</v>
       </c>
       <c r="F673" t="n">
-        <v>2176.2</v>
+        <v>420</v>
       </c>
       <c r="G673" t="n">
-        <v>2182.52</v>
+        <v>428.73</v>
       </c>
       <c r="H673" t="n">
-        <v>-6.32</v>
+        <v>-8.73</v>
       </c>
       <c r="I673" t="n">
-        <v>2109.8</v>
+        <v>409.25</v>
       </c>
       <c r="J673" t="n">
-        <v>2109.72</v>
+        <v>410.73</v>
       </c>
       <c r="K673" t="n">
-        <v>0.08</v>
+        <v>-1.48</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -73767,11 +73767,11 @@
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N673" t="n">
-        <v>2.95</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="674">
@@ -73782,35 +73782,35 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>KOTAKBANK (SEP-2026 FUT)</t>
+          <t>BHEL (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D674" t="n">
-        <v>434.28</v>
+        <v>444.95</v>
       </c>
       <c r="E674" t="n">
-        <v>-15.28</v>
+        <v>-13.95</v>
       </c>
       <c r="F674" t="n">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="G674" t="n">
-        <v>419.48</v>
+        <v>446.41</v>
       </c>
       <c r="H674" t="n">
-        <v>0.52</v>
+        <v>-13.41</v>
       </c>
       <c r="I674" t="n">
-        <v>409.25</v>
+        <v>418.2</v>
       </c>
       <c r="J674" t="n">
-        <v>414.45</v>
+        <v>418.46</v>
       </c>
       <c r="K674" t="n">
-        <v>-5.2</v>
+        <v>-0.26</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -73823,7 +73823,7 @@
         </is>
       </c>
       <c r="N674" t="n">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="675">
@@ -73834,35 +73834,35 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>BHEL (SEP-2026 FUT)</t>
+          <t>PETRONET (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>431</v>
+        <v>287.2</v>
       </c>
       <c r="D675" t="n">
-        <v>443.93</v>
+        <v>302.02</v>
       </c>
       <c r="E675" t="n">
-        <v>-12.93</v>
+        <v>-14.82</v>
       </c>
       <c r="F675" t="n">
-        <v>433</v>
+        <v>287.2</v>
       </c>
       <c r="G675" t="n">
-        <v>436.78</v>
+        <v>295.05</v>
       </c>
       <c r="H675" t="n">
-        <v>-3.78</v>
+        <v>-7.85</v>
       </c>
       <c r="I675" t="n">
-        <v>418.2</v>
+        <v>283.85</v>
       </c>
       <c r="J675" t="n">
-        <v>422.26</v>
+        <v>280.65</v>
       </c>
       <c r="K675" t="n">
-        <v>-4.06</v>
+        <v>3.2</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -73875,7 +73875,7 @@
         </is>
       </c>
       <c r="N675" t="n">
-        <v>2.91</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="676">
@@ -73886,35 +73886,35 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PETRONET (SEP-2026 FUT)</t>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>287.2</v>
+        <v>2153.5</v>
       </c>
       <c r="D676" t="n">
-        <v>285.69</v>
+        <v>2223.85</v>
       </c>
       <c r="E676" t="n">
-        <v>1.51</v>
+        <v>-70.34999999999999</v>
       </c>
       <c r="F676" t="n">
-        <v>287.2</v>
+        <v>2176.2</v>
       </c>
       <c r="G676" t="n">
-        <v>288.69</v>
+        <v>2230.64</v>
       </c>
       <c r="H676" t="n">
-        <v>-1.49</v>
+        <v>-54.44</v>
       </c>
       <c r="I676" t="n">
-        <v>283.85</v>
+        <v>2109.8</v>
       </c>
       <c r="J676" t="n">
-        <v>283.18</v>
+        <v>2090.79</v>
       </c>
       <c r="K676" t="n">
-        <v>0.67</v>
+        <v>19.01</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -73923,11 +73923,11 @@
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N676" t="n">
-        <v>0.53</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="677">
@@ -73945,28 +73945,28 @@
         <v>116.75</v>
       </c>
       <c r="D677" t="n">
-        <v>120.53</v>
+        <v>117.62</v>
       </c>
       <c r="E677" t="n">
-        <v>-3.78</v>
+        <v>-0.87</v>
       </c>
       <c r="F677" t="n">
         <v>117.79</v>
       </c>
       <c r="G677" t="n">
-        <v>117.03</v>
+        <v>119.61</v>
       </c>
       <c r="H677" t="n">
-        <v>0.76</v>
+        <v>-1.82</v>
       </c>
       <c r="I677" t="n">
         <v>114.52</v>
       </c>
       <c r="J677" t="n">
-        <v>115.37</v>
+        <v>114.34</v>
       </c>
       <c r="K677" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -73975,11 +73975,11 @@
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N677" t="n">
-        <v>3.14</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="678">
@@ -73997,28 +73997,28 @@
         <v>562.9</v>
       </c>
       <c r="D678" t="n">
-        <v>574.5700000000001</v>
+        <v>588.73</v>
       </c>
       <c r="E678" t="n">
-        <v>-11.67</v>
+        <v>-25.83</v>
       </c>
       <c r="F678" t="n">
         <v>572.35</v>
       </c>
       <c r="G678" t="n">
-        <v>571.38</v>
+        <v>583.97</v>
       </c>
       <c r="H678" t="n">
-        <v>0.97</v>
+        <v>-11.62</v>
       </c>
       <c r="I678" t="n">
         <v>546</v>
       </c>
       <c r="J678" t="n">
-        <v>550.77</v>
+        <v>545.83</v>
       </c>
       <c r="K678" t="n">
-        <v>-4.77</v>
+        <v>0.17</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -74027,11 +74027,11 @@
       </c>
       <c r="M678" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N678" t="n">
-        <v>2.03</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="679">
@@ -74049,28 +74049,28 @@
         <v>1797.3</v>
       </c>
       <c r="D679" t="n">
-        <v>1868.42</v>
+        <v>1835.52</v>
       </c>
       <c r="E679" t="n">
-        <v>-71.12</v>
+        <v>-38.22</v>
       </c>
       <c r="F679" t="n">
         <v>1813.3</v>
       </c>
       <c r="G679" t="n">
-        <v>1819.51</v>
+        <v>1859.64</v>
       </c>
       <c r="H679" t="n">
-        <v>-6.21</v>
+        <v>-46.34</v>
       </c>
       <c r="I679" t="n">
         <v>1757.3</v>
       </c>
       <c r="J679" t="n">
-        <v>1762.28</v>
+        <v>1746.48</v>
       </c>
       <c r="K679" t="n">
-        <v>-4.98</v>
+        <v>10.82</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -74079,11 +74079,11 @@
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N679" t="n">
-        <v>3.81</v>
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N679"/>
+  <dimension ref="A1:N685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35744,6 +35744,318 @@
       </c>
       <c r="N679" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="D680" t="n">
+        <v>508.32</v>
+      </c>
+      <c r="E680" t="n">
+        <v>-22.72</v>
+      </c>
+      <c r="F680" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="G680" t="n">
+        <v>508.32</v>
+      </c>
+      <c r="H680" t="n">
+        <v>-13.92</v>
+      </c>
+      <c r="I680" t="n">
+        <v>483</v>
+      </c>
+      <c r="J680" t="n">
+        <v>484.69</v>
+      </c>
+      <c r="K680" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N680" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2119.3</v>
+      </c>
+      <c r="D681" t="n">
+        <v>2124.99</v>
+      </c>
+      <c r="E681" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="F681" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G681" t="n">
+        <v>2124.99</v>
+      </c>
+      <c r="H681" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="I681" t="n">
+        <v>2107.7</v>
+      </c>
+      <c r="J681" t="n">
+        <v>2071.16</v>
+      </c>
+      <c r="K681" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N681" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="D682" t="n">
+        <v>418.59</v>
+      </c>
+      <c r="E682" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="F682" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="G682" t="n">
+        <v>418.59</v>
+      </c>
+      <c r="H682" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I682" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="J682" t="n">
+        <v>403.32</v>
+      </c>
+      <c r="K682" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N682" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>3173.5</v>
+      </c>
+      <c r="D683" t="n">
+        <v>2567.81</v>
+      </c>
+      <c r="E683" t="n">
+        <v>605.6900000000001</v>
+      </c>
+      <c r="F683" t="n">
+        <v>3267.6</v>
+      </c>
+      <c r="G683" t="n">
+        <v>3170.33</v>
+      </c>
+      <c r="H683" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="I683" t="n">
+        <v>3156.4</v>
+      </c>
+      <c r="J683" t="n">
+        <v>3153.81</v>
+      </c>
+      <c r="K683" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N683" t="n">
+        <v>23.59</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>990.8</v>
+      </c>
+      <c r="D684" t="n">
+        <v>924.3</v>
+      </c>
+      <c r="E684" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F684" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G684" t="n">
+        <v>975.54</v>
+      </c>
+      <c r="H684" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="I684" t="n">
+        <v>985.1</v>
+      </c>
+      <c r="J684" t="n">
+        <v>969.96</v>
+      </c>
+      <c r="K684" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N684" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>542</v>
+      </c>
+      <c r="D685" t="n">
+        <v>537.47</v>
+      </c>
+      <c r="E685" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F685" t="n">
+        <v>565.25</v>
+      </c>
+      <c r="G685" t="n">
+        <v>537.47</v>
+      </c>
+      <c r="H685" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="I685" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="J685" t="n">
+        <v>526.5599999999999</v>
+      </c>
+      <c r="K685" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N685" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -35757,7 +36069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38741,6 +39053,110 @@
         </is>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23592.85</v>
+      </c>
+      <c r="G58" t="n">
+        <v>23434.76</v>
+      </c>
+      <c r="H58" t="n">
+        <v>158.09</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>22960.51</v>
+      </c>
+      <c r="K58" t="n">
+        <v>158.09</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="D59" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>56996.35</v>
+      </c>
+      <c r="G59" t="n">
+        <v>56595.81</v>
+      </c>
+      <c r="H59" t="n">
+        <v>400.54</v>
+      </c>
+      <c r="I59" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="J59" t="n">
+        <v>55394.21</v>
+      </c>
+      <c r="K59" t="n">
+        <v>400.54</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38755,7 +39171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N679"/>
+  <dimension ref="A1:N685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74086,6 +74502,318 @@
         <v>2.08</v>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>OIL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="D680" t="n">
+        <v>523.0599999999999</v>
+      </c>
+      <c r="E680" t="n">
+        <v>-37.46</v>
+      </c>
+      <c r="F680" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="G680" t="n">
+        <v>490.85</v>
+      </c>
+      <c r="H680" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I680" t="n">
+        <v>483</v>
+      </c>
+      <c r="J680" t="n">
+        <v>476.14</v>
+      </c>
+      <c r="K680" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N680" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>3173.5</v>
+      </c>
+      <c r="D681" t="n">
+        <v>2652.8</v>
+      </c>
+      <c r="E681" t="n">
+        <v>520.7</v>
+      </c>
+      <c r="F681" t="n">
+        <v>3267.6</v>
+      </c>
+      <c r="G681" t="n">
+        <v>3220.03</v>
+      </c>
+      <c r="H681" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I681" t="n">
+        <v>3156.4</v>
+      </c>
+      <c r="J681" t="n">
+        <v>3102.27</v>
+      </c>
+      <c r="K681" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N681" t="n">
+        <v>19.63</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>990.8</v>
+      </c>
+      <c r="D682" t="n">
+        <v>952.12</v>
+      </c>
+      <c r="E682" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="F682" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G682" t="n">
+        <v>1002.52</v>
+      </c>
+      <c r="H682" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="I682" t="n">
+        <v>985.1</v>
+      </c>
+      <c r="J682" t="n">
+        <v>970.71</v>
+      </c>
+      <c r="K682" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N682" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2119.3</v>
+      </c>
+      <c r="D683" t="n">
+        <v>2187.95</v>
+      </c>
+      <c r="E683" t="n">
+        <v>-68.65000000000001</v>
+      </c>
+      <c r="F683" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G683" t="n">
+        <v>2143.43</v>
+      </c>
+      <c r="H683" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="I683" t="n">
+        <v>2107.7</v>
+      </c>
+      <c r="J683" t="n">
+        <v>2077.1</v>
+      </c>
+      <c r="K683" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N683" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="D684" t="n">
+        <v>425.04</v>
+      </c>
+      <c r="E684" t="n">
+        <v>-15.24</v>
+      </c>
+      <c r="F684" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="G684" t="n">
+        <v>408.95</v>
+      </c>
+      <c r="H684" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I684" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="J684" t="n">
+        <v>405.91</v>
+      </c>
+      <c r="K684" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N684" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>542</v>
+      </c>
+      <c r="D685" t="n">
+        <v>555.1799999999999</v>
+      </c>
+      <c r="E685" t="n">
+        <v>-13.18</v>
+      </c>
+      <c r="F685" t="n">
+        <v>565.25</v>
+      </c>
+      <c r="G685" t="n">
+        <v>549.89</v>
+      </c>
+      <c r="H685" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I685" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="J685" t="n">
+        <v>529.89</v>
+      </c>
+      <c r="K685" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N685" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -35758,31 +35758,31 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>485.6</v>
+        <v>489.8</v>
       </c>
       <c r="D680" t="n">
         <v>508.32</v>
       </c>
       <c r="E680" t="n">
-        <v>-22.72</v>
+        <v>-18.52</v>
       </c>
       <c r="F680" t="n">
-        <v>494.4</v>
+        <v>511.95</v>
       </c>
       <c r="G680" t="n">
         <v>508.32</v>
       </c>
       <c r="H680" t="n">
-        <v>-13.92</v>
+        <v>3.63</v>
       </c>
       <c r="I680" t="n">
-        <v>483</v>
+        <v>485.4</v>
       </c>
       <c r="J680" t="n">
         <v>484.69</v>
       </c>
       <c r="K680" t="n">
-        <v>-1.69</v>
+        <v>0.71</v>
       </c>
       <c r="L680" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         </is>
       </c>
       <c r="N680" t="n">
-        <v>4.47</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="681">
@@ -35810,31 +35810,31 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>2119.3</v>
+        <v>2153.5</v>
       </c>
       <c r="D681" t="n">
         <v>2124.99</v>
       </c>
       <c r="E681" t="n">
-        <v>-5.69</v>
+        <v>28.51</v>
       </c>
       <c r="F681" t="n">
-        <v>2160</v>
+        <v>2176.2</v>
       </c>
       <c r="G681" t="n">
         <v>2124.99</v>
       </c>
       <c r="H681" t="n">
-        <v>35.01</v>
+        <v>51.21</v>
       </c>
       <c r="I681" t="n">
-        <v>2107.7</v>
+        <v>2109.8</v>
       </c>
       <c r="J681" t="n">
         <v>2071.16</v>
       </c>
       <c r="K681" t="n">
-        <v>36.54</v>
+        <v>38.64</v>
       </c>
       <c r="L681" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         </is>
       </c>
       <c r="N681" t="n">
-        <v>0.27</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="682">
@@ -35862,31 +35862,31 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>409.8</v>
+        <v>419</v>
       </c>
       <c r="D682" t="n">
         <v>418.59</v>
       </c>
       <c r="E682" t="n">
-        <v>-8.789999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="F682" t="n">
-        <v>420.5</v>
+        <v>420</v>
       </c>
       <c r="G682" t="n">
         <v>418.59</v>
       </c>
       <c r="H682" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="I682" t="n">
-        <v>409.8</v>
+        <v>409.25</v>
       </c>
       <c r="J682" t="n">
         <v>403.32</v>
       </c>
       <c r="K682" t="n">
-        <v>6.48</v>
+        <v>5.93</v>
       </c>
       <c r="L682" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         </is>
       </c>
       <c r="N682" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="683">
@@ -35914,31 +35914,31 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>3173.5</v>
+        <v>3276</v>
       </c>
       <c r="D683" t="n">
         <v>2567.81</v>
       </c>
       <c r="E683" t="n">
-        <v>605.6900000000001</v>
+        <v>708.1900000000001</v>
       </c>
       <c r="F683" t="n">
-        <v>3267.6</v>
+        <v>3389</v>
       </c>
       <c r="G683" t="n">
         <v>3170.33</v>
       </c>
       <c r="H683" t="n">
-        <v>97.27</v>
+        <v>218.67</v>
       </c>
       <c r="I683" t="n">
-        <v>3156.4</v>
+        <v>3247.2</v>
       </c>
       <c r="J683" t="n">
         <v>3153.81</v>
       </c>
       <c r="K683" t="n">
-        <v>2.59</v>
+        <v>93.39</v>
       </c>
       <c r="L683" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         </is>
       </c>
       <c r="N683" t="n">
-        <v>23.59</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="684">
@@ -35966,31 +35966,31 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>990.8</v>
+        <v>1026.5</v>
       </c>
       <c r="D684" t="n">
         <v>924.3</v>
       </c>
       <c r="E684" t="n">
-        <v>66.5</v>
+        <v>102.2</v>
       </c>
       <c r="F684" t="n">
-        <v>1030</v>
+        <v>1030.7</v>
       </c>
       <c r="G684" t="n">
         <v>975.54</v>
       </c>
       <c r="H684" t="n">
-        <v>54.46</v>
+        <v>55.16</v>
       </c>
       <c r="I684" t="n">
-        <v>985.1</v>
+        <v>988</v>
       </c>
       <c r="J684" t="n">
         <v>969.96</v>
       </c>
       <c r="K684" t="n">
-        <v>15.14</v>
+        <v>18.04</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         </is>
       </c>
       <c r="N684" t="n">
-        <v>7.19</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="685">
@@ -36018,31 +36018,31 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>542</v>
+        <v>562.9</v>
       </c>
       <c r="D685" t="n">
         <v>537.47</v>
       </c>
       <c r="E685" t="n">
-        <v>4.53</v>
+        <v>25.43</v>
       </c>
       <c r="F685" t="n">
-        <v>565.25</v>
+        <v>572.35</v>
       </c>
       <c r="G685" t="n">
         <v>537.47</v>
       </c>
       <c r="H685" t="n">
-        <v>27.78</v>
+        <v>34.88</v>
       </c>
       <c r="I685" t="n">
-        <v>538.5</v>
+        <v>546</v>
       </c>
       <c r="J685" t="n">
         <v>526.5599999999999</v>
       </c>
       <c r="K685" t="n">
-        <v>11.94</v>
+        <v>19.44</v>
       </c>
       <c r="L685" t="inlineStr">
         <is>
@@ -36051,11 +36051,11 @@
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N685" t="n">
-        <v>0.84</v>
+        <v>4.73</v>
       </c>
     </row>
   </sheetData>
@@ -39068,31 +39068,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>23118.6</v>
+        <v>23398.1</v>
       </c>
       <c r="D58" t="n">
         <v>23118.6</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>279.5</v>
       </c>
       <c r="F58" t="n">
-        <v>23592.85</v>
+        <v>23448.1</v>
       </c>
       <c r="G58" t="n">
         <v>23434.76</v>
       </c>
       <c r="H58" t="n">
-        <v>158.09</v>
+        <v>13.34</v>
       </c>
       <c r="I58" t="n">
-        <v>23118.6</v>
+        <v>23231.4</v>
       </c>
       <c r="J58" t="n">
         <v>22960.51</v>
       </c>
       <c r="K58" t="n">
-        <v>158.09</v>
+        <v>270.89</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="59">
@@ -39120,31 +39120,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>55794.75</v>
+        <v>56606.55</v>
       </c>
       <c r="D59" t="n">
         <v>55794.75</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>811.8</v>
       </c>
       <c r="F59" t="n">
-        <v>56996.35</v>
+        <v>56645.85</v>
       </c>
       <c r="G59" t="n">
         <v>56595.81</v>
       </c>
       <c r="H59" t="n">
-        <v>400.54</v>
+        <v>50.04</v>
       </c>
       <c r="I59" t="n">
-        <v>55794.75</v>
+        <v>55699.45</v>
       </c>
       <c r="J59" t="n">
         <v>55394.21</v>
       </c>
       <c r="K59" t="n">
-        <v>400.54</v>
+        <v>305.24</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -74514,31 +74514,31 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>485.6</v>
+        <v>489.8</v>
       </c>
       <c r="D680" t="n">
         <v>523.0599999999999</v>
       </c>
       <c r="E680" t="n">
-        <v>-37.46</v>
+        <v>-33.26</v>
       </c>
       <c r="F680" t="n">
-        <v>494.4</v>
+        <v>511.95</v>
       </c>
       <c r="G680" t="n">
         <v>490.85</v>
       </c>
       <c r="H680" t="n">
-        <v>3.55</v>
+        <v>21.1</v>
       </c>
       <c r="I680" t="n">
-        <v>483</v>
+        <v>485.4</v>
       </c>
       <c r="J680" t="n">
         <v>476.14</v>
       </c>
       <c r="K680" t="n">
-        <v>6.86</v>
+        <v>9.26</v>
       </c>
       <c r="L680" t="inlineStr">
         <is>
@@ -74551,7 +74551,7 @@
         </is>
       </c>
       <c r="N680" t="n">
-        <v>7.16</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="681">
@@ -74566,31 +74566,31 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>3173.5</v>
+        <v>3276</v>
       </c>
       <c r="D681" t="n">
         <v>2652.8</v>
       </c>
       <c r="E681" t="n">
-        <v>520.7</v>
+        <v>623.2</v>
       </c>
       <c r="F681" t="n">
-        <v>3267.6</v>
+        <v>3389</v>
       </c>
       <c r="G681" t="n">
         <v>3220.03</v>
       </c>
       <c r="H681" t="n">
-        <v>47.57</v>
+        <v>168.97</v>
       </c>
       <c r="I681" t="n">
-        <v>3156.4</v>
+        <v>3247.2</v>
       </c>
       <c r="J681" t="n">
         <v>3102.27</v>
       </c>
       <c r="K681" t="n">
-        <v>54.13</v>
+        <v>144.93</v>
       </c>
       <c r="L681" t="inlineStr">
         <is>
@@ -74603,7 +74603,7 @@
         </is>
       </c>
       <c r="N681" t="n">
-        <v>19.63</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="682">
@@ -74618,31 +74618,31 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>990.8</v>
+        <v>1026.5</v>
       </c>
       <c r="D682" t="n">
         <v>952.12</v>
       </c>
       <c r="E682" t="n">
-        <v>38.68</v>
+        <v>74.38</v>
       </c>
       <c r="F682" t="n">
-        <v>1030</v>
+        <v>1030.7</v>
       </c>
       <c r="G682" t="n">
         <v>1002.52</v>
       </c>
       <c r="H682" t="n">
-        <v>27.48</v>
+        <v>28.18</v>
       </c>
       <c r="I682" t="n">
-        <v>985.1</v>
+        <v>988</v>
       </c>
       <c r="J682" t="n">
         <v>970.71</v>
       </c>
       <c r="K682" t="n">
-        <v>14.39</v>
+        <v>17.29</v>
       </c>
       <c r="L682" t="inlineStr">
         <is>
@@ -74655,7 +74655,7 @@
         </is>
       </c>
       <c r="N682" t="n">
-        <v>4.06</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="683">
@@ -74670,31 +74670,31 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>2119.3</v>
+        <v>2153.5</v>
       </c>
       <c r="D683" t="n">
         <v>2187.95</v>
       </c>
       <c r="E683" t="n">
-        <v>-68.65000000000001</v>
+        <v>-34.45</v>
       </c>
       <c r="F683" t="n">
-        <v>2160</v>
+        <v>2176.2</v>
       </c>
       <c r="G683" t="n">
         <v>2143.43</v>
       </c>
       <c r="H683" t="n">
-        <v>16.57</v>
+        <v>32.77</v>
       </c>
       <c r="I683" t="n">
-        <v>2107.7</v>
+        <v>2109.8</v>
       </c>
       <c r="J683" t="n">
         <v>2077.1</v>
       </c>
       <c r="K683" t="n">
-        <v>30.6</v>
+        <v>32.7</v>
       </c>
       <c r="L683" t="inlineStr">
         <is>
@@ -74703,11 +74703,11 @@
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N683" t="n">
-        <v>3.14</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="684">
@@ -74722,31 +74722,31 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>409.8</v>
+        <v>419</v>
       </c>
       <c r="D684" t="n">
         <v>425.04</v>
       </c>
       <c r="E684" t="n">
-        <v>-15.24</v>
+        <v>-6.04</v>
       </c>
       <c r="F684" t="n">
-        <v>420.5</v>
+        <v>420</v>
       </c>
       <c r="G684" t="n">
         <v>408.95</v>
       </c>
       <c r="H684" t="n">
-        <v>11.55</v>
+        <v>11.05</v>
       </c>
       <c r="I684" t="n">
-        <v>409.8</v>
+        <v>409.25</v>
       </c>
       <c r="J684" t="n">
         <v>405.91</v>
       </c>
       <c r="K684" t="n">
-        <v>3.89</v>
+        <v>3.34</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -74755,11 +74755,11 @@
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N684" t="n">
-        <v>3.59</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="685">
@@ -74774,31 +74774,31 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>542</v>
+        <v>562.9</v>
       </c>
       <c r="D685" t="n">
         <v>555.1799999999999</v>
       </c>
       <c r="E685" t="n">
-        <v>-13.18</v>
+        <v>7.72</v>
       </c>
       <c r="F685" t="n">
-        <v>565.25</v>
+        <v>572.35</v>
       </c>
       <c r="G685" t="n">
         <v>549.89</v>
       </c>
       <c r="H685" t="n">
-        <v>15.36</v>
+        <v>22.46</v>
       </c>
       <c r="I685" t="n">
-        <v>538.5</v>
+        <v>546</v>
       </c>
       <c r="J685" t="n">
         <v>529.89</v>
       </c>
       <c r="K685" t="n">
-        <v>8.609999999999999</v>
+        <v>16.11</v>
       </c>
       <c r="L685" t="inlineStr">
         <is>
@@ -74811,7 +74811,7 @@
         </is>
       </c>
       <c r="N685" t="n">
-        <v>2.37</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N685"/>
+  <dimension ref="A1:N692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36056,6 +36056,370 @@
       </c>
       <c r="N685" t="n">
         <v>4.73</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D686" t="n">
+        <v>473.59</v>
+      </c>
+      <c r="E686" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="F686" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="G686" t="n">
+        <v>507.49</v>
+      </c>
+      <c r="H686" t="n">
+        <v>-17.99</v>
+      </c>
+      <c r="I686" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="J686" t="n">
+        <v>487.1</v>
+      </c>
+      <c r="K686" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N686" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>415</v>
+      </c>
+      <c r="D687" t="n">
+        <v>418.73</v>
+      </c>
+      <c r="E687" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="F687" t="n">
+        <v>417.05</v>
+      </c>
+      <c r="G687" t="n">
+        <v>434.81</v>
+      </c>
+      <c r="H687" t="n">
+        <v>-17.76</v>
+      </c>
+      <c r="I687" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="J687" t="n">
+        <v>415</v>
+      </c>
+      <c r="K687" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N687" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="D688" t="n">
+        <v>1932.24</v>
+      </c>
+      <c r="E688" t="n">
+        <v>-105.14</v>
+      </c>
+      <c r="F688" t="n">
+        <v>1847</v>
+      </c>
+      <c r="G688" t="n">
+        <v>1947.92</v>
+      </c>
+      <c r="H688" t="n">
+        <v>-100.92</v>
+      </c>
+      <c r="I688" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="J688" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="K688" t="n">
+        <v>-117</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N688" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="D689" t="n">
+        <v>121.96</v>
+      </c>
+      <c r="E689" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="F689" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="G689" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="H689" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I689" t="n">
+        <v>114.63</v>
+      </c>
+      <c r="J689" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="K689" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N689" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>3211.2</v>
+      </c>
+      <c r="D690" t="n">
+        <v>4129.62</v>
+      </c>
+      <c r="E690" t="n">
+        <v>-918.42</v>
+      </c>
+      <c r="F690" t="n">
+        <v>3224.5</v>
+      </c>
+      <c r="G690" t="n">
+        <v>4129.62</v>
+      </c>
+      <c r="H690" t="n">
+        <v>-905.12</v>
+      </c>
+      <c r="I690" t="n">
+        <v>3056.6</v>
+      </c>
+      <c r="J690" t="n">
+        <v>3181.06</v>
+      </c>
+      <c r="K690" t="n">
+        <v>-124.46</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N690" t="n">
+        <v>22.24</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>543</v>
+      </c>
+      <c r="D691" t="n">
+        <v>573.23</v>
+      </c>
+      <c r="E691" t="n">
+        <v>-30.23</v>
+      </c>
+      <c r="F691" t="n">
+        <v>551.45</v>
+      </c>
+      <c r="G691" t="n">
+        <v>573.23</v>
+      </c>
+      <c r="H691" t="n">
+        <v>-21.78</v>
+      </c>
+      <c r="I691" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="J691" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="K691" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N691" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="D692" t="n">
+        <v>1093.15</v>
+      </c>
+      <c r="E692" t="n">
+        <v>-116.65</v>
+      </c>
+      <c r="F692" t="n">
+        <v>989.9</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1093.15</v>
+      </c>
+      <c r="H692" t="n">
+        <v>-103.25</v>
+      </c>
+      <c r="I692" t="n">
+        <v>963.8</v>
+      </c>
+      <c r="J692" t="n">
+        <v>974.96</v>
+      </c>
+      <c r="K692" t="n">
+        <v>-11.16</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N692" t="n">
+        <v>10.67</v>
       </c>
     </row>
   </sheetData>
@@ -36069,7 +36433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39158,6 +39522,110 @@
       </c>
       <c r="N59" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>23217.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>23217.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>23284.75</v>
+      </c>
+      <c r="G60" t="n">
+        <v>23296.2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="I60" t="n">
+        <v>23116.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>23127.55</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>56292.45</v>
+      </c>
+      <c r="D61" t="n">
+        <v>56292.45</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>56368.7</v>
+      </c>
+      <c r="G61" t="n">
+        <v>56503.36</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-134.66</v>
+      </c>
+      <c r="I61" t="n">
+        <v>55812.2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>55946.86</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-134.66</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -39171,7 +39639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N685"/>
+  <dimension ref="A1:N692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74814,6 +75282,370 @@
         <v>1.39</v>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>OIL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D686" t="n">
+        <v>485.96</v>
+      </c>
+      <c r="E686" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F686" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="G686" t="n">
+        <v>515.62</v>
+      </c>
+      <c r="H686" t="n">
+        <v>-26.12</v>
+      </c>
+      <c r="I686" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="J686" t="n">
+        <v>484.96</v>
+      </c>
+      <c r="K686" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N686" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>POLICYBZR (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="D687" t="n">
+        <v>1955.96</v>
+      </c>
+      <c r="E687" t="n">
+        <v>-128.86</v>
+      </c>
+      <c r="F687" t="n">
+        <v>1847</v>
+      </c>
+      <c r="G687" t="n">
+        <v>1934.66</v>
+      </c>
+      <c r="H687" t="n">
+        <v>-87.66</v>
+      </c>
+      <c r="I687" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="J687" t="n">
+        <v>1815.3</v>
+      </c>
+      <c r="K687" t="n">
+        <v>-105.2</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N687" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="D688" t="n">
+        <v>123.52</v>
+      </c>
+      <c r="E688" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="F688" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="G688" t="n">
+        <v>122.23</v>
+      </c>
+      <c r="H688" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="I688" t="n">
+        <v>114.63</v>
+      </c>
+      <c r="J688" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="K688" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N688" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>415</v>
+      </c>
+      <c r="D689" t="n">
+        <v>424.15</v>
+      </c>
+      <c r="E689" t="n">
+        <v>-9.15</v>
+      </c>
+      <c r="F689" t="n">
+        <v>417.05</v>
+      </c>
+      <c r="G689" t="n">
+        <v>433.44</v>
+      </c>
+      <c r="H689" t="n">
+        <v>-16.39</v>
+      </c>
+      <c r="I689" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="J689" t="n">
+        <v>416.79</v>
+      </c>
+      <c r="K689" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N689" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>3211.2</v>
+      </c>
+      <c r="D690" t="n">
+        <v>4258.51</v>
+      </c>
+      <c r="E690" t="n">
+        <v>-1047.31</v>
+      </c>
+      <c r="F690" t="n">
+        <v>3224.5</v>
+      </c>
+      <c r="G690" t="n">
+        <v>3412.02</v>
+      </c>
+      <c r="H690" t="n">
+        <v>-187.52</v>
+      </c>
+      <c r="I690" t="n">
+        <v>3056.6</v>
+      </c>
+      <c r="J690" t="n">
+        <v>3181.69</v>
+      </c>
+      <c r="K690" t="n">
+        <v>-125.09</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N690" t="n">
+        <v>24.59</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>543</v>
+      </c>
+      <c r="D691" t="n">
+        <v>593.14</v>
+      </c>
+      <c r="E691" t="n">
+        <v>-50.14</v>
+      </c>
+      <c r="F691" t="n">
+        <v>551.45</v>
+      </c>
+      <c r="G691" t="n">
+        <v>578.85</v>
+      </c>
+      <c r="H691" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="I691" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="J691" t="n">
+        <v>536.6</v>
+      </c>
+      <c r="K691" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N691" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="D692" t="n">
+        <v>1127.97</v>
+      </c>
+      <c r="E692" t="n">
+        <v>-151.47</v>
+      </c>
+      <c r="F692" t="n">
+        <v>989.9</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1038.2</v>
+      </c>
+      <c r="H692" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="I692" t="n">
+        <v>963.8</v>
+      </c>
+      <c r="J692" t="n">
+        <v>967.0700000000001</v>
+      </c>
+      <c r="K692" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N692" t="n">
+        <v>13.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -36070,31 +36070,31 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>487.6</v>
+        <v>485.6</v>
       </c>
       <c r="D686" t="n">
         <v>473.59</v>
       </c>
       <c r="E686" t="n">
-        <v>14.01</v>
+        <v>12.01</v>
       </c>
       <c r="F686" t="n">
-        <v>489.5</v>
+        <v>494.4</v>
       </c>
       <c r="G686" t="n">
         <v>507.49</v>
       </c>
       <c r="H686" t="n">
-        <v>-17.99</v>
+        <v>-13.09</v>
       </c>
       <c r="I686" t="n">
-        <v>481.4</v>
+        <v>483</v>
       </c>
       <c r="J686" t="n">
         <v>487.1</v>
       </c>
       <c r="K686" t="n">
-        <v>-5.7</v>
+        <v>-4.1</v>
       </c>
       <c r="L686" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         </is>
       </c>
       <c r="N686" t="n">
-        <v>2.96</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="687">
@@ -36122,31 +36122,31 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>415</v>
+        <v>409.8</v>
       </c>
       <c r="D687" t="n">
         <v>418.73</v>
       </c>
       <c r="E687" t="n">
-        <v>-3.73</v>
+        <v>-8.93</v>
       </c>
       <c r="F687" t="n">
-        <v>417.05</v>
+        <v>420.5</v>
       </c>
       <c r="G687" t="n">
         <v>434.81</v>
       </c>
       <c r="H687" t="n">
-        <v>-17.76</v>
+        <v>-14.31</v>
       </c>
       <c r="I687" t="n">
-        <v>409.35</v>
+        <v>409.8</v>
       </c>
       <c r="J687" t="n">
         <v>415</v>
       </c>
       <c r="K687" t="n">
-        <v>-5.65</v>
+        <v>-5.2</v>
       </c>
       <c r="L687" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         </is>
       </c>
       <c r="N687" t="n">
-        <v>0.89</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="688">
@@ -36174,31 +36174,31 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>1827.1</v>
+        <v>1736</v>
       </c>
       <c r="D688" t="n">
         <v>1932.24</v>
       </c>
       <c r="E688" t="n">
-        <v>-105.14</v>
+        <v>-196.24</v>
       </c>
       <c r="F688" t="n">
-        <v>1847</v>
+        <v>1804.3</v>
       </c>
       <c r="G688" t="n">
         <v>1947.92</v>
       </c>
       <c r="H688" t="n">
-        <v>-100.92</v>
+        <v>-143.62</v>
       </c>
       <c r="I688" t="n">
-        <v>1710.1</v>
+        <v>1736</v>
       </c>
       <c r="J688" t="n">
         <v>1827.1</v>
       </c>
       <c r="K688" t="n">
-        <v>-117</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="L688" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         </is>
       </c>
       <c r="N688" t="n">
-        <v>5.44</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="689">
@@ -36226,31 +36226,31 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>116.8</v>
+        <v>114.7</v>
       </c>
       <c r="D689" t="n">
         <v>121.96</v>
       </c>
       <c r="E689" t="n">
-        <v>-5.16</v>
+        <v>-7.26</v>
       </c>
       <c r="F689" t="n">
-        <v>117.48</v>
+        <v>117.23</v>
       </c>
       <c r="G689" t="n">
         <v>122.72</v>
       </c>
       <c r="H689" t="n">
-        <v>-5.24</v>
+        <v>-5.49</v>
       </c>
       <c r="I689" t="n">
-        <v>114.63</v>
+        <v>114.7</v>
       </c>
       <c r="J689" t="n">
         <v>116.8</v>
       </c>
       <c r="K689" t="n">
-        <v>-2.17</v>
+        <v>-2.1</v>
       </c>
       <c r="L689" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         </is>
       </c>
       <c r="N689" t="n">
-        <v>4.23</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="690">
@@ -36278,31 +36278,31 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>3211.2</v>
+        <v>3173.5</v>
       </c>
       <c r="D690" t="n">
         <v>4129.62</v>
       </c>
       <c r="E690" t="n">
-        <v>-918.42</v>
+        <v>-956.12</v>
       </c>
       <c r="F690" t="n">
-        <v>3224.5</v>
+        <v>3267.6</v>
       </c>
       <c r="G690" t="n">
         <v>4129.62</v>
       </c>
       <c r="H690" t="n">
-        <v>-905.12</v>
+        <v>-862.02</v>
       </c>
       <c r="I690" t="n">
-        <v>3056.6</v>
+        <v>3156.4</v>
       </c>
       <c r="J690" t="n">
         <v>3181.06</v>
       </c>
       <c r="K690" t="n">
-        <v>-124.46</v>
+        <v>-24.66</v>
       </c>
       <c r="L690" t="inlineStr">
         <is>
@@ -36311,11 +36311,11 @@
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N690" t="n">
-        <v>22.24</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="691">
@@ -36330,31 +36330,31 @@
         </is>
       </c>
       <c r="C691" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D691" t="n">
         <v>573.23</v>
       </c>
       <c r="E691" t="n">
-        <v>-30.23</v>
+        <v>-31.23</v>
       </c>
       <c r="F691" t="n">
-        <v>551.45</v>
+        <v>565.25</v>
       </c>
       <c r="G691" t="n">
         <v>573.23</v>
       </c>
       <c r="H691" t="n">
-        <v>-21.78</v>
+        <v>-7.98</v>
       </c>
       <c r="I691" t="n">
-        <v>529.6</v>
+        <v>538.5</v>
       </c>
       <c r="J691" t="n">
         <v>542.7</v>
       </c>
       <c r="K691" t="n">
-        <v>-13.1</v>
+        <v>-4.2</v>
       </c>
       <c r="L691" t="inlineStr">
         <is>
@@ -36363,11 +36363,11 @@
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N691" t="n">
-        <v>5.27</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="692">
@@ -36382,31 +36382,31 @@
         </is>
       </c>
       <c r="C692" t="n">
-        <v>976.5</v>
+        <v>990.8</v>
       </c>
       <c r="D692" t="n">
         <v>1093.15</v>
       </c>
       <c r="E692" t="n">
-        <v>-116.65</v>
+        <v>-102.35</v>
       </c>
       <c r="F692" t="n">
-        <v>989.9</v>
+        <v>1030</v>
       </c>
       <c r="G692" t="n">
         <v>1093.15</v>
       </c>
       <c r="H692" t="n">
-        <v>-103.25</v>
+        <v>-63.15</v>
       </c>
       <c r="I692" t="n">
-        <v>963.8</v>
+        <v>985.1</v>
       </c>
       <c r="J692" t="n">
         <v>974.96</v>
       </c>
       <c r="K692" t="n">
-        <v>-11.16</v>
+        <v>10.14</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         </is>
       </c>
       <c r="N692" t="n">
-        <v>10.67</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -39536,31 +39536,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>23217.6</v>
+        <v>23118.6</v>
       </c>
       <c r="D60" t="n">
         <v>23217.6</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="F60" t="n">
-        <v>23284.75</v>
+        <v>23592.85</v>
       </c>
       <c r="G60" t="n">
         <v>23296.2</v>
       </c>
       <c r="H60" t="n">
-        <v>-11.45</v>
+        <v>296.65</v>
       </c>
       <c r="I60" t="n">
-        <v>23116.1</v>
+        <v>23118.6</v>
       </c>
       <c r="J60" t="n">
         <v>23127.55</v>
       </c>
       <c r="K60" t="n">
-        <v>-11.45</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="61">
@@ -39588,31 +39588,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>56292.45</v>
+        <v>55794.75</v>
       </c>
       <c r="D61" t="n">
         <v>56292.45</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-497.7</v>
       </c>
       <c r="F61" t="n">
-        <v>56368.7</v>
+        <v>56996.35</v>
       </c>
       <c r="G61" t="n">
         <v>56503.36</v>
       </c>
       <c r="H61" t="n">
-        <v>-134.66</v>
+        <v>492.99</v>
       </c>
       <c r="I61" t="n">
-        <v>55812.2</v>
+        <v>55794.75</v>
       </c>
       <c r="J61" t="n">
         <v>55946.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-134.66</v>
+        <v>-152.11</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -75294,31 +75294,31 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>487.6</v>
+        <v>485.6</v>
       </c>
       <c r="D686" t="n">
         <v>485.96</v>
       </c>
       <c r="E686" t="n">
-        <v>1.64</v>
+        <v>-0.36</v>
       </c>
       <c r="F686" t="n">
-        <v>489.5</v>
+        <v>494.4</v>
       </c>
       <c r="G686" t="n">
         <v>515.62</v>
       </c>
       <c r="H686" t="n">
-        <v>-26.12</v>
+        <v>-21.22</v>
       </c>
       <c r="I686" t="n">
-        <v>481.4</v>
+        <v>483</v>
       </c>
       <c r="J686" t="n">
         <v>484.96</v>
       </c>
       <c r="K686" t="n">
-        <v>-3.56</v>
+        <v>-1.96</v>
       </c>
       <c r="L686" t="inlineStr">
         <is>
@@ -75331,7 +75331,7 @@
         </is>
       </c>
       <c r="N686" t="n">
-        <v>0.34</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="687">
@@ -75346,31 +75346,31 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>1827.1</v>
+        <v>1736</v>
       </c>
       <c r="D687" t="n">
         <v>1955.96</v>
       </c>
       <c r="E687" t="n">
-        <v>-128.86</v>
+        <v>-219.96</v>
       </c>
       <c r="F687" t="n">
-        <v>1847</v>
+        <v>1804.3</v>
       </c>
       <c r="G687" t="n">
         <v>1934.66</v>
       </c>
       <c r="H687" t="n">
-        <v>-87.66</v>
+        <v>-130.36</v>
       </c>
       <c r="I687" t="n">
-        <v>1710.1</v>
+        <v>1736</v>
       </c>
       <c r="J687" t="n">
         <v>1815.3</v>
       </c>
       <c r="K687" t="n">
-        <v>-105.2</v>
+        <v>-79.3</v>
       </c>
       <c r="L687" t="inlineStr">
         <is>
@@ -75383,7 +75383,7 @@
         </is>
       </c>
       <c r="N687" t="n">
-        <v>6.59</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="688">
@@ -75398,31 +75398,31 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>116.8</v>
+        <v>114.7</v>
       </c>
       <c r="D688" t="n">
         <v>123.52</v>
       </c>
       <c r="E688" t="n">
-        <v>-6.72</v>
+        <v>-8.82</v>
       </c>
       <c r="F688" t="n">
-        <v>117.48</v>
+        <v>117.23</v>
       </c>
       <c r="G688" t="n">
         <v>122.23</v>
       </c>
       <c r="H688" t="n">
-        <v>-4.75</v>
+        <v>-5</v>
       </c>
       <c r="I688" t="n">
-        <v>114.63</v>
+        <v>114.7</v>
       </c>
       <c r="J688" t="n">
         <v>117.12</v>
       </c>
       <c r="K688" t="n">
-        <v>-2.49</v>
+        <v>-2.42</v>
       </c>
       <c r="L688" t="inlineStr">
         <is>
@@ -75435,7 +75435,7 @@
         </is>
       </c>
       <c r="N688" t="n">
-        <v>5.44</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="689">
@@ -75450,31 +75450,31 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>415</v>
+        <v>409.8</v>
       </c>
       <c r="D689" t="n">
         <v>424.15</v>
       </c>
       <c r="E689" t="n">
-        <v>-9.15</v>
+        <v>-14.35</v>
       </c>
       <c r="F689" t="n">
-        <v>417.05</v>
+        <v>420.5</v>
       </c>
       <c r="G689" t="n">
         <v>433.44</v>
       </c>
       <c r="H689" t="n">
-        <v>-16.39</v>
+        <v>-12.94</v>
       </c>
       <c r="I689" t="n">
-        <v>409.35</v>
+        <v>409.8</v>
       </c>
       <c r="J689" t="n">
         <v>416.79</v>
       </c>
       <c r="K689" t="n">
-        <v>-7.44</v>
+        <v>-6.99</v>
       </c>
       <c r="L689" t="inlineStr">
         <is>
@@ -75487,7 +75487,7 @@
         </is>
       </c>
       <c r="N689" t="n">
-        <v>2.16</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="690">
@@ -75502,31 +75502,31 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>3211.2</v>
+        <v>3173.5</v>
       </c>
       <c r="D690" t="n">
         <v>4258.51</v>
       </c>
       <c r="E690" t="n">
-        <v>-1047.31</v>
+        <v>-1085.01</v>
       </c>
       <c r="F690" t="n">
-        <v>3224.5</v>
+        <v>3267.6</v>
       </c>
       <c r="G690" t="n">
         <v>3412.02</v>
       </c>
       <c r="H690" t="n">
-        <v>-187.52</v>
+        <v>-144.42</v>
       </c>
       <c r="I690" t="n">
-        <v>3056.6</v>
+        <v>3156.4</v>
       </c>
       <c r="J690" t="n">
         <v>3181.69</v>
       </c>
       <c r="K690" t="n">
-        <v>-125.09</v>
+        <v>-25.29</v>
       </c>
       <c r="L690" t="inlineStr">
         <is>
@@ -75539,7 +75539,7 @@
         </is>
       </c>
       <c r="N690" t="n">
-        <v>24.59</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="691">
@@ -75554,31 +75554,31 @@
         </is>
       </c>
       <c r="C691" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D691" t="n">
         <v>593.14</v>
       </c>
       <c r="E691" t="n">
-        <v>-50.14</v>
+        <v>-51.14</v>
       </c>
       <c r="F691" t="n">
-        <v>551.45</v>
+        <v>565.25</v>
       </c>
       <c r="G691" t="n">
         <v>578.85</v>
       </c>
       <c r="H691" t="n">
-        <v>-27.4</v>
+        <v>-13.6</v>
       </c>
       <c r="I691" t="n">
-        <v>529.6</v>
+        <v>538.5</v>
       </c>
       <c r="J691" t="n">
         <v>536.6</v>
       </c>
       <c r="K691" t="n">
-        <v>-7</v>
+        <v>1.9</v>
       </c>
       <c r="L691" t="inlineStr">
         <is>
@@ -75591,7 +75591,7 @@
         </is>
       </c>
       <c r="N691" t="n">
-        <v>8.449999999999999</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="692">
@@ -75606,31 +75606,31 @@
         </is>
       </c>
       <c r="C692" t="n">
-        <v>976.5</v>
+        <v>990.8</v>
       </c>
       <c r="D692" t="n">
         <v>1127.97</v>
       </c>
       <c r="E692" t="n">
-        <v>-151.47</v>
+        <v>-137.17</v>
       </c>
       <c r="F692" t="n">
-        <v>989.9</v>
+        <v>1030</v>
       </c>
       <c r="G692" t="n">
         <v>1038.2</v>
       </c>
       <c r="H692" t="n">
-        <v>-48.3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="I692" t="n">
-        <v>963.8</v>
+        <v>985.1</v>
       </c>
       <c r="J692" t="n">
         <v>967.0700000000001</v>
       </c>
       <c r="K692" t="n">
-        <v>-3.27</v>
+        <v>18.03</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
@@ -75643,7 +75643,7 @@
         </is>
       </c>
       <c r="N692" t="n">
-        <v>13.43</v>
+        <v>12.16</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N692"/>
+  <dimension ref="A1:N699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36420,6 +36420,370 @@
       </c>
       <c r="N692" t="n">
         <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>3265.2</v>
+      </c>
+      <c r="D693" t="n">
+        <v>2542.81</v>
+      </c>
+      <c r="E693" t="n">
+        <v>722.39</v>
+      </c>
+      <c r="F693" t="n">
+        <v>3304</v>
+      </c>
+      <c r="G693" t="n">
+        <v>3212.2</v>
+      </c>
+      <c r="H693" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I693" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J693" t="n">
+        <v>3215.78</v>
+      </c>
+      <c r="K693" t="n">
+        <v>-35.68</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N693" t="n">
+        <v>28.41</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="D694" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="E694" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="F694" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G694" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="H694" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="I694" t="n">
+        <v>318.25</v>
+      </c>
+      <c r="J694" t="n">
+        <v>313.71</v>
+      </c>
+      <c r="K694" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N694" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>545.9</v>
+      </c>
+      <c r="D695" t="n">
+        <v>520.29</v>
+      </c>
+      <c r="E695" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="F695" t="n">
+        <v>554.55</v>
+      </c>
+      <c r="G695" t="n">
+        <v>525.98</v>
+      </c>
+      <c r="H695" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I695" t="n">
+        <v>541.05</v>
+      </c>
+      <c r="J695" t="n">
+        <v>526.17</v>
+      </c>
+      <c r="K695" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N695" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="D696" t="n">
+        <v>903.71</v>
+      </c>
+      <c r="E696" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1004.8</v>
+      </c>
+      <c r="G696" t="n">
+        <v>968</v>
+      </c>
+      <c r="H696" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="I696" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="J696" t="n">
+        <v>968.92</v>
+      </c>
+      <c r="K696" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N696" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2148.5</v>
+      </c>
+      <c r="D697" t="n">
+        <v>2004.41</v>
+      </c>
+      <c r="E697" t="n">
+        <v>144.09</v>
+      </c>
+      <c r="F697" t="n">
+        <v>2170</v>
+      </c>
+      <c r="G697" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="H697" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="I697" t="n">
+        <v>2110</v>
+      </c>
+      <c r="J697" t="n">
+        <v>2068.96</v>
+      </c>
+      <c r="K697" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N697" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="D698" t="n">
+        <v>410.88</v>
+      </c>
+      <c r="E698" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="F698" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="G698" t="n">
+        <v>410.88</v>
+      </c>
+      <c r="H698" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="I698" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J698" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="K698" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N698" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="D699" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="E699" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F699" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="G699" t="n">
+        <v>112.41</v>
+      </c>
+      <c r="H699" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="I699" t="n">
+        <v>116.36</v>
+      </c>
+      <c r="J699" t="n">
+        <v>112.46</v>
+      </c>
+      <c r="K699" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N699" t="n">
+        <v>5.49</v>
       </c>
     </row>
   </sheetData>
@@ -36433,7 +36797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39626,6 +39990,110 @@
       </c>
       <c r="N61" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>23270.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>23270.6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>23363.55</v>
+      </c>
+      <c r="G62" t="n">
+        <v>23358.21</v>
+      </c>
+      <c r="H62" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I62" t="n">
+        <v>23193.65</v>
+      </c>
+      <c r="J62" t="n">
+        <v>23188.31</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>56055.75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>56055.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>56570.45</v>
+      </c>
+      <c r="G63" t="n">
+        <v>56404.64</v>
+      </c>
+      <c r="H63" t="n">
+        <v>165.81</v>
+      </c>
+      <c r="I63" t="n">
+        <v>56038.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>55872.69</v>
+      </c>
+      <c r="K63" t="n">
+        <v>165.81</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -39639,7 +40107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N692"/>
+  <dimension ref="A1:N699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75646,6 +76114,370 @@
         <v>12.16</v>
       </c>
     </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>3265.2</v>
+      </c>
+      <c r="D693" t="n">
+        <v>2611.53</v>
+      </c>
+      <c r="E693" t="n">
+        <v>653.67</v>
+      </c>
+      <c r="F693" t="n">
+        <v>3304</v>
+      </c>
+      <c r="G693" t="n">
+        <v>3230.22</v>
+      </c>
+      <c r="H693" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="I693" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J693" t="n">
+        <v>3132.25</v>
+      </c>
+      <c r="K693" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N693" t="n">
+        <v>25.03</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="D694" t="n">
+        <v>306.87</v>
+      </c>
+      <c r="E694" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F694" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G694" t="n">
+        <v>315.31</v>
+      </c>
+      <c r="H694" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="I694" t="n">
+        <v>318.25</v>
+      </c>
+      <c r="J694" t="n">
+        <v>312.01</v>
+      </c>
+      <c r="K694" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N694" t="n">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>545.9</v>
+      </c>
+      <c r="D695" t="n">
+        <v>536.8</v>
+      </c>
+      <c r="E695" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F695" t="n">
+        <v>554.55</v>
+      </c>
+      <c r="G695" t="n">
+        <v>539.66</v>
+      </c>
+      <c r="H695" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="I695" t="n">
+        <v>541.05</v>
+      </c>
+      <c r="J695" t="n">
+        <v>523.98</v>
+      </c>
+      <c r="K695" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N695" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="D696" t="n">
+        <v>928.78</v>
+      </c>
+      <c r="E696" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1004.8</v>
+      </c>
+      <c r="G696" t="n">
+        <v>974.1900000000001</v>
+      </c>
+      <c r="H696" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I696" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="J696" t="n">
+        <v>951.48</v>
+      </c>
+      <c r="K696" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N696" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2148.5</v>
+      </c>
+      <c r="D697" t="n">
+        <v>2061.96</v>
+      </c>
+      <c r="E697" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="F697" t="n">
+        <v>2170</v>
+      </c>
+      <c r="G697" t="n">
+        <v>2117.96</v>
+      </c>
+      <c r="H697" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="I697" t="n">
+        <v>2110</v>
+      </c>
+      <c r="J697" t="n">
+        <v>2066.87</v>
+      </c>
+      <c r="K697" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N697" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="D698" t="n">
+        <v>415.65</v>
+      </c>
+      <c r="E698" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F698" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="G698" t="n">
+        <v>404.02</v>
+      </c>
+      <c r="H698" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="I698" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J698" t="n">
+        <v>405.77</v>
+      </c>
+      <c r="K698" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N698" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="D699" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="E699" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F699" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="G699" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="H699" t="n">
+        <v>6</v>
+      </c>
+      <c r="I699" t="n">
+        <v>116.36</v>
+      </c>
+      <c r="J699" t="n">
+        <v>113.14</v>
+      </c>
+      <c r="K699" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N699" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -36434,31 +36434,31 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>3265.2</v>
+        <v>3211.2</v>
       </c>
       <c r="D693" t="n">
         <v>2542.81</v>
       </c>
       <c r="E693" t="n">
-        <v>722.39</v>
+        <v>668.39</v>
       </c>
       <c r="F693" t="n">
-        <v>3304</v>
+        <v>3224.5</v>
       </c>
       <c r="G693" t="n">
         <v>3212.2</v>
       </c>
       <c r="H693" t="n">
-        <v>91.8</v>
+        <v>12.3</v>
       </c>
       <c r="I693" t="n">
-        <v>3180.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J693" t="n">
         <v>3215.78</v>
       </c>
       <c r="K693" t="n">
-        <v>-35.68</v>
+        <v>-159.18</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         </is>
       </c>
       <c r="N693" t="n">
-        <v>28.41</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="694">
@@ -36486,31 +36486,31 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>322.35</v>
+        <v>317</v>
       </c>
       <c r="D694" t="n">
         <v>300.73</v>
       </c>
       <c r="E694" t="n">
-        <v>21.62</v>
+        <v>16.27</v>
       </c>
       <c r="F694" t="n">
-        <v>327.8</v>
+        <v>318.35</v>
       </c>
       <c r="G694" t="n">
         <v>313.49</v>
       </c>
       <c r="H694" t="n">
-        <v>14.31</v>
+        <v>4.86</v>
       </c>
       <c r="I694" t="n">
-        <v>318.25</v>
+        <v>310.8</v>
       </c>
       <c r="J694" t="n">
         <v>313.71</v>
       </c>
       <c r="K694" t="n">
-        <v>4.54</v>
+        <v>-2.91</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -36519,11 +36519,11 @@
       </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N694" t="n">
-        <v>7.19</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="695">
@@ -36538,31 +36538,31 @@
         </is>
       </c>
       <c r="C695" t="n">
-        <v>545.9</v>
+        <v>543</v>
       </c>
       <c r="D695" t="n">
         <v>520.29</v>
       </c>
       <c r="E695" t="n">
-        <v>25.61</v>
+        <v>22.71</v>
       </c>
       <c r="F695" t="n">
-        <v>554.55</v>
+        <v>551.45</v>
       </c>
       <c r="G695" t="n">
         <v>525.98</v>
       </c>
       <c r="H695" t="n">
-        <v>28.57</v>
+        <v>25.47</v>
       </c>
       <c r="I695" t="n">
-        <v>541.05</v>
+        <v>529.6</v>
       </c>
       <c r="J695" t="n">
         <v>526.17</v>
       </c>
       <c r="K695" t="n">
-        <v>14.88</v>
+        <v>3.43</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         </is>
       </c>
       <c r="N695" t="n">
-        <v>4.92</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="696">
@@ -36590,31 +36590,31 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>988.7</v>
+        <v>976.5</v>
       </c>
       <c r="D696" t="n">
         <v>903.71</v>
       </c>
       <c r="E696" t="n">
-        <v>84.98999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F696" t="n">
-        <v>1004.8</v>
+        <v>989.9</v>
       </c>
       <c r="G696" t="n">
         <v>968</v>
       </c>
       <c r="H696" t="n">
-        <v>36.8</v>
+        <v>21.9</v>
       </c>
       <c r="I696" t="n">
-        <v>976.5</v>
+        <v>963.8</v>
       </c>
       <c r="J696" t="n">
         <v>968.92</v>
       </c>
       <c r="K696" t="n">
-        <v>7.58</v>
+        <v>-5.12</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -36623,11 +36623,11 @@
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N696" t="n">
-        <v>9.4</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="697">
@@ -36642,31 +36642,31 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>2148.5</v>
+        <v>2120</v>
       </c>
       <c r="D697" t="n">
         <v>2004.41</v>
       </c>
       <c r="E697" t="n">
-        <v>144.09</v>
+        <v>115.59</v>
       </c>
       <c r="F697" t="n">
-        <v>2170</v>
+        <v>2132.9</v>
       </c>
       <c r="G697" t="n">
         <v>2068.25</v>
       </c>
       <c r="H697" t="n">
-        <v>101.75</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I697" t="n">
-        <v>2110</v>
+        <v>2041.3</v>
       </c>
       <c r="J697" t="n">
         <v>2068.96</v>
       </c>
       <c r="K697" t="n">
-        <v>41.04</v>
+        <v>-27.66</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         </is>
       </c>
       <c r="N697" t="n">
-        <v>7.19</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="698">
@@ -36694,31 +36694,31 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>416.5</v>
+        <v>415</v>
       </c>
       <c r="D698" t="n">
         <v>410.88</v>
       </c>
       <c r="E698" t="n">
-        <v>5.62</v>
+        <v>4.12</v>
       </c>
       <c r="F698" t="n">
-        <v>417.6</v>
+        <v>417.05</v>
       </c>
       <c r="G698" t="n">
         <v>410.88</v>
       </c>
       <c r="H698" t="n">
-        <v>6.72</v>
+        <v>6.17</v>
       </c>
       <c r="I698" t="n">
-        <v>412.5</v>
+        <v>409.35</v>
       </c>
       <c r="J698" t="n">
         <v>407.2</v>
       </c>
       <c r="K698" t="n">
-        <v>5.3</v>
+        <v>2.15</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         </is>
       </c>
       <c r="N698" t="n">
-        <v>1.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699">
@@ -36746,31 +36746,31 @@
         </is>
       </c>
       <c r="C699" t="n">
-        <v>116.47</v>
+        <v>116.8</v>
       </c>
       <c r="D699" t="n">
         <v>110.41</v>
       </c>
       <c r="E699" t="n">
-        <v>6.06</v>
+        <v>6.39</v>
       </c>
       <c r="F699" t="n">
-        <v>119.4</v>
+        <v>117.48</v>
       </c>
       <c r="G699" t="n">
         <v>112.41</v>
       </c>
       <c r="H699" t="n">
-        <v>6.99</v>
+        <v>5.07</v>
       </c>
       <c r="I699" t="n">
-        <v>116.36</v>
+        <v>114.63</v>
       </c>
       <c r="J699" t="n">
         <v>112.46</v>
       </c>
       <c r="K699" t="n">
-        <v>3.9</v>
+        <v>2.17</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         </is>
       </c>
       <c r="N699" t="n">
-        <v>5.49</v>
+        <v>5.79</v>
       </c>
     </row>
   </sheetData>
@@ -40004,31 +40004,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>23270.6</v>
+        <v>23217.6</v>
       </c>
       <c r="D62" t="n">
         <v>23270.6</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="F62" t="n">
-        <v>23363.55</v>
+        <v>23284.75</v>
       </c>
       <c r="G62" t="n">
         <v>23358.21</v>
       </c>
       <c r="H62" t="n">
-        <v>5.34</v>
+        <v>-73.45999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>23193.65</v>
+        <v>23116.1</v>
       </c>
       <c r="J62" t="n">
         <v>23188.31</v>
       </c>
       <c r="K62" t="n">
-        <v>5.34</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="63">
@@ -40056,31 +40056,31 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>56055.75</v>
+        <v>56292.45</v>
       </c>
       <c r="D63" t="n">
         <v>56055.75</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>236.7</v>
       </c>
       <c r="F63" t="n">
-        <v>56570.45</v>
+        <v>56368.7</v>
       </c>
       <c r="G63" t="n">
         <v>56404.64</v>
       </c>
       <c r="H63" t="n">
-        <v>165.81</v>
+        <v>-35.94</v>
       </c>
       <c r="I63" t="n">
-        <v>56038.5</v>
+        <v>55812.2</v>
       </c>
       <c r="J63" t="n">
         <v>55872.69</v>
       </c>
       <c r="K63" t="n">
-        <v>165.81</v>
+        <v>-60.49</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -76126,31 +76126,31 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>3265.2</v>
+        <v>3211.2</v>
       </c>
       <c r="D693" t="n">
         <v>2611.53</v>
       </c>
       <c r="E693" t="n">
-        <v>653.67</v>
+        <v>599.67</v>
       </c>
       <c r="F693" t="n">
-        <v>3304</v>
+        <v>3224.5</v>
       </c>
       <c r="G693" t="n">
         <v>3230.22</v>
       </c>
       <c r="H693" t="n">
-        <v>73.78</v>
+        <v>-5.72</v>
       </c>
       <c r="I693" t="n">
-        <v>3180.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J693" t="n">
         <v>3132.25</v>
       </c>
       <c r="K693" t="n">
-        <v>47.85</v>
+        <v>-75.65000000000001</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
@@ -76163,7 +76163,7 @@
         </is>
       </c>
       <c r="N693" t="n">
-        <v>25.03</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="694">
@@ -76178,31 +76178,31 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>322.35</v>
+        <v>317</v>
       </c>
       <c r="D694" t="n">
         <v>306.87</v>
       </c>
       <c r="E694" t="n">
-        <v>15.48</v>
+        <v>10.13</v>
       </c>
       <c r="F694" t="n">
-        <v>327.8</v>
+        <v>318.35</v>
       </c>
       <c r="G694" t="n">
         <v>315.31</v>
       </c>
       <c r="H694" t="n">
-        <v>12.49</v>
+        <v>3.04</v>
       </c>
       <c r="I694" t="n">
-        <v>318.25</v>
+        <v>310.8</v>
       </c>
       <c r="J694" t="n">
         <v>312.01</v>
       </c>
       <c r="K694" t="n">
-        <v>6.24</v>
+        <v>-1.21</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -76215,7 +76215,7 @@
         </is>
       </c>
       <c r="N694" t="n">
-        <v>5.04</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="695">
@@ -76230,31 +76230,31 @@
         </is>
       </c>
       <c r="C695" t="n">
-        <v>545.9</v>
+        <v>543</v>
       </c>
       <c r="D695" t="n">
         <v>536.8</v>
       </c>
       <c r="E695" t="n">
-        <v>9.1</v>
+        <v>6.2</v>
       </c>
       <c r="F695" t="n">
-        <v>554.55</v>
+        <v>551.45</v>
       </c>
       <c r="G695" t="n">
         <v>539.66</v>
       </c>
       <c r="H695" t="n">
-        <v>14.89</v>
+        <v>11.79</v>
       </c>
       <c r="I695" t="n">
-        <v>541.05</v>
+        <v>529.6</v>
       </c>
       <c r="J695" t="n">
         <v>523.98</v>
       </c>
       <c r="K695" t="n">
-        <v>17.07</v>
+        <v>5.62</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
@@ -76267,7 +76267,7 @@
         </is>
       </c>
       <c r="N695" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="696">
@@ -76282,31 +76282,31 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>988.7</v>
+        <v>976.5</v>
       </c>
       <c r="D696" t="n">
         <v>928.78</v>
       </c>
       <c r="E696" t="n">
-        <v>59.92</v>
+        <v>47.72</v>
       </c>
       <c r="F696" t="n">
-        <v>1004.8</v>
+        <v>989.9</v>
       </c>
       <c r="G696" t="n">
         <v>974.1900000000001</v>
       </c>
       <c r="H696" t="n">
-        <v>30.61</v>
+        <v>15.71</v>
       </c>
       <c r="I696" t="n">
-        <v>976.5</v>
+        <v>963.8</v>
       </c>
       <c r="J696" t="n">
         <v>951.48</v>
       </c>
       <c r="K696" t="n">
-        <v>25.02</v>
+        <v>12.32</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -76319,7 +76319,7 @@
         </is>
       </c>
       <c r="N696" t="n">
-        <v>6.45</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="697">
@@ -76334,31 +76334,31 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>2148.5</v>
+        <v>2120</v>
       </c>
       <c r="D697" t="n">
         <v>2061.96</v>
       </c>
       <c r="E697" t="n">
-        <v>86.54000000000001</v>
+        <v>58.04</v>
       </c>
       <c r="F697" t="n">
-        <v>2170</v>
+        <v>2132.9</v>
       </c>
       <c r="G697" t="n">
         <v>2117.96</v>
       </c>
       <c r="H697" t="n">
-        <v>52.04</v>
+        <v>14.94</v>
       </c>
       <c r="I697" t="n">
-        <v>2110</v>
+        <v>2041.3</v>
       </c>
       <c r="J697" t="n">
         <v>2066.87</v>
       </c>
       <c r="K697" t="n">
-        <v>43.13</v>
+        <v>-25.57</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
@@ -76371,7 +76371,7 @@
         </is>
       </c>
       <c r="N697" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="698">
@@ -76386,31 +76386,31 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>416.5</v>
+        <v>415</v>
       </c>
       <c r="D698" t="n">
         <v>415.65</v>
       </c>
       <c r="E698" t="n">
-        <v>0.85</v>
+        <v>-0.65</v>
       </c>
       <c r="F698" t="n">
-        <v>417.6</v>
+        <v>417.05</v>
       </c>
       <c r="G698" t="n">
         <v>404.02</v>
       </c>
       <c r="H698" t="n">
-        <v>13.58</v>
+        <v>13.03</v>
       </c>
       <c r="I698" t="n">
-        <v>412.5</v>
+        <v>409.35</v>
       </c>
       <c r="J698" t="n">
         <v>405.77</v>
       </c>
       <c r="K698" t="n">
-        <v>6.73</v>
+        <v>3.58</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
@@ -76423,7 +76423,7 @@
         </is>
       </c>
       <c r="N698" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="699">
@@ -76438,31 +76438,31 @@
         </is>
       </c>
       <c r="C699" t="n">
-        <v>116.47</v>
+        <v>116.8</v>
       </c>
       <c r="D699" t="n">
         <v>112.13</v>
       </c>
       <c r="E699" t="n">
-        <v>4.34</v>
+        <v>4.67</v>
       </c>
       <c r="F699" t="n">
-        <v>119.4</v>
+        <v>117.48</v>
       </c>
       <c r="G699" t="n">
         <v>113.4</v>
       </c>
       <c r="H699" t="n">
-        <v>6</v>
+        <v>4.08</v>
       </c>
       <c r="I699" t="n">
-        <v>116.36</v>
+        <v>114.63</v>
       </c>
       <c r="J699" t="n">
         <v>113.14</v>
       </c>
       <c r="K699" t="n">
-        <v>3.22</v>
+        <v>1.49</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
@@ -76475,7 +76475,7 @@
         </is>
       </c>
       <c r="N699" t="n">
-        <v>3.87</v>
+        <v>4.16</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N699"/>
+  <dimension ref="A1:N710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36784,6 +36784,578 @@
       </c>
       <c r="N699" t="n">
         <v>5.79</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="D700" t="n">
+        <v>2348.86</v>
+      </c>
+      <c r="E700" t="n">
+        <v>-140.06</v>
+      </c>
+      <c r="F700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="G700" t="n">
+        <v>2348.86</v>
+      </c>
+      <c r="H700" t="n">
+        <v>-140.06</v>
+      </c>
+      <c r="I700" t="n">
+        <v>2155.5</v>
+      </c>
+      <c r="J700" t="n">
+        <v>2187.28</v>
+      </c>
+      <c r="K700" t="n">
+        <v>-31.78</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N700" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>3260</v>
+      </c>
+      <c r="D701" t="n">
+        <v>4172</v>
+      </c>
+      <c r="E701" t="n">
+        <v>-912</v>
+      </c>
+      <c r="F701" t="n">
+        <v>3314.9</v>
+      </c>
+      <c r="G701" t="n">
+        <v>4172</v>
+      </c>
+      <c r="H701" t="n">
+        <v>-857.1</v>
+      </c>
+      <c r="I701" t="n">
+        <v>3230.1</v>
+      </c>
+      <c r="J701" t="n">
+        <v>3260</v>
+      </c>
+      <c r="K701" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N701" t="n">
+        <v>21.86</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D702" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="E702" t="n">
+        <v>-20.43</v>
+      </c>
+      <c r="F702" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="G702" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="H702" t="n">
+        <v>-17.53</v>
+      </c>
+      <c r="I702" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="J702" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="K702" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N702" t="n">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D703" t="n">
+        <v>2440.89</v>
+      </c>
+      <c r="E703" t="n">
+        <v>-170.79</v>
+      </c>
+      <c r="F703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="G703" t="n">
+        <v>2440.89</v>
+      </c>
+      <c r="H703" t="n">
+        <v>-170.79</v>
+      </c>
+      <c r="I703" t="n">
+        <v>2146.3</v>
+      </c>
+      <c r="J703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="K703" t="n">
+        <v>-123.8</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N703" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="D704" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="E704" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="F704" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G704" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="H704" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="I704" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J704" t="n">
+        <v>116.78</v>
+      </c>
+      <c r="K704" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N704" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>548.15</v>
+      </c>
+      <c r="D705" t="n">
+        <v>576.66</v>
+      </c>
+      <c r="E705" t="n">
+        <v>-28.51</v>
+      </c>
+      <c r="F705" t="n">
+        <v>552</v>
+      </c>
+      <c r="G705" t="n">
+        <v>576.66</v>
+      </c>
+      <c r="H705" t="n">
+        <v>-24.66</v>
+      </c>
+      <c r="I705" t="n">
+        <v>543.6</v>
+      </c>
+      <c r="J705" t="n">
+        <v>541.51</v>
+      </c>
+      <c r="K705" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N705" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>11282</v>
+      </c>
+      <c r="D706" t="n">
+        <v>12076.13</v>
+      </c>
+      <c r="E706" t="n">
+        <v>-794.13</v>
+      </c>
+      <c r="F706" t="n">
+        <v>11363</v>
+      </c>
+      <c r="G706" t="n">
+        <v>12076.13</v>
+      </c>
+      <c r="H706" t="n">
+        <v>-713.13</v>
+      </c>
+      <c r="I706" t="n">
+        <v>11070</v>
+      </c>
+      <c r="J706" t="n">
+        <v>11282</v>
+      </c>
+      <c r="K706" t="n">
+        <v>-212</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N706" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="D707" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="E707" t="n">
+        <v>-18.55</v>
+      </c>
+      <c r="F707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="G707" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="H707" t="n">
+        <v>-18.55</v>
+      </c>
+      <c r="I707" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="J707" t="n">
+        <v>286.71</v>
+      </c>
+      <c r="K707" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N707" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1105.23</v>
+      </c>
+      <c r="E708" t="n">
+        <v>-95.23</v>
+      </c>
+      <c r="F708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G708" t="n">
+        <v>1105.23</v>
+      </c>
+      <c r="H708" t="n">
+        <v>-95.23</v>
+      </c>
+      <c r="I708" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="J708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K708" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N708" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="D709" t="n">
+        <v>419.97</v>
+      </c>
+      <c r="E709" t="n">
+        <v>-7.47</v>
+      </c>
+      <c r="F709" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="G709" t="n">
+        <v>429.6</v>
+      </c>
+      <c r="H709" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="I709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J709" t="n">
+        <v>410.12</v>
+      </c>
+      <c r="K709" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N709" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="D710" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="E710" t="n">
+        <v>-46.46</v>
+      </c>
+      <c r="F710" t="n">
+        <v>743</v>
+      </c>
+      <c r="G710" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="H710" t="n">
+        <v>-36.21</v>
+      </c>
+      <c r="I710" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="J710" t="n">
+        <v>716.23</v>
+      </c>
+      <c r="K710" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N710" t="n">
+        <v>5.96</v>
       </c>
     </row>
   </sheetData>
@@ -36797,7 +37369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40094,6 +40666,110 @@
       </c>
       <c r="N63" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>23346.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>23346.4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>23389.15</v>
+      </c>
+      <c r="G64" t="n">
+        <v>23394.84</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="I64" t="n">
+        <v>23286.6</v>
+      </c>
+      <c r="J64" t="n">
+        <v>23292.29</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>56358.7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>56358.7</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>56497.45</v>
+      </c>
+      <c r="G65" t="n">
+        <v>56546.25</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-48.8</v>
+      </c>
+      <c r="I65" t="n">
+        <v>56073.55</v>
+      </c>
+      <c r="J65" t="n">
+        <v>56122.35</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-48.8</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -40107,7 +40783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N699"/>
+  <dimension ref="A1:N710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76478,6 +77154,578 @@
         <v>4.16</v>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>HYUNDAI (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="D700" t="n">
+        <v>2407.96</v>
+      </c>
+      <c r="E700" t="n">
+        <v>-199.16</v>
+      </c>
+      <c r="F700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="G700" t="n">
+        <v>2321.68</v>
+      </c>
+      <c r="H700" t="n">
+        <v>-112.88</v>
+      </c>
+      <c r="I700" t="n">
+        <v>2155.5</v>
+      </c>
+      <c r="J700" t="n">
+        <v>2167.33</v>
+      </c>
+      <c r="K700" t="n">
+        <v>-11.83</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N700" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>3260</v>
+      </c>
+      <c r="D701" t="n">
+        <v>4284.41</v>
+      </c>
+      <c r="E701" t="n">
+        <v>-1024.41</v>
+      </c>
+      <c r="F701" t="n">
+        <v>3314.9</v>
+      </c>
+      <c r="G701" t="n">
+        <v>3449.96</v>
+      </c>
+      <c r="H701" t="n">
+        <v>-135.06</v>
+      </c>
+      <c r="I701" t="n">
+        <v>3230.1</v>
+      </c>
+      <c r="J701" t="n">
+        <v>3181.52</v>
+      </c>
+      <c r="K701" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N701" t="n">
+        <v>23.91</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D702" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="E702" t="n">
+        <v>-27.88</v>
+      </c>
+      <c r="F702" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="G702" t="n">
+        <v>342.35</v>
+      </c>
+      <c r="H702" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="I702" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="J702" t="n">
+        <v>321.61</v>
+      </c>
+      <c r="K702" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N702" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D703" t="n">
+        <v>2484.73</v>
+      </c>
+      <c r="E703" t="n">
+        <v>-214.63</v>
+      </c>
+      <c r="F703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="G703" t="n">
+        <v>2389.46</v>
+      </c>
+      <c r="H703" t="n">
+        <v>-119.36</v>
+      </c>
+      <c r="I703" t="n">
+        <v>2146.3</v>
+      </c>
+      <c r="J703" t="n">
+        <v>2225</v>
+      </c>
+      <c r="K703" t="n">
+        <v>-78.7</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N703" t="n">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="D704" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="E704" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="F704" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G704" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="H704" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="I704" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J704" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="K704" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N704" t="n">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>548.15</v>
+      </c>
+      <c r="D705" t="n">
+        <v>594.73</v>
+      </c>
+      <c r="E705" t="n">
+        <v>-46.58</v>
+      </c>
+      <c r="F705" t="n">
+        <v>552</v>
+      </c>
+      <c r="G705" t="n">
+        <v>579.51</v>
+      </c>
+      <c r="H705" t="n">
+        <v>-27.51</v>
+      </c>
+      <c r="I705" t="n">
+        <v>543.6</v>
+      </c>
+      <c r="J705" t="n">
+        <v>535.39</v>
+      </c>
+      <c r="K705" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N705" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>11282</v>
+      </c>
+      <c r="D706" t="n">
+        <v>12185.81</v>
+      </c>
+      <c r="E706" t="n">
+        <v>-903.8099999999999</v>
+      </c>
+      <c r="F706" t="n">
+        <v>11363</v>
+      </c>
+      <c r="G706" t="n">
+        <v>11753.44</v>
+      </c>
+      <c r="H706" t="n">
+        <v>-390.44</v>
+      </c>
+      <c r="I706" t="n">
+        <v>11070</v>
+      </c>
+      <c r="J706" t="n">
+        <v>11147.83</v>
+      </c>
+      <c r="K706" t="n">
+        <v>-77.83</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N706" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>PETRONET (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="D707" t="n">
+        <v>316.71</v>
+      </c>
+      <c r="E707" t="n">
+        <v>-24.11</v>
+      </c>
+      <c r="F707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="G707" t="n">
+        <v>305.45</v>
+      </c>
+      <c r="H707" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="I707" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="J707" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="K707" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N707" t="n">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1130.15</v>
+      </c>
+      <c r="E708" t="n">
+        <v>-120.15</v>
+      </c>
+      <c r="F708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G708" t="n">
+        <v>1063.77</v>
+      </c>
+      <c r="H708" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="I708" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="J708" t="n">
+        <v>989.4400000000001</v>
+      </c>
+      <c r="K708" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N708" t="n">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="D709" t="n">
+        <v>424.85</v>
+      </c>
+      <c r="E709" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="F709" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="G709" t="n">
+        <v>428.07</v>
+      </c>
+      <c r="H709" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="I709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J709" t="n">
+        <v>408.82</v>
+      </c>
+      <c r="K709" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N709" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="D710" t="n">
+        <v>794.84</v>
+      </c>
+      <c r="E710" t="n">
+        <v>-62.09</v>
+      </c>
+      <c r="F710" t="n">
+        <v>743</v>
+      </c>
+      <c r="G710" t="n">
+        <v>766.51</v>
+      </c>
+      <c r="H710" t="n">
+        <v>-23.51</v>
+      </c>
+      <c r="I710" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="J710" t="n">
+        <v>721.71</v>
+      </c>
+      <c r="K710" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N710" t="n">
+        <v>7.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -36798,31 +36798,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2208.8</v>
+        <v>2160</v>
       </c>
       <c r="D700" t="n">
         <v>2348.86</v>
       </c>
       <c r="E700" t="n">
-        <v>-140.06</v>
+        <v>-188.86</v>
       </c>
       <c r="F700" t="n">
-        <v>2208.8</v>
+        <v>2232.1</v>
       </c>
       <c r="G700" t="n">
         <v>2348.86</v>
       </c>
       <c r="H700" t="n">
-        <v>-140.06</v>
+        <v>-116.76</v>
       </c>
       <c r="I700" t="n">
-        <v>2155.5</v>
+        <v>2143</v>
       </c>
       <c r="J700" t="n">
         <v>2187.28</v>
       </c>
       <c r="K700" t="n">
-        <v>-31.78</v>
+        <v>-44.28</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -36831,11 +36831,11 @@
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N700" t="n">
-        <v>5.96</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="701">
@@ -36850,31 +36850,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3260</v>
+        <v>3211.2</v>
       </c>
       <c r="D701" t="n">
         <v>4172</v>
       </c>
       <c r="E701" t="n">
-        <v>-912</v>
+        <v>-960.8</v>
       </c>
       <c r="F701" t="n">
-        <v>3314.9</v>
+        <v>3224.5</v>
       </c>
       <c r="G701" t="n">
         <v>4172</v>
       </c>
       <c r="H701" t="n">
-        <v>-857.1</v>
+        <v>-947.5</v>
       </c>
       <c r="I701" t="n">
-        <v>3230.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J701" t="n">
         <v>3260</v>
       </c>
       <c r="K701" t="n">
-        <v>-29.9</v>
+        <v>-203.4</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -36883,11 +36883,11 @@
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N701" t="n">
-        <v>21.86</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="702">
@@ -36902,31 +36902,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>326.85</v>
+        <v>322.35</v>
       </c>
       <c r="D702" t="n">
         <v>347.28</v>
       </c>
       <c r="E702" t="n">
-        <v>-20.43</v>
+        <v>-24.93</v>
       </c>
       <c r="F702" t="n">
-        <v>329.75</v>
+        <v>327.8</v>
       </c>
       <c r="G702" t="n">
         <v>347.28</v>
       </c>
       <c r="H702" t="n">
-        <v>-17.53</v>
+        <v>-19.48</v>
       </c>
       <c r="I702" t="n">
-        <v>325.7</v>
+        <v>318.25</v>
       </c>
       <c r="J702" t="n">
         <v>323.67</v>
       </c>
       <c r="K702" t="n">
-        <v>2.03</v>
+        <v>-5.42</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -36935,11 +36935,11 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N702" t="n">
-        <v>5.88</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="703">
@@ -36954,31 +36954,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2270.1</v>
+        <v>2120</v>
       </c>
       <c r="D703" t="n">
         <v>2440.89</v>
       </c>
       <c r="E703" t="n">
-        <v>-170.79</v>
+        <v>-320.89</v>
       </c>
       <c r="F703" t="n">
-        <v>2270.1</v>
+        <v>2132.9</v>
       </c>
       <c r="G703" t="n">
         <v>2440.89</v>
       </c>
       <c r="H703" t="n">
-        <v>-170.79</v>
+        <v>-307.99</v>
       </c>
       <c r="I703" t="n">
-        <v>2146.3</v>
+        <v>2041.3</v>
       </c>
       <c r="J703" t="n">
         <v>2270.1</v>
       </c>
       <c r="K703" t="n">
-        <v>-123.8</v>
+        <v>-228.8</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         </is>
       </c>
       <c r="N703" t="n">
-        <v>7</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="704">
@@ -37006,31 +37006,31 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>117.27</v>
+        <v>116.47</v>
       </c>
       <c r="D704" t="n">
         <v>125.05</v>
       </c>
       <c r="E704" t="n">
-        <v>-7.78</v>
+        <v>-8.58</v>
       </c>
       <c r="F704" t="n">
-        <v>117.5</v>
+        <v>119.4</v>
       </c>
       <c r="G704" t="n">
         <v>125.05</v>
       </c>
       <c r="H704" t="n">
-        <v>-7.55</v>
+        <v>-5.65</v>
       </c>
       <c r="I704" t="n">
-        <v>116.5</v>
+        <v>116.36</v>
       </c>
       <c r="J704" t="n">
         <v>116.78</v>
       </c>
       <c r="K704" t="n">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         </is>
       </c>
       <c r="N704" t="n">
-        <v>6.22</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="705">
@@ -37058,31 +37058,31 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>548.15</v>
+        <v>543</v>
       </c>
       <c r="D705" t="n">
         <v>576.66</v>
       </c>
       <c r="E705" t="n">
-        <v>-28.51</v>
+        <v>-33.66</v>
       </c>
       <c r="F705" t="n">
-        <v>552</v>
+        <v>551.45</v>
       </c>
       <c r="G705" t="n">
         <v>576.66</v>
       </c>
       <c r="H705" t="n">
-        <v>-24.66</v>
+        <v>-25.21</v>
       </c>
       <c r="I705" t="n">
-        <v>543.6</v>
+        <v>529.6</v>
       </c>
       <c r="J705" t="n">
         <v>541.51</v>
       </c>
       <c r="K705" t="n">
-        <v>2.09</v>
+        <v>-11.91</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -37091,11 +37091,11 @@
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N705" t="n">
-        <v>4.94</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="706">
@@ -37110,31 +37110,31 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>11282</v>
+        <v>10930</v>
       </c>
       <c r="D706" t="n">
         <v>12076.13</v>
       </c>
       <c r="E706" t="n">
-        <v>-794.13</v>
+        <v>-1146.13</v>
       </c>
       <c r="F706" t="n">
-        <v>11363</v>
+        <v>11090</v>
       </c>
       <c r="G706" t="n">
         <v>12076.13</v>
       </c>
       <c r="H706" t="n">
-        <v>-713.13</v>
+        <v>-986.13</v>
       </c>
       <c r="I706" t="n">
-        <v>11070</v>
+        <v>10925</v>
       </c>
       <c r="J706" t="n">
         <v>11282</v>
       </c>
       <c r="K706" t="n">
-        <v>-212</v>
+        <v>-357</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         </is>
       </c>
       <c r="N706" t="n">
-        <v>6.58</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="707">
@@ -37162,31 +37162,31 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>292.6</v>
+        <v>283.45</v>
       </c>
       <c r="D707" t="n">
         <v>311.15</v>
       </c>
       <c r="E707" t="n">
-        <v>-18.55</v>
+        <v>-27.7</v>
       </c>
       <c r="F707" t="n">
-        <v>292.6</v>
+        <v>285</v>
       </c>
       <c r="G707" t="n">
         <v>311.15</v>
       </c>
       <c r="H707" t="n">
-        <v>-18.55</v>
+        <v>-26.15</v>
       </c>
       <c r="I707" t="n">
-        <v>284.1</v>
+        <v>281.7</v>
       </c>
       <c r="J707" t="n">
         <v>286.71</v>
       </c>
       <c r="K707" t="n">
-        <v>-2.61</v>
+        <v>-5.01</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -37195,11 +37195,11 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N707" t="n">
-        <v>5.96</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="708">
@@ -37214,31 +37214,31 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1010</v>
+        <v>976.5</v>
       </c>
       <c r="D708" t="n">
         <v>1105.23</v>
       </c>
       <c r="E708" t="n">
-        <v>-95.23</v>
+        <v>-128.73</v>
       </c>
       <c r="F708" t="n">
-        <v>1010</v>
+        <v>989.9</v>
       </c>
       <c r="G708" t="n">
         <v>1105.23</v>
       </c>
       <c r="H708" t="n">
-        <v>-95.23</v>
+        <v>-115.33</v>
       </c>
       <c r="I708" t="n">
-        <v>988.7</v>
+        <v>963.8</v>
       </c>
       <c r="J708" t="n">
         <v>1010</v>
       </c>
       <c r="K708" t="n">
-        <v>-21.3</v>
+        <v>-46.2</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         </is>
       </c>
       <c r="N708" t="n">
-        <v>8.619999999999999</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="709">
@@ -37266,22 +37266,22 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>412.5</v>
+        <v>416.5</v>
       </c>
       <c r="D709" t="n">
         <v>419.97</v>
       </c>
       <c r="E709" t="n">
-        <v>-7.47</v>
+        <v>-3.47</v>
       </c>
       <c r="F709" t="n">
-        <v>419.2</v>
+        <v>417.6</v>
       </c>
       <c r="G709" t="n">
         <v>429.6</v>
       </c>
       <c r="H709" t="n">
-        <v>-10.4</v>
+        <v>-12</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
@@ -37303,7 +37303,7 @@
         </is>
       </c>
       <c r="N709" t="n">
-        <v>1.78</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="710">
@@ -37318,31 +37318,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>732.75</v>
+        <v>726.65</v>
       </c>
       <c r="D710" t="n">
         <v>779.21</v>
       </c>
       <c r="E710" t="n">
-        <v>-46.46</v>
+        <v>-52.56</v>
       </c>
       <c r="F710" t="n">
-        <v>743</v>
+        <v>729.8</v>
       </c>
       <c r="G710" t="n">
         <v>779.21</v>
       </c>
       <c r="H710" t="n">
-        <v>-36.21</v>
+        <v>-49.41</v>
       </c>
       <c r="I710" t="n">
-        <v>722.6</v>
+        <v>712.55</v>
       </c>
       <c r="J710" t="n">
         <v>716.23</v>
       </c>
       <c r="K710" t="n">
-        <v>6.37</v>
+        <v>-3.68</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         </is>
       </c>
       <c r="N710" t="n">
-        <v>5.96</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -40680,31 +40680,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23346.4</v>
+        <v>23270.6</v>
       </c>
       <c r="D64" t="n">
         <v>23346.4</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>-75.8</v>
       </c>
       <c r="F64" t="n">
-        <v>23389.15</v>
+        <v>23363.55</v>
       </c>
       <c r="G64" t="n">
         <v>23394.84</v>
       </c>
       <c r="H64" t="n">
-        <v>-5.69</v>
+        <v>-31.29</v>
       </c>
       <c r="I64" t="n">
-        <v>23286.6</v>
+        <v>23193.65</v>
       </c>
       <c r="J64" t="n">
         <v>23292.29</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.69</v>
+        <v>-98.64</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="65">
@@ -40732,31 +40732,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>56358.7</v>
+        <v>56055.75</v>
       </c>
       <c r="D65" t="n">
         <v>56358.7</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>-302.95</v>
       </c>
       <c r="F65" t="n">
-        <v>56497.45</v>
+        <v>56570.45</v>
       </c>
       <c r="G65" t="n">
         <v>56546.25</v>
       </c>
       <c r="H65" t="n">
-        <v>-48.8</v>
+        <v>24.2</v>
       </c>
       <c r="I65" t="n">
-        <v>56073.55</v>
+        <v>56038.5</v>
       </c>
       <c r="J65" t="n">
         <v>56122.35</v>
       </c>
       <c r="K65" t="n">
-        <v>-48.8</v>
+        <v>-83.84999999999999</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -77166,31 +77166,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2208.8</v>
+        <v>2160</v>
       </c>
       <c r="D700" t="n">
         <v>2407.96</v>
       </c>
       <c r="E700" t="n">
-        <v>-199.16</v>
+        <v>-247.96</v>
       </c>
       <c r="F700" t="n">
-        <v>2208.8</v>
+        <v>2232.1</v>
       </c>
       <c r="G700" t="n">
         <v>2321.68</v>
       </c>
       <c r="H700" t="n">
-        <v>-112.88</v>
+        <v>-89.58</v>
       </c>
       <c r="I700" t="n">
-        <v>2155.5</v>
+        <v>2143</v>
       </c>
       <c r="J700" t="n">
         <v>2167.33</v>
       </c>
       <c r="K700" t="n">
-        <v>-11.83</v>
+        <v>-24.33</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -77203,7 +77203,7 @@
         </is>
       </c>
       <c r="N700" t="n">
-        <v>8.27</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="701">
@@ -77218,31 +77218,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3260</v>
+        <v>3211.2</v>
       </c>
       <c r="D701" t="n">
         <v>4284.41</v>
       </c>
       <c r="E701" t="n">
-        <v>-1024.41</v>
+        <v>-1073.21</v>
       </c>
       <c r="F701" t="n">
-        <v>3314.9</v>
+        <v>3224.5</v>
       </c>
       <c r="G701" t="n">
         <v>3449.96</v>
       </c>
       <c r="H701" t="n">
-        <v>-135.06</v>
+        <v>-225.46</v>
       </c>
       <c r="I701" t="n">
-        <v>3230.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J701" t="n">
         <v>3181.52</v>
       </c>
       <c r="K701" t="n">
-        <v>48.58</v>
+        <v>-124.92</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         </is>
       </c>
       <c r="N701" t="n">
-        <v>23.91</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="702">
@@ -77270,31 +77270,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>326.85</v>
+        <v>322.35</v>
       </c>
       <c r="D702" t="n">
         <v>354.73</v>
       </c>
       <c r="E702" t="n">
-        <v>-27.88</v>
+        <v>-32.38</v>
       </c>
       <c r="F702" t="n">
-        <v>329.75</v>
+        <v>327.8</v>
       </c>
       <c r="G702" t="n">
         <v>342.35</v>
       </c>
       <c r="H702" t="n">
-        <v>-12.6</v>
+        <v>-14.55</v>
       </c>
       <c r="I702" t="n">
-        <v>325.7</v>
+        <v>318.25</v>
       </c>
       <c r="J702" t="n">
         <v>321.61</v>
       </c>
       <c r="K702" t="n">
-        <v>4.09</v>
+        <v>-3.36</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -77307,7 +77307,7 @@
         </is>
       </c>
       <c r="N702" t="n">
-        <v>7.86</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="703">
@@ -77322,31 +77322,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2270.1</v>
+        <v>2120</v>
       </c>
       <c r="D703" t="n">
         <v>2484.73</v>
       </c>
       <c r="E703" t="n">
-        <v>-214.63</v>
+        <v>-364.73</v>
       </c>
       <c r="F703" t="n">
-        <v>2270.1</v>
+        <v>2132.9</v>
       </c>
       <c r="G703" t="n">
         <v>2389.46</v>
       </c>
       <c r="H703" t="n">
-        <v>-119.36</v>
+        <v>-256.56</v>
       </c>
       <c r="I703" t="n">
-        <v>2146.3</v>
+        <v>2041.3</v>
       </c>
       <c r="J703" t="n">
         <v>2225</v>
       </c>
       <c r="K703" t="n">
-        <v>-78.7</v>
+        <v>-183.7</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -77359,7 +77359,7 @@
         </is>
       </c>
       <c r="N703" t="n">
-        <v>8.640000000000001</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="704">
@@ -77374,31 +77374,31 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>117.27</v>
+        <v>116.47</v>
       </c>
       <c r="D704" t="n">
         <v>127.13</v>
       </c>
       <c r="E704" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.66</v>
       </c>
       <c r="F704" t="n">
-        <v>117.5</v>
+        <v>119.4</v>
       </c>
       <c r="G704" t="n">
         <v>122.28</v>
       </c>
       <c r="H704" t="n">
-        <v>-4.78</v>
+        <v>-2.88</v>
       </c>
       <c r="I704" t="n">
-        <v>116.5</v>
+        <v>116.36</v>
       </c>
       <c r="J704" t="n">
         <v>115.8</v>
       </c>
       <c r="K704" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -77411,7 +77411,7 @@
         </is>
       </c>
       <c r="N704" t="n">
-        <v>7.76</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="705">
@@ -77426,31 +77426,31 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>548.15</v>
+        <v>543</v>
       </c>
       <c r="D705" t="n">
         <v>594.73</v>
       </c>
       <c r="E705" t="n">
-        <v>-46.58</v>
+        <v>-51.73</v>
       </c>
       <c r="F705" t="n">
-        <v>552</v>
+        <v>551.45</v>
       </c>
       <c r="G705" t="n">
         <v>579.51</v>
       </c>
       <c r="H705" t="n">
-        <v>-27.51</v>
+        <v>-28.06</v>
       </c>
       <c r="I705" t="n">
-        <v>543.6</v>
+        <v>529.6</v>
       </c>
       <c r="J705" t="n">
         <v>535.39</v>
       </c>
       <c r="K705" t="n">
-        <v>8.210000000000001</v>
+        <v>-5.79</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -77463,7 +77463,7 @@
         </is>
       </c>
       <c r="N705" t="n">
-        <v>7.83</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="706">
@@ -77478,31 +77478,31 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>11282</v>
+        <v>10930</v>
       </c>
       <c r="D706" t="n">
         <v>12185.81</v>
       </c>
       <c r="E706" t="n">
-        <v>-903.8099999999999</v>
+        <v>-1255.81</v>
       </c>
       <c r="F706" t="n">
-        <v>11363</v>
+        <v>11090</v>
       </c>
       <c r="G706" t="n">
         <v>11753.44</v>
       </c>
       <c r="H706" t="n">
-        <v>-390.44</v>
+        <v>-663.4400000000001</v>
       </c>
       <c r="I706" t="n">
-        <v>11070</v>
+        <v>10925</v>
       </c>
       <c r="J706" t="n">
         <v>11147.83</v>
       </c>
       <c r="K706" t="n">
-        <v>-77.83</v>
+        <v>-222.83</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -77515,7 +77515,7 @@
         </is>
       </c>
       <c r="N706" t="n">
-        <v>7.42</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="707">
@@ -77530,31 +77530,31 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>292.6</v>
+        <v>283.45</v>
       </c>
       <c r="D707" t="n">
         <v>316.71</v>
       </c>
       <c r="E707" t="n">
-        <v>-24.11</v>
+        <v>-33.26</v>
       </c>
       <c r="F707" t="n">
-        <v>292.6</v>
+        <v>285</v>
       </c>
       <c r="G707" t="n">
         <v>305.45</v>
       </c>
       <c r="H707" t="n">
-        <v>-12.85</v>
+        <v>-20.45</v>
       </c>
       <c r="I707" t="n">
-        <v>284.1</v>
+        <v>281.7</v>
       </c>
       <c r="J707" t="n">
         <v>288.65</v>
       </c>
       <c r="K707" t="n">
-        <v>-4.55</v>
+        <v>-6.95</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -77567,7 +77567,7 @@
         </is>
       </c>
       <c r="N707" t="n">
-        <v>7.61</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="708">
@@ -77582,31 +77582,31 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1010</v>
+        <v>976.5</v>
       </c>
       <c r="D708" t="n">
         <v>1130.15</v>
       </c>
       <c r="E708" t="n">
-        <v>-120.15</v>
+        <v>-153.65</v>
       </c>
       <c r="F708" t="n">
-        <v>1010</v>
+        <v>989.9</v>
       </c>
       <c r="G708" t="n">
         <v>1063.77</v>
       </c>
       <c r="H708" t="n">
-        <v>-53.77</v>
+        <v>-73.87</v>
       </c>
       <c r="I708" t="n">
-        <v>988.7</v>
+        <v>963.8</v>
       </c>
       <c r="J708" t="n">
         <v>989.4400000000001</v>
       </c>
       <c r="K708" t="n">
-        <v>-0.74</v>
+        <v>-25.64</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -77619,7 +77619,7 @@
         </is>
       </c>
       <c r="N708" t="n">
-        <v>10.63</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="709">
@@ -77634,22 +77634,22 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>412.5</v>
+        <v>416.5</v>
       </c>
       <c r="D709" t="n">
         <v>424.85</v>
       </c>
       <c r="E709" t="n">
-        <v>-12.35</v>
+        <v>-8.35</v>
       </c>
       <c r="F709" t="n">
-        <v>419.2</v>
+        <v>417.6</v>
       </c>
       <c r="G709" t="n">
         <v>428.07</v>
       </c>
       <c r="H709" t="n">
-        <v>-8.869999999999999</v>
+        <v>-10.47</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
@@ -77667,11 +77667,11 @@
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N709" t="n">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="710">
@@ -77686,31 +77686,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>732.75</v>
+        <v>726.65</v>
       </c>
       <c r="D710" t="n">
         <v>794.84</v>
       </c>
       <c r="E710" t="n">
-        <v>-62.09</v>
+        <v>-68.19</v>
       </c>
       <c r="F710" t="n">
-        <v>743</v>
+        <v>729.8</v>
       </c>
       <c r="G710" t="n">
         <v>766.51</v>
       </c>
       <c r="H710" t="n">
-        <v>-23.51</v>
+        <v>-36.71</v>
       </c>
       <c r="I710" t="n">
-        <v>722.6</v>
+        <v>712.55</v>
       </c>
       <c r="J710" t="n">
         <v>721.71</v>
       </c>
       <c r="K710" t="n">
-        <v>0.89</v>
+        <v>-9.16</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -77723,7 +77723,7 @@
         </is>
       </c>
       <c r="N710" t="n">
-        <v>7.81</v>
+        <v>8.58</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -36798,31 +36798,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2160</v>
+        <v>2208.8</v>
       </c>
       <c r="D700" t="n">
-        <v>2348.86</v>
+        <v>2047.46</v>
       </c>
       <c r="E700" t="n">
-        <v>-188.86</v>
+        <v>161.34</v>
       </c>
       <c r="F700" t="n">
-        <v>2232.1</v>
+        <v>2208.8</v>
       </c>
       <c r="G700" t="n">
-        <v>2348.86</v>
+        <v>2132.74</v>
       </c>
       <c r="H700" t="n">
-        <v>-116.76</v>
+        <v>76.06</v>
       </c>
       <c r="I700" t="n">
-        <v>2143</v>
+        <v>2155.5</v>
       </c>
       <c r="J700" t="n">
-        <v>2187.28</v>
+        <v>2137.07</v>
       </c>
       <c r="K700" t="n">
-        <v>-44.28</v>
+        <v>18.43</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         </is>
       </c>
       <c r="N700" t="n">
-        <v>8.039999999999999</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="701">
@@ -36850,31 +36850,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3211.2</v>
+        <v>3260</v>
       </c>
       <c r="D701" t="n">
-        <v>4172</v>
+        <v>2542.79</v>
       </c>
       <c r="E701" t="n">
-        <v>-960.8</v>
+        <v>717.21</v>
       </c>
       <c r="F701" t="n">
-        <v>3224.5</v>
+        <v>3314.9</v>
       </c>
       <c r="G701" t="n">
-        <v>4172</v>
+        <v>3184.23</v>
       </c>
       <c r="H701" t="n">
-        <v>-947.5</v>
+        <v>130.67</v>
       </c>
       <c r="I701" t="n">
-        <v>3056.6</v>
+        <v>3230.1</v>
       </c>
       <c r="J701" t="n">
-        <v>3260</v>
+        <v>3191.99</v>
       </c>
       <c r="K701" t="n">
-        <v>-203.4</v>
+        <v>38.11</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         </is>
       </c>
       <c r="N701" t="n">
-        <v>23.03</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="702">
@@ -36902,31 +36902,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="D702" t="n">
-        <v>347.28</v>
+        <v>305.81</v>
       </c>
       <c r="E702" t="n">
-        <v>-24.93</v>
+        <v>21.04</v>
       </c>
       <c r="F702" t="n">
-        <v>327.8</v>
+        <v>329.75</v>
       </c>
       <c r="G702" t="n">
-        <v>347.28</v>
+        <v>315.6</v>
       </c>
       <c r="H702" t="n">
-        <v>-19.48</v>
+        <v>14.15</v>
       </c>
       <c r="I702" t="n">
-        <v>318.25</v>
+        <v>325.7</v>
       </c>
       <c r="J702" t="n">
-        <v>323.67</v>
+        <v>316.24</v>
       </c>
       <c r="K702" t="n">
-        <v>-5.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         </is>
       </c>
       <c r="N702" t="n">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="703">
@@ -36954,31 +36954,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2120</v>
+        <v>2270.1</v>
       </c>
       <c r="D703" t="n">
-        <v>2440.89</v>
+        <v>2004.42</v>
       </c>
       <c r="E703" t="n">
-        <v>-320.89</v>
+        <v>265.68</v>
       </c>
       <c r="F703" t="n">
-        <v>2132.9</v>
+        <v>2270.1</v>
       </c>
       <c r="G703" t="n">
-        <v>2440.89</v>
+        <v>2224.27</v>
       </c>
       <c r="H703" t="n">
-        <v>-307.99</v>
+        <v>45.83</v>
       </c>
       <c r="I703" t="n">
-        <v>2041.3</v>
+        <v>2146.3</v>
       </c>
       <c r="J703" t="n">
-        <v>2270.1</v>
+        <v>2229.93</v>
       </c>
       <c r="K703" t="n">
-        <v>-228.8</v>
+        <v>-83.63</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         </is>
       </c>
       <c r="N703" t="n">
-        <v>13.15</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="704">
@@ -37002,35 +37002,35 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>116.47</v>
+        <v>548.15</v>
       </c>
       <c r="D704" t="n">
-        <v>125.05</v>
+        <v>520.29</v>
       </c>
       <c r="E704" t="n">
-        <v>-8.58</v>
+        <v>27.86</v>
       </c>
       <c r="F704" t="n">
-        <v>119.4</v>
+        <v>552</v>
       </c>
       <c r="G704" t="n">
-        <v>125.05</v>
+        <v>528.05</v>
       </c>
       <c r="H704" t="n">
-        <v>-5.65</v>
+        <v>23.95</v>
       </c>
       <c r="I704" t="n">
-        <v>116.36</v>
+        <v>543.6</v>
       </c>
       <c r="J704" t="n">
-        <v>116.78</v>
+        <v>529.08</v>
       </c>
       <c r="K704" t="n">
-        <v>-0.42</v>
+        <v>14.52</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -37039,11 +37039,11 @@
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N704" t="n">
-        <v>6.86</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="705">
@@ -37054,35 +37054,35 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>543</v>
+        <v>117.27</v>
       </c>
       <c r="D705" t="n">
-        <v>576.66</v>
+        <v>110.1</v>
       </c>
       <c r="E705" t="n">
-        <v>-33.66</v>
+        <v>7.17</v>
       </c>
       <c r="F705" t="n">
-        <v>551.45</v>
+        <v>117.5</v>
       </c>
       <c r="G705" t="n">
-        <v>576.66</v>
+        <v>113.84</v>
       </c>
       <c r="H705" t="n">
-        <v>-25.21</v>
+        <v>3.66</v>
       </c>
       <c r="I705" t="n">
-        <v>529.6</v>
+        <v>116.5</v>
       </c>
       <c r="J705" t="n">
-        <v>541.51</v>
+        <v>114.1</v>
       </c>
       <c r="K705" t="n">
-        <v>-11.91</v>
+        <v>2.4</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         </is>
       </c>
       <c r="N705" t="n">
-        <v>5.84</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="706">
@@ -37110,31 +37110,31 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>10930</v>
+        <v>11282</v>
       </c>
       <c r="D706" t="n">
-        <v>12076.13</v>
+        <v>10360.47</v>
       </c>
       <c r="E706" t="n">
-        <v>-1146.13</v>
+        <v>921.53</v>
       </c>
       <c r="F706" t="n">
-        <v>11090</v>
+        <v>11363</v>
       </c>
       <c r="G706" t="n">
-        <v>12076.13</v>
+        <v>10957.24</v>
       </c>
       <c r="H706" t="n">
-        <v>-986.13</v>
+        <v>405.76</v>
       </c>
       <c r="I706" t="n">
-        <v>10925</v>
+        <v>11070</v>
       </c>
       <c r="J706" t="n">
-        <v>11282</v>
+        <v>11060.34</v>
       </c>
       <c r="K706" t="n">
-        <v>-357</v>
+        <v>9.66</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         </is>
       </c>
       <c r="N706" t="n">
-        <v>9.49</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="707">
@@ -37158,35 +37158,35 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>283.45</v>
+        <v>1010</v>
       </c>
       <c r="D707" t="n">
-        <v>311.15</v>
+        <v>903.71</v>
       </c>
       <c r="E707" t="n">
-        <v>-27.7</v>
+        <v>106.29</v>
       </c>
       <c r="F707" t="n">
-        <v>285</v>
+        <v>1010</v>
       </c>
       <c r="G707" t="n">
-        <v>311.15</v>
+        <v>985.89</v>
       </c>
       <c r="H707" t="n">
-        <v>-26.15</v>
+        <v>24.11</v>
       </c>
       <c r="I707" t="n">
-        <v>281.7</v>
+        <v>988.7</v>
       </c>
       <c r="J707" t="n">
-        <v>286.71</v>
+        <v>988.27</v>
       </c>
       <c r="K707" t="n">
-        <v>-5.01</v>
+        <v>0.43</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -37195,11 +37195,11 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N707" t="n">
-        <v>8.9</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="708">
@@ -37210,39 +37210,39 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>976.5</v>
+        <v>292.6</v>
       </c>
       <c r="D708" t="n">
-        <v>1105.23</v>
+        <v>268.68</v>
       </c>
       <c r="E708" t="n">
-        <v>-128.73</v>
+        <v>23.92</v>
       </c>
       <c r="F708" t="n">
-        <v>989.9</v>
+        <v>292.6</v>
       </c>
       <c r="G708" t="n">
-        <v>1105.23</v>
+        <v>279.66</v>
       </c>
       <c r="H708" t="n">
-        <v>-115.33</v>
+        <v>12.94</v>
       </c>
       <c r="I708" t="n">
-        <v>963.8</v>
+        <v>284.1</v>
       </c>
       <c r="J708" t="n">
-        <v>1010</v>
+        <v>280.13</v>
       </c>
       <c r="K708" t="n">
-        <v>-46.2</v>
+        <v>3.97</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
@@ -37251,7 +37251,7 @@
         </is>
       </c>
       <c r="N708" t="n">
-        <v>11.65</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="709">
@@ -37266,31 +37266,31 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="D709" t="n">
-        <v>419.97</v>
+        <v>412.37</v>
       </c>
       <c r="E709" t="n">
-        <v>-3.47</v>
+        <v>0.13</v>
       </c>
       <c r="F709" t="n">
-        <v>417.6</v>
+        <v>419.2</v>
       </c>
       <c r="G709" t="n">
-        <v>429.6</v>
+        <v>412.37</v>
       </c>
       <c r="H709" t="n">
-        <v>-12</v>
+        <v>6.83</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
       </c>
       <c r="J709" t="n">
-        <v>410.12</v>
+        <v>400.72</v>
       </c>
       <c r="K709" t="n">
-        <v>2.38</v>
+        <v>11.78</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         </is>
       </c>
       <c r="N709" t="n">
-        <v>0.83</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="710">
@@ -37318,31 +37318,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="D710" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
       <c r="E710" t="n">
-        <v>-52.56</v>
+        <v>43.96</v>
       </c>
       <c r="F710" t="n">
-        <v>729.8</v>
+        <v>743</v>
       </c>
       <c r="G710" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
       <c r="H710" t="n">
-        <v>-49.41</v>
+        <v>54.21</v>
       </c>
       <c r="I710" t="n">
-        <v>712.55</v>
+        <v>722.6</v>
       </c>
       <c r="J710" t="n">
-        <v>716.23</v>
+        <v>699.79</v>
       </c>
       <c r="K710" t="n">
-        <v>-3.68</v>
+        <v>22.81</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -37351,11 +37351,11 @@
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N710" t="n">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
     </row>
   </sheetData>
@@ -40680,31 +40680,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23270.6</v>
+        <v>23346.4</v>
       </c>
       <c r="D64" t="n">
         <v>23346.4</v>
       </c>
       <c r="E64" t="n">
-        <v>-75.8</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>23363.55</v>
+        <v>23389.15</v>
       </c>
       <c r="G64" t="n">
         <v>23394.84</v>
       </c>
       <c r="H64" t="n">
-        <v>-31.29</v>
+        <v>-5.69</v>
       </c>
       <c r="I64" t="n">
-        <v>23193.65</v>
+        <v>23286.6</v>
       </c>
       <c r="J64" t="n">
         <v>23292.29</v>
       </c>
       <c r="K64" t="n">
-        <v>-98.64</v>
+        <v>-5.69</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -40732,31 +40732,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>56055.75</v>
+        <v>56358.7</v>
       </c>
       <c r="D65" t="n">
         <v>56358.7</v>
       </c>
       <c r="E65" t="n">
-        <v>-302.95</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>56570.45</v>
+        <v>56497.45</v>
       </c>
       <c r="G65" t="n">
         <v>56546.25</v>
       </c>
       <c r="H65" t="n">
-        <v>24.2</v>
+        <v>-48.8</v>
       </c>
       <c r="I65" t="n">
-        <v>56038.5</v>
+        <v>56073.55</v>
       </c>
       <c r="J65" t="n">
         <v>56122.35</v>
       </c>
       <c r="K65" t="n">
-        <v>-83.84999999999999</v>
+        <v>-48.8</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -77166,31 +77166,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2160</v>
+        <v>2208.8</v>
       </c>
       <c r="D700" t="n">
-        <v>2407.96</v>
+        <v>2098.67</v>
       </c>
       <c r="E700" t="n">
-        <v>-247.96</v>
+        <v>110.13</v>
       </c>
       <c r="F700" t="n">
-        <v>2232.1</v>
+        <v>2208.8</v>
       </c>
       <c r="G700" t="n">
-        <v>2321.68</v>
+        <v>2154.4</v>
       </c>
       <c r="H700" t="n">
-        <v>-89.58</v>
+        <v>54.4</v>
       </c>
       <c r="I700" t="n">
-        <v>2143</v>
+        <v>2155.5</v>
       </c>
       <c r="J700" t="n">
-        <v>2167.33</v>
+        <v>2117.25</v>
       </c>
       <c r="K700" t="n">
-        <v>-24.33</v>
+        <v>38.25</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -77199,11 +77199,11 @@
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N700" t="n">
-        <v>10.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="701">
@@ -77218,31 +77218,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3211.2</v>
+        <v>3260</v>
       </c>
       <c r="D701" t="n">
-        <v>4284.41</v>
+        <v>2610.95</v>
       </c>
       <c r="E701" t="n">
-        <v>-1073.21</v>
+        <v>649.05</v>
       </c>
       <c r="F701" t="n">
-        <v>3224.5</v>
+        <v>3314.9</v>
       </c>
       <c r="G701" t="n">
-        <v>3449.96</v>
+        <v>3201.4</v>
       </c>
       <c r="H701" t="n">
-        <v>-225.46</v>
+        <v>113.5</v>
       </c>
       <c r="I701" t="n">
-        <v>3056.6</v>
+        <v>3230.1</v>
       </c>
       <c r="J701" t="n">
-        <v>3181.52</v>
+        <v>3108.01</v>
       </c>
       <c r="K701" t="n">
-        <v>-124.92</v>
+        <v>122.09</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -77251,11 +77251,11 @@
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N701" t="n">
-        <v>25.05</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="702">
@@ -77270,31 +77270,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="D702" t="n">
-        <v>354.73</v>
+        <v>312.32</v>
       </c>
       <c r="E702" t="n">
-        <v>-32.38</v>
+        <v>14.53</v>
       </c>
       <c r="F702" t="n">
-        <v>327.8</v>
+        <v>329.75</v>
       </c>
       <c r="G702" t="n">
-        <v>342.35</v>
+        <v>317.69</v>
       </c>
       <c r="H702" t="n">
-        <v>-14.55</v>
+        <v>12.06</v>
       </c>
       <c r="I702" t="n">
-        <v>318.25</v>
+        <v>325.7</v>
       </c>
       <c r="J702" t="n">
-        <v>321.61</v>
+        <v>314.18</v>
       </c>
       <c r="K702" t="n">
-        <v>-3.36</v>
+        <v>11.52</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -77303,11 +77303,11 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N702" t="n">
-        <v>9.130000000000001</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="703">
@@ -77322,31 +77322,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2120</v>
+        <v>2270.1</v>
       </c>
       <c r="D703" t="n">
-        <v>2484.73</v>
+        <v>2040.12</v>
       </c>
       <c r="E703" t="n">
-        <v>-364.73</v>
+        <v>229.98</v>
       </c>
       <c r="F703" t="n">
-        <v>2132.9</v>
+        <v>2270.1</v>
       </c>
       <c r="G703" t="n">
-        <v>2389.46</v>
+        <v>2217.3</v>
       </c>
       <c r="H703" t="n">
-        <v>-256.56</v>
+        <v>52.8</v>
       </c>
       <c r="I703" t="n">
-        <v>2041.3</v>
+        <v>2146.3</v>
       </c>
       <c r="J703" t="n">
-        <v>2225</v>
+        <v>2173.59</v>
       </c>
       <c r="K703" t="n">
-        <v>-183.7</v>
+        <v>-27.29</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -77355,11 +77355,11 @@
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N703" t="n">
-        <v>14.68</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="704">
@@ -77370,35 +77370,35 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>PNB (SEP-2026 FUT)</t>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>116.47</v>
+        <v>548.15</v>
       </c>
       <c r="D704" t="n">
-        <v>127.13</v>
+        <v>536.51</v>
       </c>
       <c r="E704" t="n">
-        <v>-10.66</v>
+        <v>11.64</v>
       </c>
       <c r="F704" t="n">
-        <v>119.4</v>
+        <v>552</v>
       </c>
       <c r="G704" t="n">
-        <v>122.28</v>
+        <v>537.75</v>
       </c>
       <c r="H704" t="n">
-        <v>-2.88</v>
+        <v>14.25</v>
       </c>
       <c r="I704" t="n">
-        <v>116.36</v>
+        <v>543.6</v>
       </c>
       <c r="J704" t="n">
-        <v>115.8</v>
+        <v>523.01</v>
       </c>
       <c r="K704" t="n">
-        <v>0.5600000000000001</v>
+        <v>20.59</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -77407,11 +77407,11 @@
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N704" t="n">
-        <v>8.390000000000001</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="705">
@@ -77422,48 +77422,48 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>LICHSGFIN (SEP-2026 FUT)</t>
+          <t>PNB (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>543</v>
+        <v>117.27</v>
       </c>
       <c r="D705" t="n">
-        <v>594.73</v>
+        <v>111.91</v>
       </c>
       <c r="E705" t="n">
-        <v>-51.73</v>
+        <v>5.36</v>
       </c>
       <c r="F705" t="n">
-        <v>551.45</v>
+        <v>117.5</v>
       </c>
       <c r="G705" t="n">
-        <v>579.51</v>
+        <v>113.46</v>
       </c>
       <c r="H705" t="n">
-        <v>-28.06</v>
+        <v>4.04</v>
       </c>
       <c r="I705" t="n">
-        <v>529.6</v>
+        <v>116.5</v>
       </c>
       <c r="J705" t="n">
-        <v>535.39</v>
+        <v>113.13</v>
       </c>
       <c r="K705" t="n">
-        <v>-5.79</v>
+        <v>3.37</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N705" t="n">
-        <v>8.699999999999999</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="706">
@@ -77478,44 +77478,44 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>10930</v>
+        <v>11282</v>
       </c>
       <c r="D706" t="n">
-        <v>12185.81</v>
+        <v>10453.03</v>
       </c>
       <c r="E706" t="n">
-        <v>-1255.81</v>
+        <v>828.97</v>
       </c>
       <c r="F706" t="n">
-        <v>11090</v>
+        <v>11363</v>
       </c>
       <c r="G706" t="n">
-        <v>11753.44</v>
+        <v>10906.61</v>
       </c>
       <c r="H706" t="n">
-        <v>-663.4400000000001</v>
+        <v>456.39</v>
       </c>
       <c r="I706" t="n">
-        <v>10925</v>
+        <v>11070</v>
       </c>
       <c r="J706" t="n">
-        <v>11147.83</v>
+        <v>10890.28</v>
       </c>
       <c r="K706" t="n">
-        <v>-222.83</v>
+        <v>179.72</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N706" t="n">
-        <v>10.31</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="707">
@@ -77526,35 +77526,35 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>PETRONET (SEP-2026 FUT)</t>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>283.45</v>
+        <v>1010</v>
       </c>
       <c r="D707" t="n">
-        <v>316.71</v>
+        <v>923.95</v>
       </c>
       <c r="E707" t="n">
-        <v>-33.26</v>
+        <v>86.05</v>
       </c>
       <c r="F707" t="n">
-        <v>285</v>
+        <v>1010</v>
       </c>
       <c r="G707" t="n">
-        <v>305.45</v>
+        <v>987.13</v>
       </c>
       <c r="H707" t="n">
-        <v>-20.45</v>
+        <v>22.87</v>
       </c>
       <c r="I707" t="n">
-        <v>281.7</v>
+        <v>988.7</v>
       </c>
       <c r="J707" t="n">
-        <v>288.65</v>
+        <v>966.58</v>
       </c>
       <c r="K707" t="n">
-        <v>-6.95</v>
+        <v>22.12</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -77563,11 +77563,11 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N707" t="n">
-        <v>10.5</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="708">
@@ -77578,35 +77578,35 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>MOTILALOFS (SEP-2026 FUT)</t>
+          <t>PETRONET (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>976.5</v>
+        <v>292.6</v>
       </c>
       <c r="D708" t="n">
-        <v>1130.15</v>
+        <v>273.45</v>
       </c>
       <c r="E708" t="n">
-        <v>-153.65</v>
+        <v>19.15</v>
       </c>
       <c r="F708" t="n">
-        <v>989.9</v>
+        <v>292.6</v>
       </c>
       <c r="G708" t="n">
-        <v>1063.77</v>
+        <v>283.45</v>
       </c>
       <c r="H708" t="n">
-        <v>-73.87</v>
+        <v>9.15</v>
       </c>
       <c r="I708" t="n">
-        <v>963.8</v>
+        <v>284.1</v>
       </c>
       <c r="J708" t="n">
-        <v>989.4400000000001</v>
+        <v>281.99</v>
       </c>
       <c r="K708" t="n">
-        <v>-25.64</v>
+        <v>2.11</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -77615,11 +77615,11 @@
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N708" t="n">
-        <v>13.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="709">
@@ -77634,31 +77634,31 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="D709" t="n">
-        <v>424.85</v>
+        <v>417.1</v>
       </c>
       <c r="E709" t="n">
-        <v>-8.35</v>
+        <v>-4.6</v>
       </c>
       <c r="F709" t="n">
-        <v>417.6</v>
+        <v>419.2</v>
       </c>
       <c r="G709" t="n">
-        <v>428.07</v>
+        <v>397.23</v>
       </c>
       <c r="H709" t="n">
-        <v>-10.47</v>
+        <v>21.97</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
       </c>
       <c r="J709" t="n">
-        <v>408.82</v>
+        <v>399.37</v>
       </c>
       <c r="K709" t="n">
-        <v>3.68</v>
+        <v>13.13</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -77671,7 +77671,7 @@
         </is>
       </c>
       <c r="N709" t="n">
-        <v>1.97</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="710">
@@ -77686,31 +77686,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="D710" t="n">
-        <v>794.84</v>
+        <v>702.5</v>
       </c>
       <c r="E710" t="n">
-        <v>-68.19</v>
+        <v>30.25</v>
       </c>
       <c r="F710" t="n">
-        <v>729.8</v>
+        <v>743</v>
       </c>
       <c r="G710" t="n">
-        <v>766.51</v>
+        <v>711.28</v>
       </c>
       <c r="H710" t="n">
-        <v>-36.71</v>
+        <v>31.72</v>
       </c>
       <c r="I710" t="n">
-        <v>712.55</v>
+        <v>722.6</v>
       </c>
       <c r="J710" t="n">
-        <v>721.71</v>
+        <v>705.04</v>
       </c>
       <c r="K710" t="n">
-        <v>-9.16</v>
+        <v>17.56</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -77719,11 +77719,11 @@
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N710" t="n">
-        <v>8.58</v>
+        <v>4.31</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N710"/>
+  <dimension ref="A1:N719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37356,6 +37356,474 @@
       </c>
       <c r="N710" t="n">
         <v>6.38</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="D711" t="n">
+        <v>418.25</v>
+      </c>
+      <c r="E711" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F711" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="G711" t="n">
+        <v>439.96</v>
+      </c>
+      <c r="H711" t="n">
+        <v>-19.36</v>
+      </c>
+      <c r="I711" t="n">
+        <v>414.55</v>
+      </c>
+      <c r="J711" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="K711" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N711" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D712" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="E712" t="n">
+        <v>-26.19</v>
+      </c>
+      <c r="F712" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G712" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="H712" t="n">
+        <v>-25.59</v>
+      </c>
+      <c r="I712" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="J712" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="K712" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N712" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>11409</v>
+      </c>
+      <c r="D713" t="n">
+        <v>12523.22</v>
+      </c>
+      <c r="E713" t="n">
+        <v>-1114.22</v>
+      </c>
+      <c r="F713" t="n">
+        <v>11434</v>
+      </c>
+      <c r="G713" t="n">
+        <v>12523.22</v>
+      </c>
+      <c r="H713" t="n">
+        <v>-1089.22</v>
+      </c>
+      <c r="I713" t="n">
+        <v>11227</v>
+      </c>
+      <c r="J713" t="n">
+        <v>11366.84</v>
+      </c>
+      <c r="K713" t="n">
+        <v>-139.84</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N713" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>568</v>
+      </c>
+      <c r="D714" t="n">
+        <v>603.2</v>
+      </c>
+      <c r="E714" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="F714" t="n">
+        <v>574.15</v>
+      </c>
+      <c r="G714" t="n">
+        <v>603.71</v>
+      </c>
+      <c r="H714" t="n">
+        <v>-29.56</v>
+      </c>
+      <c r="I714" t="n">
+        <v>543.65</v>
+      </c>
+      <c r="J714" t="n">
+        <v>568</v>
+      </c>
+      <c r="K714" t="n">
+        <v>-24.35</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N714" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>118</v>
+      </c>
+      <c r="D715" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="E715" t="n">
+        <v>-8.69</v>
+      </c>
+      <c r="F715" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="G715" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="H715" t="n">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="I715" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="J715" t="n">
+        <v>118</v>
+      </c>
+      <c r="K715" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N715" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2181.1</v>
+      </c>
+      <c r="D716" t="n">
+        <v>2489.97</v>
+      </c>
+      <c r="E716" t="n">
+        <v>-308.87</v>
+      </c>
+      <c r="F716" t="n">
+        <v>2229</v>
+      </c>
+      <c r="G716" t="n">
+        <v>2489.97</v>
+      </c>
+      <c r="H716" t="n">
+        <v>-260.97</v>
+      </c>
+      <c r="I716" t="n">
+        <v>2178.7</v>
+      </c>
+      <c r="J716" t="n">
+        <v>2142.17</v>
+      </c>
+      <c r="K716" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N716" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>745</v>
+      </c>
+      <c r="D717" t="n">
+        <v>798.89</v>
+      </c>
+      <c r="E717" t="n">
+        <v>-53.89</v>
+      </c>
+      <c r="F717" t="n">
+        <v>755</v>
+      </c>
+      <c r="G717" t="n">
+        <v>798.89</v>
+      </c>
+      <c r="H717" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="I717" t="n">
+        <v>741</v>
+      </c>
+      <c r="J717" t="n">
+        <v>740.17</v>
+      </c>
+      <c r="K717" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N717" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>995</v>
+      </c>
+      <c r="D718" t="n">
+        <v>1120.93</v>
+      </c>
+      <c r="E718" t="n">
+        <v>-125.93</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1009.8</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1120.93</v>
+      </c>
+      <c r="H718" t="n">
+        <v>-111.13</v>
+      </c>
+      <c r="I718" t="n">
+        <v>993.2</v>
+      </c>
+      <c r="J718" t="n">
+        <v>995</v>
+      </c>
+      <c r="K718" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N718" t="n">
+        <v>11.23</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>3209</v>
+      </c>
+      <c r="D719" t="n">
+        <v>4147.04</v>
+      </c>
+      <c r="E719" t="n">
+        <v>-938.04</v>
+      </c>
+      <c r="F719" t="n">
+        <v>3268</v>
+      </c>
+      <c r="G719" t="n">
+        <v>4147.04</v>
+      </c>
+      <c r="H719" t="n">
+        <v>-879.04</v>
+      </c>
+      <c r="I719" t="n">
+        <v>3155.5</v>
+      </c>
+      <c r="J719" t="n">
+        <v>3202.25</v>
+      </c>
+      <c r="K719" t="n">
+        <v>-46.75</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N719" t="n">
+        <v>22.62</v>
       </c>
     </row>
   </sheetData>
@@ -37369,7 +37837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40769,6 +41237,110 @@
         </is>
       </c>
       <c r="N65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>23414.3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>23414.3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>23466.8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>23482.46</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-15.66</v>
+      </c>
+      <c r="I66" t="n">
+        <v>23314.8</v>
+      </c>
+      <c r="J66" t="n">
+        <v>23330.46</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-15.66</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>56470.65</v>
+      </c>
+      <c r="D67" t="n">
+        <v>56470.65</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>56668.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>56669.39</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I67" t="n">
+        <v>56269.55</v>
+      </c>
+      <c r="J67" t="n">
+        <v>56270.74</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40783,7 +41355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N710"/>
+  <dimension ref="A1:N719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77726,6 +78298,474 @@
         <v>4.31</v>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D711" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="E711" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="F711" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G711" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="H711" t="n">
+        <v>-20.42</v>
+      </c>
+      <c r="I711" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="J711" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="K711" t="n">
+        <v>-8.93</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N711" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>11409</v>
+      </c>
+      <c r="D712" t="n">
+        <v>12702.02</v>
+      </c>
+      <c r="E712" t="n">
+        <v>-1293.02</v>
+      </c>
+      <c r="F712" t="n">
+        <v>11434</v>
+      </c>
+      <c r="G712" t="n">
+        <v>12086.52</v>
+      </c>
+      <c r="H712" t="n">
+        <v>-652.52</v>
+      </c>
+      <c r="I712" t="n">
+        <v>11227</v>
+      </c>
+      <c r="J712" t="n">
+        <v>11431.9</v>
+      </c>
+      <c r="K712" t="n">
+        <v>-204.9</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N712" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>568</v>
+      </c>
+      <c r="D713" t="n">
+        <v>620.83</v>
+      </c>
+      <c r="E713" t="n">
+        <v>-52.83</v>
+      </c>
+      <c r="F713" t="n">
+        <v>574.15</v>
+      </c>
+      <c r="G713" t="n">
+        <v>610.25</v>
+      </c>
+      <c r="H713" t="n">
+        <v>-36.1</v>
+      </c>
+      <c r="I713" t="n">
+        <v>543.65</v>
+      </c>
+      <c r="J713" t="n">
+        <v>562.87</v>
+      </c>
+      <c r="K713" t="n">
+        <v>-19.22</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N713" t="n">
+        <v>8.51</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="D714" t="n">
+        <v>422.93</v>
+      </c>
+      <c r="E714" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="F714" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="G714" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="H714" t="n">
+        <v>-17.55</v>
+      </c>
+      <c r="I714" t="n">
+        <v>414.55</v>
+      </c>
+      <c r="J714" t="n">
+        <v>416.59</v>
+      </c>
+      <c r="K714" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N714" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>118</v>
+      </c>
+      <c r="D715" t="n">
+        <v>128.58</v>
+      </c>
+      <c r="E715" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="F715" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="G715" t="n">
+        <v>125.08</v>
+      </c>
+      <c r="H715" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I715" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="J715" t="n">
+        <v>118.19</v>
+      </c>
+      <c r="K715" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N715" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2181.1</v>
+      </c>
+      <c r="D716" t="n">
+        <v>2561.31</v>
+      </c>
+      <c r="E716" t="n">
+        <v>-380.21</v>
+      </c>
+      <c r="F716" t="n">
+        <v>2229</v>
+      </c>
+      <c r="G716" t="n">
+        <v>2342.08</v>
+      </c>
+      <c r="H716" t="n">
+        <v>-113.08</v>
+      </c>
+      <c r="I716" t="n">
+        <v>2178.7</v>
+      </c>
+      <c r="J716" t="n">
+        <v>2162.32</v>
+      </c>
+      <c r="K716" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N716" t="n">
+        <v>14.84</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>745</v>
+      </c>
+      <c r="D717" t="n">
+        <v>812.5599999999999</v>
+      </c>
+      <c r="E717" t="n">
+        <v>-67.56</v>
+      </c>
+      <c r="F717" t="n">
+        <v>755</v>
+      </c>
+      <c r="G717" t="n">
+        <v>791.35</v>
+      </c>
+      <c r="H717" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="I717" t="n">
+        <v>741</v>
+      </c>
+      <c r="J717" t="n">
+        <v>744.9299999999999</v>
+      </c>
+      <c r="K717" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N717" t="n">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>995</v>
+      </c>
+      <c r="D718" t="n">
+        <v>1151.52</v>
+      </c>
+      <c r="E718" t="n">
+        <v>-156.52</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1009.8</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1067.07</v>
+      </c>
+      <c r="H718" t="n">
+        <v>-57.27</v>
+      </c>
+      <c r="I718" t="n">
+        <v>993.2</v>
+      </c>
+      <c r="J718" t="n">
+        <v>987.4299999999999</v>
+      </c>
+      <c r="K718" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N718" t="n">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>3209</v>
+      </c>
+      <c r="D719" t="n">
+        <v>4283.34</v>
+      </c>
+      <c r="E719" t="n">
+        <v>-1074.34</v>
+      </c>
+      <c r="F719" t="n">
+        <v>3268</v>
+      </c>
+      <c r="G719" t="n">
+        <v>3459.43</v>
+      </c>
+      <c r="H719" t="n">
+        <v>-191.43</v>
+      </c>
+      <c r="I719" t="n">
+        <v>3155.5</v>
+      </c>
+      <c r="J719" t="n">
+        <v>3171.38</v>
+      </c>
+      <c r="K719" t="n">
+        <v>-15.88</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N719" t="n">
+        <v>25.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -37370,31 +37370,31 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>414.8</v>
+        <v>412.5</v>
       </c>
       <c r="D711" t="n">
         <v>418.25</v>
       </c>
       <c r="E711" t="n">
-        <v>-3.45</v>
+        <v>-5.75</v>
       </c>
       <c r="F711" t="n">
-        <v>420.6</v>
+        <v>419.2</v>
       </c>
       <c r="G711" t="n">
         <v>439.96</v>
       </c>
       <c r="H711" t="n">
-        <v>-19.36</v>
+        <v>-20.76</v>
       </c>
       <c r="I711" t="n">
-        <v>414.55</v>
+        <v>412.5</v>
       </c>
       <c r="J711" t="n">
         <v>414.8</v>
       </c>
       <c r="K711" t="n">
-        <v>-0.25</v>
+        <v>-2.3</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         </is>
       </c>
       <c r="N711" t="n">
-        <v>0.82</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="712">
@@ -37422,31 +37422,31 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>335.9</v>
+        <v>326.85</v>
       </c>
       <c r="D712" t="n">
         <v>362.09</v>
       </c>
       <c r="E712" t="n">
-        <v>-26.19</v>
+        <v>-35.24</v>
       </c>
       <c r="F712" t="n">
-        <v>336.5</v>
+        <v>329.75</v>
       </c>
       <c r="G712" t="n">
         <v>362.09</v>
       </c>
       <c r="H712" t="n">
-        <v>-25.59</v>
+        <v>-32.34</v>
       </c>
       <c r="I712" t="n">
-        <v>326.85</v>
+        <v>325.7</v>
       </c>
       <c r="J712" t="n">
         <v>335.9</v>
       </c>
       <c r="K712" t="n">
-        <v>-9.050000000000001</v>
+        <v>-10.2</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         </is>
       </c>
       <c r="N712" t="n">
-        <v>7.23</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="713">
@@ -37474,31 +37474,31 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>11409</v>
+        <v>11217</v>
       </c>
       <c r="D713" t="n">
         <v>12523.22</v>
       </c>
       <c r="E713" t="n">
-        <v>-1114.22</v>
+        <v>-1306.22</v>
       </c>
       <c r="F713" t="n">
-        <v>11434</v>
+        <v>11297.53</v>
       </c>
       <c r="G713" t="n">
         <v>12523.22</v>
       </c>
       <c r="H713" t="n">
-        <v>-1089.22</v>
+        <v>-1225.69</v>
       </c>
       <c r="I713" t="n">
-        <v>11227</v>
+        <v>11006.22</v>
       </c>
       <c r="J713" t="n">
         <v>11366.84</v>
       </c>
       <c r="K713" t="n">
-        <v>-139.84</v>
+        <v>-360.62</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
@@ -37507,11 +37507,11 @@
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N713" t="n">
-        <v>8.9</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="714">
@@ -37526,31 +37526,31 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>568</v>
+        <v>548.15</v>
       </c>
       <c r="D714" t="n">
         <v>603.2</v>
       </c>
       <c r="E714" t="n">
-        <v>-35.2</v>
+        <v>-55.05</v>
       </c>
       <c r="F714" t="n">
-        <v>574.15</v>
+        <v>552</v>
       </c>
       <c r="G714" t="n">
         <v>603.71</v>
       </c>
       <c r="H714" t="n">
-        <v>-29.56</v>
+        <v>-51.71</v>
       </c>
       <c r="I714" t="n">
-        <v>543.65</v>
+        <v>543.6</v>
       </c>
       <c r="J714" t="n">
         <v>568</v>
       </c>
       <c r="K714" t="n">
-        <v>-24.35</v>
+        <v>-24.4</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         </is>
       </c>
       <c r="N714" t="n">
-        <v>5.84</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="715">
@@ -37578,31 +37578,31 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>118</v>
+        <v>117.27</v>
       </c>
       <c r="D715" t="n">
         <v>126.69</v>
       </c>
       <c r="E715" t="n">
-        <v>-8.69</v>
+        <v>-9.42</v>
       </c>
       <c r="F715" t="n">
-        <v>118.58</v>
+        <v>117.5</v>
       </c>
       <c r="G715" t="n">
         <v>126.69</v>
       </c>
       <c r="H715" t="n">
-        <v>-8.109999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="I715" t="n">
-        <v>116.64</v>
+        <v>116.5</v>
       </c>
       <c r="J715" t="n">
         <v>118</v>
       </c>
       <c r="K715" t="n">
-        <v>-1.36</v>
+        <v>-1.5</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         </is>
       </c>
       <c r="N715" t="n">
-        <v>6.86</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="716">
@@ -37630,31 +37630,31 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2181.1</v>
+        <v>2270.1</v>
       </c>
       <c r="D716" t="n">
         <v>2489.97</v>
       </c>
       <c r="E716" t="n">
-        <v>-308.87</v>
+        <v>-219.87</v>
       </c>
       <c r="F716" t="n">
-        <v>2229</v>
+        <v>2270.1</v>
       </c>
       <c r="G716" t="n">
         <v>2489.97</v>
       </c>
       <c r="H716" t="n">
-        <v>-260.97</v>
+        <v>-219.87</v>
       </c>
       <c r="I716" t="n">
-        <v>2178.7</v>
+        <v>2146.3</v>
       </c>
       <c r="J716" t="n">
         <v>2142.17</v>
       </c>
       <c r="K716" t="n">
-        <v>36.53</v>
+        <v>4.13</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         </is>
       </c>
       <c r="N716" t="n">
-        <v>12.4</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="717">
@@ -37682,31 +37682,31 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>745</v>
+        <v>732.75</v>
       </c>
       <c r="D717" t="n">
         <v>798.89</v>
       </c>
       <c r="E717" t="n">
-        <v>-53.89</v>
+        <v>-66.14</v>
       </c>
       <c r="F717" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G717" t="n">
         <v>798.89</v>
       </c>
       <c r="H717" t="n">
-        <v>-43.89</v>
+        <v>-55.89</v>
       </c>
       <c r="I717" t="n">
-        <v>741</v>
+        <v>722.6</v>
       </c>
       <c r="J717" t="n">
         <v>740.17</v>
       </c>
       <c r="K717" t="n">
-        <v>0.83</v>
+        <v>-17.57</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -37715,11 +37715,11 @@
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N717" t="n">
-        <v>6.75</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="718">
@@ -37734,31 +37734,31 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="D718" t="n">
         <v>1120.93</v>
       </c>
       <c r="E718" t="n">
-        <v>-125.93</v>
+        <v>-110.93</v>
       </c>
       <c r="F718" t="n">
-        <v>1009.8</v>
+        <v>1010</v>
       </c>
       <c r="G718" t="n">
         <v>1120.93</v>
       </c>
       <c r="H718" t="n">
-        <v>-111.13</v>
+        <v>-110.93</v>
       </c>
       <c r="I718" t="n">
-        <v>993.2</v>
+        <v>988.7</v>
       </c>
       <c r="J718" t="n">
         <v>995</v>
       </c>
       <c r="K718" t="n">
-        <v>-1.8</v>
+        <v>-6.3</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         </is>
       </c>
       <c r="N718" t="n">
-        <v>11.23</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="719">
@@ -37786,31 +37786,31 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>3209</v>
+        <v>3260</v>
       </c>
       <c r="D719" t="n">
         <v>4147.04</v>
       </c>
       <c r="E719" t="n">
-        <v>-938.04</v>
+        <v>-887.04</v>
       </c>
       <c r="F719" t="n">
-        <v>3268</v>
+        <v>3314.9</v>
       </c>
       <c r="G719" t="n">
         <v>4147.04</v>
       </c>
       <c r="H719" t="n">
-        <v>-879.04</v>
+        <v>-832.14</v>
       </c>
       <c r="I719" t="n">
-        <v>3155.5</v>
+        <v>3230.1</v>
       </c>
       <c r="J719" t="n">
         <v>3202.25</v>
       </c>
       <c r="K719" t="n">
-        <v>-46.75</v>
+        <v>27.85</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         </is>
       </c>
       <c r="N719" t="n">
-        <v>22.62</v>
+        <v>21.39</v>
       </c>
     </row>
   </sheetData>
@@ -41252,31 +41252,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>23414.3</v>
+        <v>23346.4</v>
       </c>
       <c r="D66" t="n">
         <v>23414.3</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>23466.8</v>
+        <v>23389.15</v>
       </c>
       <c r="G66" t="n">
         <v>23482.46</v>
       </c>
       <c r="H66" t="n">
-        <v>-15.66</v>
+        <v>-93.31</v>
       </c>
       <c r="I66" t="n">
-        <v>23314.8</v>
+        <v>23286.6</v>
       </c>
       <c r="J66" t="n">
         <v>23330.46</v>
       </c>
       <c r="K66" t="n">
-        <v>-15.66</v>
+        <v>-43.86</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="67">
@@ -41304,31 +41304,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>56470.65</v>
+        <v>56358.7</v>
       </c>
       <c r="D67" t="n">
         <v>56470.65</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>-111.95</v>
       </c>
       <c r="F67" t="n">
-        <v>56668.2</v>
+        <v>56497.45</v>
       </c>
       <c r="G67" t="n">
         <v>56669.39</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.19</v>
+        <v>-171.94</v>
       </c>
       <c r="I67" t="n">
-        <v>56269.55</v>
+        <v>56073.55</v>
       </c>
       <c r="J67" t="n">
         <v>56270.74</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.19</v>
+        <v>-197.19</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -78310,31 +78310,31 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>335.9</v>
+        <v>326.85</v>
       </c>
       <c r="D711" t="n">
         <v>368.2</v>
       </c>
       <c r="E711" t="n">
-        <v>-32.3</v>
+        <v>-41.35</v>
       </c>
       <c r="F711" t="n">
-        <v>336.5</v>
+        <v>329.75</v>
       </c>
       <c r="G711" t="n">
         <v>356.92</v>
       </c>
       <c r="H711" t="n">
-        <v>-20.42</v>
+        <v>-27.17</v>
       </c>
       <c r="I711" t="n">
-        <v>326.85</v>
+        <v>325.7</v>
       </c>
       <c r="J711" t="n">
         <v>335.78</v>
       </c>
       <c r="K711" t="n">
-        <v>-8.93</v>
+        <v>-10.08</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
@@ -78347,7 +78347,7 @@
         </is>
       </c>
       <c r="N711" t="n">
-        <v>8.77</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="712">
@@ -78362,31 +78362,31 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>11409</v>
+        <v>11217</v>
       </c>
       <c r="D712" t="n">
         <v>12702.02</v>
       </c>
       <c r="E712" t="n">
-        <v>-1293.02</v>
+        <v>-1485.02</v>
       </c>
       <c r="F712" t="n">
-        <v>11434</v>
+        <v>11297.53</v>
       </c>
       <c r="G712" t="n">
         <v>12086.52</v>
       </c>
       <c r="H712" t="n">
-        <v>-652.52</v>
+        <v>-788.99</v>
       </c>
       <c r="I712" t="n">
-        <v>11227</v>
+        <v>11006.22</v>
       </c>
       <c r="J712" t="n">
         <v>11431.9</v>
       </c>
       <c r="K712" t="n">
-        <v>-204.9</v>
+        <v>-425.68</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -78399,7 +78399,7 @@
         </is>
       </c>
       <c r="N712" t="n">
-        <v>10.18</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="713">
@@ -78414,31 +78414,31 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>568</v>
+        <v>548.15</v>
       </c>
       <c r="D713" t="n">
         <v>620.83</v>
       </c>
       <c r="E713" t="n">
-        <v>-52.83</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="F713" t="n">
-        <v>574.15</v>
+        <v>552</v>
       </c>
       <c r="G713" t="n">
         <v>610.25</v>
       </c>
       <c r="H713" t="n">
-        <v>-36.1</v>
+        <v>-58.25</v>
       </c>
       <c r="I713" t="n">
-        <v>543.65</v>
+        <v>543.6</v>
       </c>
       <c r="J713" t="n">
         <v>562.87</v>
       </c>
       <c r="K713" t="n">
-        <v>-19.22</v>
+        <v>-19.27</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
@@ -78451,7 +78451,7 @@
         </is>
       </c>
       <c r="N713" t="n">
-        <v>8.51</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="714">
@@ -78466,31 +78466,31 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>414.8</v>
+        <v>412.5</v>
       </c>
       <c r="D714" t="n">
         <v>422.93</v>
       </c>
       <c r="E714" t="n">
-        <v>-8.130000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="F714" t="n">
-        <v>420.6</v>
+        <v>419.2</v>
       </c>
       <c r="G714" t="n">
         <v>438.15</v>
       </c>
       <c r="H714" t="n">
-        <v>-17.55</v>
+        <v>-18.95</v>
       </c>
       <c r="I714" t="n">
-        <v>414.55</v>
+        <v>412.5</v>
       </c>
       <c r="J714" t="n">
         <v>416.59</v>
       </c>
       <c r="K714" t="n">
-        <v>-2.04</v>
+        <v>-4.09</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
@@ -78503,7 +78503,7 @@
         </is>
       </c>
       <c r="N714" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="715">
@@ -78518,31 +78518,31 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>118</v>
+        <v>117.27</v>
       </c>
       <c r="D715" t="n">
         <v>128.58</v>
       </c>
       <c r="E715" t="n">
-        <v>-10.58</v>
+        <v>-11.31</v>
       </c>
       <c r="F715" t="n">
-        <v>118.58</v>
+        <v>117.5</v>
       </c>
       <c r="G715" t="n">
         <v>125.08</v>
       </c>
       <c r="H715" t="n">
-        <v>-6.5</v>
+        <v>-7.58</v>
       </c>
       <c r="I715" t="n">
-        <v>116.64</v>
+        <v>116.5</v>
       </c>
       <c r="J715" t="n">
         <v>118.19</v>
       </c>
       <c r="K715" t="n">
-        <v>-1.55</v>
+        <v>-1.69</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
@@ -78555,7 +78555,7 @@
         </is>
       </c>
       <c r="N715" t="n">
-        <v>8.23</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="716">
@@ -78570,31 +78570,31 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2181.1</v>
+        <v>2270.1</v>
       </c>
       <c r="D716" t="n">
         <v>2561.31</v>
       </c>
       <c r="E716" t="n">
-        <v>-380.21</v>
+        <v>-291.21</v>
       </c>
       <c r="F716" t="n">
-        <v>2229</v>
+        <v>2270.1</v>
       </c>
       <c r="G716" t="n">
         <v>2342.08</v>
       </c>
       <c r="H716" t="n">
-        <v>-113.08</v>
+        <v>-71.98</v>
       </c>
       <c r="I716" t="n">
-        <v>2178.7</v>
+        <v>2146.3</v>
       </c>
       <c r="J716" t="n">
         <v>2162.32</v>
       </c>
       <c r="K716" t="n">
-        <v>16.38</v>
+        <v>-16.02</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -78607,7 +78607,7 @@
         </is>
       </c>
       <c r="N716" t="n">
-        <v>14.84</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="717">
@@ -78622,31 +78622,31 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>745</v>
+        <v>732.75</v>
       </c>
       <c r="D717" t="n">
         <v>812.5599999999999</v>
       </c>
       <c r="E717" t="n">
-        <v>-67.56</v>
+        <v>-79.81</v>
       </c>
       <c r="F717" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G717" t="n">
         <v>791.35</v>
       </c>
       <c r="H717" t="n">
-        <v>-36.35</v>
+        <v>-48.35</v>
       </c>
       <c r="I717" t="n">
-        <v>741</v>
+        <v>722.6</v>
       </c>
       <c r="J717" t="n">
         <v>744.9299999999999</v>
       </c>
       <c r="K717" t="n">
-        <v>-3.93</v>
+        <v>-22.33</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -78659,7 +78659,7 @@
         </is>
       </c>
       <c r="N717" t="n">
-        <v>8.31</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="718">
@@ -78674,31 +78674,31 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="D718" t="n">
         <v>1151.52</v>
       </c>
       <c r="E718" t="n">
-        <v>-156.52</v>
+        <v>-141.52</v>
       </c>
       <c r="F718" t="n">
-        <v>1009.8</v>
+        <v>1010</v>
       </c>
       <c r="G718" t="n">
         <v>1067.07</v>
       </c>
       <c r="H718" t="n">
-        <v>-57.27</v>
+        <v>-57.07</v>
       </c>
       <c r="I718" t="n">
-        <v>993.2</v>
+        <v>988.7</v>
       </c>
       <c r="J718" t="n">
         <v>987.4299999999999</v>
       </c>
       <c r="K718" t="n">
-        <v>5.77</v>
+        <v>1.27</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -78711,7 +78711,7 @@
         </is>
       </c>
       <c r="N718" t="n">
-        <v>13.59</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="719">
@@ -78726,31 +78726,31 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>3209</v>
+        <v>3260</v>
       </c>
       <c r="D719" t="n">
         <v>4283.34</v>
       </c>
       <c r="E719" t="n">
-        <v>-1074.34</v>
+        <v>-1023.34</v>
       </c>
       <c r="F719" t="n">
-        <v>3268</v>
+        <v>3314.9</v>
       </c>
       <c r="G719" t="n">
         <v>3459.43</v>
       </c>
       <c r="H719" t="n">
-        <v>-191.43</v>
+        <v>-144.53</v>
       </c>
       <c r="I719" t="n">
-        <v>3155.5</v>
+        <v>3230.1</v>
       </c>
       <c r="J719" t="n">
         <v>3171.38</v>
       </c>
       <c r="K719" t="n">
-        <v>-15.88</v>
+        <v>58.72</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
@@ -78763,7 +78763,7 @@
         </is>
       </c>
       <c r="N719" t="n">
-        <v>25.08</v>
+        <v>23.89</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N719"/>
+  <dimension ref="A1:N728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37824,6 +37824,474 @@
       </c>
       <c r="N719" t="n">
         <v>21.39</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>342</v>
+      </c>
+      <c r="D720" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="E720" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="F720" t="n">
+        <v>342</v>
+      </c>
+      <c r="G720" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="H720" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="I720" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="J720" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="K720" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N720" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D721" t="n">
+        <v>2017.19</v>
+      </c>
+      <c r="E721" t="n">
+        <v>177.81</v>
+      </c>
+      <c r="F721" t="n">
+        <v>2199.3</v>
+      </c>
+      <c r="G721" t="n">
+        <v>2056.08</v>
+      </c>
+      <c r="H721" t="n">
+        <v>143.22</v>
+      </c>
+      <c r="I721" t="n">
+        <v>2159.9</v>
+      </c>
+      <c r="J721" t="n">
+        <v>2099.05</v>
+      </c>
+      <c r="K721" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N721" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>3262.6</v>
+      </c>
+      <c r="D722" t="n">
+        <v>2585.25</v>
+      </c>
+      <c r="E722" t="n">
+        <v>677.35</v>
+      </c>
+      <c r="F722" t="n">
+        <v>3289.8</v>
+      </c>
+      <c r="G722" t="n">
+        <v>3126.44</v>
+      </c>
+      <c r="H722" t="n">
+        <v>163.36</v>
+      </c>
+      <c r="I722" t="n">
+        <v>3212.8</v>
+      </c>
+      <c r="J722" t="n">
+        <v>3194.38</v>
+      </c>
+      <c r="K722" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N722" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D723" t="n">
+        <v>914.61</v>
+      </c>
+      <c r="E723" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="F723" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G723" t="n">
+        <v>960.98</v>
+      </c>
+      <c r="H723" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="I723" t="n">
+        <v>995.6</v>
+      </c>
+      <c r="J723" t="n">
+        <v>981.71</v>
+      </c>
+      <c r="K723" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N723" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D724" t="n">
+        <v>1646.63</v>
+      </c>
+      <c r="E724" t="n">
+        <v>158.37</v>
+      </c>
+      <c r="F724" t="n">
+        <v>1806.4</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1646.63</v>
+      </c>
+      <c r="H724" t="n">
+        <v>159.77</v>
+      </c>
+      <c r="I724" t="n">
+        <v>1773.7</v>
+      </c>
+      <c r="J724" t="n">
+        <v>1711.38</v>
+      </c>
+      <c r="K724" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N724" t="n">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="D725" t="n">
+        <v>410.23</v>
+      </c>
+      <c r="E725" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F725" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="G725" t="n">
+        <v>410.23</v>
+      </c>
+      <c r="H725" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="I725" t="n">
+        <v>412.55</v>
+      </c>
+      <c r="J725" t="n">
+        <v>400.19</v>
+      </c>
+      <c r="K725" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N725" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>117</v>
+      </c>
+      <c r="D726" t="n">
+        <v>109.17</v>
+      </c>
+      <c r="E726" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F726" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="G726" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="H726" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I726" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="J726" t="n">
+        <v>113.84</v>
+      </c>
+      <c r="K726" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N726" t="n">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>565</v>
+      </c>
+      <c r="D727" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="E727" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="F727" t="n">
+        <v>573.95</v>
+      </c>
+      <c r="G727" t="n">
+        <v>518.02</v>
+      </c>
+      <c r="H727" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="I727" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="J727" t="n">
+        <v>536.4</v>
+      </c>
+      <c r="K727" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N727" t="n">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="D728" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="E728" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="F728" t="n">
+        <v>749.4</v>
+      </c>
+      <c r="G728" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="H728" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="I728" t="n">
+        <v>735.75</v>
+      </c>
+      <c r="J728" t="n">
+        <v>709.86</v>
+      </c>
+      <c r="K728" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N728" t="n">
+        <v>8.16</v>
       </c>
     </row>
   </sheetData>
@@ -37837,7 +38305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41342,6 +41810,110 @@
       </c>
       <c r="N67" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>23329</v>
+      </c>
+      <c r="D68" t="n">
+        <v>23329</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>23489</v>
+      </c>
+      <c r="G68" t="n">
+        <v>23450.09</v>
+      </c>
+      <c r="H68" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="I68" t="n">
+        <v>23285.75</v>
+      </c>
+      <c r="J68" t="n">
+        <v>23246.84</v>
+      </c>
+      <c r="K68" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>56215.55</v>
+      </c>
+      <c r="D69" t="n">
+        <v>56215.55</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>56671.1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>56555.45</v>
+      </c>
+      <c r="H69" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="I69" t="n">
+        <v>56106.95</v>
+      </c>
+      <c r="J69" t="n">
+        <v>55991.3</v>
+      </c>
+      <c r="K69" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -41355,7 +41927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N719"/>
+  <dimension ref="A1:N728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78766,6 +79338,474 @@
         <v>23.89</v>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>342</v>
+      </c>
+      <c r="D720" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="E720" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="F720" t="n">
+        <v>342</v>
+      </c>
+      <c r="G720" t="n">
+        <v>327.26</v>
+      </c>
+      <c r="H720" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="I720" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="J720" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="K720" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N720" t="n">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D721" t="n">
+        <v>2078.32</v>
+      </c>
+      <c r="E721" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="F721" t="n">
+        <v>2199.3</v>
+      </c>
+      <c r="G721" t="n">
+        <v>2125.06</v>
+      </c>
+      <c r="H721" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="I721" t="n">
+        <v>2159.9</v>
+      </c>
+      <c r="J721" t="n">
+        <v>2108.62</v>
+      </c>
+      <c r="K721" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N721" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>3262.6</v>
+      </c>
+      <c r="D722" t="n">
+        <v>2666.23</v>
+      </c>
+      <c r="E722" t="n">
+        <v>596.37</v>
+      </c>
+      <c r="F722" t="n">
+        <v>3289.8</v>
+      </c>
+      <c r="G722" t="n">
+        <v>3161.65</v>
+      </c>
+      <c r="H722" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="I722" t="n">
+        <v>3212.8</v>
+      </c>
+      <c r="J722" t="n">
+        <v>3131.81</v>
+      </c>
+      <c r="K722" t="n">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N722" t="n">
+        <v>22.37</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D723" t="n">
+        <v>937.3200000000001</v>
+      </c>
+      <c r="E723" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="F723" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G723" t="n">
+        <v>969.9299999999999</v>
+      </c>
+      <c r="H723" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="I723" t="n">
+        <v>995.6</v>
+      </c>
+      <c r="J723" t="n">
+        <v>971.3099999999999</v>
+      </c>
+      <c r="K723" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N723" t="n">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>POLICYBZR (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D724" t="n">
+        <v>1701.96</v>
+      </c>
+      <c r="E724" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="F724" t="n">
+        <v>1806.4</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1752.87</v>
+      </c>
+      <c r="H724" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="I724" t="n">
+        <v>1773.7</v>
+      </c>
+      <c r="J724" t="n">
+        <v>1729.69</v>
+      </c>
+      <c r="K724" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N724" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>117</v>
+      </c>
+      <c r="D725" t="n">
+        <v>110.78</v>
+      </c>
+      <c r="E725" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="F725" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="G725" t="n">
+        <v>111.63</v>
+      </c>
+      <c r="H725" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I725" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="J725" t="n">
+        <v>113.71</v>
+      </c>
+      <c r="K725" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N725" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="D726" t="n">
+        <v>414.7</v>
+      </c>
+      <c r="E726" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="F726" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="G726" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="H726" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="I726" t="n">
+        <v>412.55</v>
+      </c>
+      <c r="J726" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="K726" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N726" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>565</v>
+      </c>
+      <c r="D727" t="n">
+        <v>534.26</v>
+      </c>
+      <c r="E727" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="F727" t="n">
+        <v>573.95</v>
+      </c>
+      <c r="G727" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="H727" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="I727" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="J727" t="n">
+        <v>541.96</v>
+      </c>
+      <c r="K727" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N727" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="D728" t="n">
+        <v>692.15</v>
+      </c>
+      <c r="E728" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F728" t="n">
+        <v>749.4</v>
+      </c>
+      <c r="G728" t="n">
+        <v>703.84</v>
+      </c>
+      <c r="H728" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="I728" t="n">
+        <v>735.75</v>
+      </c>
+      <c r="J728" t="n">
+        <v>714.38</v>
+      </c>
+      <c r="K728" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N728" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -37838,31 +37838,31 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>342</v>
+        <v>335.9</v>
       </c>
       <c r="D720" t="n">
         <v>311.19</v>
       </c>
       <c r="E720" t="n">
-        <v>30.81</v>
+        <v>24.71</v>
       </c>
       <c r="F720" t="n">
-        <v>342</v>
+        <v>336.5</v>
       </c>
       <c r="G720" t="n">
         <v>326.69</v>
       </c>
       <c r="H720" t="n">
-        <v>15.31</v>
+        <v>9.81</v>
       </c>
       <c r="I720" t="n">
-        <v>334.65</v>
+        <v>326.85</v>
       </c>
       <c r="J720" t="n">
         <v>333.75</v>
       </c>
       <c r="K720" t="n">
-        <v>0.9</v>
+        <v>-6.9</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         </is>
       </c>
       <c r="N720" t="n">
-        <v>9.9</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="721">
@@ -37890,31 +37890,31 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>2195</v>
+        <v>2181.1</v>
       </c>
       <c r="D721" t="n">
         <v>2017.19</v>
       </c>
       <c r="E721" t="n">
-        <v>177.81</v>
+        <v>163.91</v>
       </c>
       <c r="F721" t="n">
-        <v>2199.3</v>
+        <v>2229</v>
       </c>
       <c r="G721" t="n">
         <v>2056.08</v>
       </c>
       <c r="H721" t="n">
-        <v>143.22</v>
+        <v>172.92</v>
       </c>
       <c r="I721" t="n">
-        <v>2159.9</v>
+        <v>2178.7</v>
       </c>
       <c r="J721" t="n">
         <v>2099.05</v>
       </c>
       <c r="K721" t="n">
-        <v>60.85</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         </is>
       </c>
       <c r="N721" t="n">
-        <v>8.81</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="722">
@@ -37942,31 +37942,31 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>3262.6</v>
+        <v>3209</v>
       </c>
       <c r="D722" t="n">
         <v>2585.25</v>
       </c>
       <c r="E722" t="n">
-        <v>677.35</v>
+        <v>623.75</v>
       </c>
       <c r="F722" t="n">
-        <v>3289.8</v>
+        <v>3268</v>
       </c>
       <c r="G722" t="n">
         <v>3126.44</v>
       </c>
       <c r="H722" t="n">
-        <v>163.36</v>
+        <v>141.56</v>
       </c>
       <c r="I722" t="n">
-        <v>3212.8</v>
+        <v>3155.5</v>
       </c>
       <c r="J722" t="n">
         <v>3194.38</v>
       </c>
       <c r="K722" t="n">
-        <v>18.42</v>
+        <v>-38.88</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         </is>
       </c>
       <c r="N722" t="n">
-        <v>26.2</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="723">
@@ -37994,31 +37994,31 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="D723" t="n">
         <v>914.61</v>
       </c>
       <c r="E723" t="n">
-        <v>92.39</v>
+        <v>80.39</v>
       </c>
       <c r="F723" t="n">
-        <v>1025</v>
+        <v>1009.8</v>
       </c>
       <c r="G723" t="n">
         <v>960.98</v>
       </c>
       <c r="H723" t="n">
-        <v>64.02</v>
+        <v>48.82</v>
       </c>
       <c r="I723" t="n">
-        <v>995.6</v>
+        <v>993.2</v>
       </c>
       <c r="J723" t="n">
         <v>981.71</v>
       </c>
       <c r="K723" t="n">
-        <v>13.89</v>
+        <v>11.49</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="N723" t="n">
-        <v>10.1</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="724">
@@ -38046,31 +38046,31 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1805</v>
+        <v>1793</v>
       </c>
       <c r="D724" t="n">
         <v>1646.63</v>
       </c>
       <c r="E724" t="n">
-        <v>158.37</v>
+        <v>146.37</v>
       </c>
       <c r="F724" t="n">
-        <v>1806.4</v>
+        <v>1804.4</v>
       </c>
       <c r="G724" t="n">
         <v>1646.63</v>
       </c>
       <c r="H724" t="n">
-        <v>159.77</v>
+        <v>157.77</v>
       </c>
       <c r="I724" t="n">
-        <v>1773.7</v>
+        <v>1745</v>
       </c>
       <c r="J724" t="n">
         <v>1711.38</v>
       </c>
       <c r="K724" t="n">
-        <v>62.32</v>
+        <v>33.62</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         </is>
       </c>
       <c r="N724" t="n">
-        <v>9.619999999999999</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="725">
@@ -38098,31 +38098,31 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>412.65</v>
+        <v>414.8</v>
       </c>
       <c r="D725" t="n">
         <v>410.23</v>
       </c>
       <c r="E725" t="n">
-        <v>2.42</v>
+        <v>4.57</v>
       </c>
       <c r="F725" t="n">
-        <v>417.8</v>
+        <v>420.6</v>
       </c>
       <c r="G725" t="n">
         <v>410.23</v>
       </c>
       <c r="H725" t="n">
-        <v>7.57</v>
+        <v>10.37</v>
       </c>
       <c r="I725" t="n">
-        <v>412.55</v>
+        <v>414.55</v>
       </c>
       <c r="J725" t="n">
         <v>400.19</v>
       </c>
       <c r="K725" t="n">
-        <v>12.36</v>
+        <v>14.36</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         </is>
       </c>
       <c r="N725" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="726">
@@ -38150,31 +38150,31 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D726" t="n">
         <v>109.17</v>
       </c>
       <c r="E726" t="n">
-        <v>7.83</v>
+        <v>8.83</v>
       </c>
       <c r="F726" t="n">
-        <v>118.74</v>
+        <v>118.58</v>
       </c>
       <c r="G726" t="n">
         <v>111.44</v>
       </c>
       <c r="H726" t="n">
-        <v>7.3</v>
+        <v>7.14</v>
       </c>
       <c r="I726" t="n">
-        <v>116.7</v>
+        <v>116.64</v>
       </c>
       <c r="J726" t="n">
         <v>113.84</v>
       </c>
       <c r="K726" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         </is>
       </c>
       <c r="N726" t="n">
-        <v>7.17</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="727">
@@ -38202,31 +38202,31 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D727" t="n">
         <v>517.55</v>
       </c>
       <c r="E727" t="n">
-        <v>47.45</v>
+        <v>50.45</v>
       </c>
       <c r="F727" t="n">
-        <v>573.95</v>
+        <v>574.15</v>
       </c>
       <c r="G727" t="n">
         <v>518.02</v>
       </c>
       <c r="H727" t="n">
-        <v>55.93</v>
+        <v>56.13</v>
       </c>
       <c r="I727" t="n">
-        <v>563.2</v>
+        <v>543.65</v>
       </c>
       <c r="J727" t="n">
         <v>536.4</v>
       </c>
       <c r="K727" t="n">
-        <v>26.8</v>
+        <v>7.25</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         </is>
       </c>
       <c r="N727" t="n">
-        <v>9.17</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="728">
@@ -38254,31 +38254,31 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>736.25</v>
+        <v>745</v>
       </c>
       <c r="D728" t="n">
         <v>680.7</v>
       </c>
       <c r="E728" t="n">
-        <v>55.55</v>
+        <v>64.3</v>
       </c>
       <c r="F728" t="n">
-        <v>749.4</v>
+        <v>755</v>
       </c>
       <c r="G728" t="n">
         <v>680.7</v>
       </c>
       <c r="H728" t="n">
-        <v>68.7</v>
+        <v>74.3</v>
       </c>
       <c r="I728" t="n">
-        <v>735.75</v>
+        <v>741</v>
       </c>
       <c r="J728" t="n">
         <v>709.86</v>
       </c>
       <c r="K728" t="n">
-        <v>25.89</v>
+        <v>31.14</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         </is>
       </c>
       <c r="N728" t="n">
-        <v>8.16</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -41824,31 +41824,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>23329</v>
+        <v>23414.3</v>
       </c>
       <c r="D68" t="n">
         <v>23329</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="F68" t="n">
-        <v>23489</v>
+        <v>23466.8</v>
       </c>
       <c r="G68" t="n">
         <v>23450.09</v>
       </c>
       <c r="H68" t="n">
-        <v>38.91</v>
+        <v>16.71</v>
       </c>
       <c r="I68" t="n">
-        <v>23285.75</v>
+        <v>23314.8</v>
       </c>
       <c r="J68" t="n">
         <v>23246.84</v>
       </c>
       <c r="K68" t="n">
-        <v>38.91</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="69">
@@ -41876,31 +41876,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>56215.55</v>
+        <v>56470.65</v>
       </c>
       <c r="D69" t="n">
         <v>56215.55</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>255.1</v>
       </c>
       <c r="F69" t="n">
-        <v>56671.1</v>
+        <v>56668.2</v>
       </c>
       <c r="G69" t="n">
         <v>56555.45</v>
       </c>
       <c r="H69" t="n">
-        <v>115.65</v>
+        <v>112.75</v>
       </c>
       <c r="I69" t="n">
-        <v>56106.95</v>
+        <v>56269.55</v>
       </c>
       <c r="J69" t="n">
         <v>55991.3</v>
       </c>
       <c r="K69" t="n">
-        <v>115.65</v>
+        <v>278.25</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -79350,31 +79350,31 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>342</v>
+        <v>335.9</v>
       </c>
       <c r="D720" t="n">
         <v>316.74</v>
       </c>
       <c r="E720" t="n">
-        <v>25.26</v>
+        <v>19.16</v>
       </c>
       <c r="F720" t="n">
-        <v>342</v>
+        <v>336.5</v>
       </c>
       <c r="G720" t="n">
         <v>327.26</v>
       </c>
       <c r="H720" t="n">
-        <v>14.74</v>
+        <v>9.24</v>
       </c>
       <c r="I720" t="n">
-        <v>334.65</v>
+        <v>326.85</v>
       </c>
       <c r="J720" t="n">
         <v>331.59</v>
       </c>
       <c r="K720" t="n">
-        <v>3.06</v>
+        <v>-4.74</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
@@ -79387,7 +79387,7 @@
         </is>
       </c>
       <c r="N720" t="n">
-        <v>7.97</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="721">
@@ -79402,31 +79402,31 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>2195</v>
+        <v>2181.1</v>
       </c>
       <c r="D721" t="n">
         <v>2078.32</v>
       </c>
       <c r="E721" t="n">
-        <v>116.68</v>
+        <v>102.78</v>
       </c>
       <c r="F721" t="n">
-        <v>2199.3</v>
+        <v>2229</v>
       </c>
       <c r="G721" t="n">
         <v>2125.06</v>
       </c>
       <c r="H721" t="n">
-        <v>74.23999999999999</v>
+        <v>103.94</v>
       </c>
       <c r="I721" t="n">
-        <v>2159.9</v>
+        <v>2178.7</v>
       </c>
       <c r="J721" t="n">
         <v>2108.62</v>
       </c>
       <c r="K721" t="n">
-        <v>51.28</v>
+        <v>70.08</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -79439,7 +79439,7 @@
         </is>
       </c>
       <c r="N721" t="n">
-        <v>5.61</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="722">
@@ -79454,31 +79454,31 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>3262.6</v>
+        <v>3209</v>
       </c>
       <c r="D722" t="n">
         <v>2666.23</v>
       </c>
       <c r="E722" t="n">
-        <v>596.37</v>
+        <v>542.77</v>
       </c>
       <c r="F722" t="n">
-        <v>3289.8</v>
+        <v>3268</v>
       </c>
       <c r="G722" t="n">
         <v>3161.65</v>
       </c>
       <c r="H722" t="n">
-        <v>128.15</v>
+        <v>106.35</v>
       </c>
       <c r="I722" t="n">
-        <v>3212.8</v>
+        <v>3155.5</v>
       </c>
       <c r="J722" t="n">
         <v>3131.81</v>
       </c>
       <c r="K722" t="n">
-        <v>80.98999999999999</v>
+        <v>23.69</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
@@ -79491,7 +79491,7 @@
         </is>
       </c>
       <c r="N722" t="n">
-        <v>22.37</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="723">
@@ -79506,31 +79506,31 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="D723" t="n">
         <v>937.3200000000001</v>
       </c>
       <c r="E723" t="n">
-        <v>69.68000000000001</v>
+        <v>57.68</v>
       </c>
       <c r="F723" t="n">
-        <v>1025</v>
+        <v>1009.8</v>
       </c>
       <c r="G723" t="n">
         <v>969.9299999999999</v>
       </c>
       <c r="H723" t="n">
-        <v>55.07</v>
+        <v>39.87</v>
       </c>
       <c r="I723" t="n">
-        <v>995.6</v>
+        <v>993.2</v>
       </c>
       <c r="J723" t="n">
         <v>971.3099999999999</v>
       </c>
       <c r="K723" t="n">
-        <v>24.29</v>
+        <v>21.89</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -79543,7 +79543,7 @@
         </is>
       </c>
       <c r="N723" t="n">
-        <v>7.43</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="724">
@@ -79558,31 +79558,31 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1805</v>
+        <v>1793</v>
       </c>
       <c r="D724" t="n">
         <v>1701.96</v>
       </c>
       <c r="E724" t="n">
-        <v>103.04</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="F724" t="n">
-        <v>1806.4</v>
+        <v>1804.4</v>
       </c>
       <c r="G724" t="n">
         <v>1752.87</v>
       </c>
       <c r="H724" t="n">
-        <v>53.53</v>
+        <v>51.53</v>
       </c>
       <c r="I724" t="n">
-        <v>1773.7</v>
+        <v>1745</v>
       </c>
       <c r="J724" t="n">
         <v>1729.69</v>
       </c>
       <c r="K724" t="n">
-        <v>44.01</v>
+        <v>15.31</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -79595,7 +79595,7 @@
         </is>
       </c>
       <c r="N724" t="n">
-        <v>6.05</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="725">
@@ -79610,31 +79610,31 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D725" t="n">
         <v>110.78</v>
       </c>
       <c r="E725" t="n">
-        <v>6.22</v>
+        <v>7.22</v>
       </c>
       <c r="F725" t="n">
-        <v>118.74</v>
+        <v>118.58</v>
       </c>
       <c r="G725" t="n">
         <v>111.63</v>
       </c>
       <c r="H725" t="n">
-        <v>7.11</v>
+        <v>6.95</v>
       </c>
       <c r="I725" t="n">
-        <v>116.7</v>
+        <v>116.64</v>
       </c>
       <c r="J725" t="n">
         <v>113.71</v>
       </c>
       <c r="K725" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -79647,7 +79647,7 @@
         </is>
       </c>
       <c r="N725" t="n">
-        <v>5.61</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="726">
@@ -79662,31 +79662,31 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>412.65</v>
+        <v>414.8</v>
       </c>
       <c r="D726" t="n">
         <v>414.7</v>
       </c>
       <c r="E726" t="n">
-        <v>-2.05</v>
+        <v>0.1</v>
       </c>
       <c r="F726" t="n">
-        <v>417.8</v>
+        <v>420.6</v>
       </c>
       <c r="G726" t="n">
         <v>392.26</v>
       </c>
       <c r="H726" t="n">
-        <v>25.54</v>
+        <v>28.34</v>
       </c>
       <c r="I726" t="n">
-        <v>412.55</v>
+        <v>414.55</v>
       </c>
       <c r="J726" t="n">
         <v>402.15</v>
       </c>
       <c r="K726" t="n">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -79699,7 +79699,7 @@
         </is>
       </c>
       <c r="N726" t="n">
-        <v>0.49</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="727">
@@ -79714,31 +79714,31 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D727" t="n">
         <v>534.26</v>
       </c>
       <c r="E727" t="n">
-        <v>30.74</v>
+        <v>33.74</v>
       </c>
       <c r="F727" t="n">
-        <v>573.95</v>
+        <v>574.15</v>
       </c>
       <c r="G727" t="n">
         <v>548.01</v>
       </c>
       <c r="H727" t="n">
-        <v>25.94</v>
+        <v>26.14</v>
       </c>
       <c r="I727" t="n">
-        <v>563.2</v>
+        <v>543.65</v>
       </c>
       <c r="J727" t="n">
         <v>541.96</v>
       </c>
       <c r="K727" t="n">
-        <v>21.24</v>
+        <v>1.69</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
@@ -79751,7 +79751,7 @@
         </is>
       </c>
       <c r="N727" t="n">
-        <v>5.75</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="728">
@@ -79766,31 +79766,31 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>736.25</v>
+        <v>745</v>
       </c>
       <c r="D728" t="n">
         <v>692.15</v>
       </c>
       <c r="E728" t="n">
-        <v>44.1</v>
+        <v>52.85</v>
       </c>
       <c r="F728" t="n">
-        <v>749.4</v>
+        <v>755</v>
       </c>
       <c r="G728" t="n">
         <v>703.84</v>
       </c>
       <c r="H728" t="n">
-        <v>45.56</v>
+        <v>51.16</v>
       </c>
       <c r="I728" t="n">
-        <v>735.75</v>
+        <v>741</v>
       </c>
       <c r="J728" t="n">
         <v>714.38</v>
       </c>
       <c r="K728" t="n">
-        <v>21.37</v>
+        <v>26.62</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
@@ -79803,7 +79803,7 @@
         </is>
       </c>
       <c r="N728" t="n">
-        <v>6.37</v>
+        <v>7.64</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N728"/>
+  <dimension ref="A1:N738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38292,6 +38292,526 @@
       </c>
       <c r="N728" t="n">
         <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="D729" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="E729" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="F729" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="G729" t="n">
+        <v>435.67</v>
+      </c>
+      <c r="H729" t="n">
+        <v>-18.42</v>
+      </c>
+      <c r="I729" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="J729" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="K729" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N729" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="D730" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="E730" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="F730" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G730" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="H730" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="I730" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="J730" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="K730" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N730" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="D731" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="E731" t="n">
+        <v>-30.16</v>
+      </c>
+      <c r="F731" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="G731" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="H731" t="n">
+        <v>-28.41</v>
+      </c>
+      <c r="I731" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="J731" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="K731" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N731" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D732" t="n">
+        <v>4234.94</v>
+      </c>
+      <c r="E732" t="n">
+        <v>-860.9400000000001</v>
+      </c>
+      <c r="F732" t="n">
+        <v>3374</v>
+      </c>
+      <c r="G732" t="n">
+        <v>4234.94</v>
+      </c>
+      <c r="H732" t="n">
+        <v>-860.9400000000001</v>
+      </c>
+      <c r="I732" t="n">
+        <v>3237.5</v>
+      </c>
+      <c r="J732" t="n">
+        <v>3374</v>
+      </c>
+      <c r="K732" t="n">
+        <v>-136.5</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N732" t="n">
+        <v>20.33</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>1886.3</v>
+      </c>
+      <c r="D733" t="n">
+        <v>2070.4</v>
+      </c>
+      <c r="E733" t="n">
+        <v>-184.1</v>
+      </c>
+      <c r="F733" t="n">
+        <v>1904.9</v>
+      </c>
+      <c r="G733" t="n">
+        <v>2070.4</v>
+      </c>
+      <c r="H733" t="n">
+        <v>-165.5</v>
+      </c>
+      <c r="I733" t="n">
+        <v>1793</v>
+      </c>
+      <c r="J733" t="n">
+        <v>1856.48</v>
+      </c>
+      <c r="K733" t="n">
+        <v>-63.48</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N733" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="D734" t="n">
+        <v>1148.51</v>
+      </c>
+      <c r="E734" t="n">
+        <v>-106.01</v>
+      </c>
+      <c r="F734" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G734" t="n">
+        <v>1148.51</v>
+      </c>
+      <c r="H734" t="n">
+        <v>-90.51000000000001</v>
+      </c>
+      <c r="I734" t="n">
+        <v>1009.2</v>
+      </c>
+      <c r="J734" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="K734" t="n">
+        <v>-33.3</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N734" t="n">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="D735" t="n">
+        <v>12466.15</v>
+      </c>
+      <c r="E735" t="n">
+        <v>-1017.15</v>
+      </c>
+      <c r="F735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="G735" t="n">
+        <v>12466.15</v>
+      </c>
+      <c r="H735" t="n">
+        <v>-1017.15</v>
+      </c>
+      <c r="I735" t="n">
+        <v>11195</v>
+      </c>
+      <c r="J735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="K735" t="n">
+        <v>-254</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N735" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="D736" t="n">
+        <v>633.33</v>
+      </c>
+      <c r="E736" t="n">
+        <v>-60.83</v>
+      </c>
+      <c r="F736" t="n">
+        <v>576.7</v>
+      </c>
+      <c r="G736" t="n">
+        <v>633.33</v>
+      </c>
+      <c r="H736" t="n">
+        <v>-56.63</v>
+      </c>
+      <c r="I736" t="n">
+        <v>564.05</v>
+      </c>
+      <c r="J736" t="n">
+        <v>563.5599999999999</v>
+      </c>
+      <c r="K736" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N736" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D737" t="n">
+        <v>2392.35</v>
+      </c>
+      <c r="E737" t="n">
+        <v>-197.35</v>
+      </c>
+      <c r="F737" t="n">
+        <v>2204</v>
+      </c>
+      <c r="G737" t="n">
+        <v>2392.35</v>
+      </c>
+      <c r="H737" t="n">
+        <v>-188.35</v>
+      </c>
+      <c r="I737" t="n">
+        <v>2178</v>
+      </c>
+      <c r="J737" t="n">
+        <v>2162.51</v>
+      </c>
+      <c r="K737" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N737" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="D738" t="n">
+        <v>820.46</v>
+      </c>
+      <c r="E738" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="F738" t="n">
+        <v>744</v>
+      </c>
+      <c r="G738" t="n">
+        <v>820.46</v>
+      </c>
+      <c r="H738" t="n">
+        <v>-76.45999999999999</v>
+      </c>
+      <c r="I738" t="n">
+        <v>736.15</v>
+      </c>
+      <c r="J738" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="K738" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N738" t="n">
+        <v>9.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -38305,7 +38825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41914,6 +42434,110 @@
       </c>
       <c r="N69" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>23446.8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>23446.8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>23466.9</v>
+      </c>
+      <c r="G70" t="n">
+        <v>23492.61</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-25.71</v>
+      </c>
+      <c r="I70" t="n">
+        <v>23349.55</v>
+      </c>
+      <c r="J70" t="n">
+        <v>23375.26</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-25.71</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>56548.9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>56548.9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>56623.8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>56711.91</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-88.11</v>
+      </c>
+      <c r="I71" t="n">
+        <v>56209.65</v>
+      </c>
+      <c r="J71" t="n">
+        <v>56297.76</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-88.11</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -41927,7 +42551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N728"/>
+  <dimension ref="A1:N738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79806,6 +80430,526 @@
         <v>7.64</v>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="D729" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="E729" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="F729" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G729" t="n">
+        <v>127.38</v>
+      </c>
+      <c r="H729" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="I729" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="J729" t="n">
+        <v>119.12</v>
+      </c>
+      <c r="K729" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N729" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="D730" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="E730" t="n">
+        <v>-36.75</v>
+      </c>
+      <c r="F730" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="G730" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="H730" t="n">
+        <v>-26.09</v>
+      </c>
+      <c r="I730" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="J730" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="K730" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N730" t="n">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D731" t="n">
+        <v>4348.37</v>
+      </c>
+      <c r="E731" t="n">
+        <v>-974.37</v>
+      </c>
+      <c r="F731" t="n">
+        <v>3374</v>
+      </c>
+      <c r="G731" t="n">
+        <v>3690.82</v>
+      </c>
+      <c r="H731" t="n">
+        <v>-316.82</v>
+      </c>
+      <c r="I731" t="n">
+        <v>3237.5</v>
+      </c>
+      <c r="J731" t="n">
+        <v>3355.49</v>
+      </c>
+      <c r="K731" t="n">
+        <v>-117.99</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N731" t="n">
+        <v>22.41</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>POLICYBZR (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>1886.3</v>
+      </c>
+      <c r="D732" t="n">
+        <v>2134.3</v>
+      </c>
+      <c r="E732" t="n">
+        <v>-248</v>
+      </c>
+      <c r="F732" t="n">
+        <v>1904.9</v>
+      </c>
+      <c r="G732" t="n">
+        <v>2065.01</v>
+      </c>
+      <c r="H732" t="n">
+        <v>-160.11</v>
+      </c>
+      <c r="I732" t="n">
+        <v>1793</v>
+      </c>
+      <c r="J732" t="n">
+        <v>1874.8</v>
+      </c>
+      <c r="K732" t="n">
+        <v>-81.8</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N732" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="D733" t="n">
+        <v>1169.99</v>
+      </c>
+      <c r="E733" t="n">
+        <v>-127.49</v>
+      </c>
+      <c r="F733" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G733" t="n">
+        <v>1133.36</v>
+      </c>
+      <c r="H733" t="n">
+        <v>-75.36</v>
+      </c>
+      <c r="I733" t="n">
+        <v>1009.2</v>
+      </c>
+      <c r="J733" t="n">
+        <v>1041.9</v>
+      </c>
+      <c r="K733" t="n">
+        <v>-32.7</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N733" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="D734" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E734" t="n">
+        <v>-12.32</v>
+      </c>
+      <c r="F734" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="G734" t="n">
+        <v>443.76</v>
+      </c>
+      <c r="H734" t="n">
+        <v>-26.51</v>
+      </c>
+      <c r="I734" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="J734" t="n">
+        <v>417.01</v>
+      </c>
+      <c r="K734" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N734" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="D735" t="n">
+        <v>12632.97</v>
+      </c>
+      <c r="E735" t="n">
+        <v>-1183.97</v>
+      </c>
+      <c r="F735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="G735" t="n">
+        <v>12329.35</v>
+      </c>
+      <c r="H735" t="n">
+        <v>-880.35</v>
+      </c>
+      <c r="I735" t="n">
+        <v>11195</v>
+      </c>
+      <c r="J735" t="n">
+        <v>11527.72</v>
+      </c>
+      <c r="K735" t="n">
+        <v>-332.72</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N735" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="D736" t="n">
+        <v>652.76</v>
+      </c>
+      <c r="E736" t="n">
+        <v>-80.26000000000001</v>
+      </c>
+      <c r="F736" t="n">
+        <v>576.7</v>
+      </c>
+      <c r="G736" t="n">
+        <v>626.63</v>
+      </c>
+      <c r="H736" t="n">
+        <v>-49.93</v>
+      </c>
+      <c r="I736" t="n">
+        <v>564.05</v>
+      </c>
+      <c r="J736" t="n">
+        <v>569.1</v>
+      </c>
+      <c r="K736" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N736" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D737" t="n">
+        <v>2463.75</v>
+      </c>
+      <c r="E737" t="n">
+        <v>-268.75</v>
+      </c>
+      <c r="F737" t="n">
+        <v>2204</v>
+      </c>
+      <c r="G737" t="n">
+        <v>2400.67</v>
+      </c>
+      <c r="H737" t="n">
+        <v>-196.67</v>
+      </c>
+      <c r="I737" t="n">
+        <v>2178</v>
+      </c>
+      <c r="J737" t="n">
+        <v>2183.28</v>
+      </c>
+      <c r="K737" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N737" t="n">
+        <v>10.91</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="D738" t="n">
+        <v>833.16</v>
+      </c>
+      <c r="E738" t="n">
+        <v>-89.45999999999999</v>
+      </c>
+      <c r="F738" t="n">
+        <v>744</v>
+      </c>
+      <c r="G738" t="n">
+        <v>802.47</v>
+      </c>
+      <c r="H738" t="n">
+        <v>-58.47</v>
+      </c>
+      <c r="I738" t="n">
+        <v>736.15</v>
+      </c>
+      <c r="J738" t="n">
+        <v>747.65</v>
+      </c>
+      <c r="K738" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N738" t="n">
+        <v>10.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -38306,31 +38306,31 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>413.25</v>
+        <v>412.65</v>
       </c>
       <c r="D729" t="n">
         <v>421.2</v>
       </c>
       <c r="E729" t="n">
-        <v>-7.95</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="F729" t="n">
-        <v>417.25</v>
+        <v>417.8</v>
       </c>
       <c r="G729" t="n">
         <v>435.67</v>
       </c>
       <c r="H729" t="n">
-        <v>-18.42</v>
+        <v>-17.87</v>
       </c>
       <c r="I729" t="n">
-        <v>411.35</v>
+        <v>412.55</v>
       </c>
       <c r="J729" t="n">
         <v>413.25</v>
       </c>
       <c r="K729" t="n">
-        <v>-1.9</v>
+        <v>-0.7</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         </is>
       </c>
       <c r="N729" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="730">
@@ -38358,31 +38358,31 @@
         </is>
       </c>
       <c r="C730" t="n">
-        <v>118.3</v>
+        <v>117</v>
       </c>
       <c r="D730" t="n">
         <v>129.19</v>
       </c>
       <c r="E730" t="n">
-        <v>-10.89</v>
+        <v>-12.19</v>
       </c>
       <c r="F730" t="n">
-        <v>118.9</v>
+        <v>118.74</v>
       </c>
       <c r="G730" t="n">
         <v>129.19</v>
       </c>
       <c r="H730" t="n">
-        <v>-10.29</v>
+        <v>-10.45</v>
       </c>
       <c r="I730" t="n">
-        <v>116.61</v>
+        <v>116.7</v>
       </c>
       <c r="J730" t="n">
         <v>118.3</v>
       </c>
       <c r="K730" t="n">
-        <v>-1.69</v>
+        <v>-1.6</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         </is>
       </c>
       <c r="N730" t="n">
-        <v>8.43</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="731">
@@ -38410,31 +38410,31 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>342.65</v>
+        <v>342</v>
       </c>
       <c r="D731" t="n">
         <v>372.81</v>
       </c>
       <c r="E731" t="n">
-        <v>-30.16</v>
+        <v>-30.81</v>
       </c>
       <c r="F731" t="n">
-        <v>344.4</v>
+        <v>342</v>
       </c>
       <c r="G731" t="n">
         <v>372.81</v>
       </c>
       <c r="H731" t="n">
-        <v>-28.41</v>
+        <v>-30.81</v>
       </c>
       <c r="I731" t="n">
-        <v>340.55</v>
+        <v>334.65</v>
       </c>
       <c r="J731" t="n">
         <v>342.65</v>
       </c>
       <c r="K731" t="n">
-        <v>-2.1</v>
+        <v>-8</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
@@ -38443,11 +38443,11 @@
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N731" t="n">
-        <v>8.09</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="732">
@@ -38462,31 +38462,31 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>3374</v>
+        <v>3262.6</v>
       </c>
       <c r="D732" t="n">
         <v>4234.94</v>
       </c>
       <c r="E732" t="n">
-        <v>-860.9400000000001</v>
+        <v>-972.34</v>
       </c>
       <c r="F732" t="n">
-        <v>3374</v>
+        <v>3289.8</v>
       </c>
       <c r="G732" t="n">
         <v>4234.94</v>
       </c>
       <c r="H732" t="n">
-        <v>-860.9400000000001</v>
+        <v>-945.14</v>
       </c>
       <c r="I732" t="n">
-        <v>3237.5</v>
+        <v>3212.8</v>
       </c>
       <c r="J732" t="n">
         <v>3374</v>
       </c>
       <c r="K732" t="n">
-        <v>-136.5</v>
+        <v>-161.2</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         </is>
       </c>
       <c r="N732" t="n">
-        <v>20.33</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="733">
@@ -38514,31 +38514,31 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>1886.3</v>
+        <v>1805</v>
       </c>
       <c r="D733" t="n">
         <v>2070.4</v>
       </c>
       <c r="E733" t="n">
-        <v>-184.1</v>
+        <v>-265.4</v>
       </c>
       <c r="F733" t="n">
-        <v>1904.9</v>
+        <v>1806.4</v>
       </c>
       <c r="G733" t="n">
         <v>2070.4</v>
       </c>
       <c r="H733" t="n">
-        <v>-165.5</v>
+        <v>-264</v>
       </c>
       <c r="I733" t="n">
-        <v>1793</v>
+        <v>1773.7</v>
       </c>
       <c r="J733" t="n">
         <v>1856.48</v>
       </c>
       <c r="K733" t="n">
-        <v>-63.48</v>
+        <v>-82.78</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>8.890000000000001</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="734">
@@ -38566,31 +38566,31 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>1042.5</v>
+        <v>1007</v>
       </c>
       <c r="D734" t="n">
         <v>1148.51</v>
       </c>
       <c r="E734" t="n">
-        <v>-106.01</v>
+        <v>-141.51</v>
       </c>
       <c r="F734" t="n">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="G734" t="n">
         <v>1148.51</v>
       </c>
       <c r="H734" t="n">
-        <v>-90.51000000000001</v>
+        <v>-123.51</v>
       </c>
       <c r="I734" t="n">
-        <v>1009.2</v>
+        <v>995.6</v>
       </c>
       <c r="J734" t="n">
         <v>1042.5</v>
       </c>
       <c r="K734" t="n">
-        <v>-33.3</v>
+        <v>-46.9</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         </is>
       </c>
       <c r="N734" t="n">
-        <v>9.23</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="735">
@@ -38618,31 +38618,31 @@
         </is>
       </c>
       <c r="C735" t="n">
-        <v>11449</v>
+        <v>11185</v>
       </c>
       <c r="D735" t="n">
         <v>12466.15</v>
       </c>
       <c r="E735" t="n">
-        <v>-1017.15</v>
+        <v>-1281.15</v>
       </c>
       <c r="F735" t="n">
-        <v>11449</v>
+        <v>11389</v>
       </c>
       <c r="G735" t="n">
         <v>12466.15</v>
       </c>
       <c r="H735" t="n">
-        <v>-1017.15</v>
+        <v>-1077.15</v>
       </c>
       <c r="I735" t="n">
-        <v>11195</v>
+        <v>11103</v>
       </c>
       <c r="J735" t="n">
         <v>11449</v>
       </c>
       <c r="K735" t="n">
-        <v>-254</v>
+        <v>-346</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         </is>
       </c>
       <c r="N735" t="n">
-        <v>8.16</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="736">
@@ -38670,31 +38670,31 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>572.5</v>
+        <v>565</v>
       </c>
       <c r="D736" t="n">
         <v>633.33</v>
       </c>
       <c r="E736" t="n">
-        <v>-60.83</v>
+        <v>-68.33</v>
       </c>
       <c r="F736" t="n">
-        <v>576.7</v>
+        <v>573.95</v>
       </c>
       <c r="G736" t="n">
         <v>633.33</v>
       </c>
       <c r="H736" t="n">
-        <v>-56.63</v>
+        <v>-59.38</v>
       </c>
       <c r="I736" t="n">
-        <v>564.05</v>
+        <v>563.2</v>
       </c>
       <c r="J736" t="n">
         <v>563.5599999999999</v>
       </c>
       <c r="K736" t="n">
-        <v>0.49</v>
+        <v>-0.36</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         </is>
       </c>
       <c r="N736" t="n">
-        <v>9.6</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="737">
@@ -38731,22 +38731,22 @@
         <v>-197.35</v>
       </c>
       <c r="F737" t="n">
-        <v>2204</v>
+        <v>2199.3</v>
       </c>
       <c r="G737" t="n">
         <v>2392.35</v>
       </c>
       <c r="H737" t="n">
-        <v>-188.35</v>
+        <v>-193.05</v>
       </c>
       <c r="I737" t="n">
-        <v>2178</v>
+        <v>2159.9</v>
       </c>
       <c r="J737" t="n">
         <v>2162.51</v>
       </c>
       <c r="K737" t="n">
-        <v>15.49</v>
+        <v>-2.61</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
@@ -38774,31 +38774,31 @@
         </is>
       </c>
       <c r="C738" t="n">
-        <v>743.7</v>
+        <v>736.25</v>
       </c>
       <c r="D738" t="n">
         <v>820.46</v>
       </c>
       <c r="E738" t="n">
-        <v>-76.76000000000001</v>
+        <v>-84.20999999999999</v>
       </c>
       <c r="F738" t="n">
-        <v>744</v>
+        <v>749.4</v>
       </c>
       <c r="G738" t="n">
         <v>820.46</v>
       </c>
       <c r="H738" t="n">
-        <v>-76.45999999999999</v>
+        <v>-71.06</v>
       </c>
       <c r="I738" t="n">
-        <v>736.15</v>
+        <v>735.75</v>
       </c>
       <c r="J738" t="n">
         <v>743.7</v>
       </c>
       <c r="K738" t="n">
-        <v>-7.55</v>
+        <v>-7.95</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         </is>
       </c>
       <c r="N738" t="n">
-        <v>9.359999999999999</v>
+        <v>10.26</v>
       </c>
     </row>
   </sheetData>
@@ -42448,31 +42448,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>23446.8</v>
+        <v>23414.3</v>
       </c>
       <c r="D70" t="n">
         <v>23446.8</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>-32.5</v>
       </c>
       <c r="F70" t="n">
-        <v>23466.9</v>
+        <v>23466.8</v>
       </c>
       <c r="G70" t="n">
         <v>23492.61</v>
       </c>
       <c r="H70" t="n">
-        <v>-25.71</v>
+        <v>-25.81</v>
       </c>
       <c r="I70" t="n">
-        <v>23349.55</v>
+        <v>23314.8</v>
       </c>
       <c r="J70" t="n">
         <v>23375.26</v>
       </c>
       <c r="K70" t="n">
-        <v>-25.71</v>
+        <v>-60.46</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="71">
@@ -42500,31 +42500,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>56548.9</v>
+        <v>56470.65</v>
       </c>
       <c r="D71" t="n">
         <v>56548.9</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>-78.25</v>
       </c>
       <c r="F71" t="n">
-        <v>56623.8</v>
+        <v>56668.2</v>
       </c>
       <c r="G71" t="n">
         <v>56711.91</v>
       </c>
       <c r="H71" t="n">
-        <v>-88.11</v>
+        <v>-43.71</v>
       </c>
       <c r="I71" t="n">
-        <v>56209.65</v>
+        <v>56269.55</v>
       </c>
       <c r="J71" t="n">
         <v>56297.76</v>
       </c>
       <c r="K71" t="n">
-        <v>-88.11</v>
+        <v>-28.21</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -80442,31 +80442,31 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>118.3</v>
+        <v>117</v>
       </c>
       <c r="D729" t="n">
         <v>130.6</v>
       </c>
       <c r="E729" t="n">
-        <v>-12.3</v>
+        <v>-13.6</v>
       </c>
       <c r="F729" t="n">
-        <v>118.9</v>
+        <v>118.74</v>
       </c>
       <c r="G729" t="n">
         <v>127.38</v>
       </c>
       <c r="H729" t="n">
-        <v>-8.48</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I729" t="n">
-        <v>116.61</v>
+        <v>116.7</v>
       </c>
       <c r="J729" t="n">
         <v>119.12</v>
       </c>
       <c r="K729" t="n">
-        <v>-2.51</v>
+        <v>-2.42</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
@@ -80479,7 +80479,7 @@
         </is>
       </c>
       <c r="N729" t="n">
-        <v>9.42</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="730">
@@ -80494,31 +80494,31 @@
         </is>
       </c>
       <c r="C730" t="n">
-        <v>342.65</v>
+        <v>342</v>
       </c>
       <c r="D730" t="n">
         <v>379.4</v>
       </c>
       <c r="E730" t="n">
-        <v>-36.75</v>
+        <v>-37.4</v>
       </c>
       <c r="F730" t="n">
-        <v>344.4</v>
+        <v>342</v>
       </c>
       <c r="G730" t="n">
         <v>370.49</v>
       </c>
       <c r="H730" t="n">
-        <v>-26.09</v>
+        <v>-28.49</v>
       </c>
       <c r="I730" t="n">
-        <v>340.55</v>
+        <v>334.65</v>
       </c>
       <c r="J730" t="n">
         <v>343.91</v>
       </c>
       <c r="K730" t="n">
-        <v>-3.36</v>
+        <v>-9.26</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
@@ -80531,7 +80531,7 @@
         </is>
       </c>
       <c r="N730" t="n">
-        <v>9.69</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="731">
@@ -80546,31 +80546,31 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>3374</v>
+        <v>3262.6</v>
       </c>
       <c r="D731" t="n">
         <v>4348.37</v>
       </c>
       <c r="E731" t="n">
-        <v>-974.37</v>
+        <v>-1085.77</v>
       </c>
       <c r="F731" t="n">
-        <v>3374</v>
+        <v>3289.8</v>
       </c>
       <c r="G731" t="n">
         <v>3690.82</v>
       </c>
       <c r="H731" t="n">
-        <v>-316.82</v>
+        <v>-401.02</v>
       </c>
       <c r="I731" t="n">
-        <v>3237.5</v>
+        <v>3212.8</v>
       </c>
       <c r="J731" t="n">
         <v>3355.49</v>
       </c>
       <c r="K731" t="n">
-        <v>-117.99</v>
+        <v>-142.69</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
@@ -80583,7 +80583,7 @@
         </is>
       </c>
       <c r="N731" t="n">
-        <v>22.41</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="732">
@@ -80598,31 +80598,31 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>1886.3</v>
+        <v>1805</v>
       </c>
       <c r="D732" t="n">
         <v>2134.3</v>
       </c>
       <c r="E732" t="n">
-        <v>-248</v>
+        <v>-329.3</v>
       </c>
       <c r="F732" t="n">
-        <v>1904.9</v>
+        <v>1806.4</v>
       </c>
       <c r="G732" t="n">
         <v>2065.01</v>
       </c>
       <c r="H732" t="n">
-        <v>-160.11</v>
+        <v>-258.61</v>
       </c>
       <c r="I732" t="n">
-        <v>1793</v>
+        <v>1773.7</v>
       </c>
       <c r="J732" t="n">
         <v>1874.8</v>
       </c>
       <c r="K732" t="n">
-        <v>-81.8</v>
+        <v>-101.1</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -80635,7 +80635,7 @@
         </is>
       </c>
       <c r="N732" t="n">
-        <v>11.62</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="733">
@@ -80650,31 +80650,31 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>1042.5</v>
+        <v>1007</v>
       </c>
       <c r="D733" t="n">
         <v>1169.99</v>
       </c>
       <c r="E733" t="n">
-        <v>-127.49</v>
+        <v>-162.99</v>
       </c>
       <c r="F733" t="n">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="G733" t="n">
         <v>1133.36</v>
       </c>
       <c r="H733" t="n">
-        <v>-75.36</v>
+        <v>-108.36</v>
       </c>
       <c r="I733" t="n">
-        <v>1009.2</v>
+        <v>995.6</v>
       </c>
       <c r="J733" t="n">
         <v>1041.9</v>
       </c>
       <c r="K733" t="n">
-        <v>-32.7</v>
+        <v>-46.3</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -80687,7 +80687,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>10.9</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="734">
@@ -80702,31 +80702,31 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>413.25</v>
+        <v>412.65</v>
       </c>
       <c r="D734" t="n">
         <v>425.57</v>
       </c>
       <c r="E734" t="n">
-        <v>-12.32</v>
+        <v>-12.92</v>
       </c>
       <c r="F734" t="n">
-        <v>417.25</v>
+        <v>417.8</v>
       </c>
       <c r="G734" t="n">
         <v>443.76</v>
       </c>
       <c r="H734" t="n">
-        <v>-26.51</v>
+        <v>-25.96</v>
       </c>
       <c r="I734" t="n">
-        <v>411.35</v>
+        <v>412.55</v>
       </c>
       <c r="J734" t="n">
         <v>417.01</v>
       </c>
       <c r="K734" t="n">
-        <v>-5.66</v>
+        <v>-4.46</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
@@ -80739,7 +80739,7 @@
         </is>
       </c>
       <c r="N734" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="735">
@@ -80754,31 +80754,31 @@
         </is>
       </c>
       <c r="C735" t="n">
-        <v>11449</v>
+        <v>11185</v>
       </c>
       <c r="D735" t="n">
         <v>12632.97</v>
       </c>
       <c r="E735" t="n">
-        <v>-1183.97</v>
+        <v>-1447.97</v>
       </c>
       <c r="F735" t="n">
-        <v>11449</v>
+        <v>11389</v>
       </c>
       <c r="G735" t="n">
         <v>12329.35</v>
       </c>
       <c r="H735" t="n">
-        <v>-880.35</v>
+        <v>-940.35</v>
       </c>
       <c r="I735" t="n">
-        <v>11195</v>
+        <v>11103</v>
       </c>
       <c r="J735" t="n">
         <v>11527.72</v>
       </c>
       <c r="K735" t="n">
-        <v>-332.72</v>
+        <v>-424.72</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -80791,7 +80791,7 @@
         </is>
       </c>
       <c r="N735" t="n">
-        <v>9.369999999999999</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="736">
@@ -80806,31 +80806,31 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>572.5</v>
+        <v>565</v>
       </c>
       <c r="D736" t="n">
         <v>652.76</v>
       </c>
       <c r="E736" t="n">
-        <v>-80.26000000000001</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="F736" t="n">
-        <v>576.7</v>
+        <v>573.95</v>
       </c>
       <c r="G736" t="n">
         <v>626.63</v>
       </c>
       <c r="H736" t="n">
-        <v>-49.93</v>
+        <v>-52.68</v>
       </c>
       <c r="I736" t="n">
-        <v>564.05</v>
+        <v>563.2</v>
       </c>
       <c r="J736" t="n">
         <v>569.1</v>
       </c>
       <c r="K736" t="n">
-        <v>-5.05</v>
+        <v>-5.9</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -80843,7 +80843,7 @@
         </is>
       </c>
       <c r="N736" t="n">
-        <v>12.3</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="737">
@@ -80867,22 +80867,22 @@
         <v>-268.75</v>
       </c>
       <c r="F737" t="n">
-        <v>2204</v>
+        <v>2199.3</v>
       </c>
       <c r="G737" t="n">
         <v>2400.67</v>
       </c>
       <c r="H737" t="n">
-        <v>-196.67</v>
+        <v>-201.37</v>
       </c>
       <c r="I737" t="n">
-        <v>2178</v>
+        <v>2159.9</v>
       </c>
       <c r="J737" t="n">
         <v>2183.28</v>
       </c>
       <c r="K737" t="n">
-        <v>-5.28</v>
+        <v>-23.38</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
@@ -80910,31 +80910,31 @@
         </is>
       </c>
       <c r="C738" t="n">
-        <v>743.7</v>
+        <v>736.25</v>
       </c>
       <c r="D738" t="n">
         <v>833.16</v>
       </c>
       <c r="E738" t="n">
-        <v>-89.45999999999999</v>
+        <v>-96.91</v>
       </c>
       <c r="F738" t="n">
-        <v>744</v>
+        <v>749.4</v>
       </c>
       <c r="G738" t="n">
         <v>802.47</v>
       </c>
       <c r="H738" t="n">
-        <v>-58.47</v>
+        <v>-53.07</v>
       </c>
       <c r="I738" t="n">
-        <v>736.15</v>
+        <v>735.75</v>
       </c>
       <c r="J738" t="n">
         <v>747.65</v>
       </c>
       <c r="K738" t="n">
-        <v>-11.5</v>
+        <v>-11.9</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         </is>
       </c>
       <c r="N738" t="n">
-        <v>10.74</v>
+        <v>11.63</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N738"/>
+  <dimension ref="A1:N743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38812,6 +38812,266 @@
       </c>
       <c r="N738" t="n">
         <v>10.26</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D739" t="n">
+        <v>310.23</v>
+      </c>
+      <c r="E739" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="F739" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="G739" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="H739" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="I739" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="J739" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="K739" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N739" t="n">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="D740" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="E740" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F740" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="G740" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="H740" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="I740" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="J740" t="n">
+        <v>114.33</v>
+      </c>
+      <c r="K740" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N740" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>2184.8</v>
+      </c>
+      <c r="D741" t="n">
+        <v>2020.61</v>
+      </c>
+      <c r="E741" t="n">
+        <v>164.19</v>
+      </c>
+      <c r="F741" t="n">
+        <v>2204.9</v>
+      </c>
+      <c r="G741" t="n">
+        <v>2020.61</v>
+      </c>
+      <c r="H741" t="n">
+        <v>184.29</v>
+      </c>
+      <c r="I741" t="n">
+        <v>2158.2</v>
+      </c>
+      <c r="J741" t="n">
+        <v>2074.47</v>
+      </c>
+      <c r="K741" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N741" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D742" t="n">
+        <v>903.25</v>
+      </c>
+      <c r="E742" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="F742" t="n">
+        <v>1044.9</v>
+      </c>
+      <c r="G742" t="n">
+        <v>964.13</v>
+      </c>
+      <c r="H742" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="I742" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J742" t="n">
+        <v>994.59</v>
+      </c>
+      <c r="K742" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N742" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>564.25</v>
+      </c>
+      <c r="D743" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="E743" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="F743" t="n">
+        <v>571.9</v>
+      </c>
+      <c r="G743" t="n">
+        <v>507.47</v>
+      </c>
+      <c r="H743" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I743" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="J743" t="n">
+        <v>534.17</v>
+      </c>
+      <c r="K743" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N743" t="n">
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -38825,7 +39085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42538,6 +42798,110 @@
       </c>
       <c r="N71" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>23063.1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>23063.1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>23281.95</v>
+      </c>
+      <c r="G72" t="n">
+        <v>23214.65</v>
+      </c>
+      <c r="H72" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>23046.15</v>
+      </c>
+      <c r="J72" t="n">
+        <v>22978.85</v>
+      </c>
+      <c r="K72" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>55438.5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>55438.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>55918.4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>55790.86</v>
+      </c>
+      <c r="H73" t="n">
+        <v>127.54</v>
+      </c>
+      <c r="I73" t="n">
+        <v>55341.2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>55213.66</v>
+      </c>
+      <c r="K73" t="n">
+        <v>127.54</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -42551,7 +42915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N738"/>
+  <dimension ref="A1:N743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80950,6 +81314,266 @@
         <v>11.63</v>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D739" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="E739" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="F739" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="G739" t="n">
+        <v>316.28</v>
+      </c>
+      <c r="H739" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="I739" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="J739" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="K739" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N739" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="D740" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="E740" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="F740" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="G740" t="n">
+        <v>110.04</v>
+      </c>
+      <c r="H740" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="I740" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="J740" t="n">
+        <v>113.32</v>
+      </c>
+      <c r="K740" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N740" t="n">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>2184.8</v>
+      </c>
+      <c r="D741" t="n">
+        <v>2075.61</v>
+      </c>
+      <c r="E741" t="n">
+        <v>109.19</v>
+      </c>
+      <c r="F741" t="n">
+        <v>2204.9</v>
+      </c>
+      <c r="G741" t="n">
+        <v>2078.76</v>
+      </c>
+      <c r="H741" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="I741" t="n">
+        <v>2158.2</v>
+      </c>
+      <c r="J741" t="n">
+        <v>2092.98</v>
+      </c>
+      <c r="K741" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N741" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D742" t="n">
+        <v>926.9</v>
+      </c>
+      <c r="E742" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F742" t="n">
+        <v>1044.9</v>
+      </c>
+      <c r="G742" t="n">
+        <v>971.46</v>
+      </c>
+      <c r="H742" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="I742" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J742" t="n">
+        <v>979.79</v>
+      </c>
+      <c r="K742" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N742" t="n">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>564.25</v>
+      </c>
+      <c r="D743" t="n">
+        <v>522.72</v>
+      </c>
+      <c r="E743" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="F743" t="n">
+        <v>571.9</v>
+      </c>
+      <c r="G743" t="n">
+        <v>538.37</v>
+      </c>
+      <c r="H743" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="I743" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="J743" t="n">
+        <v>539.35</v>
+      </c>
+      <c r="K743" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N743" t="n">
+        <v>7.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -38826,31 +38826,31 @@
         </is>
       </c>
       <c r="C739" t="n">
-        <v>335.5</v>
+        <v>342.65</v>
       </c>
       <c r="D739" t="n">
         <v>310.23</v>
       </c>
       <c r="E739" t="n">
-        <v>25.27</v>
+        <v>32.42</v>
       </c>
       <c r="F739" t="n">
-        <v>343.6</v>
+        <v>344.4</v>
       </c>
       <c r="G739" t="n">
         <v>316.21</v>
       </c>
       <c r="H739" t="n">
-        <v>27.39</v>
+        <v>28.19</v>
       </c>
       <c r="I739" t="n">
-        <v>333.55</v>
+        <v>340.55</v>
       </c>
       <c r="J739" t="n">
         <v>326.2</v>
       </c>
       <c r="K739" t="n">
-        <v>7.35</v>
+        <v>14.35</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         </is>
       </c>
       <c r="N739" t="n">
-        <v>8.15</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="740">
@@ -38878,31 +38878,31 @@
         </is>
       </c>
       <c r="C740" t="n">
-        <v>117.12</v>
+        <v>118.3</v>
       </c>
       <c r="D740" t="n">
         <v>106.94</v>
       </c>
       <c r="E740" t="n">
-        <v>10.18</v>
+        <v>11.36</v>
       </c>
       <c r="F740" t="n">
-        <v>118.67</v>
+        <v>118.9</v>
       </c>
       <c r="G740" t="n">
         <v>110.58</v>
       </c>
       <c r="H740" t="n">
-        <v>8.09</v>
+        <v>8.32</v>
       </c>
       <c r="I740" t="n">
-        <v>117.06</v>
+        <v>116.61</v>
       </c>
       <c r="J740" t="n">
         <v>114.33</v>
       </c>
       <c r="K740" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         </is>
       </c>
       <c r="N740" t="n">
-        <v>9.52</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="741">
@@ -38930,31 +38930,31 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>2184.8</v>
+        <v>2195</v>
       </c>
       <c r="D741" t="n">
         <v>2020.61</v>
       </c>
       <c r="E741" t="n">
-        <v>164.19</v>
+        <v>174.39</v>
       </c>
       <c r="F741" t="n">
-        <v>2204.9</v>
+        <v>2204</v>
       </c>
       <c r="G741" t="n">
         <v>2020.61</v>
       </c>
       <c r="H741" t="n">
-        <v>184.29</v>
+        <v>183.39</v>
       </c>
       <c r="I741" t="n">
-        <v>2158.2</v>
+        <v>2178</v>
       </c>
       <c r="J741" t="n">
         <v>2074.47</v>
       </c>
       <c r="K741" t="n">
-        <v>83.73</v>
+        <v>103.53</v>
       </c>
       <c r="L741" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         </is>
       </c>
       <c r="N741" t="n">
-        <v>8.130000000000001</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="742">
@@ -38982,31 +38982,31 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>1022</v>
+        <v>1042.5</v>
       </c>
       <c r="D742" t="n">
         <v>903.25</v>
       </c>
       <c r="E742" t="n">
-        <v>118.75</v>
+        <v>139.25</v>
       </c>
       <c r="F742" t="n">
-        <v>1044.9</v>
+        <v>1058</v>
       </c>
       <c r="G742" t="n">
         <v>964.13</v>
       </c>
       <c r="H742" t="n">
-        <v>80.77</v>
+        <v>93.87</v>
       </c>
       <c r="I742" t="n">
-        <v>1014</v>
+        <v>1009.2</v>
       </c>
       <c r="J742" t="n">
         <v>994.59</v>
       </c>
       <c r="K742" t="n">
-        <v>19.41</v>
+        <v>14.61</v>
       </c>
       <c r="L742" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         </is>
       </c>
       <c r="N742" t="n">
-        <v>13.15</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="743">
@@ -39034,31 +39034,31 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>564.25</v>
+        <v>572.5</v>
       </c>
       <c r="D743" t="n">
         <v>507.4</v>
       </c>
       <c r="E743" t="n">
-        <v>56.85</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>571.9</v>
+        <v>576.7</v>
       </c>
       <c r="G743" t="n">
         <v>507.47</v>
       </c>
       <c r="H743" t="n">
-        <v>64.43000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="I743" t="n">
-        <v>563.8</v>
+        <v>564.05</v>
       </c>
       <c r="J743" t="n">
         <v>534.17</v>
       </c>
       <c r="K743" t="n">
-        <v>29.63</v>
+        <v>29.88</v>
       </c>
       <c r="L743" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="N743" t="n">
-        <v>11.2</v>
+        <v>12.83</v>
       </c>
     </row>
   </sheetData>
@@ -42812,31 +42812,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>23063.1</v>
+        <v>23446.8</v>
       </c>
       <c r="D72" t="n">
         <v>23063.1</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>383.7</v>
       </c>
       <c r="F72" t="n">
-        <v>23281.95</v>
+        <v>23466.9</v>
       </c>
       <c r="G72" t="n">
         <v>23214.65</v>
       </c>
       <c r="H72" t="n">
-        <v>67.3</v>
+        <v>252.25</v>
       </c>
       <c r="I72" t="n">
-        <v>23046.15</v>
+        <v>23349.55</v>
       </c>
       <c r="J72" t="n">
         <v>22978.85</v>
       </c>
       <c r="K72" t="n">
-        <v>67.3</v>
+        <v>370.7</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="73">
@@ -42864,31 +42864,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>55438.5</v>
+        <v>56548.9</v>
       </c>
       <c r="D73" t="n">
         <v>55438.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1110.4</v>
       </c>
       <c r="F73" t="n">
-        <v>55918.4</v>
+        <v>56623.8</v>
       </c>
       <c r="G73" t="n">
         <v>55790.86</v>
       </c>
       <c r="H73" t="n">
-        <v>127.54</v>
+        <v>832.9400000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>55341.2</v>
+        <v>56209.65</v>
       </c>
       <c r="J73" t="n">
         <v>55213.66</v>
       </c>
       <c r="K73" t="n">
-        <v>127.54</v>
+        <v>995.99</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -81326,31 +81326,31 @@
         </is>
       </c>
       <c r="C739" t="n">
-        <v>335.5</v>
+        <v>342.65</v>
       </c>
       <c r="D739" t="n">
         <v>315.63</v>
       </c>
       <c r="E739" t="n">
-        <v>19.87</v>
+        <v>27.02</v>
       </c>
       <c r="F739" t="n">
-        <v>343.6</v>
+        <v>344.4</v>
       </c>
       <c r="G739" t="n">
         <v>316.28</v>
       </c>
       <c r="H739" t="n">
-        <v>27.32</v>
+        <v>28.12</v>
       </c>
       <c r="I739" t="n">
-        <v>333.55</v>
+        <v>340.55</v>
       </c>
       <c r="J739" t="n">
         <v>323.75</v>
       </c>
       <c r="K739" t="n">
-        <v>9.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -81363,7 +81363,7 @@
         </is>
       </c>
       <c r="N739" t="n">
-        <v>6.3</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="740">
@@ -81378,31 +81378,31 @@
         </is>
       </c>
       <c r="C740" t="n">
-        <v>117.12</v>
+        <v>118.3</v>
       </c>
       <c r="D740" t="n">
         <v>108.4</v>
       </c>
       <c r="E740" t="n">
-        <v>8.720000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F740" t="n">
-        <v>118.67</v>
+        <v>118.9</v>
       </c>
       <c r="G740" t="n">
         <v>110.04</v>
       </c>
       <c r="H740" t="n">
-        <v>8.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I740" t="n">
-        <v>117.06</v>
+        <v>116.61</v>
       </c>
       <c r="J740" t="n">
         <v>113.32</v>
       </c>
       <c r="K740" t="n">
-        <v>3.74</v>
+        <v>3.29</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>
@@ -81415,7 +81415,7 @@
         </is>
       </c>
       <c r="N740" t="n">
-        <v>8.039999999999999</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="741">
@@ -81430,31 +81430,31 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>2184.8</v>
+        <v>2195</v>
       </c>
       <c r="D741" t="n">
         <v>2075.61</v>
       </c>
       <c r="E741" t="n">
-        <v>109.19</v>
+        <v>119.39</v>
       </c>
       <c r="F741" t="n">
-        <v>2204.9</v>
+        <v>2204</v>
       </c>
       <c r="G741" t="n">
         <v>2078.76</v>
       </c>
       <c r="H741" t="n">
-        <v>126.14</v>
+        <v>125.24</v>
       </c>
       <c r="I741" t="n">
-        <v>2158.2</v>
+        <v>2178</v>
       </c>
       <c r="J741" t="n">
         <v>2092.98</v>
       </c>
       <c r="K741" t="n">
-        <v>65.22</v>
+        <v>85.02</v>
       </c>
       <c r="L741" t="inlineStr">
         <is>
@@ -81467,7 +81467,7 @@
         </is>
       </c>
       <c r="N741" t="n">
-        <v>5.26</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="742">
@@ -81482,31 +81482,31 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>1022</v>
+        <v>1042.5</v>
       </c>
       <c r="D742" t="n">
         <v>926.9</v>
       </c>
       <c r="E742" t="n">
-        <v>95.09999999999999</v>
+        <v>115.6</v>
       </c>
       <c r="F742" t="n">
-        <v>1044.9</v>
+        <v>1058</v>
       </c>
       <c r="G742" t="n">
         <v>971.46</v>
       </c>
       <c r="H742" t="n">
-        <v>73.44</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="I742" t="n">
-        <v>1014</v>
+        <v>1009.2</v>
       </c>
       <c r="J742" t="n">
         <v>979.79</v>
       </c>
       <c r="K742" t="n">
-        <v>34.21</v>
+        <v>29.41</v>
       </c>
       <c r="L742" t="inlineStr">
         <is>
@@ -81519,7 +81519,7 @@
         </is>
       </c>
       <c r="N742" t="n">
-        <v>10.26</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="743">
@@ -81534,31 +81534,31 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>564.25</v>
+        <v>572.5</v>
       </c>
       <c r="D743" t="n">
         <v>522.72</v>
       </c>
       <c r="E743" t="n">
-        <v>41.53</v>
+        <v>49.78</v>
       </c>
       <c r="F743" t="n">
-        <v>571.9</v>
+        <v>576.7</v>
       </c>
       <c r="G743" t="n">
         <v>538.37</v>
       </c>
       <c r="H743" t="n">
-        <v>33.53</v>
+        <v>38.33</v>
       </c>
       <c r="I743" t="n">
-        <v>563.8</v>
+        <v>564.05</v>
       </c>
       <c r="J743" t="n">
         <v>539.35</v>
       </c>
       <c r="K743" t="n">
-        <v>24.45</v>
+        <v>24.7</v>
       </c>
       <c r="L743" t="inlineStr">
         <is>
@@ -81571,7 +81571,7 @@
         </is>
       </c>
       <c r="N743" t="n">
-        <v>7.94</v>
+        <v>9.52</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N743"/>
+  <dimension ref="A1:N748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39072,6 +39072,266 @@
       </c>
       <c r="N743" t="n">
         <v>12.83</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D744" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="E744" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="F744" t="n">
+        <v>118.01</v>
+      </c>
+      <c r="G744" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="H744" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="I744" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="J744" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="K744" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N744" t="n">
+        <v>10.51</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="D745" t="n">
+        <v>2425.1</v>
+      </c>
+      <c r="E745" t="n">
+        <v>-210.4</v>
+      </c>
+      <c r="F745" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G745" t="n">
+        <v>2425.1</v>
+      </c>
+      <c r="H745" t="n">
+        <v>-206.1</v>
+      </c>
+      <c r="I745" t="n">
+        <v>2176.5</v>
+      </c>
+      <c r="J745" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="K745" t="n">
+        <v>-38.2</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N745" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D746" t="n">
+        <v>1197.14</v>
+      </c>
+      <c r="E746" t="n">
+        <v>-168.14</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1197.14</v>
+      </c>
+      <c r="H746" t="n">
+        <v>-150.14</v>
+      </c>
+      <c r="I746" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="J746" t="n">
+        <v>1029</v>
+      </c>
+      <c r="K746" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N746" t="n">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>335</v>
+      </c>
+      <c r="D747" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="E747" t="n">
+        <v>-37.97</v>
+      </c>
+      <c r="F747" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="G747" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="H747" t="n">
+        <v>-33.07</v>
+      </c>
+      <c r="I747" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="J747" t="n">
+        <v>335</v>
+      </c>
+      <c r="K747" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N747" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>566</v>
+      </c>
+      <c r="D748" t="n">
+        <v>643.73</v>
+      </c>
+      <c r="E748" t="n">
+        <v>-77.73</v>
+      </c>
+      <c r="F748" t="n">
+        <v>569.55</v>
+      </c>
+      <c r="G748" t="n">
+        <v>643.73</v>
+      </c>
+      <c r="H748" t="n">
+        <v>-74.18000000000001</v>
+      </c>
+      <c r="I748" t="n">
+        <v>558.6</v>
+      </c>
+      <c r="J748" t="n">
+        <v>566</v>
+      </c>
+      <c r="K748" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N748" t="n">
+        <v>12.07</v>
       </c>
     </row>
   </sheetData>
@@ -39085,7 +39345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42902,6 +43162,110 @@
       </c>
       <c r="N73" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>23140.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>23140.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>23162.7</v>
+      </c>
+      <c r="G74" t="n">
+        <v>23195.15</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-32.45</v>
+      </c>
+      <c r="I74" t="n">
+        <v>23020.95</v>
+      </c>
+      <c r="J74" t="n">
+        <v>23053.4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-32.45</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>55580.4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>55580.4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>55762.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>55770.75</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="I75" t="n">
+        <v>55373.75</v>
+      </c>
+      <c r="J75" t="n">
+        <v>55381.9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -42915,7 +43279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N743"/>
+  <dimension ref="A1:N748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81574,6 +81938,266 @@
         <v>9.52</v>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D744" t="n">
+        <v>132.46</v>
+      </c>
+      <c r="E744" t="n">
+        <v>-15.86</v>
+      </c>
+      <c r="F744" t="n">
+        <v>118.01</v>
+      </c>
+      <c r="G744" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="H744" t="n">
+        <v>-10.62</v>
+      </c>
+      <c r="I744" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="J744" t="n">
+        <v>119.59</v>
+      </c>
+      <c r="K744" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N744" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="D745" t="n">
+        <v>2493.86</v>
+      </c>
+      <c r="E745" t="n">
+        <v>-279.16</v>
+      </c>
+      <c r="F745" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G745" t="n">
+        <v>2465.31</v>
+      </c>
+      <c r="H745" t="n">
+        <v>-246.31</v>
+      </c>
+      <c r="I745" t="n">
+        <v>2176.5</v>
+      </c>
+      <c r="J745" t="n">
+        <v>2255.6</v>
+      </c>
+      <c r="K745" t="n">
+        <v>-79.09999999999999</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N745" t="n">
+        <v>11.19</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D746" t="n">
+        <v>1234.44</v>
+      </c>
+      <c r="E746" t="n">
+        <v>-205.44</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1148.44</v>
+      </c>
+      <c r="H746" t="n">
+        <v>-101.44</v>
+      </c>
+      <c r="I746" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="J746" t="n">
+        <v>1045.84</v>
+      </c>
+      <c r="K746" t="n">
+        <v>-26.44</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N746" t="n">
+        <v>16.64</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>335</v>
+      </c>
+      <c r="D747" t="n">
+        <v>381.62</v>
+      </c>
+      <c r="E747" t="n">
+        <v>-46.62</v>
+      </c>
+      <c r="F747" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="G747" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="H747" t="n">
+        <v>-31.21</v>
+      </c>
+      <c r="I747" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="J747" t="n">
+        <v>342.49</v>
+      </c>
+      <c r="K747" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N747" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>566</v>
+      </c>
+      <c r="D748" t="n">
+        <v>664.58</v>
+      </c>
+      <c r="E748" t="n">
+        <v>-98.58</v>
+      </c>
+      <c r="F748" t="n">
+        <v>569.55</v>
+      </c>
+      <c r="G748" t="n">
+        <v>632.4299999999999</v>
+      </c>
+      <c r="H748" t="n">
+        <v>-62.88</v>
+      </c>
+      <c r="I748" t="n">
+        <v>558.6</v>
+      </c>
+      <c r="J748" t="n">
+        <v>574.74</v>
+      </c>
+      <c r="K748" t="n">
+        <v>-16.14</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N748" t="n">
+        <v>14.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39086,31 +39086,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>116.6</v>
+        <v>117.12</v>
       </c>
       <c r="D744" t="n">
         <v>130.3</v>
       </c>
       <c r="E744" t="n">
-        <v>-13.7</v>
+        <v>-13.18</v>
       </c>
       <c r="F744" t="n">
-        <v>118.01</v>
+        <v>118.67</v>
       </c>
       <c r="G744" t="n">
         <v>130.3</v>
       </c>
       <c r="H744" t="n">
-        <v>-12.29</v>
+        <v>-11.63</v>
       </c>
       <c r="I744" t="n">
-        <v>116.23</v>
+        <v>117.06</v>
       </c>
       <c r="J744" t="n">
         <v>116.6</v>
       </c>
       <c r="K744" t="n">
-        <v>-0.37</v>
+        <v>0.46</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         </is>
       </c>
       <c r="N744" t="n">
-        <v>10.51</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="745">
@@ -39138,31 +39138,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2214.7</v>
+        <v>2184.8</v>
       </c>
       <c r="D745" t="n">
         <v>2425.1</v>
       </c>
       <c r="E745" t="n">
-        <v>-210.4</v>
+        <v>-240.3</v>
       </c>
       <c r="F745" t="n">
-        <v>2219</v>
+        <v>2204.9</v>
       </c>
       <c r="G745" t="n">
         <v>2425.1</v>
       </c>
       <c r="H745" t="n">
-        <v>-206.1</v>
+        <v>-220.2</v>
       </c>
       <c r="I745" t="n">
-        <v>2176.5</v>
+        <v>2158.2</v>
       </c>
       <c r="J745" t="n">
         <v>2214.7</v>
       </c>
       <c r="K745" t="n">
-        <v>-38.2</v>
+        <v>-56.5</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>8.68</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="746">
@@ -39190,31 +39190,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="D746" t="n">
         <v>1197.14</v>
       </c>
       <c r="E746" t="n">
-        <v>-168.14</v>
+        <v>-175.14</v>
       </c>
       <c r="F746" t="n">
-        <v>1047</v>
+        <v>1044.9</v>
       </c>
       <c r="G746" t="n">
         <v>1197.14</v>
       </c>
       <c r="H746" t="n">
-        <v>-150.14</v>
+        <v>-152.24</v>
       </c>
       <c r="I746" t="n">
-        <v>1019.4</v>
+        <v>1014</v>
       </c>
       <c r="J746" t="n">
         <v>1029</v>
       </c>
       <c r="K746" t="n">
-        <v>-9.6</v>
+        <v>-15</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         </is>
       </c>
       <c r="N746" t="n">
-        <v>14.05</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="747">
@@ -39242,31 +39242,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335</v>
+        <v>335.5</v>
       </c>
       <c r="D747" t="n">
         <v>372.97</v>
       </c>
       <c r="E747" t="n">
-        <v>-37.97</v>
+        <v>-37.47</v>
       </c>
       <c r="F747" t="n">
-        <v>339.9</v>
+        <v>343.6</v>
       </c>
       <c r="G747" t="n">
         <v>372.97</v>
       </c>
       <c r="H747" t="n">
-        <v>-33.07</v>
+        <v>-29.37</v>
       </c>
       <c r="I747" t="n">
-        <v>331.7</v>
+        <v>333.55</v>
       </c>
       <c r="J747" t="n">
         <v>335</v>
       </c>
       <c r="K747" t="n">
-        <v>-3.3</v>
+        <v>-1.45</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         </is>
       </c>
       <c r="N747" t="n">
-        <v>10.18</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="748">
@@ -39294,31 +39294,31 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>566</v>
+        <v>564.25</v>
       </c>
       <c r="D748" t="n">
         <v>643.73</v>
       </c>
       <c r="E748" t="n">
-        <v>-77.73</v>
+        <v>-79.48</v>
       </c>
       <c r="F748" t="n">
-        <v>569.55</v>
+        <v>571.9</v>
       </c>
       <c r="G748" t="n">
         <v>643.73</v>
       </c>
       <c r="H748" t="n">
-        <v>-74.18000000000001</v>
+        <v>-71.83</v>
       </c>
       <c r="I748" t="n">
-        <v>558.6</v>
+        <v>563.8</v>
       </c>
       <c r="J748" t="n">
         <v>566</v>
       </c>
       <c r="K748" t="n">
-        <v>-7.4</v>
+        <v>-2.2</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         </is>
       </c>
       <c r="N748" t="n">
-        <v>12.07</v>
+        <v>12.35</v>
       </c>
     </row>
   </sheetData>
@@ -43176,31 +43176,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>23140.5</v>
+        <v>23063.1</v>
       </c>
       <c r="D74" t="n">
         <v>23140.5</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>-77.40000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>23162.7</v>
+        <v>23281.95</v>
       </c>
       <c r="G74" t="n">
         <v>23195.15</v>
       </c>
       <c r="H74" t="n">
-        <v>-32.45</v>
+        <v>86.8</v>
       </c>
       <c r="I74" t="n">
-        <v>23020.95</v>
+        <v>23046.15</v>
       </c>
       <c r="J74" t="n">
         <v>23053.4</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.45</v>
+        <v>-7.25</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="75">
@@ -43228,31 +43228,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>55580.4</v>
+        <v>55438.5</v>
       </c>
       <c r="D75" t="n">
         <v>55580.4</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>-141.9</v>
       </c>
       <c r="F75" t="n">
-        <v>55762.6</v>
+        <v>55918.4</v>
       </c>
       <c r="G75" t="n">
         <v>55770.75</v>
       </c>
       <c r="H75" t="n">
-        <v>-8.15</v>
+        <v>147.65</v>
       </c>
       <c r="I75" t="n">
-        <v>55373.75</v>
+        <v>55341.2</v>
       </c>
       <c r="J75" t="n">
         <v>55381.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.15</v>
+        <v>-40.7</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -81950,31 +81950,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>116.6</v>
+        <v>117.12</v>
       </c>
       <c r="D744" t="n">
         <v>132.46</v>
       </c>
       <c r="E744" t="n">
-        <v>-15.86</v>
+        <v>-15.34</v>
       </c>
       <c r="F744" t="n">
-        <v>118.01</v>
+        <v>118.67</v>
       </c>
       <c r="G744" t="n">
         <v>128.63</v>
       </c>
       <c r="H744" t="n">
-        <v>-10.62</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="I744" t="n">
-        <v>116.23</v>
+        <v>117.06</v>
       </c>
       <c r="J744" t="n">
         <v>119.59</v>
       </c>
       <c r="K744" t="n">
-        <v>-3.36</v>
+        <v>-2.53</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -81987,7 +81987,7 @@
         </is>
       </c>
       <c r="N744" t="n">
-        <v>11.97</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="745">
@@ -82002,31 +82002,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2214.7</v>
+        <v>2184.8</v>
       </c>
       <c r="D745" t="n">
         <v>2493.86</v>
       </c>
       <c r="E745" t="n">
-        <v>-279.16</v>
+        <v>-309.06</v>
       </c>
       <c r="F745" t="n">
-        <v>2219</v>
+        <v>2204.9</v>
       </c>
       <c r="G745" t="n">
         <v>2465.31</v>
       </c>
       <c r="H745" t="n">
-        <v>-246.31</v>
+        <v>-260.41</v>
       </c>
       <c r="I745" t="n">
-        <v>2176.5</v>
+        <v>2158.2</v>
       </c>
       <c r="J745" t="n">
         <v>2255.6</v>
       </c>
       <c r="K745" t="n">
-        <v>-79.09999999999999</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -82039,7 +82039,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>11.19</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="746">
@@ -82054,31 +82054,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="D746" t="n">
         <v>1234.44</v>
       </c>
       <c r="E746" t="n">
-        <v>-205.44</v>
+        <v>-212.44</v>
       </c>
       <c r="F746" t="n">
-        <v>1047</v>
+        <v>1044.9</v>
       </c>
       <c r="G746" t="n">
         <v>1148.44</v>
       </c>
       <c r="H746" t="n">
-        <v>-101.44</v>
+        <v>-103.54</v>
       </c>
       <c r="I746" t="n">
-        <v>1019.4</v>
+        <v>1014</v>
       </c>
       <c r="J746" t="n">
         <v>1045.84</v>
       </c>
       <c r="K746" t="n">
-        <v>-26.44</v>
+        <v>-31.84</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -82091,7 +82091,7 @@
         </is>
       </c>
       <c r="N746" t="n">
-        <v>16.64</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="747">
@@ -82106,31 +82106,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335</v>
+        <v>335.5</v>
       </c>
       <c r="D747" t="n">
         <v>381.62</v>
       </c>
       <c r="E747" t="n">
-        <v>-46.62</v>
+        <v>-46.12</v>
       </c>
       <c r="F747" t="n">
-        <v>339.9</v>
+        <v>343.6</v>
       </c>
       <c r="G747" t="n">
         <v>371.11</v>
       </c>
       <c r="H747" t="n">
-        <v>-31.21</v>
+        <v>-27.51</v>
       </c>
       <c r="I747" t="n">
-        <v>331.7</v>
+        <v>333.55</v>
       </c>
       <c r="J747" t="n">
         <v>342.49</v>
       </c>
       <c r="K747" t="n">
-        <v>-10.79</v>
+        <v>-8.94</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -82143,7 +82143,7 @@
         </is>
       </c>
       <c r="N747" t="n">
-        <v>12.22</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="748">
@@ -82158,31 +82158,31 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>566</v>
+        <v>564.25</v>
       </c>
       <c r="D748" t="n">
         <v>664.58</v>
       </c>
       <c r="E748" t="n">
-        <v>-98.58</v>
+        <v>-100.33</v>
       </c>
       <c r="F748" t="n">
-        <v>569.55</v>
+        <v>571.9</v>
       </c>
       <c r="G748" t="n">
         <v>632.4299999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>-62.88</v>
+        <v>-60.53</v>
       </c>
       <c r="I748" t="n">
-        <v>558.6</v>
+        <v>563.8</v>
       </c>
       <c r="J748" t="n">
         <v>574.74</v>
       </c>
       <c r="K748" t="n">
-        <v>-16.14</v>
+        <v>-10.94</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
@@ -82195,7 +82195,7 @@
         </is>
       </c>
       <c r="N748" t="n">
-        <v>14.83</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39086,31 +39086,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="D744" t="n">
-        <v>130.3</v>
+        <v>105.88</v>
       </c>
       <c r="E744" t="n">
-        <v>-13.18</v>
+        <v>10.72</v>
       </c>
       <c r="F744" t="n">
-        <v>118.67</v>
+        <v>118.01</v>
       </c>
       <c r="G744" t="n">
-        <v>130.3</v>
+        <v>110.44</v>
       </c>
       <c r="H744" t="n">
-        <v>-11.63</v>
+        <v>7.57</v>
       </c>
       <c r="I744" t="n">
-        <v>117.06</v>
+        <v>116.23</v>
       </c>
       <c r="J744" t="n">
-        <v>116.6</v>
+        <v>113.51</v>
       </c>
       <c r="K744" t="n">
-        <v>0.46</v>
+        <v>2.72</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N744" t="n">
@@ -39138,31 +39138,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2184.8</v>
+        <v>2214.7</v>
       </c>
       <c r="D745" t="n">
-        <v>2425.1</v>
+        <v>2011.21</v>
       </c>
       <c r="E745" t="n">
-        <v>-240.3</v>
+        <v>203.49</v>
       </c>
       <c r="F745" t="n">
-        <v>2204.9</v>
+        <v>2219</v>
       </c>
       <c r="G745" t="n">
-        <v>2425.1</v>
+        <v>2062.42</v>
       </c>
       <c r="H745" t="n">
-        <v>-220.2</v>
+        <v>156.58</v>
       </c>
       <c r="I745" t="n">
-        <v>2158.2</v>
+        <v>2176.5</v>
       </c>
       <c r="J745" t="n">
-        <v>2214.7</v>
+        <v>2109.91</v>
       </c>
       <c r="K745" t="n">
-        <v>-56.5</v>
+        <v>66.59</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>9.91</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="746">
@@ -39190,31 +39190,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="D746" t="n">
-        <v>1197.14</v>
+        <v>885.48</v>
       </c>
       <c r="E746" t="n">
-        <v>-175.14</v>
+        <v>143.52</v>
       </c>
       <c r="F746" t="n">
-        <v>1044.9</v>
+        <v>1047</v>
       </c>
       <c r="G746" t="n">
-        <v>1197.14</v>
+        <v>972.63</v>
       </c>
       <c r="H746" t="n">
-        <v>-152.24</v>
+        <v>74.37</v>
       </c>
       <c r="I746" t="n">
-        <v>1014</v>
+        <v>1019.4</v>
       </c>
       <c r="J746" t="n">
-        <v>1029</v>
+        <v>995.54</v>
       </c>
       <c r="K746" t="n">
-        <v>-15</v>
+        <v>23.86</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -39223,11 +39223,11 @@
       </c>
       <c r="M746" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N746" t="n">
-        <v>14.63</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="747">
@@ -39242,31 +39242,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="D747" t="n">
-        <v>372.97</v>
+        <v>303.76</v>
       </c>
       <c r="E747" t="n">
-        <v>-37.47</v>
+        <v>31.24</v>
       </c>
       <c r="F747" t="n">
-        <v>343.6</v>
+        <v>339.9</v>
       </c>
       <c r="G747" t="n">
-        <v>372.97</v>
+        <v>313.46</v>
       </c>
       <c r="H747" t="n">
-        <v>-29.37</v>
+        <v>26.44</v>
       </c>
       <c r="I747" t="n">
-        <v>333.55</v>
+        <v>331.7</v>
       </c>
       <c r="J747" t="n">
-        <v>335</v>
+        <v>320.72</v>
       </c>
       <c r="K747" t="n">
-        <v>-1.45</v>
+        <v>10.98</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -39275,11 +39275,11 @@
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N747" t="n">
-        <v>10.05</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="748">
@@ -39294,31 +39294,31 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="D748" t="n">
-        <v>643.73</v>
+        <v>500.09</v>
       </c>
       <c r="E748" t="n">
-        <v>-79.48</v>
+        <v>65.91</v>
       </c>
       <c r="F748" t="n">
-        <v>571.9</v>
+        <v>569.55</v>
       </c>
       <c r="G748" t="n">
-        <v>643.73</v>
+        <v>513.4</v>
       </c>
       <c r="H748" t="n">
-        <v>-71.83</v>
+        <v>56.15</v>
       </c>
       <c r="I748" t="n">
-        <v>563.8</v>
+        <v>558.6</v>
       </c>
       <c r="J748" t="n">
-        <v>566</v>
+        <v>534.8</v>
       </c>
       <c r="K748" t="n">
-        <v>-2.2</v>
+        <v>23.8</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
@@ -39327,11 +39327,11 @@
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N748" t="n">
-        <v>12.35</v>
+        <v>13.18</v>
       </c>
     </row>
   </sheetData>
@@ -43176,31 +43176,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>23063.1</v>
+        <v>23140.5</v>
       </c>
       <c r="D74" t="n">
         <v>23140.5</v>
       </c>
       <c r="E74" t="n">
-        <v>-77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>23281.95</v>
+        <v>23162.7</v>
       </c>
       <c r="G74" t="n">
         <v>23195.15</v>
       </c>
       <c r="H74" t="n">
-        <v>86.8</v>
+        <v>-32.45</v>
       </c>
       <c r="I74" t="n">
-        <v>23046.15</v>
+        <v>23020.95</v>
       </c>
       <c r="J74" t="n">
         <v>23053.4</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.25</v>
+        <v>-32.45</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -43228,31 +43228,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>55438.5</v>
+        <v>55580.4</v>
       </c>
       <c r="D75" t="n">
         <v>55580.4</v>
       </c>
       <c r="E75" t="n">
-        <v>-141.9</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>55918.4</v>
+        <v>55762.6</v>
       </c>
       <c r="G75" t="n">
         <v>55770.75</v>
       </c>
       <c r="H75" t="n">
-        <v>147.65</v>
+        <v>-8.15</v>
       </c>
       <c r="I75" t="n">
-        <v>55341.2</v>
+        <v>55373.75</v>
       </c>
       <c r="J75" t="n">
         <v>55381.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-40.7</v>
+        <v>-8.15</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -81950,31 +81950,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="D744" t="n">
-        <v>132.46</v>
+        <v>107.61</v>
       </c>
       <c r="E744" t="n">
-        <v>-15.34</v>
+        <v>8.99</v>
       </c>
       <c r="F744" t="n">
-        <v>118.67</v>
+        <v>118.01</v>
       </c>
       <c r="G744" t="n">
-        <v>128.63</v>
+        <v>110.41</v>
       </c>
       <c r="H744" t="n">
-        <v>-9.960000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I744" t="n">
-        <v>117.06</v>
+        <v>116.23</v>
       </c>
       <c r="J744" t="n">
-        <v>119.59</v>
+        <v>112.84</v>
       </c>
       <c r="K744" t="n">
-        <v>-2.53</v>
+        <v>3.39</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -81983,11 +81983,11 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N744" t="n">
-        <v>11.58</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="745">
@@ -82002,31 +82002,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2184.8</v>
+        <v>2214.7</v>
       </c>
       <c r="D745" t="n">
-        <v>2493.86</v>
+        <v>2067.93</v>
       </c>
       <c r="E745" t="n">
-        <v>-309.06</v>
+        <v>146.77</v>
       </c>
       <c r="F745" t="n">
-        <v>2204.9</v>
+        <v>2219</v>
       </c>
       <c r="G745" t="n">
-        <v>2465.31</v>
+        <v>2116.15</v>
       </c>
       <c r="H745" t="n">
-        <v>-260.41</v>
+        <v>102.85</v>
       </c>
       <c r="I745" t="n">
-        <v>2158.2</v>
+        <v>2176.5</v>
       </c>
       <c r="J745" t="n">
-        <v>2255.6</v>
+        <v>2128.24</v>
       </c>
       <c r="K745" t="n">
-        <v>-97.40000000000001</v>
+        <v>48.26</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -82035,11 +82035,11 @@
       </c>
       <c r="M745" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N745" t="n">
-        <v>12.39</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="746">
@@ -82054,31 +82054,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="D746" t="n">
-        <v>1234.44</v>
+        <v>912.9400000000001</v>
       </c>
       <c r="E746" t="n">
-        <v>-212.44</v>
+        <v>116.06</v>
       </c>
       <c r="F746" t="n">
-        <v>1044.9</v>
+        <v>1047</v>
       </c>
       <c r="G746" t="n">
-        <v>1148.44</v>
+        <v>985.79</v>
       </c>
       <c r="H746" t="n">
-        <v>-103.54</v>
+        <v>61.21</v>
       </c>
       <c r="I746" t="n">
-        <v>1014</v>
+        <v>1019.4</v>
       </c>
       <c r="J746" t="n">
-        <v>1045.84</v>
+        <v>986.78</v>
       </c>
       <c r="K746" t="n">
-        <v>-31.84</v>
+        <v>32.62</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -82087,11 +82087,11 @@
       </c>
       <c r="M746" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N746" t="n">
-        <v>17.21</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="747">
@@ -82106,31 +82106,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="D747" t="n">
-        <v>381.62</v>
+        <v>310.76</v>
       </c>
       <c r="E747" t="n">
-        <v>-46.12</v>
+        <v>24.24</v>
       </c>
       <c r="F747" t="n">
-        <v>343.6</v>
+        <v>339.9</v>
       </c>
       <c r="G747" t="n">
-        <v>371.11</v>
+        <v>318.55</v>
       </c>
       <c r="H747" t="n">
-        <v>-27.51</v>
+        <v>21.35</v>
       </c>
       <c r="I747" t="n">
-        <v>333.55</v>
+        <v>331.7</v>
       </c>
       <c r="J747" t="n">
-        <v>342.49</v>
+        <v>323.15</v>
       </c>
       <c r="K747" t="n">
-        <v>-8.94</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -82139,11 +82139,11 @@
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N747" t="n">
-        <v>12.09</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="748">
@@ -82158,44 +82158,44 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="D748" t="n">
-        <v>664.58</v>
+        <v>516.21</v>
       </c>
       <c r="E748" t="n">
-        <v>-100.33</v>
+        <v>49.79</v>
       </c>
       <c r="F748" t="n">
-        <v>571.9</v>
+        <v>569.55</v>
       </c>
       <c r="G748" t="n">
-        <v>632.4299999999999</v>
+        <v>542.86</v>
       </c>
       <c r="H748" t="n">
-        <v>-60.53</v>
+        <v>26.69</v>
       </c>
       <c r="I748" t="n">
-        <v>563.8</v>
+        <v>558.6</v>
       </c>
       <c r="J748" t="n">
-        <v>574.74</v>
+        <v>542.28</v>
       </c>
       <c r="K748" t="n">
-        <v>-10.94</v>
+        <v>16.32</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N748" t="n">
-        <v>15.1</v>
+        <v>9.65</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N748"/>
+  <dimension ref="A1:N752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39332,6 +39332,214 @@
       </c>
       <c r="N748" t="n">
         <v>13.18</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="D749" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="E749" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F749" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="G749" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="H749" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="I749" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="J749" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="K749" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N749" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2197</v>
+      </c>
+      <c r="D750" t="n">
+        <v>2438.65</v>
+      </c>
+      <c r="E750" t="n">
+        <v>-241.65</v>
+      </c>
+      <c r="F750" t="n">
+        <v>2210.2</v>
+      </c>
+      <c r="G750" t="n">
+        <v>2438.65</v>
+      </c>
+      <c r="H750" t="n">
+        <v>-228.45</v>
+      </c>
+      <c r="I750" t="n">
+        <v>2174.9</v>
+      </c>
+      <c r="J750" t="n">
+        <v>2197</v>
+      </c>
+      <c r="K750" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N750" t="n">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="D751" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="E751" t="n">
+        <v>-36.96</v>
+      </c>
+      <c r="F751" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="G751" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="H751" t="n">
+        <v>-32.81</v>
+      </c>
+      <c r="I751" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="J751" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="K751" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N751" t="n">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>564.15</v>
+      </c>
+      <c r="D752" t="n">
+        <v>643.61</v>
+      </c>
+      <c r="E752" t="n">
+        <v>-79.45999999999999</v>
+      </c>
+      <c r="F752" t="n">
+        <v>574.7</v>
+      </c>
+      <c r="G752" t="n">
+        <v>643.61</v>
+      </c>
+      <c r="H752" t="n">
+        <v>-68.91</v>
+      </c>
+      <c r="I752" t="n">
+        <v>562.5</v>
+      </c>
+      <c r="J752" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="K752" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N752" t="n">
+        <v>12.35</v>
       </c>
     </row>
   </sheetData>
@@ -39345,7 +39553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43265,6 +43473,110 @@
         </is>
       </c>
       <c r="N75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>22780.25</v>
+      </c>
+      <c r="D76" t="n">
+        <v>22780.25</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>23080.25</v>
+      </c>
+      <c r="G76" t="n">
+        <v>22986.26</v>
+      </c>
+      <c r="H76" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>22762.2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>22668.21</v>
+      </c>
+      <c r="K76" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>54471.65</v>
+      </c>
+      <c r="D77" t="n">
+        <v>54471.65</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>55390.1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>55095.26</v>
+      </c>
+      <c r="H77" t="n">
+        <v>294.84</v>
+      </c>
+      <c r="I77" t="n">
+        <v>54437.7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>54142.86</v>
+      </c>
+      <c r="K77" t="n">
+        <v>294.84</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43279,7 +43591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N748"/>
+  <dimension ref="A1:N752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82198,6 +82510,214 @@
         <v>9.65</v>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="D749" t="n">
+        <v>324.23</v>
+      </c>
+      <c r="E749" t="n">
+        <v>-34.38</v>
+      </c>
+      <c r="F749" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="G749" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="H749" t="n">
+        <v>-23.26</v>
+      </c>
+      <c r="I749" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="J749" t="n">
+        <v>292.96</v>
+      </c>
+      <c r="K749" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N749" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2197</v>
+      </c>
+      <c r="D750" t="n">
+        <v>2505.61</v>
+      </c>
+      <c r="E750" t="n">
+        <v>-308.61</v>
+      </c>
+      <c r="F750" t="n">
+        <v>2210.2</v>
+      </c>
+      <c r="G750" t="n">
+        <v>2414.24</v>
+      </c>
+      <c r="H750" t="n">
+        <v>-204.04</v>
+      </c>
+      <c r="I750" t="n">
+        <v>2174.9</v>
+      </c>
+      <c r="J750" t="n">
+        <v>2208.53</v>
+      </c>
+      <c r="K750" t="n">
+        <v>-33.63</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N750" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="D751" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="E751" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="F751" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="G751" t="n">
+        <v>362.33</v>
+      </c>
+      <c r="H751" t="n">
+        <v>-27.23</v>
+      </c>
+      <c r="I751" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="J751" t="n">
+        <v>333.66</v>
+      </c>
+      <c r="K751" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N751" t="n">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>564.15</v>
+      </c>
+      <c r="D752" t="n">
+        <v>663.28</v>
+      </c>
+      <c r="E752" t="n">
+        <v>-99.13</v>
+      </c>
+      <c r="F752" t="n">
+        <v>574.7</v>
+      </c>
+      <c r="G752" t="n">
+        <v>621.72</v>
+      </c>
+      <c r="H752" t="n">
+        <v>-47.02</v>
+      </c>
+      <c r="I752" t="n">
+        <v>562.5</v>
+      </c>
+      <c r="J752" t="n">
+        <v>565.83</v>
+      </c>
+      <c r="K752" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N752" t="n">
+        <v>14.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39346,31 +39346,31 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>289.85</v>
+        <v>286.5</v>
       </c>
       <c r="D749" t="n">
         <v>317.85</v>
       </c>
       <c r="E749" t="n">
-        <v>-28</v>
+        <v>-31.35</v>
       </c>
       <c r="F749" t="n">
-        <v>293.05</v>
+        <v>286.5</v>
       </c>
       <c r="G749" t="n">
         <v>317.85</v>
       </c>
       <c r="H749" t="n">
-        <v>-24.8</v>
+        <v>-31.35</v>
       </c>
       <c r="I749" t="n">
-        <v>285.75</v>
+        <v>283.4</v>
       </c>
       <c r="J749" t="n">
         <v>289.85</v>
       </c>
       <c r="K749" t="n">
-        <v>-4.1</v>
+        <v>-6.45</v>
       </c>
       <c r="L749" t="inlineStr">
         <is>
@@ -39379,11 +39379,11 @@
       </c>
       <c r="M749" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N749" t="n">
-        <v>8.81</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="750">
@@ -39398,31 +39398,31 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>2197</v>
+        <v>2214.7</v>
       </c>
       <c r="D750" t="n">
         <v>2438.65</v>
       </c>
       <c r="E750" t="n">
-        <v>-241.65</v>
+        <v>-223.95</v>
       </c>
       <c r="F750" t="n">
-        <v>2210.2</v>
+        <v>2219</v>
       </c>
       <c r="G750" t="n">
         <v>2438.65</v>
       </c>
       <c r="H750" t="n">
-        <v>-228.45</v>
+        <v>-219.65</v>
       </c>
       <c r="I750" t="n">
-        <v>2174.9</v>
+        <v>2176.5</v>
       </c>
       <c r="J750" t="n">
         <v>2197</v>
       </c>
       <c r="K750" t="n">
-        <v>-22.1</v>
+        <v>-20.5</v>
       </c>
       <c r="L750" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         </is>
       </c>
       <c r="N750" t="n">
-        <v>9.91</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="751">
@@ -39450,31 +39450,31 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>330.95</v>
+        <v>335</v>
       </c>
       <c r="D751" t="n">
         <v>367.91</v>
       </c>
       <c r="E751" t="n">
-        <v>-36.96</v>
+        <v>-32.91</v>
       </c>
       <c r="F751" t="n">
-        <v>335.1</v>
+        <v>339.9</v>
       </c>
       <c r="G751" t="n">
         <v>367.91</v>
       </c>
       <c r="H751" t="n">
-        <v>-32.81</v>
+        <v>-28.01</v>
       </c>
       <c r="I751" t="n">
-        <v>328.45</v>
+        <v>331.7</v>
       </c>
       <c r="J751" t="n">
         <v>330.95</v>
       </c>
       <c r="K751" t="n">
-        <v>-2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L751" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="N751" t="n">
-        <v>10.05</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="752">
@@ -39502,31 +39502,31 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>564.15</v>
+        <v>566</v>
       </c>
       <c r="D752" t="n">
         <v>643.61</v>
       </c>
       <c r="E752" t="n">
-        <v>-79.45999999999999</v>
+        <v>-77.61</v>
       </c>
       <c r="F752" t="n">
-        <v>574.7</v>
+        <v>569.55</v>
       </c>
       <c r="G752" t="n">
         <v>643.61</v>
       </c>
       <c r="H752" t="n">
-        <v>-68.91</v>
+        <v>-74.06</v>
       </c>
       <c r="I752" t="n">
-        <v>562.5</v>
+        <v>558.6</v>
       </c>
       <c r="J752" t="n">
         <v>558.45</v>
       </c>
       <c r="K752" t="n">
-        <v>4.05</v>
+        <v>0.15</v>
       </c>
       <c r="L752" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         </is>
       </c>
       <c r="N752" t="n">
-        <v>12.35</v>
+        <v>12.06</v>
       </c>
     </row>
   </sheetData>
@@ -43488,31 +43488,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22780.25</v>
+        <v>23140.5</v>
       </c>
       <c r="D76" t="n">
         <v>22780.25</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>360.25</v>
       </c>
       <c r="F76" t="n">
-        <v>23080.25</v>
+        <v>23162.7</v>
       </c>
       <c r="G76" t="n">
         <v>22986.26</v>
       </c>
       <c r="H76" t="n">
-        <v>93.98999999999999</v>
+        <v>176.44</v>
       </c>
       <c r="I76" t="n">
-        <v>22762.2</v>
+        <v>23020.95</v>
       </c>
       <c r="J76" t="n">
         <v>22668.21</v>
       </c>
       <c r="K76" t="n">
-        <v>93.98999999999999</v>
+        <v>352.74</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="77">
@@ -43540,31 +43540,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>54471.65</v>
+        <v>55580.4</v>
       </c>
       <c r="D77" t="n">
         <v>54471.65</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1108.75</v>
       </c>
       <c r="F77" t="n">
-        <v>55390.1</v>
+        <v>55762.6</v>
       </c>
       <c r="G77" t="n">
         <v>55095.26</v>
       </c>
       <c r="H77" t="n">
-        <v>294.84</v>
+        <v>667.34</v>
       </c>
       <c r="I77" t="n">
-        <v>54437.7</v>
+        <v>55373.75</v>
       </c>
       <c r="J77" t="n">
         <v>54142.86</v>
       </c>
       <c r="K77" t="n">
-        <v>294.84</v>
+        <v>1230.89</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
     </row>
   </sheetData>
@@ -82522,31 +82522,31 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>289.85</v>
+        <v>286.5</v>
       </c>
       <c r="D749" t="n">
         <v>324.23</v>
       </c>
       <c r="E749" t="n">
-        <v>-34.38</v>
+        <v>-37.73</v>
       </c>
       <c r="F749" t="n">
-        <v>293.05</v>
+        <v>286.5</v>
       </c>
       <c r="G749" t="n">
         <v>316.31</v>
       </c>
       <c r="H749" t="n">
-        <v>-23.26</v>
+        <v>-29.81</v>
       </c>
       <c r="I749" t="n">
-        <v>285.75</v>
+        <v>283.4</v>
       </c>
       <c r="J749" t="n">
         <v>292.96</v>
       </c>
       <c r="K749" t="n">
-        <v>-7.21</v>
+        <v>-9.56</v>
       </c>
       <c r="L749" t="inlineStr">
         <is>
@@ -82559,7 +82559,7 @@
         </is>
       </c>
       <c r="N749" t="n">
-        <v>10.6</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="750">
@@ -82574,31 +82574,31 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>2197</v>
+        <v>2214.7</v>
       </c>
       <c r="D750" t="n">
         <v>2505.61</v>
       </c>
       <c r="E750" t="n">
-        <v>-308.61</v>
+        <v>-290.91</v>
       </c>
       <c r="F750" t="n">
-        <v>2210.2</v>
+        <v>2219</v>
       </c>
       <c r="G750" t="n">
         <v>2414.24</v>
       </c>
       <c r="H750" t="n">
-        <v>-204.04</v>
+        <v>-195.24</v>
       </c>
       <c r="I750" t="n">
-        <v>2174.9</v>
+        <v>2176.5</v>
       </c>
       <c r="J750" t="n">
         <v>2208.53</v>
       </c>
       <c r="K750" t="n">
-        <v>-33.63</v>
+        <v>-32.03</v>
       </c>
       <c r="L750" t="inlineStr">
         <is>
@@ -82611,7 +82611,7 @@
         </is>
       </c>
       <c r="N750" t="n">
-        <v>12.32</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="751">
@@ -82626,31 +82626,31 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>330.95</v>
+        <v>335</v>
       </c>
       <c r="D751" t="n">
         <v>376.55</v>
       </c>
       <c r="E751" t="n">
-        <v>-45.6</v>
+        <v>-41.55</v>
       </c>
       <c r="F751" t="n">
-        <v>335.1</v>
+        <v>339.9</v>
       </c>
       <c r="G751" t="n">
         <v>362.33</v>
       </c>
       <c r="H751" t="n">
-        <v>-27.23</v>
+        <v>-22.43</v>
       </c>
       <c r="I751" t="n">
-        <v>328.45</v>
+        <v>331.7</v>
       </c>
       <c r="J751" t="n">
         <v>333.66</v>
       </c>
       <c r="K751" t="n">
-        <v>-5.21</v>
+        <v>-1.96</v>
       </c>
       <c r="L751" t="inlineStr">
         <is>
@@ -82663,7 +82663,7 @@
         </is>
       </c>
       <c r="N751" t="n">
-        <v>12.11</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="752">
@@ -82678,31 +82678,31 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>564.15</v>
+        <v>566</v>
       </c>
       <c r="D752" t="n">
         <v>663.28</v>
       </c>
       <c r="E752" t="n">
-        <v>-99.13</v>
+        <v>-97.28</v>
       </c>
       <c r="F752" t="n">
-        <v>574.7</v>
+        <v>569.55</v>
       </c>
       <c r="G752" t="n">
         <v>621.72</v>
       </c>
       <c r="H752" t="n">
-        <v>-47.02</v>
+        <v>-52.17</v>
       </c>
       <c r="I752" t="n">
-        <v>562.5</v>
+        <v>558.6</v>
       </c>
       <c r="J752" t="n">
         <v>565.83</v>
       </c>
       <c r="K752" t="n">
-        <v>-3.33</v>
+        <v>-7.23</v>
       </c>
       <c r="L752" t="inlineStr">
         <is>
@@ -82715,7 +82715,7 @@
         </is>
       </c>
       <c r="N752" t="n">
-        <v>14.95</v>
+        <v>14.67</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N752"/>
+  <dimension ref="A1:N755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39540,6 +39540,162 @@
       </c>
       <c r="N752" t="n">
         <v>12.06</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2188.6</v>
+      </c>
+      <c r="D753" t="n">
+        <v>2003.52</v>
+      </c>
+      <c r="E753" t="n">
+        <v>185.08</v>
+      </c>
+      <c r="F753" t="n">
+        <v>2217.8</v>
+      </c>
+      <c r="G753" t="n">
+        <v>2051.83</v>
+      </c>
+      <c r="H753" t="n">
+        <v>165.97</v>
+      </c>
+      <c r="I753" t="n">
+        <v>2172.1</v>
+      </c>
+      <c r="J753" t="n">
+        <v>2120.68</v>
+      </c>
+      <c r="K753" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N753" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="D754" t="n">
+        <v>300.91</v>
+      </c>
+      <c r="E754" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="F754" t="n">
+        <v>333</v>
+      </c>
+      <c r="G754" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="H754" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="I754" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="J754" t="n">
+        <v>321.78</v>
+      </c>
+      <c r="K754" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N754" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="D755" t="n">
+        <v>486.22</v>
+      </c>
+      <c r="E755" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="F755" t="n">
+        <v>566.75</v>
+      </c>
+      <c r="G755" t="n">
+        <v>493.58</v>
+      </c>
+      <c r="H755" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="I755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="J755" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="K755" t="n">
+        <v>22</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N755" t="n">
+        <v>12.81</v>
       </c>
     </row>
   </sheetData>
@@ -39553,7 +39709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43578,6 +43734,110 @@
       </c>
       <c r="N77" t="n">
         <v>2.04</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>22716.2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>22716.2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>22753.25</v>
+      </c>
+      <c r="G78" t="n">
+        <v>22789.75</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>22569.65</v>
+      </c>
+      <c r="J78" t="n">
+        <v>22606.15</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>54259.95</v>
+      </c>
+      <c r="D79" t="n">
+        <v>54259.95</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>54405.3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>54514.94</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-109.64</v>
+      </c>
+      <c r="I79" t="n">
+        <v>53785.7</v>
+      </c>
+      <c r="J79" t="n">
+        <v>53895.34</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-109.64</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -43591,7 +43851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N752"/>
+  <dimension ref="A1:N755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82718,6 +82978,162 @@
         <v>14.67</v>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2188.6</v>
+      </c>
+      <c r="D753" t="n">
+        <v>2058.34</v>
+      </c>
+      <c r="E753" t="n">
+        <v>130.26</v>
+      </c>
+      <c r="F753" t="n">
+        <v>2217.8</v>
+      </c>
+      <c r="G753" t="n">
+        <v>2098.83</v>
+      </c>
+      <c r="H753" t="n">
+        <v>118.97</v>
+      </c>
+      <c r="I753" t="n">
+        <v>2172.1</v>
+      </c>
+      <c r="J753" t="n">
+        <v>2133.15</v>
+      </c>
+      <c r="K753" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N753" t="n">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="D754" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="E754" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F754" t="n">
+        <v>333</v>
+      </c>
+      <c r="G754" t="n">
+        <v>313.53</v>
+      </c>
+      <c r="H754" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="I754" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="J754" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="K754" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N754" t="n">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="D755" t="n">
+        <v>501.04</v>
+      </c>
+      <c r="E755" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="F755" t="n">
+        <v>566.75</v>
+      </c>
+      <c r="G755" t="n">
+        <v>527.55</v>
+      </c>
+      <c r="H755" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="I755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="J755" t="n">
+        <v>533.36</v>
+      </c>
+      <c r="K755" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N755" t="n">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39554,31 +39554,31 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2188.6</v>
+        <v>2197</v>
       </c>
       <c r="D753" t="n">
         <v>2003.52</v>
       </c>
       <c r="E753" t="n">
-        <v>185.08</v>
+        <v>193.48</v>
       </c>
       <c r="F753" t="n">
-        <v>2217.8</v>
+        <v>2210.2</v>
       </c>
       <c r="G753" t="n">
         <v>2051.83</v>
       </c>
       <c r="H753" t="n">
-        <v>165.97</v>
+        <v>158.37</v>
       </c>
       <c r="I753" t="n">
-        <v>2172.1</v>
+        <v>2174.9</v>
       </c>
       <c r="J753" t="n">
         <v>2120.68</v>
       </c>
       <c r="K753" t="n">
-        <v>51.42</v>
+        <v>54.22</v>
       </c>
       <c r="L753" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         </is>
       </c>
       <c r="N753" t="n">
-        <v>9.24</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="754">
@@ -39606,31 +39606,31 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>327.85</v>
+        <v>330.95</v>
       </c>
       <c r="D754" t="n">
         <v>300.91</v>
       </c>
       <c r="E754" t="n">
-        <v>26.94</v>
+        <v>30.04</v>
       </c>
       <c r="F754" t="n">
-        <v>333</v>
+        <v>335.1</v>
       </c>
       <c r="G754" t="n">
         <v>311.19</v>
       </c>
       <c r="H754" t="n">
-        <v>21.81</v>
+        <v>23.91</v>
       </c>
       <c r="I754" t="n">
-        <v>323.65</v>
+        <v>328.45</v>
       </c>
       <c r="J754" t="n">
         <v>321.78</v>
       </c>
       <c r="K754" t="n">
-        <v>1.87</v>
+        <v>6.67</v>
       </c>
       <c r="L754" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         </is>
       </c>
       <c r="N754" t="n">
-        <v>8.949999999999999</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="755">
@@ -39658,31 +39658,31 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>548.5</v>
+        <v>564.15</v>
       </c>
       <c r="D755" t="n">
         <v>486.22</v>
       </c>
       <c r="E755" t="n">
-        <v>62.28</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="F755" t="n">
-        <v>566.75</v>
+        <v>574.7</v>
       </c>
       <c r="G755" t="n">
         <v>493.58</v>
       </c>
       <c r="H755" t="n">
-        <v>73.17</v>
+        <v>81.12</v>
       </c>
       <c r="I755" t="n">
-        <v>548.5</v>
+        <v>562.5</v>
       </c>
       <c r="J755" t="n">
         <v>526.5</v>
       </c>
       <c r="K755" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L755" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         </is>
       </c>
       <c r="N755" t="n">
-        <v>12.81</v>
+        <v>16.03</v>
       </c>
     </row>
   </sheetData>
@@ -43748,31 +43748,31 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>22716.2</v>
+        <v>22780.25</v>
       </c>
       <c r="D78" t="n">
         <v>22716.2</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>64.05</v>
       </c>
       <c r="F78" t="n">
-        <v>22753.25</v>
+        <v>23080.25</v>
       </c>
       <c r="G78" t="n">
         <v>22789.75</v>
       </c>
       <c r="H78" t="n">
-        <v>-36.5</v>
+        <v>290.5</v>
       </c>
       <c r="I78" t="n">
-        <v>22569.65</v>
+        <v>22762.2</v>
       </c>
       <c r="J78" t="n">
         <v>22606.15</v>
       </c>
       <c r="K78" t="n">
-        <v>-36.5</v>
+        <v>156.05</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="79">
@@ -43800,31 +43800,31 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>54259.95</v>
+        <v>54471.65</v>
       </c>
       <c r="D79" t="n">
         <v>54259.95</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>211.7</v>
       </c>
       <c r="F79" t="n">
-        <v>54405.3</v>
+        <v>55390.1</v>
       </c>
       <c r="G79" t="n">
         <v>54514.94</v>
       </c>
       <c r="H79" t="n">
-        <v>-109.64</v>
+        <v>875.16</v>
       </c>
       <c r="I79" t="n">
-        <v>53785.7</v>
+        <v>54437.7</v>
       </c>
       <c r="J79" t="n">
         <v>53895.34</v>
       </c>
       <c r="K79" t="n">
-        <v>-109.64</v>
+        <v>542.36</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -82990,31 +82990,31 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2188.6</v>
+        <v>2197</v>
       </c>
       <c r="D753" t="n">
         <v>2058.34</v>
       </c>
       <c r="E753" t="n">
-        <v>130.26</v>
+        <v>138.66</v>
       </c>
       <c r="F753" t="n">
-        <v>2217.8</v>
+        <v>2210.2</v>
       </c>
       <c r="G753" t="n">
         <v>2098.83</v>
       </c>
       <c r="H753" t="n">
-        <v>118.97</v>
+        <v>111.37</v>
       </c>
       <c r="I753" t="n">
-        <v>2172.1</v>
+        <v>2174.9</v>
       </c>
       <c r="J753" t="n">
         <v>2133.15</v>
       </c>
       <c r="K753" t="n">
-        <v>38.95</v>
+        <v>41.75</v>
       </c>
       <c r="L753" t="inlineStr">
         <is>
@@ -83027,7 +83027,7 @@
         </is>
       </c>
       <c r="N753" t="n">
-        <v>6.33</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="754">
@@ -83042,31 +83042,31 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>327.85</v>
+        <v>330.95</v>
       </c>
       <c r="D754" t="n">
         <v>308.25</v>
       </c>
       <c r="E754" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
       <c r="F754" t="n">
-        <v>333</v>
+        <v>335.1</v>
       </c>
       <c r="G754" t="n">
         <v>313.53</v>
       </c>
       <c r="H754" t="n">
-        <v>19.47</v>
+        <v>21.57</v>
       </c>
       <c r="I754" t="n">
-        <v>323.65</v>
+        <v>328.45</v>
       </c>
       <c r="J754" t="n">
         <v>320.26</v>
       </c>
       <c r="K754" t="n">
-        <v>3.39</v>
+        <v>8.19</v>
       </c>
       <c r="L754" t="inlineStr">
         <is>
@@ -83079,7 +83079,7 @@
         </is>
       </c>
       <c r="N754" t="n">
-        <v>6.36</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="755">
@@ -83094,31 +83094,31 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>548.5</v>
+        <v>564.15</v>
       </c>
       <c r="D755" t="n">
         <v>501.04</v>
       </c>
       <c r="E755" t="n">
-        <v>47.46</v>
+        <v>63.11</v>
       </c>
       <c r="F755" t="n">
-        <v>566.75</v>
+        <v>574.7</v>
       </c>
       <c r="G755" t="n">
         <v>527.55</v>
       </c>
       <c r="H755" t="n">
-        <v>39.2</v>
+        <v>47.15</v>
       </c>
       <c r="I755" t="n">
-        <v>548.5</v>
+        <v>562.5</v>
       </c>
       <c r="J755" t="n">
         <v>533.36</v>
       </c>
       <c r="K755" t="n">
-        <v>15.14</v>
+        <v>29.14</v>
       </c>
       <c r="L755" t="inlineStr">
         <is>
@@ -83131,7 +83131,7 @@
         </is>
       </c>
       <c r="N755" t="n">
-        <v>9.470000000000001</v>
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N755"/>
+  <dimension ref="A1:N758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39696,6 +39696,162 @@
       </c>
       <c r="N755" t="n">
         <v>16.03</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>674</v>
+      </c>
+      <c r="D756" t="n">
+        <v>731.29</v>
+      </c>
+      <c r="E756" t="n">
+        <v>-57.29</v>
+      </c>
+      <c r="F756" t="n">
+        <v>674</v>
+      </c>
+      <c r="G756" t="n">
+        <v>731.29</v>
+      </c>
+      <c r="H756" t="n">
+        <v>-57.29</v>
+      </c>
+      <c r="I756" t="n">
+        <v>653</v>
+      </c>
+      <c r="J756" t="n">
+        <v>669.98</v>
+      </c>
+      <c r="K756" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N756" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="D757" t="n">
+        <v>2420.81</v>
+      </c>
+      <c r="E757" t="n">
+        <v>-230.71</v>
+      </c>
+      <c r="F757" t="n">
+        <v>2224.5</v>
+      </c>
+      <c r="G757" t="n">
+        <v>2420.81</v>
+      </c>
+      <c r="H757" t="n">
+        <v>-196.31</v>
+      </c>
+      <c r="I757" t="n">
+        <v>2181.6</v>
+      </c>
+      <c r="J757" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="K757" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N757" t="n">
+        <v>9.529999999999999</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="D758" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="E758" t="n">
+        <v>-15.15</v>
+      </c>
+      <c r="F758" t="n">
+        <v>184.37</v>
+      </c>
+      <c r="G758" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="H758" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="I758" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="J758" t="n">
+        <v>177.37</v>
+      </c>
+      <c r="K758" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N758" t="n">
+        <v>7.83</v>
       </c>
     </row>
   </sheetData>
@@ -39709,7 +39865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43838,6 +43994,110 @@
       </c>
       <c r="N79" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="D80" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>22809.35</v>
+      </c>
+      <c r="G80" t="n">
+        <v>22754.8</v>
+      </c>
+      <c r="H80" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="I80" t="n">
+        <v>22595.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>22540.65</v>
+      </c>
+      <c r="K80" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>54633.05</v>
+      </c>
+      <c r="D81" t="n">
+        <v>54633.05</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>55135.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>55120.94</v>
+      </c>
+      <c r="H81" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="I81" t="n">
+        <v>54174.3</v>
+      </c>
+      <c r="J81" t="n">
+        <v>54159.74</v>
+      </c>
+      <c r="K81" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -43851,7 +44111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N755"/>
+  <dimension ref="A1:N758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83134,6 +83394,162 @@
         <v>12.6</v>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>674</v>
+      </c>
+      <c r="D756" t="n">
+        <v>750.4400000000001</v>
+      </c>
+      <c r="E756" t="n">
+        <v>-76.44</v>
+      </c>
+      <c r="F756" t="n">
+        <v>674</v>
+      </c>
+      <c r="G756" t="n">
+        <v>739.09</v>
+      </c>
+      <c r="H756" t="n">
+        <v>-65.09</v>
+      </c>
+      <c r="I756" t="n">
+        <v>653</v>
+      </c>
+      <c r="J756" t="n">
+        <v>677.89</v>
+      </c>
+      <c r="K756" t="n">
+        <v>-24.89</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N756" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="D757" t="n">
+        <v>2488.18</v>
+      </c>
+      <c r="E757" t="n">
+        <v>-298.08</v>
+      </c>
+      <c r="F757" t="n">
+        <v>2224.5</v>
+      </c>
+      <c r="G757" t="n">
+        <v>2405.33</v>
+      </c>
+      <c r="H757" t="n">
+        <v>-180.83</v>
+      </c>
+      <c r="I757" t="n">
+        <v>2181.6</v>
+      </c>
+      <c r="J757" t="n">
+        <v>2200.03</v>
+      </c>
+      <c r="K757" t="n">
+        <v>-18.43</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N757" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BANDHANBNK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="D758" t="n">
+        <v>200.55</v>
+      </c>
+      <c r="E758" t="n">
+        <v>-22.32</v>
+      </c>
+      <c r="F758" t="n">
+        <v>184.37</v>
+      </c>
+      <c r="G758" t="n">
+        <v>197.43</v>
+      </c>
+      <c r="H758" t="n">
+        <v>-13.06</v>
+      </c>
+      <c r="I758" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="J758" t="n">
+        <v>177.81</v>
+      </c>
+      <c r="K758" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N758" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39710,22 +39710,22 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="D756" t="n">
         <v>731.29</v>
       </c>
       <c r="E756" t="n">
-        <v>-57.29</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="F756" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G756" t="n">
         <v>731.29</v>
       </c>
       <c r="H756" t="n">
-        <v>-57.29</v>
+        <v>-56.29</v>
       </c>
       <c r="I756" t="n">
         <v>653</v>
@@ -39747,7 +39747,7 @@
         </is>
       </c>
       <c r="N756" t="n">
-        <v>7.83</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="757">
@@ -39762,31 +39762,31 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>2190.1</v>
+        <v>2188.6</v>
       </c>
       <c r="D757" t="n">
         <v>2420.81</v>
       </c>
       <c r="E757" t="n">
-        <v>-230.71</v>
+        <v>-232.21</v>
       </c>
       <c r="F757" t="n">
-        <v>2224.5</v>
+        <v>2217.8</v>
       </c>
       <c r="G757" t="n">
         <v>2420.81</v>
       </c>
       <c r="H757" t="n">
-        <v>-196.31</v>
+        <v>-203.01</v>
       </c>
       <c r="I757" t="n">
-        <v>2181.6</v>
+        <v>2172.1</v>
       </c>
       <c r="J757" t="n">
         <v>2190.1</v>
       </c>
       <c r="K757" t="n">
-        <v>-8.5</v>
+        <v>-18</v>
       </c>
       <c r="L757" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         </is>
       </c>
       <c r="N757" t="n">
-        <v>9.529999999999999</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="758">
@@ -39814,31 +39814,31 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>178.23</v>
+        <v>185.31</v>
       </c>
       <c r="D758" t="n">
         <v>193.38</v>
       </c>
       <c r="E758" t="n">
-        <v>-15.15</v>
+        <v>-8.07</v>
       </c>
       <c r="F758" t="n">
-        <v>184.37</v>
+        <v>185.31</v>
       </c>
       <c r="G758" t="n">
         <v>193.38</v>
       </c>
       <c r="H758" t="n">
-        <v>-9.01</v>
+        <v>-8.07</v>
       </c>
       <c r="I758" t="n">
-        <v>177.26</v>
+        <v>179.3</v>
       </c>
       <c r="J758" t="n">
         <v>177.37</v>
       </c>
       <c r="K758" t="n">
-        <v>-0.11</v>
+        <v>1.93</v>
       </c>
       <c r="L758" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         </is>
       </c>
       <c r="N758" t="n">
-        <v>7.83</v>
+        <v>4.17</v>
       </c>
     </row>
   </sheetData>
@@ -44008,31 +44008,31 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>22620.45</v>
+        <v>22716.2</v>
       </c>
       <c r="D80" t="n">
         <v>22620.45</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>95.75</v>
       </c>
       <c r="F80" t="n">
-        <v>22809.35</v>
+        <v>22753.25</v>
       </c>
       <c r="G80" t="n">
         <v>22754.8</v>
       </c>
       <c r="H80" t="n">
-        <v>54.55</v>
+        <v>-1.55</v>
       </c>
       <c r="I80" t="n">
-        <v>22595.2</v>
+        <v>22569.65</v>
       </c>
       <c r="J80" t="n">
         <v>22540.65</v>
       </c>
       <c r="K80" t="n">
-        <v>54.55</v>
+        <v>29</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="81">
@@ -44060,31 +44060,31 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>54633.05</v>
+        <v>54259.95</v>
       </c>
       <c r="D81" t="n">
         <v>54633.05</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>-373.1</v>
       </c>
       <c r="F81" t="n">
-        <v>55135.5</v>
+        <v>54405.3</v>
       </c>
       <c r="G81" t="n">
         <v>55120.94</v>
       </c>
       <c r="H81" t="n">
-        <v>14.56</v>
+        <v>-715.64</v>
       </c>
       <c r="I81" t="n">
-        <v>54174.3</v>
+        <v>53785.7</v>
       </c>
       <c r="J81" t="n">
         <v>54159.74</v>
       </c>
       <c r="K81" t="n">
-        <v>14.56</v>
+        <v>-374.04</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -83406,22 +83406,22 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="D756" t="n">
         <v>750.4400000000001</v>
       </c>
       <c r="E756" t="n">
-        <v>-76.44</v>
+        <v>-97.44</v>
       </c>
       <c r="F756" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G756" t="n">
         <v>739.09</v>
       </c>
       <c r="H756" t="n">
-        <v>-65.09</v>
+        <v>-64.09</v>
       </c>
       <c r="I756" t="n">
         <v>653</v>
@@ -83443,7 +83443,7 @@
         </is>
       </c>
       <c r="N756" t="n">
-        <v>10.19</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="757">
@@ -83458,31 +83458,31 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>2190.1</v>
+        <v>2188.6</v>
       </c>
       <c r="D757" t="n">
         <v>2488.18</v>
       </c>
       <c r="E757" t="n">
-        <v>-298.08</v>
+        <v>-299.58</v>
       </c>
       <c r="F757" t="n">
-        <v>2224.5</v>
+        <v>2217.8</v>
       </c>
       <c r="G757" t="n">
         <v>2405.33</v>
       </c>
       <c r="H757" t="n">
-        <v>-180.83</v>
+        <v>-187.53</v>
       </c>
       <c r="I757" t="n">
-        <v>2181.6</v>
+        <v>2172.1</v>
       </c>
       <c r="J757" t="n">
         <v>2200.03</v>
       </c>
       <c r="K757" t="n">
-        <v>-18.43</v>
+        <v>-27.93</v>
       </c>
       <c r="L757" t="inlineStr">
         <is>
@@ -83495,7 +83495,7 @@
         </is>
       </c>
       <c r="N757" t="n">
-        <v>11.98</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="758">
@@ -83510,31 +83510,31 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>178.23</v>
+        <v>185.31</v>
       </c>
       <c r="D758" t="n">
         <v>200.55</v>
       </c>
       <c r="E758" t="n">
-        <v>-22.32</v>
+        <v>-15.24</v>
       </c>
       <c r="F758" t="n">
-        <v>184.37</v>
+        <v>185.31</v>
       </c>
       <c r="G758" t="n">
         <v>197.43</v>
       </c>
       <c r="H758" t="n">
-        <v>-13.06</v>
+        <v>-12.12</v>
       </c>
       <c r="I758" t="n">
-        <v>177.26</v>
+        <v>179.3</v>
       </c>
       <c r="J758" t="n">
         <v>177.81</v>
       </c>
       <c r="K758" t="n">
-        <v>-0.55</v>
+        <v>1.49</v>
       </c>
       <c r="L758" t="inlineStr">
         <is>
@@ -83547,7 +83547,7 @@
         </is>
       </c>
       <c r="N758" t="n">
-        <v>11.13</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N758"/>
+  <dimension ref="A1:N759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39852,6 +39852,58 @@
       </c>
       <c r="N758" t="n">
         <v>4.17</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D759" t="n">
+        <v>2338.52</v>
+      </c>
+      <c r="E759" t="n">
+        <v>196.48</v>
+      </c>
+      <c r="F759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G759" t="n">
+        <v>2406.77</v>
+      </c>
+      <c r="H759" t="n">
+        <v>128.23</v>
+      </c>
+      <c r="I759" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J759" t="n">
+        <v>2466.59</v>
+      </c>
+      <c r="K759" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N759" t="n">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -39865,7 +39917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44098,6 +44150,110 @@
       </c>
       <c r="N81" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="D82" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>22610.6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>22615.94</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="I82" t="n">
+        <v>22217.3</v>
+      </c>
+      <c r="J82" t="n">
+        <v>22222.64</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>54450.75</v>
+      </c>
+      <c r="D83" t="n">
+        <v>54450.75</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>55091.45</v>
+      </c>
+      <c r="G83" t="n">
+        <v>55005.94</v>
+      </c>
+      <c r="H83" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="I83" t="n">
+        <v>54066.6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>53981.09</v>
+      </c>
+      <c r="K83" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -44111,7 +44267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N758"/>
+  <dimension ref="A1:N759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83550,6 +83706,58 @@
         <v>7.6</v>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D759" t="n">
+        <v>2402.86</v>
+      </c>
+      <c r="E759" t="n">
+        <v>132.14</v>
+      </c>
+      <c r="F759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G759" t="n">
+        <v>2442.98</v>
+      </c>
+      <c r="H759" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="I759" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J759" t="n">
+        <v>2459.43</v>
+      </c>
+      <c r="K759" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N759" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39866,31 +39866,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2535</v>
+        <v>2503.8</v>
       </c>
       <c r="D759" t="n">
         <v>2338.52</v>
       </c>
       <c r="E759" t="n">
-        <v>196.48</v>
+        <v>165.28</v>
       </c>
       <c r="F759" t="n">
-        <v>2535</v>
+        <v>2552</v>
       </c>
       <c r="G759" t="n">
         <v>2406.77</v>
       </c>
       <c r="H759" t="n">
-        <v>128.23</v>
+        <v>145.23</v>
       </c>
       <c r="I759" t="n">
-        <v>2476.1</v>
+        <v>2455</v>
       </c>
       <c r="J759" t="n">
         <v>2466.59</v>
       </c>
       <c r="K759" t="n">
-        <v>9.51</v>
+        <v>-11.59</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>8.4</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>
@@ -44164,31 +44164,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>22421.95</v>
+        <v>22620.45</v>
       </c>
       <c r="D82" t="n">
         <v>22421.95</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>198.5</v>
       </c>
       <c r="F82" t="n">
-        <v>22610.6</v>
+        <v>22809.35</v>
       </c>
       <c r="G82" t="n">
         <v>22615.94</v>
       </c>
       <c r="H82" t="n">
-        <v>-5.34</v>
+        <v>193.41</v>
       </c>
       <c r="I82" t="n">
-        <v>22217.3</v>
+        <v>22595.2</v>
       </c>
       <c r="J82" t="n">
         <v>22222.64</v>
       </c>
       <c r="K82" t="n">
-        <v>-5.34</v>
+        <v>372.56</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="83">
@@ -44216,31 +44216,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>54450.75</v>
+        <v>54633.05</v>
       </c>
       <c r="D83" t="n">
         <v>54450.75</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>182.3</v>
       </c>
       <c r="F83" t="n">
-        <v>55091.45</v>
+        <v>55135.5</v>
       </c>
       <c r="G83" t="n">
         <v>55005.94</v>
       </c>
       <c r="H83" t="n">
-        <v>85.51000000000001</v>
+        <v>129.56</v>
       </c>
       <c r="I83" t="n">
-        <v>54066.6</v>
+        <v>54174.3</v>
       </c>
       <c r="J83" t="n">
         <v>53981.09</v>
       </c>
       <c r="K83" t="n">
-        <v>85.51000000000001</v>
+        <v>193.21</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -83718,31 +83718,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2535</v>
+        <v>2503.8</v>
       </c>
       <c r="D759" t="n">
         <v>2402.86</v>
       </c>
       <c r="E759" t="n">
-        <v>132.14</v>
+        <v>100.94</v>
       </c>
       <c r="F759" t="n">
-        <v>2535</v>
+        <v>2552</v>
       </c>
       <c r="G759" t="n">
         <v>2442.98</v>
       </c>
       <c r="H759" t="n">
-        <v>92.02</v>
+        <v>109.02</v>
       </c>
       <c r="I759" t="n">
-        <v>2476.1</v>
+        <v>2455</v>
       </c>
       <c r="J759" t="n">
         <v>2459.43</v>
       </c>
       <c r="K759" t="n">
-        <v>16.67</v>
+        <v>-4.43</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -83755,7 +83755,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39866,31 +39866,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2503.8</v>
+        <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2338.52</v>
+        <v>2735.89</v>
       </c>
       <c r="E759" t="n">
-        <v>165.28</v>
+        <v>-200.89</v>
       </c>
       <c r="F759" t="n">
-        <v>2552</v>
+        <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2406.77</v>
+        <v>2735.89</v>
       </c>
       <c r="H759" t="n">
-        <v>145.23</v>
+        <v>-200.89</v>
       </c>
       <c r="I759" t="n">
-        <v>2455</v>
+        <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2466.59</v>
+        <v>2535</v>
       </c>
       <c r="K759" t="n">
-        <v>-11.59</v>
+        <v>-58.9</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>7.07</v>
+        <v>7.34</v>
       </c>
     </row>
   </sheetData>
@@ -44164,31 +44164,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>22620.45</v>
+        <v>22421.95</v>
       </c>
       <c r="D82" t="n">
         <v>22421.95</v>
       </c>
       <c r="E82" t="n">
-        <v>198.5</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>22809.35</v>
+        <v>22610.6</v>
       </c>
       <c r="G82" t="n">
         <v>22615.94</v>
       </c>
       <c r="H82" t="n">
-        <v>193.41</v>
+        <v>-5.34</v>
       </c>
       <c r="I82" t="n">
-        <v>22595.2</v>
+        <v>22217.3</v>
       </c>
       <c r="J82" t="n">
         <v>22222.64</v>
       </c>
       <c r="K82" t="n">
-        <v>372.56</v>
+        <v>-5.34</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -44216,31 +44216,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>54633.05</v>
+        <v>54450.75</v>
       </c>
       <c r="D83" t="n">
         <v>54450.75</v>
       </c>
       <c r="E83" t="n">
-        <v>182.3</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>55135.5</v>
+        <v>55091.45</v>
       </c>
       <c r="G83" t="n">
         <v>55005.94</v>
       </c>
       <c r="H83" t="n">
-        <v>129.56</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>54174.3</v>
+        <v>54066.6</v>
       </c>
       <c r="J83" t="n">
         <v>53981.09</v>
       </c>
       <c r="K83" t="n">
-        <v>193.21</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -83718,31 +83718,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2503.8</v>
+        <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2402.86</v>
+        <v>2810.76</v>
       </c>
       <c r="E759" t="n">
-        <v>100.94</v>
+        <v>-275.76</v>
       </c>
       <c r="F759" t="n">
-        <v>2552</v>
+        <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2442.98</v>
+        <v>2741.85</v>
       </c>
       <c r="H759" t="n">
-        <v>109.02</v>
+        <v>-206.85</v>
       </c>
       <c r="I759" t="n">
-        <v>2455</v>
+        <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2459.43</v>
+        <v>2537.2</v>
       </c>
       <c r="K759" t="n">
-        <v>-4.43</v>
+        <v>-61.1</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -83751,11 +83751,11 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N759" t="n">
-        <v>4.2</v>
+        <v>9.81</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39869,28 +39869,28 @@
         <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2735.89</v>
+        <v>2367.65</v>
       </c>
       <c r="E759" t="n">
-        <v>-200.89</v>
+        <v>167.35</v>
       </c>
       <c r="F759" t="n">
         <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2735.89</v>
+        <v>2494.26</v>
       </c>
       <c r="H759" t="n">
-        <v>-200.89</v>
+        <v>40.74</v>
       </c>
       <c r="I759" t="n">
         <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2535</v>
+        <v>2463</v>
       </c>
       <c r="K759" t="n">
-        <v>-58.9</v>
+        <v>13.1</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39899,11 +39899,11 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N759" t="n">
-        <v>7.34</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>
@@ -83721,28 +83721,28 @@
         <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2810.76</v>
+        <v>2432.44</v>
       </c>
       <c r="E759" t="n">
-        <v>-275.76</v>
+        <v>102.56</v>
       </c>
       <c r="F759" t="n">
         <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2741.85</v>
+        <v>2518.61</v>
       </c>
       <c r="H759" t="n">
-        <v>-206.85</v>
+        <v>16.39</v>
       </c>
       <c r="I759" t="n">
         <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2537.2</v>
+        <v>2442.61</v>
       </c>
       <c r="K759" t="n">
-        <v>-61.1</v>
+        <v>33.49</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -83751,11 +83751,11 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N759" t="n">
-        <v>9.81</v>
+        <v>4.22</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N759"/>
+  <dimension ref="A1:N762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39904,6 +39904,162 @@
       </c>
       <c r="N759" t="n">
         <v>7.07</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="D760" t="n">
+        <v>701.3200000000001</v>
+      </c>
+      <c r="E760" t="n">
+        <v>-42.92</v>
+      </c>
+      <c r="F760" t="n">
+        <v>671.1</v>
+      </c>
+      <c r="G760" t="n">
+        <v>701.3200000000001</v>
+      </c>
+      <c r="H760" t="n">
+        <v>-30.22</v>
+      </c>
+      <c r="I760" t="n">
+        <v>650.55</v>
+      </c>
+      <c r="J760" t="n">
+        <v>658.6799999999999</v>
+      </c>
+      <c r="K760" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N760" t="n">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="D761" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="E761" t="n">
+        <v>-16.46</v>
+      </c>
+      <c r="F761" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="G761" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="H761" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="I761" t="n">
+        <v>283.45</v>
+      </c>
+      <c r="J761" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="K761" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N761" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D762" t="n">
+        <v>2714.2</v>
+      </c>
+      <c r="E762" t="n">
+        <v>-179.2</v>
+      </c>
+      <c r="F762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G762" t="n">
+        <v>2714.2</v>
+      </c>
+      <c r="H762" t="n">
+        <v>-179.2</v>
+      </c>
+      <c r="I762" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J762" t="n">
+        <v>2479.87</v>
+      </c>
+      <c r="K762" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N762" t="n">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -39917,7 +40073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44254,6 +44410,110 @@
       </c>
       <c r="N83" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="D84" t="n">
+        <v>22439.25</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>22610.6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>22575</v>
+      </c>
+      <c r="H84" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I84" t="n">
+        <v>22217.3</v>
+      </c>
+      <c r="J84" t="n">
+        <v>22350.3</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-133</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>54450.75</v>
+      </c>
+      <c r="D85" t="n">
+        <v>54583.35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-132.6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>55091.45</v>
+      </c>
+      <c r="G85" t="n">
+        <v>55060.46</v>
+      </c>
+      <c r="H85" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="I85" t="n">
+        <v>54066.6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>54238.41</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-171.81</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -44267,7 +44527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N759"/>
+  <dimension ref="A1:N762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83758,6 +84018,162 @@
         <v>4.22</v>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="D760" t="n">
+        <v>720.0700000000001</v>
+      </c>
+      <c r="E760" t="n">
+        <v>-61.67</v>
+      </c>
+      <c r="F760" t="n">
+        <v>671.1</v>
+      </c>
+      <c r="G760" t="n">
+        <v>713.02</v>
+      </c>
+      <c r="H760" t="n">
+        <v>-41.92</v>
+      </c>
+      <c r="I760" t="n">
+        <v>650.55</v>
+      </c>
+      <c r="J760" t="n">
+        <v>666.23</v>
+      </c>
+      <c r="K760" t="n">
+        <v>-15.68</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N760" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="D761" t="n">
+        <v>308.01</v>
+      </c>
+      <c r="E761" t="n">
+        <v>-22.51</v>
+      </c>
+      <c r="F761" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="G761" t="n">
+        <v>305.07</v>
+      </c>
+      <c r="H761" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="I761" t="n">
+        <v>283.45</v>
+      </c>
+      <c r="J761" t="n">
+        <v>288.29</v>
+      </c>
+      <c r="K761" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N761" t="n">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D762" t="n">
+        <v>2788.44</v>
+      </c>
+      <c r="E762" t="n">
+        <v>-253.44</v>
+      </c>
+      <c r="F762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G762" t="n">
+        <v>2670.73</v>
+      </c>
+      <c r="H762" t="n">
+        <v>-135.73</v>
+      </c>
+      <c r="I762" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J762" t="n">
+        <v>2492.97</v>
+      </c>
+      <c r="K762" t="n">
+        <v>-16.87</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N762" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -39918,31 +39918,31 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>658.4</v>
+        <v>673</v>
       </c>
       <c r="D760" t="n">
         <v>701.3200000000001</v>
       </c>
       <c r="E760" t="n">
-        <v>-42.92</v>
+        <v>-28.32</v>
       </c>
       <c r="F760" t="n">
-        <v>671.1</v>
+        <v>676.5</v>
       </c>
       <c r="G760" t="n">
         <v>701.3200000000001</v>
       </c>
       <c r="H760" t="n">
-        <v>-30.22</v>
+        <v>-24.82</v>
       </c>
       <c r="I760" t="n">
-        <v>650.55</v>
+        <v>664</v>
       </c>
       <c r="J760" t="n">
         <v>658.6799999999999</v>
       </c>
       <c r="K760" t="n">
-        <v>-8.130000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="L760" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="N760" t="n">
-        <v>6.12</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="761">
@@ -40022,31 +40022,31 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>2535</v>
+        <v>2479</v>
       </c>
       <c r="D762" t="n">
         <v>2714.2</v>
       </c>
       <c r="E762" t="n">
-        <v>-179.2</v>
+        <v>-235.2</v>
       </c>
       <c r="F762" t="n">
-        <v>2535</v>
+        <v>2539.3</v>
       </c>
       <c r="G762" t="n">
         <v>2714.2</v>
       </c>
       <c r="H762" t="n">
-        <v>-179.2</v>
+        <v>-174.9</v>
       </c>
       <c r="I762" t="n">
-        <v>2476.1</v>
+        <v>2464.7</v>
       </c>
       <c r="J762" t="n">
         <v>2479.87</v>
       </c>
       <c r="K762" t="n">
-        <v>-3.77</v>
+        <v>-15.17</v>
       </c>
       <c r="L762" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         </is>
       </c>
       <c r="N762" t="n">
-        <v>6.6</v>
+        <v>8.67</v>
       </c>
     </row>
   </sheetData>
@@ -84030,31 +84030,31 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>658.4</v>
+        <v>673</v>
       </c>
       <c r="D760" t="n">
         <v>720.0700000000001</v>
       </c>
       <c r="E760" t="n">
-        <v>-61.67</v>
+        <v>-47.07</v>
       </c>
       <c r="F760" t="n">
-        <v>671.1</v>
+        <v>676.5</v>
       </c>
       <c r="G760" t="n">
         <v>713.02</v>
       </c>
       <c r="H760" t="n">
-        <v>-41.92</v>
+        <v>-36.52</v>
       </c>
       <c r="I760" t="n">
-        <v>650.55</v>
+        <v>664</v>
       </c>
       <c r="J760" t="n">
         <v>666.23</v>
       </c>
       <c r="K760" t="n">
-        <v>-15.68</v>
+        <v>-2.23</v>
       </c>
       <c r="L760" t="inlineStr">
         <is>
@@ -84067,7 +84067,7 @@
         </is>
       </c>
       <c r="N760" t="n">
-        <v>8.56</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="761">
@@ -84134,31 +84134,31 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>2535</v>
+        <v>2479</v>
       </c>
       <c r="D762" t="n">
         <v>2788.44</v>
       </c>
       <c r="E762" t="n">
-        <v>-253.44</v>
+        <v>-309.44</v>
       </c>
       <c r="F762" t="n">
-        <v>2535</v>
+        <v>2539.3</v>
       </c>
       <c r="G762" t="n">
         <v>2670.73</v>
       </c>
       <c r="H762" t="n">
-        <v>-135.73</v>
+        <v>-131.43</v>
       </c>
       <c r="I762" t="n">
-        <v>2476.1</v>
+        <v>2464.7</v>
       </c>
       <c r="J762" t="n">
         <v>2492.97</v>
       </c>
       <c r="K762" t="n">
-        <v>-16.87</v>
+        <v>-28.27</v>
       </c>
       <c r="L762" t="inlineStr">
         <is>
@@ -84171,7 +84171,7 @@
         </is>
       </c>
       <c r="N762" t="n">
-        <v>9.09</v>
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N762"/>
+  <dimension ref="A1:N767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40060,6 +40060,266 @@
       </c>
       <c r="N762" t="n">
         <v>8.67</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="D763" t="n">
+        <v>283.53</v>
+      </c>
+      <c r="E763" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="F763" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="G763" t="n">
+        <v>286.43</v>
+      </c>
+      <c r="H763" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="I763" t="n">
+        <v>291</v>
+      </c>
+      <c r="J763" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="K763" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N763" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>329</v>
+      </c>
+      <c r="D764" t="n">
+        <v>313.17</v>
+      </c>
+      <c r="E764" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="F764" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="G764" t="n">
+        <v>321.15</v>
+      </c>
+      <c r="H764" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="I764" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="J764" t="n">
+        <v>323.31</v>
+      </c>
+      <c r="K764" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N764" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>666.1</v>
+      </c>
+      <c r="D765" t="n">
+        <v>644.3200000000001</v>
+      </c>
+      <c r="E765" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="F765" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="G765" t="n">
+        <v>644.3200000000001</v>
+      </c>
+      <c r="H765" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="I765" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="J765" t="n">
+        <v>645.47</v>
+      </c>
+      <c r="K765" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N765" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>1081.15</v>
+      </c>
+      <c r="D766" t="n">
+        <v>1029.87</v>
+      </c>
+      <c r="E766" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="F766" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G766" t="n">
+        <v>1064.98</v>
+      </c>
+      <c r="H766" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="I766" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="J766" t="n">
+        <v>1072.47</v>
+      </c>
+      <c r="K766" t="n">
+        <v>-55.37</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N766" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D767" t="n">
+        <v>2301.62</v>
+      </c>
+      <c r="E767" t="n">
+        <v>198.38</v>
+      </c>
+      <c r="F767" t="n">
+        <v>2508.9</v>
+      </c>
+      <c r="G767" t="n">
+        <v>2388.74</v>
+      </c>
+      <c r="H767" t="n">
+        <v>120.16</v>
+      </c>
+      <c r="I767" t="n">
+        <v>2464.5</v>
+      </c>
+      <c r="J767" t="n">
+        <v>2416.47</v>
+      </c>
+      <c r="K767" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N767" t="n">
+        <v>8.619999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40073,7 +40333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44514,6 +44774,110 @@
       </c>
       <c r="N85" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>22847.6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-71.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>22561.6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>22633.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-71.5</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>55128.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>55128.4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>55201</v>
+      </c>
+      <c r="G87" t="n">
+        <v>55274.69</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-73.69</v>
+      </c>
+      <c r="I87" t="n">
+        <v>54834.75</v>
+      </c>
+      <c r="J87" t="n">
+        <v>54908.44</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-73.69</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -44527,7 +44891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N762"/>
+  <dimension ref="A1:N767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84174,6 +84538,266 @@
         <v>11.1</v>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="D763" t="n">
+        <v>289.65</v>
+      </c>
+      <c r="E763" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F763" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="G763" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="H763" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I763" t="n">
+        <v>291</v>
+      </c>
+      <c r="J763" t="n">
+        <v>292.32</v>
+      </c>
+      <c r="K763" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N763" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>329</v>
+      </c>
+      <c r="D764" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="E764" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="F764" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="G764" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="H764" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I764" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="J764" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="K764" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N764" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>666.1</v>
+      </c>
+      <c r="D765" t="n">
+        <v>660.8099999999999</v>
+      </c>
+      <c r="E765" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F765" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="G765" t="n">
+        <v>658.62</v>
+      </c>
+      <c r="H765" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="I765" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="J765" t="n">
+        <v>652.54</v>
+      </c>
+      <c r="K765" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N765" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>1081.15</v>
+      </c>
+      <c r="D766" t="n">
+        <v>1055.59</v>
+      </c>
+      <c r="E766" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="F766" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G766" t="n">
+        <v>1069.1</v>
+      </c>
+      <c r="H766" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I766" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="J766" t="n">
+        <v>1059.08</v>
+      </c>
+      <c r="K766" t="n">
+        <v>-41.98</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N766" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D767" t="n">
+        <v>2366.4</v>
+      </c>
+      <c r="E767" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="F767" t="n">
+        <v>2508.9</v>
+      </c>
+      <c r="G767" t="n">
+        <v>2477.8</v>
+      </c>
+      <c r="H767" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I767" t="n">
+        <v>2464.5</v>
+      </c>
+      <c r="J767" t="n">
+        <v>2444.55</v>
+      </c>
+      <c r="K767" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N767" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -40074,31 +40074,31 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>297.5</v>
+        <v>290</v>
       </c>
       <c r="D763" t="n">
         <v>283.53</v>
       </c>
       <c r="E763" t="n">
-        <v>13.97</v>
+        <v>6.47</v>
       </c>
       <c r="F763" t="n">
-        <v>297.85</v>
+        <v>294</v>
       </c>
       <c r="G763" t="n">
         <v>286.43</v>
       </c>
       <c r="H763" t="n">
-        <v>11.42</v>
+        <v>7.57</v>
       </c>
       <c r="I763" t="n">
-        <v>291</v>
+        <v>286.5</v>
       </c>
       <c r="J763" t="n">
         <v>289.45</v>
       </c>
       <c r="K763" t="n">
-        <v>1.55</v>
+        <v>-2.95</v>
       </c>
       <c r="L763" t="inlineStr">
         <is>
@@ -40107,11 +40107,11 @@
       </c>
       <c r="M763" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N763" t="n">
-        <v>4.93</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="764">
@@ -40126,31 +40126,31 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>329</v>
+        <v>320.8</v>
       </c>
       <c r="D764" t="n">
         <v>313.17</v>
       </c>
       <c r="E764" t="n">
-        <v>15.83</v>
+        <v>7.63</v>
       </c>
       <c r="F764" t="n">
-        <v>330.2</v>
+        <v>322.85</v>
       </c>
       <c r="G764" t="n">
         <v>321.15</v>
       </c>
       <c r="H764" t="n">
-        <v>9.050000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="I764" t="n">
-        <v>319.1</v>
+        <v>308.1</v>
       </c>
       <c r="J764" t="n">
         <v>323.31</v>
       </c>
       <c r="K764" t="n">
-        <v>-4.21</v>
+        <v>-15.21</v>
       </c>
       <c r="L764" t="inlineStr">
         <is>
@@ -40159,11 +40159,11 @@
       </c>
       <c r="M764" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N764" t="n">
-        <v>5.05</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="765">
@@ -40178,31 +40178,31 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>666.1</v>
+        <v>673</v>
       </c>
       <c r="D765" t="n">
         <v>644.3200000000001</v>
       </c>
       <c r="E765" t="n">
-        <v>21.78</v>
+        <v>28.68</v>
       </c>
       <c r="F765" t="n">
-        <v>675.5</v>
+        <v>676.5</v>
       </c>
       <c r="G765" t="n">
         <v>644.3200000000001</v>
       </c>
       <c r="H765" t="n">
-        <v>31.18</v>
+        <v>32.18</v>
       </c>
       <c r="I765" t="n">
-        <v>664.95</v>
+        <v>664</v>
       </c>
       <c r="J765" t="n">
         <v>645.47</v>
       </c>
       <c r="K765" t="n">
-        <v>19.48</v>
+        <v>18.53</v>
       </c>
       <c r="L765" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         </is>
       </c>
       <c r="N765" t="n">
-        <v>3.38</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="766">
@@ -40230,31 +40230,31 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>1081.15</v>
+        <v>1011.1</v>
       </c>
       <c r="D766" t="n">
         <v>1029.87</v>
       </c>
       <c r="E766" t="n">
-        <v>51.28</v>
+        <v>-18.77</v>
       </c>
       <c r="F766" t="n">
-        <v>1086</v>
+        <v>1018.9</v>
       </c>
       <c r="G766" t="n">
         <v>1064.98</v>
       </c>
       <c r="H766" t="n">
-        <v>21.02</v>
+        <v>-46.08</v>
       </c>
       <c r="I766" t="n">
-        <v>1017.1</v>
+        <v>987.9</v>
       </c>
       <c r="J766" t="n">
         <v>1072.47</v>
       </c>
       <c r="K766" t="n">
-        <v>-55.37</v>
+        <v>-84.56999999999999</v>
       </c>
       <c r="L766" t="inlineStr">
         <is>
@@ -40263,11 +40263,11 @@
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N766" t="n">
-        <v>4.98</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="767">
@@ -40282,31 +40282,31 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>2500</v>
+        <v>2479</v>
       </c>
       <c r="D767" t="n">
         <v>2301.62</v>
       </c>
       <c r="E767" t="n">
-        <v>198.38</v>
+        <v>177.38</v>
       </c>
       <c r="F767" t="n">
-        <v>2508.9</v>
+        <v>2539.3</v>
       </c>
       <c r="G767" t="n">
         <v>2388.74</v>
       </c>
       <c r="H767" t="n">
-        <v>120.16</v>
+        <v>150.56</v>
       </c>
       <c r="I767" t="n">
-        <v>2464.5</v>
+        <v>2464.7</v>
       </c>
       <c r="J767" t="n">
         <v>2416.47</v>
       </c>
       <c r="K767" t="n">
-        <v>48.03</v>
+        <v>48.23</v>
       </c>
       <c r="L767" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         </is>
       </c>
       <c r="N767" t="n">
-        <v>8.619999999999999</v>
+        <v>7.71</v>
       </c>
     </row>
   </sheetData>
@@ -44788,31 +44788,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>22776.1</v>
+        <v>22555.75</v>
       </c>
       <c r="D86" t="n">
         <v>22776.1</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>-220.35</v>
       </c>
       <c r="F86" t="n">
-        <v>22776.1</v>
+        <v>22621.8</v>
       </c>
       <c r="G86" t="n">
         <v>22847.6</v>
       </c>
       <c r="H86" t="n">
-        <v>-71.5</v>
+        <v>-225.8</v>
       </c>
       <c r="I86" t="n">
-        <v>22561.6</v>
+        <v>22397.1</v>
       </c>
       <c r="J86" t="n">
         <v>22633.1</v>
       </c>
       <c r="K86" t="n">
-        <v>-71.5</v>
+        <v>-236</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="87">
@@ -44840,31 +44840,31 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>55128.4</v>
+        <v>54714.1</v>
       </c>
       <c r="D87" t="n">
         <v>55128.4</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>-414.3</v>
       </c>
       <c r="F87" t="n">
-        <v>55201</v>
+        <v>55192.65</v>
       </c>
       <c r="G87" t="n">
         <v>55274.69</v>
       </c>
       <c r="H87" t="n">
-        <v>-73.69</v>
+        <v>-82.04000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>54834.75</v>
+        <v>54370.6</v>
       </c>
       <c r="J87" t="n">
         <v>54908.44</v>
       </c>
       <c r="K87" t="n">
-        <v>-73.69</v>
+        <v>-537.84</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -84550,31 +84550,31 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>297.5</v>
+        <v>290</v>
       </c>
       <c r="D763" t="n">
         <v>289.65</v>
       </c>
       <c r="E763" t="n">
-        <v>7.85</v>
+        <v>0.35</v>
       </c>
       <c r="F763" t="n">
-        <v>297.85</v>
+        <v>294</v>
       </c>
       <c r="G763" t="n">
         <v>293.05</v>
       </c>
       <c r="H763" t="n">
-        <v>4.8</v>
+        <v>0.95</v>
       </c>
       <c r="I763" t="n">
-        <v>291</v>
+        <v>286.5</v>
       </c>
       <c r="J763" t="n">
         <v>292.32</v>
       </c>
       <c r="K763" t="n">
-        <v>-1.32</v>
+        <v>-5.82</v>
       </c>
       <c r="L763" t="inlineStr">
         <is>
@@ -84587,7 +84587,7 @@
         </is>
       </c>
       <c r="N763" t="n">
-        <v>2.71</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="764">
@@ -84602,31 +84602,31 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>329</v>
+        <v>320.8</v>
       </c>
       <c r="D764" t="n">
         <v>321.68</v>
       </c>
       <c r="E764" t="n">
-        <v>7.32</v>
+        <v>-0.88</v>
       </c>
       <c r="F764" t="n">
-        <v>330.2</v>
+        <v>322.85</v>
       </c>
       <c r="G764" t="n">
         <v>325.78</v>
       </c>
       <c r="H764" t="n">
-        <v>4.42</v>
+        <v>-2.93</v>
       </c>
       <c r="I764" t="n">
-        <v>319.1</v>
+        <v>308.1</v>
       </c>
       <c r="J764" t="n">
         <v>321.93</v>
       </c>
       <c r="K764" t="n">
-        <v>-2.83</v>
+        <v>-13.83</v>
       </c>
       <c r="L764" t="inlineStr">
         <is>
@@ -84639,7 +84639,7 @@
         </is>
       </c>
       <c r="N764" t="n">
-        <v>2.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="765">
@@ -84654,31 +84654,31 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>666.1</v>
+        <v>673</v>
       </c>
       <c r="D765" t="n">
         <v>660.8099999999999</v>
       </c>
       <c r="E765" t="n">
-        <v>5.29</v>
+        <v>12.19</v>
       </c>
       <c r="F765" t="n">
-        <v>675.5</v>
+        <v>676.5</v>
       </c>
       <c r="G765" t="n">
         <v>658.62</v>
       </c>
       <c r="H765" t="n">
-        <v>16.88</v>
+        <v>17.88</v>
       </c>
       <c r="I765" t="n">
-        <v>664.95</v>
+        <v>664</v>
       </c>
       <c r="J765" t="n">
         <v>652.54</v>
       </c>
       <c r="K765" t="n">
-        <v>12.41</v>
+        <v>11.46</v>
       </c>
       <c r="L765" t="inlineStr">
         <is>
@@ -84691,7 +84691,7 @@
         </is>
       </c>
       <c r="N765" t="n">
-        <v>0.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="766">
@@ -84706,31 +84706,31 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>1081.15</v>
+        <v>1011.1</v>
       </c>
       <c r="D766" t="n">
         <v>1055.59</v>
       </c>
       <c r="E766" t="n">
-        <v>25.56</v>
+        <v>-44.49</v>
       </c>
       <c r="F766" t="n">
-        <v>1086</v>
+        <v>1018.9</v>
       </c>
       <c r="G766" t="n">
         <v>1069.1</v>
       </c>
       <c r="H766" t="n">
-        <v>16.9</v>
+        <v>-50.2</v>
       </c>
       <c r="I766" t="n">
-        <v>1017.1</v>
+        <v>987.9</v>
       </c>
       <c r="J766" t="n">
         <v>1059.08</v>
       </c>
       <c r="K766" t="n">
-        <v>-41.98</v>
+        <v>-71.18000000000001</v>
       </c>
       <c r="L766" t="inlineStr">
         <is>
@@ -84739,11 +84739,11 @@
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N766" t="n">
-        <v>2.42</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="767">
@@ -84758,31 +84758,31 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>2500</v>
+        <v>2479</v>
       </c>
       <c r="D767" t="n">
         <v>2366.4</v>
       </c>
       <c r="E767" t="n">
-        <v>133.6</v>
+        <v>112.6</v>
       </c>
       <c r="F767" t="n">
-        <v>2508.9</v>
+        <v>2539.3</v>
       </c>
       <c r="G767" t="n">
         <v>2477.8</v>
       </c>
       <c r="H767" t="n">
-        <v>31.1</v>
+        <v>61.5</v>
       </c>
       <c r="I767" t="n">
-        <v>2464.5</v>
+        <v>2464.7</v>
       </c>
       <c r="J767" t="n">
         <v>2444.55</v>
       </c>
       <c r="K767" t="n">
-        <v>19.95</v>
+        <v>20.15</v>
       </c>
       <c r="L767" t="inlineStr">
         <is>
@@ -84795,7 +84795,7 @@
         </is>
       </c>
       <c r="N767" t="n">
-        <v>5.65</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N767"/>
+  <dimension ref="A1:N770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40320,6 +40320,162 @@
       </c>
       <c r="N767" t="n">
         <v>7.71</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>328</v>
+      </c>
+      <c r="D768" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="E768" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="F768" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="G768" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="H768" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I768" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="J768" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="K768" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N768" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>297</v>
+      </c>
+      <c r="D769" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="E769" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="F769" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="G769" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="H769" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="I769" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="J769" t="n">
+        <v>289.16</v>
+      </c>
+      <c r="K769" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N769" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D770" t="n">
+        <v>2714.22</v>
+      </c>
+      <c r="E770" t="n">
+        <v>-214.22</v>
+      </c>
+      <c r="F770" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G770" t="n">
+        <v>2714.22</v>
+      </c>
+      <c r="H770" t="n">
+        <v>-184.22</v>
+      </c>
+      <c r="I770" t="n">
+        <v>2480.1</v>
+      </c>
+      <c r="J770" t="n">
+        <v>2413.41</v>
+      </c>
+      <c r="K770" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N770" t="n">
+        <v>7.89</v>
       </c>
     </row>
   </sheetData>
@@ -40333,7 +40489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44878,6 +45034,110 @@
       </c>
       <c r="N87" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>22603.05</v>
+      </c>
+      <c r="D88" t="n">
+        <v>22603.05</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>22717.65</v>
+      </c>
+      <c r="G88" t="n">
+        <v>22698.36</v>
+      </c>
+      <c r="H88" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="I88" t="n">
+        <v>22546.3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>22527.01</v>
+      </c>
+      <c r="K88" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>55055.55</v>
+      </c>
+      <c r="D89" t="n">
+        <v>55055.55</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>55340.7</v>
+      </c>
+      <c r="G89" t="n">
+        <v>55385.44</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-44.74</v>
+      </c>
+      <c r="I89" t="n">
+        <v>54636.2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>54680.94</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-44.74</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -44891,7 +45151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N767"/>
+  <dimension ref="A1:N770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84798,6 +85058,162 @@
         <v>4.76</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>328</v>
+      </c>
+      <c r="D768" t="n">
+        <v>348.18</v>
+      </c>
+      <c r="E768" t="n">
+        <v>-20.18</v>
+      </c>
+      <c r="F768" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="G768" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="H768" t="n">
+        <v>-11.27</v>
+      </c>
+      <c r="I768" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="J768" t="n">
+        <v>319.69</v>
+      </c>
+      <c r="K768" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N768" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>297</v>
+      </c>
+      <c r="D769" t="n">
+        <v>312.78</v>
+      </c>
+      <c r="E769" t="n">
+        <v>-15.78</v>
+      </c>
+      <c r="F769" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="G769" t="n">
+        <v>309.54</v>
+      </c>
+      <c r="H769" t="n">
+        <v>-9.94</v>
+      </c>
+      <c r="I769" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="J769" t="n">
+        <v>290.89</v>
+      </c>
+      <c r="K769" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N769" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D770" t="n">
+        <v>2789.2</v>
+      </c>
+      <c r="E770" t="n">
+        <v>-289.2</v>
+      </c>
+      <c r="F770" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G770" t="n">
+        <v>2620.65</v>
+      </c>
+      <c r="H770" t="n">
+        <v>-90.65000000000001</v>
+      </c>
+      <c r="I770" t="n">
+        <v>2480.1</v>
+      </c>
+      <c r="J770" t="n">
+        <v>2437.44</v>
+      </c>
+      <c r="K770" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N770" t="n">
+        <v>10.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -40334,31 +40334,31 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D768" t="n">
         <v>338.67</v>
       </c>
       <c r="E768" t="n">
-        <v>-10.67</v>
+        <v>-9.67</v>
       </c>
       <c r="F768" t="n">
-        <v>332.7</v>
+        <v>330.2</v>
       </c>
       <c r="G768" t="n">
         <v>338.67</v>
       </c>
       <c r="H768" t="n">
-        <v>-5.97</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I768" t="n">
-        <v>324.6</v>
+        <v>319.1</v>
       </c>
       <c r="J768" t="n">
         <v>320.57</v>
       </c>
       <c r="K768" t="n">
-        <v>4.03</v>
+        <v>-1.47</v>
       </c>
       <c r="L768" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         </is>
       </c>
       <c r="N768" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="769">
@@ -40386,31 +40386,31 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>297</v>
+        <v>297.5</v>
       </c>
       <c r="D769" t="n">
         <v>306.21</v>
       </c>
       <c r="E769" t="n">
-        <v>-9.210000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="F769" t="n">
-        <v>299.6</v>
+        <v>297.85</v>
       </c>
       <c r="G769" t="n">
         <v>306.21</v>
       </c>
       <c r="H769" t="n">
-        <v>-6.61</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I769" t="n">
-        <v>294.25</v>
+        <v>291</v>
       </c>
       <c r="J769" t="n">
         <v>289.16</v>
       </c>
       <c r="K769" t="n">
-        <v>5.09</v>
+        <v>1.84</v>
       </c>
       <c r="L769" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         </is>
       </c>
       <c r="N769" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="770">
@@ -45048,31 +45048,31 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>22603.05</v>
+        <v>22776.1</v>
       </c>
       <c r="D88" t="n">
         <v>22603.05</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>173.05</v>
       </c>
       <c r="F88" t="n">
-        <v>22717.65</v>
+        <v>22776.1</v>
       </c>
       <c r="G88" t="n">
         <v>22698.36</v>
       </c>
       <c r="H88" t="n">
-        <v>19.29</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>22546.3</v>
+        <v>22561.6</v>
       </c>
       <c r="J88" t="n">
         <v>22527.01</v>
       </c>
       <c r="K88" t="n">
-        <v>19.29</v>
+        <v>34.59</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="89">
@@ -45100,31 +45100,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>55055.55</v>
+        <v>55128.4</v>
       </c>
       <c r="D89" t="n">
         <v>55055.55</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>55340.7</v>
+        <v>55201</v>
       </c>
       <c r="G89" t="n">
         <v>55385.44</v>
       </c>
       <c r="H89" t="n">
-        <v>-44.74</v>
+        <v>-184.44</v>
       </c>
       <c r="I89" t="n">
-        <v>54636.2</v>
+        <v>54834.75</v>
       </c>
       <c r="J89" t="n">
         <v>54680.94</v>
       </c>
       <c r="K89" t="n">
-        <v>-44.74</v>
+        <v>153.81</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -85070,31 +85070,31 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D768" t="n">
         <v>348.18</v>
       </c>
       <c r="E768" t="n">
-        <v>-20.18</v>
+        <v>-19.18</v>
       </c>
       <c r="F768" t="n">
-        <v>332.7</v>
+        <v>330.2</v>
       </c>
       <c r="G768" t="n">
         <v>343.97</v>
       </c>
       <c r="H768" t="n">
-        <v>-11.27</v>
+        <v>-13.77</v>
       </c>
       <c r="I768" t="n">
-        <v>324.6</v>
+        <v>319.1</v>
       </c>
       <c r="J768" t="n">
         <v>319.69</v>
       </c>
       <c r="K768" t="n">
-        <v>4.91</v>
+        <v>-0.59</v>
       </c>
       <c r="L768" t="inlineStr">
         <is>
@@ -85107,7 +85107,7 @@
         </is>
       </c>
       <c r="N768" t="n">
-        <v>5.8</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="769">
@@ -85122,31 +85122,31 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>297</v>
+        <v>297.5</v>
       </c>
       <c r="D769" t="n">
         <v>312.78</v>
       </c>
       <c r="E769" t="n">
-        <v>-15.78</v>
+        <v>-15.28</v>
       </c>
       <c r="F769" t="n">
-        <v>299.6</v>
+        <v>297.85</v>
       </c>
       <c r="G769" t="n">
         <v>309.54</v>
       </c>
       <c r="H769" t="n">
-        <v>-9.94</v>
+        <v>-11.69</v>
       </c>
       <c r="I769" t="n">
-        <v>294.25</v>
+        <v>291</v>
       </c>
       <c r="J769" t="n">
         <v>290.89</v>
       </c>
       <c r="K769" t="n">
-        <v>3.36</v>
+        <v>0.11</v>
       </c>
       <c r="L769" t="inlineStr">
         <is>
@@ -85159,7 +85159,7 @@
         </is>
       </c>
       <c r="N769" t="n">
-        <v>5.05</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="770">

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N770"/>
+  <dimension ref="A1:N771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40476,6 +40476,58 @@
       </c>
       <c r="N770" t="n">
         <v>7.89</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="D771" t="n">
+        <v>282.54</v>
+      </c>
+      <c r="E771" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="F771" t="n">
+        <v>296.95</v>
+      </c>
+      <c r="G771" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="H771" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I771" t="n">
+        <v>288</v>
+      </c>
+      <c r="J771" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="K771" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N771" t="n">
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -40489,7 +40541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45138,6 +45190,110 @@
       </c>
       <c r="N89" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>22231.8</v>
+      </c>
+      <c r="D90" t="n">
+        <v>22231.8</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>22599.05</v>
+      </c>
+      <c r="G90" t="n">
+        <v>22493.94</v>
+      </c>
+      <c r="H90" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="I90" t="n">
+        <v>22179.9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>22074.79</v>
+      </c>
+      <c r="K90" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>54515.05</v>
+      </c>
+      <c r="D91" t="n">
+        <v>54515.05</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>55043</v>
+      </c>
+      <c r="G91" t="n">
+        <v>54910.99</v>
+      </c>
+      <c r="H91" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="I91" t="n">
+        <v>54383.15</v>
+      </c>
+      <c r="J91" t="n">
+        <v>54251.14</v>
+      </c>
+      <c r="K91" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -45151,7 +45307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N770"/>
+  <dimension ref="A1:N771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85214,6 +85370,58 @@
         <v>10.37</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="D771" t="n">
+        <v>288.66</v>
+      </c>
+      <c r="E771" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F771" t="n">
+        <v>296.95</v>
+      </c>
+      <c r="G771" t="n">
+        <v>287.99</v>
+      </c>
+      <c r="H771" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I771" t="n">
+        <v>288</v>
+      </c>
+      <c r="J771" t="n">
+        <v>287.29</v>
+      </c>
+      <c r="K771" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N771" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -45204,31 +45204,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>22231.8</v>
+        <v>22603.05</v>
       </c>
       <c r="D90" t="n">
         <v>22231.8</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>371.25</v>
       </c>
       <c r="F90" t="n">
-        <v>22599.05</v>
+        <v>22717.65</v>
       </c>
       <c r="G90" t="n">
         <v>22493.94</v>
       </c>
       <c r="H90" t="n">
-        <v>105.11</v>
+        <v>223.71</v>
       </c>
       <c r="I90" t="n">
-        <v>22179.9</v>
+        <v>22546.3</v>
       </c>
       <c r="J90" t="n">
         <v>22074.79</v>
       </c>
       <c r="K90" t="n">
-        <v>105.11</v>
+        <v>471.51</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="91">
@@ -45256,31 +45256,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>54515.05</v>
+        <v>55055.55</v>
       </c>
       <c r="D91" t="n">
         <v>54515.05</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>540.5</v>
       </c>
       <c r="F91" t="n">
-        <v>55043</v>
+        <v>55340.7</v>
       </c>
       <c r="G91" t="n">
         <v>54910.99</v>
       </c>
       <c r="H91" t="n">
-        <v>132.01</v>
+        <v>429.71</v>
       </c>
       <c r="I91" t="n">
-        <v>54383.15</v>
+        <v>54636.2</v>
       </c>
       <c r="J91" t="n">
         <v>54251.14</v>
       </c>
       <c r="K91" t="n">
-        <v>132.01</v>
+        <v>385.06</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N771"/>
+  <dimension ref="A1:N772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40528,6 +40528,58 @@
       </c>
       <c r="N771" t="n">
         <v>2.11</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D772" t="n">
+        <v>300.03</v>
+      </c>
+      <c r="E772" t="n">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="F772" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G772" t="n">
+        <v>300.03</v>
+      </c>
+      <c r="H772" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="I772" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J772" t="n">
+        <v>284.73</v>
+      </c>
+      <c r="K772" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N772" t="n">
+        <v>2.84</v>
       </c>
     </row>
   </sheetData>
@@ -40541,7 +40593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45294,6 +45346,110 @@
       </c>
       <c r="N91" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="D92" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>22580.75</v>
+      </c>
+      <c r="G92" t="n">
+        <v>22635.89</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-55.14</v>
+      </c>
+      <c r="I92" t="n">
+        <v>22294.75</v>
+      </c>
+      <c r="J92" t="n">
+        <v>22349.89</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-55.14</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>55256.65</v>
+      </c>
+      <c r="D93" t="n">
+        <v>55256.65</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>55419.3</v>
+      </c>
+      <c r="G93" t="n">
+        <v>55578.24</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-158.94</v>
+      </c>
+      <c r="I93" t="n">
+        <v>54617.2</v>
+      </c>
+      <c r="J93" t="n">
+        <v>54776.14</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-158.94</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -45307,7 +45463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N771"/>
+  <dimension ref="A1:N772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85422,6 +85578,58 @@
         <v>0.06</v>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D772" t="n">
+        <v>306.93</v>
+      </c>
+      <c r="E772" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="F772" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G772" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="H772" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="I772" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J772" t="n">
+        <v>287.19</v>
+      </c>
+      <c r="K772" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N772" t="n">
+        <v>5.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -40542,31 +40542,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>291.5</v>
+        <v>288.5</v>
       </c>
       <c r="D772" t="n">
         <v>300.03</v>
       </c>
       <c r="E772" t="n">
-        <v>-8.529999999999999</v>
+        <v>-11.53</v>
       </c>
       <c r="F772" t="n">
-        <v>295.45</v>
+        <v>296.95</v>
       </c>
       <c r="G772" t="n">
         <v>300.03</v>
       </c>
       <c r="H772" t="n">
-        <v>-4.58</v>
+        <v>-3.08</v>
       </c>
       <c r="I772" t="n">
-        <v>289.15</v>
+        <v>288</v>
       </c>
       <c r="J772" t="n">
         <v>284.73</v>
       </c>
       <c r="K772" t="n">
-        <v>4.42</v>
+        <v>3.27</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="N772" t="n">
-        <v>2.84</v>
+        <v>3.84</v>
       </c>
     </row>
   </sheetData>
@@ -45360,31 +45360,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>22520.45</v>
+        <v>22231.8</v>
       </c>
       <c r="D92" t="n">
         <v>22520.45</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>-288.65</v>
       </c>
       <c r="F92" t="n">
-        <v>22580.75</v>
+        <v>22599.05</v>
       </c>
       <c r="G92" t="n">
         <v>22635.89</v>
       </c>
       <c r="H92" t="n">
-        <v>-55.14</v>
+        <v>-36.84</v>
       </c>
       <c r="I92" t="n">
-        <v>22294.75</v>
+        <v>22179.9</v>
       </c>
       <c r="J92" t="n">
         <v>22349.89</v>
       </c>
       <c r="K92" t="n">
-        <v>-55.14</v>
+        <v>-169.99</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="93">
@@ -45412,31 +45412,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>55256.65</v>
+        <v>54515.05</v>
       </c>
       <c r="D93" t="n">
         <v>55256.65</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>-741.6</v>
       </c>
       <c r="F93" t="n">
-        <v>55419.3</v>
+        <v>55043</v>
       </c>
       <c r="G93" t="n">
         <v>55578.24</v>
       </c>
       <c r="H93" t="n">
-        <v>-158.94</v>
+        <v>-535.24</v>
       </c>
       <c r="I93" t="n">
-        <v>54617.2</v>
+        <v>54383.15</v>
       </c>
       <c r="J93" t="n">
         <v>54776.14</v>
       </c>
       <c r="K93" t="n">
-        <v>-158.94</v>
+        <v>-392.99</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
@@ -85590,31 +85590,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>291.5</v>
+        <v>288.5</v>
       </c>
       <c r="D772" t="n">
         <v>306.93</v>
       </c>
       <c r="E772" t="n">
-        <v>-15.43</v>
+        <v>-18.43</v>
       </c>
       <c r="F772" t="n">
-        <v>295.45</v>
+        <v>296.95</v>
       </c>
       <c r="G772" t="n">
         <v>304.03</v>
       </c>
       <c r="H772" t="n">
-        <v>-8.58</v>
+        <v>-7.08</v>
       </c>
       <c r="I772" t="n">
-        <v>289.15</v>
+        <v>288</v>
       </c>
       <c r="J772" t="n">
         <v>287.19</v>
       </c>
       <c r="K772" t="n">
-        <v>1.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -85627,7 +85627,7 @@
         </is>
       </c>
       <c r="N772" t="n">
-        <v>5.03</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -40542,31 +40542,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>288.5</v>
+        <v>291.5</v>
       </c>
       <c r="D772" t="n">
-        <v>300.03</v>
+        <v>282.54</v>
       </c>
       <c r="E772" t="n">
-        <v>-11.53</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>296.95</v>
+        <v>295.45</v>
       </c>
       <c r="G772" t="n">
-        <v>300.03</v>
+        <v>287.22</v>
       </c>
       <c r="H772" t="n">
-        <v>-3.08</v>
+        <v>8.23</v>
       </c>
       <c r="I772" t="n">
-        <v>288</v>
+        <v>289.15</v>
       </c>
       <c r="J772" t="n">
-        <v>284.73</v>
+        <v>281.63</v>
       </c>
       <c r="K772" t="n">
-        <v>3.27</v>
+        <v>7.52</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -40575,11 +40575,11 @@
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N772" t="n">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
     </row>
   </sheetData>
@@ -45360,31 +45360,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>22231.8</v>
+        <v>22520.45</v>
       </c>
       <c r="D92" t="n">
         <v>22520.45</v>
       </c>
       <c r="E92" t="n">
-        <v>-288.65</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>22599.05</v>
+        <v>22580.75</v>
       </c>
       <c r="G92" t="n">
         <v>22635.89</v>
       </c>
       <c r="H92" t="n">
-        <v>-36.84</v>
+        <v>-55.14</v>
       </c>
       <c r="I92" t="n">
-        <v>22179.9</v>
+        <v>22294.75</v>
       </c>
       <c r="J92" t="n">
         <v>22349.89</v>
       </c>
       <c r="K92" t="n">
-        <v>-169.99</v>
+        <v>-55.14</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -45412,31 +45412,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>54515.05</v>
+        <v>55256.65</v>
       </c>
       <c r="D93" t="n">
         <v>55256.65</v>
       </c>
       <c r="E93" t="n">
-        <v>-741.6</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>55043</v>
+        <v>55419.3</v>
       </c>
       <c r="G93" t="n">
         <v>55578.24</v>
       </c>
       <c r="H93" t="n">
-        <v>-535.24</v>
+        <v>-158.94</v>
       </c>
       <c r="I93" t="n">
-        <v>54383.15</v>
+        <v>54617.2</v>
       </c>
       <c r="J93" t="n">
         <v>54776.14</v>
       </c>
       <c r="K93" t="n">
-        <v>-392.99</v>
+        <v>-158.94</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -85590,31 +85590,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>288.5</v>
+        <v>291.5</v>
       </c>
       <c r="D772" t="n">
-        <v>306.93</v>
+        <v>288.99</v>
       </c>
       <c r="E772" t="n">
-        <v>-18.43</v>
+        <v>2.51</v>
       </c>
       <c r="F772" t="n">
-        <v>296.95</v>
+        <v>295.45</v>
       </c>
       <c r="G772" t="n">
-        <v>304.03</v>
+        <v>293.14</v>
       </c>
       <c r="H772" t="n">
-        <v>-7.08</v>
+        <v>2.31</v>
       </c>
       <c r="I772" t="n">
-        <v>288</v>
+        <v>289.15</v>
       </c>
       <c r="J772" t="n">
-        <v>287.19</v>
+        <v>284.01</v>
       </c>
       <c r="K772" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.14</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -85623,11 +85623,11 @@
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N772" t="n">
-        <v>6</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N772"/>
+  <dimension ref="A1:N774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40580,6 +40580,110 @@
       </c>
       <c r="N772" t="n">
         <v>3.17</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>441</v>
+      </c>
+      <c r="D773" t="n">
+        <v>450.22</v>
+      </c>
+      <c r="E773" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="F773" t="n">
+        <v>445.25</v>
+      </c>
+      <c r="G773" t="n">
+        <v>450.22</v>
+      </c>
+      <c r="H773" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="I773" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="J773" t="n">
+        <v>430.76</v>
+      </c>
+      <c r="K773" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N773" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D774" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="E774" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="F774" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G774" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="H774" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I774" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J774" t="n">
+        <v>283.47</v>
+      </c>
+      <c r="K774" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N774" t="n">
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>
@@ -40593,7 +40697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N93"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45450,6 +45554,110 @@
       </c>
       <c r="N93" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="D94" t="n">
+        <v>22400</v>
+      </c>
+      <c r="E94" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="F94" t="n">
+        <v>22580.75</v>
+      </c>
+      <c r="G94" t="n">
+        <v>22583.29</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="I94" t="n">
+        <v>22294.75</v>
+      </c>
+      <c r="J94" t="n">
+        <v>22284.54</v>
+      </c>
+      <c r="K94" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>55256.65</v>
+      </c>
+      <c r="D95" t="n">
+        <v>54904.05</v>
+      </c>
+      <c r="E95" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>55419.3</v>
+      </c>
+      <c r="G95" t="n">
+        <v>55310.65</v>
+      </c>
+      <c r="H95" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="I95" t="n">
+        <v>54617.2</v>
+      </c>
+      <c r="J95" t="n">
+        <v>54603.25</v>
+      </c>
+      <c r="K95" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -45463,7 +45671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N772"/>
+  <dimension ref="A1:N774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85630,6 +85838,110 @@
         <v>0.87</v>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>441</v>
+      </c>
+      <c r="D773" t="n">
+        <v>461.54</v>
+      </c>
+      <c r="E773" t="n">
+        <v>-20.54</v>
+      </c>
+      <c r="F773" t="n">
+        <v>445.25</v>
+      </c>
+      <c r="G773" t="n">
+        <v>457.73</v>
+      </c>
+      <c r="H773" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="I773" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="J773" t="n">
+        <v>435.19</v>
+      </c>
+      <c r="K773" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N773" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D774" t="n">
+        <v>307.44</v>
+      </c>
+      <c r="E774" t="n">
+        <v>-15.94</v>
+      </c>
+      <c r="F774" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G774" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="H774" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="I774" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J774" t="n">
+        <v>285.84</v>
+      </c>
+      <c r="K774" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N774" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -45568,31 +45568,31 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>22520.45</v>
+        <v>22363.35</v>
       </c>
       <c r="D94" t="n">
         <v>22400</v>
       </c>
       <c r="E94" t="n">
-        <v>120.45</v>
+        <v>-36.65</v>
       </c>
       <c r="F94" t="n">
-        <v>22580.75</v>
+        <v>22651.1</v>
       </c>
       <c r="G94" t="n">
         <v>22583.29</v>
       </c>
       <c r="H94" t="n">
-        <v>-2.54</v>
+        <v>67.81</v>
       </c>
       <c r="I94" t="n">
-        <v>22294.75</v>
+        <v>22304.45</v>
       </c>
       <c r="J94" t="n">
         <v>22284.54</v>
       </c>
       <c r="K94" t="n">
-        <v>10.21</v>
+        <v>19.91</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="95">
@@ -45620,31 +45620,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>55256.65</v>
+        <v>54918</v>
       </c>
       <c r="D95" t="n">
         <v>54904.05</v>
       </c>
       <c r="E95" t="n">
-        <v>352.6</v>
+        <v>13.95</v>
       </c>
       <c r="F95" t="n">
-        <v>55419.3</v>
+        <v>55416.45</v>
       </c>
       <c r="G95" t="n">
         <v>55310.65</v>
       </c>
       <c r="H95" t="n">
-        <v>108.65</v>
+        <v>105.8</v>
       </c>
       <c r="I95" t="n">
-        <v>54617.2</v>
+        <v>54708.8</v>
       </c>
       <c r="J95" t="n">
         <v>54603.25</v>
       </c>
       <c r="K95" t="n">
-        <v>13.95</v>
+        <v>105.55</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0.64</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N774"/>
+  <dimension ref="A1:N777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40684,6 +40684,162 @@
       </c>
       <c r="N774" t="n">
         <v>3.08</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D775" t="n">
+        <v>2135.91</v>
+      </c>
+      <c r="E775" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="F775" t="n">
+        <v>2188.7</v>
+      </c>
+      <c r="G775" t="n">
+        <v>2209.02</v>
+      </c>
+      <c r="H775" t="n">
+        <v>-20.32</v>
+      </c>
+      <c r="I775" t="n">
+        <v>2130.5</v>
+      </c>
+      <c r="J775" t="n">
+        <v>2185</v>
+      </c>
+      <c r="K775" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N775" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>290</v>
+      </c>
+      <c r="D776" t="n">
+        <v>283.33</v>
+      </c>
+      <c r="E776" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F776" t="n">
+        <v>291.35</v>
+      </c>
+      <c r="G776" t="n">
+        <v>287.59</v>
+      </c>
+      <c r="H776" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I776" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="J776" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="K776" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N776" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>439</v>
+      </c>
+      <c r="D777" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="E777" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="F777" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="G777" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="H777" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I777" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="J777" t="n">
+        <v>428.79</v>
+      </c>
+      <c r="K777" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N777" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -40697,7 +40853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45658,6 +45814,110 @@
       </c>
       <c r="N95" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="D96" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="G96" t="n">
+        <v>22866.45</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-144.5</v>
+      </c>
+      <c r="I96" t="n">
+        <v>22288.45</v>
+      </c>
+      <c r="J96" t="n">
+        <v>22432.95</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-144.5</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>55481.05</v>
+      </c>
+      <c r="D97" t="n">
+        <v>55481.05</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>55551.75</v>
+      </c>
+      <c r="G97" t="n">
+        <v>55776.55</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-224.8</v>
+      </c>
+      <c r="I97" t="n">
+        <v>54735.95</v>
+      </c>
+      <c r="J97" t="n">
+        <v>54960.75</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-224.8</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -45671,7 +45931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N774"/>
+  <dimension ref="A1:N777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85942,6 +86202,162 @@
         <v>5.18</v>
       </c>
     </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D775" t="n">
+        <v>2196.65</v>
+      </c>
+      <c r="E775" t="n">
+        <v>-11.65</v>
+      </c>
+      <c r="F775" t="n">
+        <v>2188.7</v>
+      </c>
+      <c r="G775" t="n">
+        <v>2224.62</v>
+      </c>
+      <c r="H775" t="n">
+        <v>-35.92</v>
+      </c>
+      <c r="I775" t="n">
+        <v>2130.5</v>
+      </c>
+      <c r="J775" t="n">
+        <v>2147.52</v>
+      </c>
+      <c r="K775" t="n">
+        <v>-17.02</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N775" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>290</v>
+      </c>
+      <c r="D776" t="n">
+        <v>289.52</v>
+      </c>
+      <c r="E776" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F776" t="n">
+        <v>291.35</v>
+      </c>
+      <c r="G776" t="n">
+        <v>293.01</v>
+      </c>
+      <c r="H776" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="I776" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="J776" t="n">
+        <v>286.76</v>
+      </c>
+      <c r="K776" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N776" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>439</v>
+      </c>
+      <c r="D777" t="n">
+        <v>444.29</v>
+      </c>
+      <c r="E777" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="F777" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="G777" t="n">
+        <v>444.87</v>
+      </c>
+      <c r="H777" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="I777" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="J777" t="n">
+        <v>433.08</v>
+      </c>
+      <c r="K777" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N777" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -40698,31 +40698,31 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>2185</v>
+        <v>2157.4</v>
       </c>
       <c r="D775" t="n">
         <v>2135.91</v>
       </c>
       <c r="E775" t="n">
-        <v>49.09</v>
+        <v>21.49</v>
       </c>
       <c r="F775" t="n">
-        <v>2188.7</v>
+        <v>2170</v>
       </c>
       <c r="G775" t="n">
         <v>2209.02</v>
       </c>
       <c r="H775" t="n">
-        <v>-20.32</v>
+        <v>-39.02</v>
       </c>
       <c r="I775" t="n">
-        <v>2130.5</v>
+        <v>2109.4</v>
       </c>
       <c r="J775" t="n">
         <v>2185</v>
       </c>
       <c r="K775" t="n">
-        <v>-54.5</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="L775" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         </is>
       </c>
       <c r="N775" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="776">
@@ -40750,31 +40750,31 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>290</v>
+        <v>290.5</v>
       </c>
       <c r="D776" t="n">
         <v>283.33</v>
       </c>
       <c r="E776" t="n">
-        <v>6.67</v>
+        <v>7.17</v>
       </c>
       <c r="F776" t="n">
-        <v>291.35</v>
+        <v>294.05</v>
       </c>
       <c r="G776" t="n">
         <v>287.59</v>
       </c>
       <c r="H776" t="n">
-        <v>3.76</v>
+        <v>6.46</v>
       </c>
       <c r="I776" t="n">
-        <v>288.15</v>
+        <v>288.5</v>
       </c>
       <c r="J776" t="n">
         <v>284.6</v>
       </c>
       <c r="K776" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="L776" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         </is>
       </c>
       <c r="N776" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="777">
@@ -40802,31 +40802,31 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>439</v>
+        <v>443.4</v>
       </c>
       <c r="D777" t="n">
         <v>433.45</v>
       </c>
       <c r="E777" t="n">
-        <v>5.55</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F777" t="n">
-        <v>443.35</v>
+        <v>443.65</v>
       </c>
       <c r="G777" t="n">
         <v>433.45</v>
       </c>
       <c r="H777" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="I777" t="n">
-        <v>437.5</v>
+        <v>438.9</v>
       </c>
       <c r="J777" t="n">
         <v>428.79</v>
       </c>
       <c r="K777" t="n">
-        <v>8.710000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="L777" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="N777" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -45828,31 +45828,31 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>22721.95</v>
+        <v>22363.35</v>
       </c>
       <c r="D96" t="n">
         <v>22721.95</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>-358.6</v>
       </c>
       <c r="F96" t="n">
-        <v>22721.95</v>
+        <v>22651.1</v>
       </c>
       <c r="G96" t="n">
         <v>22866.45</v>
       </c>
       <c r="H96" t="n">
-        <v>-144.5</v>
+        <v>-215.35</v>
       </c>
       <c r="I96" t="n">
-        <v>22288.45</v>
+        <v>22304.45</v>
       </c>
       <c r="J96" t="n">
         <v>22432.95</v>
       </c>
       <c r="K96" t="n">
-        <v>-144.5</v>
+        <v>-128.5</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="97">
@@ -45880,31 +45880,31 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>55481.05</v>
+        <v>54918</v>
       </c>
       <c r="D97" t="n">
         <v>55481.05</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>-563.05</v>
       </c>
       <c r="F97" t="n">
-        <v>55551.75</v>
+        <v>55416.45</v>
       </c>
       <c r="G97" t="n">
         <v>55776.55</v>
       </c>
       <c r="H97" t="n">
-        <v>-224.8</v>
+        <v>-360.1</v>
       </c>
       <c r="I97" t="n">
-        <v>54735.95</v>
+        <v>54708.8</v>
       </c>
       <c r="J97" t="n">
         <v>54960.75</v>
       </c>
       <c r="K97" t="n">
-        <v>-224.8</v>
+        <v>-251.95</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -86214,31 +86214,31 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>2185</v>
+        <v>2157.4</v>
       </c>
       <c r="D775" t="n">
         <v>2196.65</v>
       </c>
       <c r="E775" t="n">
-        <v>-11.65</v>
+        <v>-39.25</v>
       </c>
       <c r="F775" t="n">
-        <v>2188.7</v>
+        <v>2170</v>
       </c>
       <c r="G775" t="n">
         <v>2224.62</v>
       </c>
       <c r="H775" t="n">
-        <v>-35.92</v>
+        <v>-54.62</v>
       </c>
       <c r="I775" t="n">
-        <v>2130.5</v>
+        <v>2109.4</v>
       </c>
       <c r="J775" t="n">
         <v>2147.52</v>
       </c>
       <c r="K775" t="n">
-        <v>-17.02</v>
+        <v>-38.12</v>
       </c>
       <c r="L775" t="inlineStr">
         <is>
@@ -86251,7 +86251,7 @@
         </is>
       </c>
       <c r="N775" t="n">
-        <v>0.53</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="776">
@@ -86266,31 +86266,31 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>290</v>
+        <v>290.5</v>
       </c>
       <c r="D776" t="n">
         <v>289.52</v>
       </c>
       <c r="E776" t="n">
-        <v>0.48</v>
+        <v>0.98</v>
       </c>
       <c r="F776" t="n">
-        <v>291.35</v>
+        <v>294.05</v>
       </c>
       <c r="G776" t="n">
         <v>293.01</v>
       </c>
       <c r="H776" t="n">
-        <v>-1.66</v>
+        <v>1.04</v>
       </c>
       <c r="I776" t="n">
-        <v>288.15</v>
+        <v>288.5</v>
       </c>
       <c r="J776" t="n">
         <v>286.76</v>
       </c>
       <c r="K776" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="L776" t="inlineStr">
         <is>
@@ -86303,7 +86303,7 @@
         </is>
       </c>
       <c r="N776" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="777">
@@ -86318,31 +86318,31 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>439</v>
+        <v>443.4</v>
       </c>
       <c r="D777" t="n">
         <v>444.29</v>
       </c>
       <c r="E777" t="n">
-        <v>-5.29</v>
+        <v>-0.89</v>
       </c>
       <c r="F777" t="n">
-        <v>443.35</v>
+        <v>443.65</v>
       </c>
       <c r="G777" t="n">
         <v>444.87</v>
       </c>
       <c r="H777" t="n">
-        <v>-1.52</v>
+        <v>-1.22</v>
       </c>
       <c r="I777" t="n">
-        <v>437.5</v>
+        <v>438.9</v>
       </c>
       <c r="J777" t="n">
         <v>433.08</v>
       </c>
       <c r="K777" t="n">
-        <v>4.42</v>
+        <v>5.82</v>
       </c>
       <c r="L777" t="inlineStr">
         <is>
@@ -86355,7 +86355,7 @@
         </is>
       </c>
       <c r="N777" t="n">
-        <v>1.19</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N777"/>
+  <dimension ref="A1:N780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40840,6 +40840,162 @@
       </c>
       <c r="N777" t="n">
         <v>2.3</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="D778" t="n">
+        <v>302.76</v>
+      </c>
+      <c r="E778" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="F778" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="G778" t="n">
+        <v>302.76</v>
+      </c>
+      <c r="H778" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="I778" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="J778" t="n">
+        <v>290.92</v>
+      </c>
+      <c r="K778" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N778" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>5898</v>
+      </c>
+      <c r="D779" t="n">
+        <v>5989.53</v>
+      </c>
+      <c r="E779" t="n">
+        <v>-91.53</v>
+      </c>
+      <c r="F779" t="n">
+        <v>6078</v>
+      </c>
+      <c r="G779" t="n">
+        <v>6000.96</v>
+      </c>
+      <c r="H779" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="I779" t="n">
+        <v>5882.5</v>
+      </c>
+      <c r="J779" t="n">
+        <v>5822.94</v>
+      </c>
+      <c r="K779" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N779" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>438.05</v>
+      </c>
+      <c r="D780" t="n">
+        <v>451.69</v>
+      </c>
+      <c r="E780" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="F780" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="G780" t="n">
+        <v>451.69</v>
+      </c>
+      <c r="H780" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="I780" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="J780" t="n">
+        <v>427.29</v>
+      </c>
+      <c r="K780" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N780" t="n">
+        <v>3.02</v>
       </c>
     </row>
   </sheetData>
@@ -40853,7 +41009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45918,6 +46074,110 @@
       </c>
       <c r="N97" t="n">
         <v>1.01</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>22757.95</v>
+      </c>
+      <c r="G98" t="n">
+        <v>22734.11</v>
+      </c>
+      <c r="H98" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="I98" t="n">
+        <v>22558.95</v>
+      </c>
+      <c r="J98" t="n">
+        <v>22535.11</v>
+      </c>
+      <c r="K98" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>55316</v>
+      </c>
+      <c r="D99" t="n">
+        <v>55316</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>55644.7</v>
+      </c>
+      <c r="G99" t="n">
+        <v>55584.4</v>
+      </c>
+      <c r="H99" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>55168.2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>55107.9</v>
+      </c>
+      <c r="K99" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -45931,7 +46191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N777"/>
+  <dimension ref="A1:N780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86358,6 +86618,162 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="D778" t="n">
+        <v>308.82</v>
+      </c>
+      <c r="E778" t="n">
+        <v>-15.87</v>
+      </c>
+      <c r="F778" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="G778" t="n">
+        <v>300.87</v>
+      </c>
+      <c r="H778" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="I778" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="J778" t="n">
+        <v>289.54</v>
+      </c>
+      <c r="K778" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N778" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>5898</v>
+      </c>
+      <c r="D779" t="n">
+        <v>6174.12</v>
+      </c>
+      <c r="E779" t="n">
+        <v>-276.12</v>
+      </c>
+      <c r="F779" t="n">
+        <v>6078</v>
+      </c>
+      <c r="G779" t="n">
+        <v>6119.23</v>
+      </c>
+      <c r="H779" t="n">
+        <v>-41.23</v>
+      </c>
+      <c r="I779" t="n">
+        <v>5882.5</v>
+      </c>
+      <c r="J779" t="n">
+        <v>5782.81</v>
+      </c>
+      <c r="K779" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N779" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>438.05</v>
+      </c>
+      <c r="D780" t="n">
+        <v>462.78</v>
+      </c>
+      <c r="E780" t="n">
+        <v>-24.73</v>
+      </c>
+      <c r="F780" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="G780" t="n">
+        <v>451.82</v>
+      </c>
+      <c r="H780" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="I780" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="J780" t="n">
+        <v>431.5</v>
+      </c>
+      <c r="K780" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N780" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -40854,31 +40854,31 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>292.95</v>
+        <v>290</v>
       </c>
       <c r="D778" t="n">
         <v>302.76</v>
       </c>
       <c r="E778" t="n">
-        <v>-9.81</v>
+        <v>-12.76</v>
       </c>
       <c r="F778" t="n">
-        <v>295.05</v>
+        <v>291.35</v>
       </c>
       <c r="G778" t="n">
         <v>302.76</v>
       </c>
       <c r="H778" t="n">
-        <v>-7.71</v>
+        <v>-11.41</v>
       </c>
       <c r="I778" t="n">
-        <v>288.45</v>
+        <v>288.15</v>
       </c>
       <c r="J778" t="n">
         <v>290.92</v>
       </c>
       <c r="K778" t="n">
-        <v>-2.47</v>
+        <v>-2.77</v>
       </c>
       <c r="L778" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         </is>
       </c>
       <c r="N778" t="n">
-        <v>3.24</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="779">
@@ -40906,31 +40906,31 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>5898</v>
+        <v>5988</v>
       </c>
       <c r="D779" t="n">
         <v>5989.53</v>
       </c>
       <c r="E779" t="n">
-        <v>-91.53</v>
+        <v>-1.53</v>
       </c>
       <c r="F779" t="n">
-        <v>6078</v>
+        <v>6008.5</v>
       </c>
       <c r="G779" t="n">
         <v>6000.96</v>
       </c>
       <c r="H779" t="n">
-        <v>77.04000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="I779" t="n">
-        <v>5882.5</v>
+        <v>5787</v>
       </c>
       <c r="J779" t="n">
         <v>5822.94</v>
       </c>
       <c r="K779" t="n">
-        <v>59.56</v>
+        <v>-35.94</v>
       </c>
       <c r="L779" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         </is>
       </c>
       <c r="N779" t="n">
-        <v>1.53</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="780">
@@ -40958,31 +40958,31 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>438.05</v>
+        <v>439</v>
       </c>
       <c r="D780" t="n">
         <v>451.69</v>
       </c>
       <c r="E780" t="n">
-        <v>-13.64</v>
+        <v>-12.69</v>
       </c>
       <c r="F780" t="n">
-        <v>444.9</v>
+        <v>443.35</v>
       </c>
       <c r="G780" t="n">
         <v>451.69</v>
       </c>
       <c r="H780" t="n">
-        <v>-6.79</v>
+        <v>-8.34</v>
       </c>
       <c r="I780" t="n">
-        <v>437.2</v>
+        <v>437.5</v>
       </c>
       <c r="J780" t="n">
         <v>427.29</v>
       </c>
       <c r="K780" t="n">
-        <v>9.91</v>
+        <v>10.21</v>
       </c>
       <c r="L780" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         </is>
       </c>
       <c r="N780" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
     </row>
   </sheetData>
@@ -46088,31 +46088,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>22622.7</v>
+        <v>22721.95</v>
       </c>
       <c r="D98" t="n">
         <v>22622.7</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>99.25</v>
       </c>
       <c r="F98" t="n">
-        <v>22757.95</v>
+        <v>22721.95</v>
       </c>
       <c r="G98" t="n">
         <v>22734.11</v>
       </c>
       <c r="H98" t="n">
-        <v>23.84</v>
+        <v>-12.16</v>
       </c>
       <c r="I98" t="n">
-        <v>22558.95</v>
+        <v>22288.45</v>
       </c>
       <c r="J98" t="n">
         <v>22535.11</v>
       </c>
       <c r="K98" t="n">
-        <v>23.84</v>
+        <v>-246.66</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="99">
@@ -46140,31 +46140,31 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>55316</v>
+        <v>55481.05</v>
       </c>
       <c r="D99" t="n">
         <v>55316</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>165.05</v>
       </c>
       <c r="F99" t="n">
-        <v>55644.7</v>
+        <v>55551.75</v>
       </c>
       <c r="G99" t="n">
         <v>55584.4</v>
       </c>
       <c r="H99" t="n">
-        <v>60.3</v>
+        <v>-32.65</v>
       </c>
       <c r="I99" t="n">
-        <v>55168.2</v>
+        <v>54735.95</v>
       </c>
       <c r="J99" t="n">
         <v>55107.9</v>
       </c>
       <c r="K99" t="n">
-        <v>60.3</v>
+        <v>-371.95</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -86630,31 +86630,31 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>292.95</v>
+        <v>290</v>
       </c>
       <c r="D778" t="n">
         <v>308.82</v>
       </c>
       <c r="E778" t="n">
-        <v>-15.87</v>
+        <v>-18.82</v>
       </c>
       <c r="F778" t="n">
-        <v>295.05</v>
+        <v>291.35</v>
       </c>
       <c r="G778" t="n">
         <v>300.87</v>
       </c>
       <c r="H778" t="n">
-        <v>-5.82</v>
+        <v>-9.52</v>
       </c>
       <c r="I778" t="n">
-        <v>288.45</v>
+        <v>288.15</v>
       </c>
       <c r="J778" t="n">
         <v>289.54</v>
       </c>
       <c r="K778" t="n">
-        <v>-1.09</v>
+        <v>-1.39</v>
       </c>
       <c r="L778" t="inlineStr">
         <is>
@@ -86667,7 +86667,7 @@
         </is>
       </c>
       <c r="N778" t="n">
-        <v>5.14</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="779">
@@ -86682,31 +86682,31 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>5898</v>
+        <v>5988</v>
       </c>
       <c r="D779" t="n">
         <v>6174.12</v>
       </c>
       <c r="E779" t="n">
-        <v>-276.12</v>
+        <v>-186.12</v>
       </c>
       <c r="F779" t="n">
-        <v>6078</v>
+        <v>6008.5</v>
       </c>
       <c r="G779" t="n">
         <v>6119.23</v>
       </c>
       <c r="H779" t="n">
-        <v>-41.23</v>
+        <v>-110.73</v>
       </c>
       <c r="I779" t="n">
-        <v>5882.5</v>
+        <v>5787</v>
       </c>
       <c r="J779" t="n">
         <v>5782.81</v>
       </c>
       <c r="K779" t="n">
-        <v>99.69</v>
+        <v>4.19</v>
       </c>
       <c r="L779" t="inlineStr">
         <is>
@@ -86719,7 +86719,7 @@
         </is>
       </c>
       <c r="N779" t="n">
-        <v>4.47</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="780">
@@ -86734,31 +86734,31 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>438.05</v>
+        <v>439</v>
       </c>
       <c r="D780" t="n">
         <v>462.78</v>
       </c>
       <c r="E780" t="n">
-        <v>-24.73</v>
+        <v>-23.78</v>
       </c>
       <c r="F780" t="n">
-        <v>444.9</v>
+        <v>443.35</v>
       </c>
       <c r="G780" t="n">
         <v>451.82</v>
       </c>
       <c r="H780" t="n">
-        <v>-6.92</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I780" t="n">
-        <v>437.2</v>
+        <v>437.5</v>
       </c>
       <c r="J780" t="n">
         <v>431.5</v>
       </c>
       <c r="K780" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L780" t="inlineStr">
         <is>
@@ -86771,7 +86771,7 @@
         </is>
       </c>
       <c r="N780" t="n">
-        <v>5.34</v>
+        <v>5.14</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N780"/>
+  <dimension ref="A1:N784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40996,6 +40996,214 @@
       </c>
       <c r="N780" t="n">
         <v>2.81</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="D781" t="n">
+        <v>438.85</v>
+      </c>
+      <c r="E781" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F781" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="G781" t="n">
+        <v>438.85</v>
+      </c>
+      <c r="H781" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I781" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="J781" t="n">
+        <v>437.52</v>
+      </c>
+      <c r="K781" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N781" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D782" t="n">
+        <v>5885.19</v>
+      </c>
+      <c r="E782" t="n">
+        <v>-45.19</v>
+      </c>
+      <c r="F782" t="n">
+        <v>6010</v>
+      </c>
+      <c r="G782" t="n">
+        <v>5885.19</v>
+      </c>
+      <c r="H782" t="n">
+        <v>124.81</v>
+      </c>
+      <c r="I782" t="n">
+        <v>5791.5</v>
+      </c>
+      <c r="J782" t="n">
+        <v>5722</v>
+      </c>
+      <c r="K782" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N782" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="D783" t="n">
+        <v>285.02</v>
+      </c>
+      <c r="E783" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F783" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G783" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="H783" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I783" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="J783" t="n">
+        <v>294.09</v>
+      </c>
+      <c r="K783" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N783" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="D784" t="n">
+        <v>2414.33</v>
+      </c>
+      <c r="E784" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="F784" t="n">
+        <v>2485.2</v>
+      </c>
+      <c r="G784" t="n">
+        <v>2487.37</v>
+      </c>
+      <c r="H784" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="I784" t="n">
+        <v>2424.3</v>
+      </c>
+      <c r="J784" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="K784" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N784" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>
@@ -41009,7 +41217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46178,6 +46386,110 @@
       </c>
       <c r="N99" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="D100" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>23056.4</v>
+      </c>
+      <c r="G100" t="n">
+        <v>23156.7</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-100.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>22637.4</v>
+      </c>
+      <c r="J100" t="n">
+        <v>22737.7</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-100.3</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>55810.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>55810.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>56065.5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>56157.66</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-92.16</v>
+      </c>
+      <c r="I101" t="n">
+        <v>55279</v>
+      </c>
+      <c r="J101" t="n">
+        <v>55371.16</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-92.16</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -46191,7 +46503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N780"/>
+  <dimension ref="A1:N784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86774,6 +87086,214 @@
         <v>5.14</v>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="D781" t="n">
+        <v>290.74</v>
+      </c>
+      <c r="E781" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F781" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G781" t="n">
+        <v>298.71</v>
+      </c>
+      <c r="H781" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="I781" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="J781" t="n">
+        <v>291.97</v>
+      </c>
+      <c r="K781" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N781" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="D782" t="n">
+        <v>449.42</v>
+      </c>
+      <c r="E782" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="F782" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="G782" t="n">
+        <v>454.99</v>
+      </c>
+      <c r="H782" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="I782" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="J782" t="n">
+        <v>441.73</v>
+      </c>
+      <c r="K782" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N782" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="D783" t="n">
+        <v>2488.69</v>
+      </c>
+      <c r="E783" t="n">
+        <v>-35.49</v>
+      </c>
+      <c r="F783" t="n">
+        <v>2485.2</v>
+      </c>
+      <c r="G783" t="n">
+        <v>2510.45</v>
+      </c>
+      <c r="H783" t="n">
+        <v>-25.25</v>
+      </c>
+      <c r="I783" t="n">
+        <v>2424.3</v>
+      </c>
+      <c r="J783" t="n">
+        <v>2404.82</v>
+      </c>
+      <c r="K783" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N783" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D784" t="n">
+        <v>6067.45</v>
+      </c>
+      <c r="E784" t="n">
+        <v>-227.45</v>
+      </c>
+      <c r="F784" t="n">
+        <v>6010</v>
+      </c>
+      <c r="G784" t="n">
+        <v>5970.12</v>
+      </c>
+      <c r="H784" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="I784" t="n">
+        <v>5791.5</v>
+      </c>
+      <c r="J784" t="n">
+        <v>5729.58</v>
+      </c>
+      <c r="K784" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N784" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41010,31 +41010,31 @@
         </is>
       </c>
       <c r="C781" t="n">
-        <v>447.95</v>
+        <v>438.05</v>
       </c>
       <c r="D781" t="n">
         <v>438.85</v>
       </c>
       <c r="E781" t="n">
-        <v>9.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F781" t="n">
-        <v>447.95</v>
+        <v>444.9</v>
       </c>
       <c r="G781" t="n">
         <v>438.85</v>
       </c>
       <c r="H781" t="n">
-        <v>9.1</v>
+        <v>6.05</v>
       </c>
       <c r="I781" t="n">
-        <v>437.6</v>
+        <v>437.2</v>
       </c>
       <c r="J781" t="n">
         <v>437.52</v>
       </c>
       <c r="K781" t="n">
-        <v>0.08</v>
+        <v>-0.32</v>
       </c>
       <c r="L781" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>2.07</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="782">
@@ -41062,31 +41062,31 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>5840</v>
+        <v>5898</v>
       </c>
       <c r="D782" t="n">
         <v>5885.19</v>
       </c>
       <c r="E782" t="n">
-        <v>-45.19</v>
+        <v>12.81</v>
       </c>
       <c r="F782" t="n">
-        <v>6010</v>
+        <v>6078</v>
       </c>
       <c r="G782" t="n">
         <v>5885.19</v>
       </c>
       <c r="H782" t="n">
-        <v>124.81</v>
+        <v>192.81</v>
       </c>
       <c r="I782" t="n">
-        <v>5791.5</v>
+        <v>5882.5</v>
       </c>
       <c r="J782" t="n">
         <v>5722</v>
       </c>
       <c r="K782" t="n">
-        <v>69.5</v>
+        <v>160.5</v>
       </c>
       <c r="L782" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         </is>
       </c>
       <c r="N782" t="n">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="783">
@@ -41114,31 +41114,31 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>295.2</v>
+        <v>292.95</v>
       </c>
       <c r="D783" t="n">
         <v>285.02</v>
       </c>
       <c r="E783" t="n">
-        <v>10.18</v>
+        <v>7.93</v>
       </c>
       <c r="F783" t="n">
-        <v>295.2</v>
+        <v>295.05</v>
       </c>
       <c r="G783" t="n">
         <v>298.2</v>
       </c>
       <c r="H783" t="n">
-        <v>-3</v>
+        <v>-3.15</v>
       </c>
       <c r="I783" t="n">
-        <v>290.85</v>
+        <v>288.45</v>
       </c>
       <c r="J783" t="n">
         <v>294.09</v>
       </c>
       <c r="K783" t="n">
-        <v>-3.24</v>
+        <v>-5.64</v>
       </c>
       <c r="L783" t="inlineStr">
         <is>
@@ -41147,11 +41147,11 @@
       </c>
       <c r="M783" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N783" t="n">
-        <v>3.57</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="784">
@@ -41166,31 +41166,31 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>2453.2</v>
+        <v>2435.3</v>
       </c>
       <c r="D784" t="n">
         <v>2414.33</v>
       </c>
       <c r="E784" t="n">
-        <v>38.87</v>
+        <v>20.97</v>
       </c>
       <c r="F784" t="n">
-        <v>2485.2</v>
+        <v>2512.7</v>
       </c>
       <c r="G784" t="n">
         <v>2487.37</v>
       </c>
       <c r="H784" t="n">
-        <v>-2.17</v>
+        <v>25.33</v>
       </c>
       <c r="I784" t="n">
-        <v>2424.3</v>
+        <v>2420</v>
       </c>
       <c r="J784" t="n">
         <v>2453.2</v>
       </c>
       <c r="K784" t="n">
-        <v>-28.9</v>
+        <v>-33.2</v>
       </c>
       <c r="L784" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="N784" t="n">
-        <v>1.61</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -46400,31 +46400,31 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>22997.35</v>
+        <v>22622.7</v>
       </c>
       <c r="D100" t="n">
         <v>22997.35</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>-374.65</v>
       </c>
       <c r="F100" t="n">
-        <v>23056.4</v>
+        <v>22757.95</v>
       </c>
       <c r="G100" t="n">
         <v>23156.7</v>
       </c>
       <c r="H100" t="n">
-        <v>-100.3</v>
+        <v>-398.75</v>
       </c>
       <c r="I100" t="n">
-        <v>22637.4</v>
+        <v>22558.95</v>
       </c>
       <c r="J100" t="n">
         <v>22737.7</v>
       </c>
       <c r="K100" t="n">
-        <v>-100.3</v>
+        <v>-178.75</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="101">
@@ -46452,31 +46452,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>55810.5</v>
+        <v>55316</v>
       </c>
       <c r="D101" t="n">
         <v>55810.5</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>-494.5</v>
       </c>
       <c r="F101" t="n">
-        <v>56065.5</v>
+        <v>55644.7</v>
       </c>
       <c r="G101" t="n">
         <v>56157.66</v>
       </c>
       <c r="H101" t="n">
-        <v>-92.16</v>
+        <v>-512.96</v>
       </c>
       <c r="I101" t="n">
-        <v>55279</v>
+        <v>55168.2</v>
       </c>
       <c r="J101" t="n">
         <v>55371.16</v>
       </c>
       <c r="K101" t="n">
-        <v>-92.16</v>
+        <v>-202.96</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -46489,7 +46489,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -87098,31 +87098,31 @@
         </is>
       </c>
       <c r="C781" t="n">
-        <v>295.2</v>
+        <v>292.95</v>
       </c>
       <c r="D781" t="n">
         <v>290.74</v>
       </c>
       <c r="E781" t="n">
-        <v>4.46</v>
+        <v>2.21</v>
       </c>
       <c r="F781" t="n">
-        <v>295.2</v>
+        <v>295.05</v>
       </c>
       <c r="G781" t="n">
         <v>298.71</v>
       </c>
       <c r="H781" t="n">
-        <v>-3.51</v>
+        <v>-3.66</v>
       </c>
       <c r="I781" t="n">
-        <v>290.85</v>
+        <v>288.45</v>
       </c>
       <c r="J781" t="n">
         <v>291.97</v>
       </c>
       <c r="K781" t="n">
-        <v>-1.12</v>
+        <v>-3.52</v>
       </c>
       <c r="L781" t="inlineStr">
         <is>
@@ -87135,7 +87135,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>1.53</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="782">
@@ -87150,31 +87150,31 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>447.95</v>
+        <v>438.05</v>
       </c>
       <c r="D782" t="n">
         <v>449.42</v>
       </c>
       <c r="E782" t="n">
-        <v>-1.47</v>
+        <v>-11.37</v>
       </c>
       <c r="F782" t="n">
-        <v>447.95</v>
+        <v>444.9</v>
       </c>
       <c r="G782" t="n">
         <v>454.99</v>
       </c>
       <c r="H782" t="n">
-        <v>-7.04</v>
+        <v>-10.09</v>
       </c>
       <c r="I782" t="n">
-        <v>437.6</v>
+        <v>437.2</v>
       </c>
       <c r="J782" t="n">
         <v>441.73</v>
       </c>
       <c r="K782" t="n">
-        <v>-4.13</v>
+        <v>-4.53</v>
       </c>
       <c r="L782" t="inlineStr">
         <is>
@@ -87183,11 +87183,11 @@
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N782" t="n">
-        <v>0.33</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="783">
@@ -87202,31 +87202,31 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>2453.2</v>
+        <v>2435.3</v>
       </c>
       <c r="D783" t="n">
         <v>2488.69</v>
       </c>
       <c r="E783" t="n">
-        <v>-35.49</v>
+        <v>-53.39</v>
       </c>
       <c r="F783" t="n">
-        <v>2485.2</v>
+        <v>2512.7</v>
       </c>
       <c r="G783" t="n">
         <v>2510.45</v>
       </c>
       <c r="H783" t="n">
-        <v>-25.25</v>
+        <v>2.25</v>
       </c>
       <c r="I783" t="n">
-        <v>2424.3</v>
+        <v>2420</v>
       </c>
       <c r="J783" t="n">
         <v>2404.82</v>
       </c>
       <c r="K783" t="n">
-        <v>19.48</v>
+        <v>15.18</v>
       </c>
       <c r="L783" t="inlineStr">
         <is>
@@ -87239,7 +87239,7 @@
         </is>
       </c>
       <c r="N783" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="784">
@@ -87254,31 +87254,31 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>5840</v>
+        <v>5898</v>
       </c>
       <c r="D784" t="n">
         <v>6067.45</v>
       </c>
       <c r="E784" t="n">
-        <v>-227.45</v>
+        <v>-169.45</v>
       </c>
       <c r="F784" t="n">
-        <v>6010</v>
+        <v>6078</v>
       </c>
       <c r="G784" t="n">
         <v>5970.12</v>
       </c>
       <c r="H784" t="n">
-        <v>39.88</v>
+        <v>107.88</v>
       </c>
       <c r="I784" t="n">
-        <v>5791.5</v>
+        <v>5882.5</v>
       </c>
       <c r="J784" t="n">
         <v>5729.58</v>
       </c>
       <c r="K784" t="n">
-        <v>61.92</v>
+        <v>152.92</v>
       </c>
       <c r="L784" t="inlineStr">
         <is>
@@ -87291,7 +87291,7 @@
         </is>
       </c>
       <c r="N784" t="n">
-        <v>3.75</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N784"/>
+  <dimension ref="A1:N789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41204,6 +41204,266 @@
       </c>
       <c r="N784" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D785" t="n">
+        <v>116.89</v>
+      </c>
+      <c r="E785" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F785" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G785" t="n">
+        <v>116.89</v>
+      </c>
+      <c r="H785" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="I785" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J785" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="K785" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N785" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D786" t="n">
+        <v>2541.9</v>
+      </c>
+      <c r="E786" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="F786" t="n">
+        <v>2521.7</v>
+      </c>
+      <c r="G786" t="n">
+        <v>2547.58</v>
+      </c>
+      <c r="H786" t="n">
+        <v>-25.88</v>
+      </c>
+      <c r="I786" t="n">
+        <v>2455.1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>2471.86</v>
+      </c>
+      <c r="K786" t="n">
+        <v>-16.76</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N786" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="D787" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="E787" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F787" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="G787" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="H787" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I787" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J787" t="n">
+        <v>319.04</v>
+      </c>
+      <c r="K787" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N787" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D788" t="n">
+        <v>5799.55</v>
+      </c>
+      <c r="E788" t="n">
+        <v>-58.55</v>
+      </c>
+      <c r="F788" t="n">
+        <v>5755</v>
+      </c>
+      <c r="G788" t="n">
+        <v>5799.55</v>
+      </c>
+      <c r="H788" t="n">
+        <v>-44.55</v>
+      </c>
+      <c r="I788" t="n">
+        <v>5492</v>
+      </c>
+      <c r="J788" t="n">
+        <v>5576.1</v>
+      </c>
+      <c r="K788" t="n">
+        <v>-84.09999999999999</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N788" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>293</v>
+      </c>
+      <c r="D789" t="n">
+        <v>303.56</v>
+      </c>
+      <c r="E789" t="n">
+        <v>-10.56</v>
+      </c>
+      <c r="F789" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G789" t="n">
+        <v>303.56</v>
+      </c>
+      <c r="H789" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="I789" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="J789" t="n">
+        <v>288.24</v>
+      </c>
+      <c r="K789" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N789" t="n">
+        <v>3.48</v>
       </c>
     </row>
   </sheetData>
@@ -41217,7 +41477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46490,6 +46750,110 @@
       </c>
       <c r="N101" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="D102" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>23149.85</v>
+      </c>
+      <c r="G102" t="n">
+        <v>23226.06</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-76.20999999999999</v>
+      </c>
+      <c r="I102" t="n">
+        <v>22913.8</v>
+      </c>
+      <c r="J102" t="n">
+        <v>22990.01</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-76.20999999999999</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>55844</v>
+      </c>
+      <c r="D103" t="n">
+        <v>55844</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>55989.55</v>
+      </c>
+      <c r="G103" t="n">
+        <v>56046.94</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-57.39</v>
+      </c>
+      <c r="I103" t="n">
+        <v>55526.3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>55583.69</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-57.39</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -46503,7 +46867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N784"/>
+  <dimension ref="A1:N789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87294,6 +87658,266 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D785" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="E785" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F785" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G785" t="n">
+        <v>120.19</v>
+      </c>
+      <c r="H785" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="I785" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J785" t="n">
+        <v>113.71</v>
+      </c>
+      <c r="K785" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N785" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>293</v>
+      </c>
+      <c r="D786" t="n">
+        <v>309.63</v>
+      </c>
+      <c r="E786" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="F786" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G786" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="H786" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="I786" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>288.53</v>
+      </c>
+      <c r="K786" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N786" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D787" t="n">
+        <v>2622.5</v>
+      </c>
+      <c r="E787" t="n">
+        <v>-122.5</v>
+      </c>
+      <c r="F787" t="n">
+        <v>2521.7</v>
+      </c>
+      <c r="G787" t="n">
+        <v>2588.43</v>
+      </c>
+      <c r="H787" t="n">
+        <v>-66.73</v>
+      </c>
+      <c r="I787" t="n">
+        <v>2455.1</v>
+      </c>
+      <c r="J787" t="n">
+        <v>2440.66</v>
+      </c>
+      <c r="K787" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N787" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="D788" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="E788" t="n">
+        <v>-11.48</v>
+      </c>
+      <c r="F788" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="G788" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="H788" t="n">
+        <v>-8.83</v>
+      </c>
+      <c r="I788" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J788" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="K788" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N788" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D789" t="n">
+        <v>5987.47</v>
+      </c>
+      <c r="E789" t="n">
+        <v>-246.47</v>
+      </c>
+      <c r="F789" t="n">
+        <v>5755</v>
+      </c>
+      <c r="G789" t="n">
+        <v>5947.9</v>
+      </c>
+      <c r="H789" t="n">
+        <v>-192.9</v>
+      </c>
+      <c r="I789" t="n">
+        <v>5492</v>
+      </c>
+      <c r="J789" t="n">
+        <v>5601.84</v>
+      </c>
+      <c r="K789" t="n">
+        <v>-109.84</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N789" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41218,31 +41218,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>116.3</v>
+        <v>115.05</v>
       </c>
       <c r="D785" t="n">
         <v>116.89</v>
       </c>
       <c r="E785" t="n">
-        <v>-0.59</v>
+        <v>-1.84</v>
       </c>
       <c r="F785" t="n">
-        <v>116.4</v>
+        <v>118.79</v>
       </c>
       <c r="G785" t="n">
         <v>116.89</v>
       </c>
       <c r="H785" t="n">
-        <v>-0.49</v>
+        <v>1.9</v>
       </c>
       <c r="I785" t="n">
-        <v>114.1</v>
+        <v>114.63</v>
       </c>
       <c r="J785" t="n">
         <v>112.47</v>
       </c>
       <c r="K785" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="786">
@@ -41270,31 +41270,31 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>2500</v>
+        <v>2453.2</v>
       </c>
       <c r="D786" t="n">
         <v>2541.9</v>
       </c>
       <c r="E786" t="n">
-        <v>-41.9</v>
+        <v>-88.7</v>
       </c>
       <c r="F786" t="n">
-        <v>2521.7</v>
+        <v>2485.2</v>
       </c>
       <c r="G786" t="n">
         <v>2547.58</v>
       </c>
       <c r="H786" t="n">
-        <v>-25.88</v>
+        <v>-62.38</v>
       </c>
       <c r="I786" t="n">
-        <v>2455.1</v>
+        <v>2424.3</v>
       </c>
       <c r="J786" t="n">
         <v>2471.86</v>
       </c>
       <c r="K786" t="n">
-        <v>-16.76</v>
+        <v>-47.56</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -41303,11 +41303,11 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N786" t="n">
-        <v>1.65</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="787">
@@ -41322,31 +41322,31 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>325.3</v>
+        <v>323</v>
       </c>
       <c r="D787" t="n">
         <v>326.96</v>
       </c>
       <c r="E787" t="n">
-        <v>-1.66</v>
+        <v>-3.96</v>
       </c>
       <c r="F787" t="n">
-        <v>327.45</v>
+        <v>323</v>
       </c>
       <c r="G787" t="n">
         <v>328.91</v>
       </c>
       <c r="H787" t="n">
-        <v>-1.46</v>
+        <v>-5.91</v>
       </c>
       <c r="I787" t="n">
-        <v>321.35</v>
+        <v>313.6</v>
       </c>
       <c r="J787" t="n">
         <v>319.04</v>
       </c>
       <c r="K787" t="n">
-        <v>2.31</v>
+        <v>-5.44</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>0.51</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="788">
@@ -41374,31 +41374,31 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>5741</v>
+        <v>5840</v>
       </c>
       <c r="D788" t="n">
         <v>5799.55</v>
       </c>
       <c r="E788" t="n">
-        <v>-58.55</v>
+        <v>40.45</v>
       </c>
       <c r="F788" t="n">
-        <v>5755</v>
+        <v>6010</v>
       </c>
       <c r="G788" t="n">
         <v>5799.55</v>
       </c>
       <c r="H788" t="n">
-        <v>-44.55</v>
+        <v>210.45</v>
       </c>
       <c r="I788" t="n">
-        <v>5492</v>
+        <v>5791.5</v>
       </c>
       <c r="J788" t="n">
         <v>5576.1</v>
       </c>
       <c r="K788" t="n">
-        <v>-84.09999999999999</v>
+        <v>215.4</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>1.01</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="789">
@@ -41426,13 +41426,13 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>293</v>
+        <v>295.2</v>
       </c>
       <c r="D789" t="n">
         <v>303.56</v>
       </c>
       <c r="E789" t="n">
-        <v>-10.56</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F789" t="n">
         <v>295.2</v>
@@ -41444,13 +41444,13 @@
         <v>-8.359999999999999</v>
       </c>
       <c r="I789" t="n">
-        <v>290.1</v>
+        <v>290.85</v>
       </c>
       <c r="J789" t="n">
         <v>288.24</v>
       </c>
       <c r="K789" t="n">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         </is>
       </c>
       <c r="N789" t="n">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -46764,31 +46764,31 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>23146.15</v>
+        <v>22997.35</v>
       </c>
       <c r="D102" t="n">
         <v>23146.15</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>-148.8</v>
       </c>
       <c r="F102" t="n">
-        <v>23149.85</v>
+        <v>23056.4</v>
       </c>
       <c r="G102" t="n">
         <v>23226.06</v>
       </c>
       <c r="H102" t="n">
-        <v>-76.20999999999999</v>
+        <v>-169.66</v>
       </c>
       <c r="I102" t="n">
-        <v>22913.8</v>
+        <v>22637.4</v>
       </c>
       <c r="J102" t="n">
         <v>22990.01</v>
       </c>
       <c r="K102" t="n">
-        <v>-76.20999999999999</v>
+        <v>-352.61</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="103">
@@ -46816,31 +46816,31 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>55844</v>
+        <v>55810.5</v>
       </c>
       <c r="D103" t="n">
         <v>55844</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>-33.5</v>
       </c>
       <c r="F103" t="n">
-        <v>55989.55</v>
+        <v>56065.5</v>
       </c>
       <c r="G103" t="n">
         <v>56046.94</v>
       </c>
       <c r="H103" t="n">
-        <v>-57.39</v>
+        <v>18.56</v>
       </c>
       <c r="I103" t="n">
-        <v>55526.3</v>
+        <v>55279</v>
       </c>
       <c r="J103" t="n">
         <v>55583.69</v>
       </c>
       <c r="K103" t="n">
-        <v>-57.39</v>
+        <v>-304.69</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -87670,31 +87670,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>116.3</v>
+        <v>115.05</v>
       </c>
       <c r="D785" t="n">
         <v>120.37</v>
       </c>
       <c r="E785" t="n">
-        <v>-4.07</v>
+        <v>-5.32</v>
       </c>
       <c r="F785" t="n">
-        <v>116.4</v>
+        <v>118.79</v>
       </c>
       <c r="G785" t="n">
         <v>120.19</v>
       </c>
       <c r="H785" t="n">
-        <v>-3.79</v>
+        <v>-1.4</v>
       </c>
       <c r="I785" t="n">
-        <v>114.1</v>
+        <v>114.63</v>
       </c>
       <c r="J785" t="n">
         <v>113.71</v>
       </c>
       <c r="K785" t="n">
-        <v>0.39</v>
+        <v>0.92</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -87707,7 +87707,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>3.38</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="786">
@@ -87722,13 +87722,13 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>293</v>
+        <v>295.2</v>
       </c>
       <c r="D786" t="n">
         <v>309.63</v>
       </c>
       <c r="E786" t="n">
-        <v>-16.63</v>
+        <v>-14.43</v>
       </c>
       <c r="F786" t="n">
         <v>295.2</v>
@@ -87740,13 +87740,13 @@
         <v>-4.85</v>
       </c>
       <c r="I786" t="n">
-        <v>290.1</v>
+        <v>290.85</v>
       </c>
       <c r="J786" t="n">
         <v>288.53</v>
       </c>
       <c r="K786" t="n">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -87759,7 +87759,7 @@
         </is>
       </c>
       <c r="N786" t="n">
-        <v>5.37</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="787">
@@ -87774,31 +87774,31 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>2500</v>
+        <v>2453.2</v>
       </c>
       <c r="D787" t="n">
         <v>2622.5</v>
       </c>
       <c r="E787" t="n">
-        <v>-122.5</v>
+        <v>-169.3</v>
       </c>
       <c r="F787" t="n">
-        <v>2521.7</v>
+        <v>2485.2</v>
       </c>
       <c r="G787" t="n">
         <v>2588.43</v>
       </c>
       <c r="H787" t="n">
-        <v>-66.73</v>
+        <v>-103.23</v>
       </c>
       <c r="I787" t="n">
-        <v>2455.1</v>
+        <v>2424.3</v>
       </c>
       <c r="J787" t="n">
         <v>2440.66</v>
       </c>
       <c r="K787" t="n">
-        <v>14.44</v>
+        <v>-16.36</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -87811,7 +87811,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>4.67</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="788">
@@ -87826,31 +87826,31 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>325.3</v>
+        <v>323</v>
       </c>
       <c r="D788" t="n">
         <v>336.78</v>
       </c>
       <c r="E788" t="n">
-        <v>-11.48</v>
+        <v>-13.78</v>
       </c>
       <c r="F788" t="n">
-        <v>327.45</v>
+        <v>323</v>
       </c>
       <c r="G788" t="n">
         <v>336.28</v>
       </c>
       <c r="H788" t="n">
-        <v>-8.83</v>
+        <v>-13.28</v>
       </c>
       <c r="I788" t="n">
-        <v>321.35</v>
+        <v>313.6</v>
       </c>
       <c r="J788" t="n">
         <v>317.98</v>
       </c>
       <c r="K788" t="n">
-        <v>3.37</v>
+        <v>-4.38</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -87863,7 +87863,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>3.41</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="789">
@@ -87878,31 +87878,31 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>5741</v>
+        <v>5840</v>
       </c>
       <c r="D789" t="n">
         <v>5987.47</v>
       </c>
       <c r="E789" t="n">
-        <v>-246.47</v>
+        <v>-147.47</v>
       </c>
       <c r="F789" t="n">
-        <v>5755</v>
+        <v>6010</v>
       </c>
       <c r="G789" t="n">
         <v>5947.9</v>
       </c>
       <c r="H789" t="n">
-        <v>-192.9</v>
+        <v>62.1</v>
       </c>
       <c r="I789" t="n">
-        <v>5492</v>
+        <v>5791.5</v>
       </c>
       <c r="J789" t="n">
         <v>5601.84</v>
       </c>
       <c r="K789" t="n">
-        <v>-109.84</v>
+        <v>189.66</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -87911,11 +87911,11 @@
       </c>
       <c r="M789" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N789" t="n">
-        <v>4.12</v>
+        <v>2.46</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41218,31 +41218,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>115.05</v>
+        <v>116.3</v>
       </c>
       <c r="D785" t="n">
-        <v>116.89</v>
+        <v>115.38</v>
       </c>
       <c r="E785" t="n">
-        <v>-1.84</v>
+        <v>0.92</v>
       </c>
       <c r="F785" t="n">
-        <v>118.79</v>
+        <v>116.4</v>
       </c>
       <c r="G785" t="n">
-        <v>116.89</v>
+        <v>115.38</v>
       </c>
       <c r="H785" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="I785" t="n">
-        <v>114.63</v>
+        <v>114.1</v>
       </c>
       <c r="J785" t="n">
-        <v>112.47</v>
+        <v>112.62</v>
       </c>
       <c r="K785" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>1.57</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="786">
@@ -41266,35 +41266,35 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>2453.2</v>
+        <v>5741</v>
       </c>
       <c r="D786" t="n">
-        <v>2541.9</v>
+        <v>5827.26</v>
       </c>
       <c r="E786" t="n">
-        <v>-88.7</v>
+        <v>-86.26000000000001</v>
       </c>
       <c r="F786" t="n">
-        <v>2485.2</v>
+        <v>5755</v>
       </c>
       <c r="G786" t="n">
-        <v>2547.58</v>
+        <v>5827.26</v>
       </c>
       <c r="H786" t="n">
-        <v>-62.38</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="I786" t="n">
-        <v>2424.3</v>
+        <v>5492</v>
       </c>
       <c r="J786" t="n">
-        <v>2471.86</v>
+        <v>5583.31</v>
       </c>
       <c r="K786" t="n">
-        <v>-47.56</v>
+        <v>-91.31</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -41303,11 +41303,11 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N786" t="n">
-        <v>3.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="787">
@@ -41318,35 +41318,35 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="D787" t="n">
-        <v>326.96</v>
+        <v>287.21</v>
       </c>
       <c r="E787" t="n">
-        <v>-3.96</v>
+        <v>5.79</v>
       </c>
       <c r="F787" t="n">
-        <v>323</v>
+        <v>295.2</v>
       </c>
       <c r="G787" t="n">
-        <v>328.91</v>
+        <v>296.72</v>
       </c>
       <c r="H787" t="n">
-        <v>-5.91</v>
+        <v>-1.52</v>
       </c>
       <c r="I787" t="n">
-        <v>313.6</v>
+        <v>290.1</v>
       </c>
       <c r="J787" t="n">
-        <v>319.04</v>
+        <v>288.62</v>
       </c>
       <c r="K787" t="n">
-        <v>-5.44</v>
+        <v>1.48</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="788">
@@ -41370,35 +41370,35 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>5840</v>
+        <v>2500</v>
       </c>
       <c r="D788" t="n">
-        <v>5799.55</v>
+        <v>2432.05</v>
       </c>
       <c r="E788" t="n">
-        <v>40.45</v>
+        <v>67.95</v>
       </c>
       <c r="F788" t="n">
-        <v>6010</v>
+        <v>2521.7</v>
       </c>
       <c r="G788" t="n">
-        <v>5799.55</v>
+        <v>2544.05</v>
       </c>
       <c r="H788" t="n">
-        <v>210.45</v>
+        <v>-22.35</v>
       </c>
       <c r="I788" t="n">
-        <v>5791.5</v>
+        <v>2455.1</v>
       </c>
       <c r="J788" t="n">
-        <v>5576.1</v>
+        <v>2475.07</v>
       </c>
       <c r="K788" t="n">
-        <v>215.4</v>
+        <v>-19.97</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>0.7</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="789">
@@ -41422,35 +41422,35 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C789" t="n">
-        <v>295.2</v>
+        <v>325.3</v>
       </c>
       <c r="D789" t="n">
-        <v>303.56</v>
+        <v>323.93</v>
       </c>
       <c r="E789" t="n">
-        <v>-8.359999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="F789" t="n">
-        <v>295.2</v>
+        <v>327.45</v>
       </c>
       <c r="G789" t="n">
-        <v>303.56</v>
+        <v>328.46</v>
       </c>
       <c r="H789" t="n">
-        <v>-8.359999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="I789" t="n">
-        <v>290.85</v>
+        <v>321.35</v>
       </c>
       <c r="J789" t="n">
-        <v>288.24</v>
+        <v>319.46</v>
       </c>
       <c r="K789" t="n">
-        <v>2.61</v>
+        <v>1.89</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         </is>
       </c>
       <c r="N789" t="n">
-        <v>2.75</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -46764,31 +46764,31 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>22997.35</v>
+        <v>23146.15</v>
       </c>
       <c r="D102" t="n">
         <v>23146.15</v>
       </c>
       <c r="E102" t="n">
-        <v>-148.8</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>23056.4</v>
+        <v>23149.85</v>
       </c>
       <c r="G102" t="n">
         <v>23226.06</v>
       </c>
       <c r="H102" t="n">
-        <v>-169.66</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>22637.4</v>
+        <v>22913.8</v>
       </c>
       <c r="J102" t="n">
         <v>22990.01</v>
       </c>
       <c r="K102" t="n">
-        <v>-352.61</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -46816,31 +46816,31 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>55810.5</v>
+        <v>55844</v>
       </c>
       <c r="D103" t="n">
         <v>55844</v>
       </c>
       <c r="E103" t="n">
-        <v>-33.5</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>56065.5</v>
+        <v>55989.55</v>
       </c>
       <c r="G103" t="n">
         <v>56046.94</v>
       </c>
       <c r="H103" t="n">
-        <v>18.56</v>
+        <v>-57.39</v>
       </c>
       <c r="I103" t="n">
-        <v>55279</v>
+        <v>55526.3</v>
       </c>
       <c r="J103" t="n">
         <v>55583.69</v>
       </c>
       <c r="K103" t="n">
-        <v>-304.69</v>
+        <v>-57.39</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -87670,31 +87670,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>115.05</v>
+        <v>116.3</v>
       </c>
       <c r="D785" t="n">
-        <v>120.37</v>
+        <v>118.8</v>
       </c>
       <c r="E785" t="n">
-        <v>-5.32</v>
+        <v>-2.5</v>
       </c>
       <c r="F785" t="n">
-        <v>118.79</v>
+        <v>116.4</v>
       </c>
       <c r="G785" t="n">
-        <v>120.19</v>
+        <v>120.01</v>
       </c>
       <c r="H785" t="n">
-        <v>-1.4</v>
+        <v>-3.61</v>
       </c>
       <c r="I785" t="n">
-        <v>114.63</v>
+        <v>114.1</v>
       </c>
       <c r="J785" t="n">
-        <v>113.71</v>
+        <v>113.84</v>
       </c>
       <c r="K785" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -87703,11 +87703,11 @@
       </c>
       <c r="M785" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N785" t="n">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="786">
@@ -87722,31 +87722,31 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>295.2</v>
+        <v>293</v>
       </c>
       <c r="D786" t="n">
-        <v>309.63</v>
+        <v>292.9</v>
       </c>
       <c r="E786" t="n">
-        <v>-14.43</v>
+        <v>0.1</v>
       </c>
       <c r="F786" t="n">
         <v>295.2</v>
       </c>
       <c r="G786" t="n">
-        <v>300.05</v>
+        <v>299.59</v>
       </c>
       <c r="H786" t="n">
-        <v>-4.85</v>
+        <v>-4.39</v>
       </c>
       <c r="I786" t="n">
-        <v>290.85</v>
+        <v>290.1</v>
       </c>
       <c r="J786" t="n">
-        <v>288.53</v>
+        <v>288.87</v>
       </c>
       <c r="K786" t="n">
-        <v>2.32</v>
+        <v>1.23</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -87755,11 +87755,11 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N786" t="n">
-        <v>4.66</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="787">
@@ -87774,31 +87774,31 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>2453.2</v>
+        <v>2500</v>
       </c>
       <c r="D787" t="n">
-        <v>2622.5</v>
+        <v>2508.81</v>
       </c>
       <c r="E787" t="n">
-        <v>-169.3</v>
+        <v>-8.81</v>
       </c>
       <c r="F787" t="n">
-        <v>2485.2</v>
+        <v>2521.7</v>
       </c>
       <c r="G787" t="n">
-        <v>2588.43</v>
+        <v>2584.46</v>
       </c>
       <c r="H787" t="n">
-        <v>-103.23</v>
+        <v>-62.76</v>
       </c>
       <c r="I787" t="n">
-        <v>2424.3</v>
+        <v>2455.1</v>
       </c>
       <c r="J787" t="n">
-        <v>2440.66</v>
+        <v>2443.44</v>
       </c>
       <c r="K787" t="n">
-        <v>-16.36</v>
+        <v>11.66</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -87807,11 +87807,11 @@
       </c>
       <c r="M787" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N787" t="n">
-        <v>6.46</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="788">
@@ -87826,31 +87826,31 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>323</v>
+        <v>325.3</v>
       </c>
       <c r="D788" t="n">
-        <v>336.78</v>
+        <v>333.61</v>
       </c>
       <c r="E788" t="n">
-        <v>-13.78</v>
+        <v>-8.31</v>
       </c>
       <c r="F788" t="n">
-        <v>323</v>
+        <v>327.45</v>
       </c>
       <c r="G788" t="n">
-        <v>336.28</v>
+        <v>335.77</v>
       </c>
       <c r="H788" t="n">
-        <v>-13.28</v>
+        <v>-8.32</v>
       </c>
       <c r="I788" t="n">
-        <v>313.6</v>
+        <v>321.35</v>
       </c>
       <c r="J788" t="n">
-        <v>317.98</v>
+        <v>318.34</v>
       </c>
       <c r="K788" t="n">
-        <v>-4.38</v>
+        <v>3.01</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -87859,11 +87859,11 @@
       </c>
       <c r="M788" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N788" t="n">
-        <v>4.09</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="789">
@@ -87878,31 +87878,31 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>5840</v>
+        <v>5741</v>
       </c>
       <c r="D789" t="n">
-        <v>5987.47</v>
+        <v>6015.22</v>
       </c>
       <c r="E789" t="n">
-        <v>-147.47</v>
+        <v>-274.22</v>
       </c>
       <c r="F789" t="n">
-        <v>6010</v>
+        <v>5755</v>
       </c>
       <c r="G789" t="n">
-        <v>5947.9</v>
+        <v>5938.8</v>
       </c>
       <c r="H789" t="n">
-        <v>62.1</v>
+        <v>-183.8</v>
       </c>
       <c r="I789" t="n">
-        <v>5791.5</v>
+        <v>5492</v>
       </c>
       <c r="J789" t="n">
-        <v>5601.84</v>
+        <v>5608.24</v>
       </c>
       <c r="K789" t="n">
-        <v>189.66</v>
+        <v>-116.24</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -87911,11 +87911,11 @@
       </c>
       <c r="M789" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N789" t="n">
-        <v>2.46</v>
+        <v>4.56</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N789"/>
+  <dimension ref="A1:N793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41464,6 +41464,214 @@
       </c>
       <c r="N789" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D790" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="E790" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="F790" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="G790" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="H790" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I790" t="n">
+        <v>120</v>
+      </c>
+      <c r="J790" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="K790" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N790" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="D791" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="E791" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="F791" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="G791" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="H791" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="I791" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="J791" t="n">
+        <v>286.67</v>
+      </c>
+      <c r="K791" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N791" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D792" t="n">
+        <v>5650.63</v>
+      </c>
+      <c r="E792" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="F792" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G792" t="n">
+        <v>5650.63</v>
+      </c>
+      <c r="H792" t="n">
+        <v>258.37</v>
+      </c>
+      <c r="I792" t="n">
+        <v>5635</v>
+      </c>
+      <c r="J792" t="n">
+        <v>5443.83</v>
+      </c>
+      <c r="K792" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N792" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D793" t="n">
+        <v>2590.41</v>
+      </c>
+      <c r="E793" t="n">
+        <v>-90.41</v>
+      </c>
+      <c r="F793" t="n">
+        <v>2515.8</v>
+      </c>
+      <c r="G793" t="n">
+        <v>2590.41</v>
+      </c>
+      <c r="H793" t="n">
+        <v>-74.61</v>
+      </c>
+      <c r="I793" t="n">
+        <v>2453</v>
+      </c>
+      <c r="J793" t="n">
+        <v>2439.34</v>
+      </c>
+      <c r="K793" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N793" t="n">
+        <v>3.49</v>
       </c>
     </row>
   </sheetData>
@@ -41477,7 +41685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46853,6 +47061,110 @@
         </is>
       </c>
       <c r="N103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="D104" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>23175.25</v>
+      </c>
+      <c r="G104" t="n">
+        <v>23094.46</v>
+      </c>
+      <c r="H104" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="I104" t="n">
+        <v>22845</v>
+      </c>
+      <c r="J104" t="n">
+        <v>22764.21</v>
+      </c>
+      <c r="K104" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>55488.1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>55488.1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>55883.7</v>
+      </c>
+      <c r="G105" t="n">
+        <v>55804.16</v>
+      </c>
+      <c r="H105" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="I105" t="n">
+        <v>55331.1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>55251.56</v>
+      </c>
+      <c r="K105" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -46867,7 +47179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N789"/>
+  <dimension ref="A1:N793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87918,6 +88230,214 @@
         <v>4.56</v>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D790" t="n">
+        <v>127.32</v>
+      </c>
+      <c r="E790" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="F790" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="G790" t="n">
+        <v>124.96</v>
+      </c>
+      <c r="H790" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I790" t="n">
+        <v>120</v>
+      </c>
+      <c r="J790" t="n">
+        <v>118.66</v>
+      </c>
+      <c r="K790" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N790" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="D791" t="n">
+        <v>307.98</v>
+      </c>
+      <c r="E791" t="n">
+        <v>-14.33</v>
+      </c>
+      <c r="F791" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="G791" t="n">
+        <v>298.76</v>
+      </c>
+      <c r="H791" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="I791" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="J791" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="K791" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N791" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D792" t="n">
+        <v>5849.28</v>
+      </c>
+      <c r="E792" t="n">
+        <v>-159.28</v>
+      </c>
+      <c r="F792" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G792" t="n">
+        <v>5872.27</v>
+      </c>
+      <c r="H792" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="I792" t="n">
+        <v>5635</v>
+      </c>
+      <c r="J792" t="n">
+        <v>5508.81</v>
+      </c>
+      <c r="K792" t="n">
+        <v>126.19</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N792" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D793" t="n">
+        <v>2673.2</v>
+      </c>
+      <c r="E793" t="n">
+        <v>-173.2</v>
+      </c>
+      <c r="F793" t="n">
+        <v>2515.8</v>
+      </c>
+      <c r="G793" t="n">
+        <v>2572.42</v>
+      </c>
+      <c r="H793" t="n">
+        <v>-56.62</v>
+      </c>
+      <c r="I793" t="n">
+        <v>2453</v>
+      </c>
+      <c r="J793" t="n">
+        <v>2426.16</v>
+      </c>
+      <c r="K793" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N793" t="n">
+        <v>6.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41478,31 +41478,31 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>121.9</v>
+        <v>116.3</v>
       </c>
       <c r="D790" t="n">
         <v>123.86</v>
       </c>
       <c r="E790" t="n">
-        <v>-1.96</v>
+        <v>-7.56</v>
       </c>
       <c r="F790" t="n">
-        <v>125.22</v>
+        <v>116.4</v>
       </c>
       <c r="G790" t="n">
         <v>123.86</v>
       </c>
       <c r="H790" t="n">
-        <v>1.36</v>
+        <v>-7.46</v>
       </c>
       <c r="I790" t="n">
-        <v>120</v>
+        <v>114.1</v>
       </c>
       <c r="J790" t="n">
         <v>117.48</v>
       </c>
       <c r="K790" t="n">
-        <v>2.52</v>
+        <v>-3.38</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -41511,11 +41511,11 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N790" t="n">
-        <v>1.58</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="791">
@@ -41530,31 +41530,31 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293.65</v>
+        <v>293</v>
       </c>
       <c r="D791" t="n">
         <v>301.97</v>
       </c>
       <c r="E791" t="n">
-        <v>-8.32</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="F791" t="n">
-        <v>295.4</v>
+        <v>295.2</v>
       </c>
       <c r="G791" t="n">
         <v>301.97</v>
       </c>
       <c r="H791" t="n">
-        <v>-6.57</v>
+        <v>-6.77</v>
       </c>
       <c r="I791" t="n">
-        <v>291.05</v>
+        <v>290.1</v>
       </c>
       <c r="J791" t="n">
         <v>286.67</v>
       </c>
       <c r="K791" t="n">
-        <v>4.38</v>
+        <v>3.43</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         </is>
       </c>
       <c r="N791" t="n">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="792">
@@ -41582,31 +41582,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5690</v>
+        <v>5741</v>
       </c>
       <c r="D792" t="n">
         <v>5650.63</v>
       </c>
       <c r="E792" t="n">
-        <v>39.37</v>
+        <v>90.37</v>
       </c>
       <c r="F792" t="n">
-        <v>5909</v>
+        <v>5755</v>
       </c>
       <c r="G792" t="n">
         <v>5650.63</v>
       </c>
       <c r="H792" t="n">
-        <v>258.37</v>
+        <v>104.37</v>
       </c>
       <c r="I792" t="n">
-        <v>5635</v>
+        <v>5492</v>
       </c>
       <c r="J792" t="n">
         <v>5443.83</v>
       </c>
       <c r="K792" t="n">
-        <v>191.17</v>
+        <v>48.17</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="793">
@@ -41643,22 +41643,22 @@
         <v>-90.41</v>
       </c>
       <c r="F793" t="n">
-        <v>2515.8</v>
+        <v>2521.7</v>
       </c>
       <c r="G793" t="n">
         <v>2590.41</v>
       </c>
       <c r="H793" t="n">
-        <v>-74.61</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="I793" t="n">
-        <v>2453</v>
+        <v>2455.1</v>
       </c>
       <c r="J793" t="n">
         <v>2439.34</v>
       </c>
       <c r="K793" t="n">
-        <v>13.66</v>
+        <v>15.76</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -47076,31 +47076,31 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>22888.95</v>
+        <v>23146.15</v>
       </c>
       <c r="D104" t="n">
         <v>22888.95</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>257.2</v>
       </c>
       <c r="F104" t="n">
-        <v>23175.25</v>
+        <v>23149.85</v>
       </c>
       <c r="G104" t="n">
         <v>23094.46</v>
       </c>
       <c r="H104" t="n">
-        <v>80.79000000000001</v>
+        <v>55.39</v>
       </c>
       <c r="I104" t="n">
-        <v>22845</v>
+        <v>22913.8</v>
       </c>
       <c r="J104" t="n">
         <v>22764.21</v>
       </c>
       <c r="K104" t="n">
-        <v>80.79000000000001</v>
+        <v>149.59</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="105">
@@ -47128,31 +47128,31 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>55488.1</v>
+        <v>55844</v>
       </c>
       <c r="D105" t="n">
         <v>55488.1</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>355.9</v>
       </c>
       <c r="F105" t="n">
-        <v>55883.7</v>
+        <v>55989.55</v>
       </c>
       <c r="G105" t="n">
         <v>55804.16</v>
       </c>
       <c r="H105" t="n">
-        <v>79.54000000000001</v>
+        <v>185.39</v>
       </c>
       <c r="I105" t="n">
-        <v>55331.1</v>
+        <v>55526.3</v>
       </c>
       <c r="J105" t="n">
         <v>55251.56</v>
       </c>
       <c r="K105" t="n">
-        <v>79.54000000000001</v>
+        <v>274.74</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -88242,31 +88242,31 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>121.9</v>
+        <v>116.3</v>
       </c>
       <c r="D790" t="n">
         <v>127.32</v>
       </c>
       <c r="E790" t="n">
-        <v>-5.42</v>
+        <v>-11.02</v>
       </c>
       <c r="F790" t="n">
-        <v>125.22</v>
+        <v>116.4</v>
       </c>
       <c r="G790" t="n">
         <v>124.96</v>
       </c>
       <c r="H790" t="n">
-        <v>0.26</v>
+        <v>-8.56</v>
       </c>
       <c r="I790" t="n">
-        <v>120</v>
+        <v>114.1</v>
       </c>
       <c r="J790" t="n">
         <v>118.66</v>
       </c>
       <c r="K790" t="n">
-        <v>1.34</v>
+        <v>-4.56</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -88279,7 +88279,7 @@
         </is>
       </c>
       <c r="N790" t="n">
-        <v>4.26</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="791">
@@ -88294,31 +88294,31 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293.65</v>
+        <v>293</v>
       </c>
       <c r="D791" t="n">
         <v>307.98</v>
       </c>
       <c r="E791" t="n">
-        <v>-14.33</v>
+        <v>-14.98</v>
       </c>
       <c r="F791" t="n">
-        <v>295.4</v>
+        <v>295.2</v>
       </c>
       <c r="G791" t="n">
         <v>298.76</v>
       </c>
       <c r="H791" t="n">
-        <v>-3.36</v>
+        <v>-3.56</v>
       </c>
       <c r="I791" t="n">
-        <v>291.05</v>
+        <v>290.1</v>
       </c>
       <c r="J791" t="n">
         <v>287.55</v>
       </c>
       <c r="K791" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -88331,7 +88331,7 @@
         </is>
       </c>
       <c r="N791" t="n">
-        <v>4.65</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="792">
@@ -88346,31 +88346,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5690</v>
+        <v>5741</v>
       </c>
       <c r="D792" t="n">
         <v>5849.28</v>
       </c>
       <c r="E792" t="n">
-        <v>-159.28</v>
+        <v>-108.28</v>
       </c>
       <c r="F792" t="n">
-        <v>5909</v>
+        <v>5755</v>
       </c>
       <c r="G792" t="n">
         <v>5872.27</v>
       </c>
       <c r="H792" t="n">
-        <v>36.73</v>
+        <v>-117.27</v>
       </c>
       <c r="I792" t="n">
-        <v>5635</v>
+        <v>5492</v>
       </c>
       <c r="J792" t="n">
         <v>5508.81</v>
       </c>
       <c r="K792" t="n">
-        <v>126.19</v>
+        <v>-16.81</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -88383,7 +88383,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="793">
@@ -88407,22 +88407,22 @@
         <v>-173.2</v>
       </c>
       <c r="F793" t="n">
-        <v>2515.8</v>
+        <v>2521.7</v>
       </c>
       <c r="G793" t="n">
         <v>2572.42</v>
       </c>
       <c r="H793" t="n">
-        <v>-56.62</v>
+        <v>-50.72</v>
       </c>
       <c r="I793" t="n">
-        <v>2453</v>
+        <v>2455.1</v>
       </c>
       <c r="J793" t="n">
         <v>2426.16</v>
       </c>
       <c r="K793" t="n">
-        <v>26.84</v>
+        <v>28.94</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41474,35 +41474,35 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C790" t="n">
-        <v>116.3</v>
+        <v>293.65</v>
       </c>
       <c r="D790" t="n">
-        <v>123.86</v>
+        <v>287.21</v>
       </c>
       <c r="E790" t="n">
-        <v>-7.56</v>
+        <v>6.44</v>
       </c>
       <c r="F790" t="n">
-        <v>116.4</v>
+        <v>295.4</v>
       </c>
       <c r="G790" t="n">
-        <v>123.86</v>
+        <v>294.23</v>
       </c>
       <c r="H790" t="n">
-        <v>-7.46</v>
+        <v>1.17</v>
       </c>
       <c r="I790" t="n">
-        <v>114.1</v>
+        <v>291.05</v>
       </c>
       <c r="J790" t="n">
-        <v>117.48</v>
+        <v>288.65</v>
       </c>
       <c r="K790" t="n">
-        <v>-3.38</v>
+        <v>2.4</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -41511,11 +41511,11 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N790" t="n">
-        <v>6.1</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="791">
@@ -41526,35 +41526,35 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293</v>
+        <v>121.9</v>
       </c>
       <c r="D791" t="n">
-        <v>301.97</v>
+        <v>115.38</v>
       </c>
       <c r="E791" t="n">
-        <v>-8.970000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="F791" t="n">
-        <v>295.2</v>
+        <v>125.22</v>
       </c>
       <c r="G791" t="n">
-        <v>301.97</v>
+        <v>117.17</v>
       </c>
       <c r="H791" t="n">
-        <v>-6.77</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I791" t="n">
-        <v>290.1</v>
+        <v>120</v>
       </c>
       <c r="J791" t="n">
-        <v>286.67</v>
+        <v>118.29</v>
       </c>
       <c r="K791" t="n">
-        <v>3.43</v>
+        <v>1.71</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -41563,11 +41563,11 @@
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N791" t="n">
-        <v>2.97</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="792">
@@ -41582,31 +41582,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5741</v>
+        <v>5690</v>
       </c>
       <c r="D792" t="n">
-        <v>5650.63</v>
+        <v>5827.23</v>
       </c>
       <c r="E792" t="n">
-        <v>90.37</v>
+        <v>-137.23</v>
       </c>
       <c r="F792" t="n">
-        <v>5755</v>
+        <v>5909</v>
       </c>
       <c r="G792" t="n">
-        <v>5650.63</v>
+        <v>5827.23</v>
       </c>
       <c r="H792" t="n">
-        <v>104.37</v>
+        <v>81.77</v>
       </c>
       <c r="I792" t="n">
-        <v>5492</v>
+        <v>5635</v>
       </c>
       <c r="J792" t="n">
-        <v>5443.83</v>
+        <v>5481.45</v>
       </c>
       <c r="K792" t="n">
-        <v>48.17</v>
+        <v>153.55</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="793">
@@ -41637,28 +41637,28 @@
         <v>2500</v>
       </c>
       <c r="D793" t="n">
-        <v>2590.41</v>
+        <v>2432.05</v>
       </c>
       <c r="E793" t="n">
-        <v>-90.41</v>
+        <v>67.95</v>
       </c>
       <c r="F793" t="n">
-        <v>2521.7</v>
+        <v>2515.8</v>
       </c>
       <c r="G793" t="n">
-        <v>2590.41</v>
+        <v>2503.64</v>
       </c>
       <c r="H793" t="n">
-        <v>-68.70999999999999</v>
+        <v>12.16</v>
       </c>
       <c r="I793" t="n">
-        <v>2455.1</v>
+        <v>2453</v>
       </c>
       <c r="J793" t="n">
-        <v>2439.34</v>
+        <v>2456.14</v>
       </c>
       <c r="K793" t="n">
-        <v>15.76</v>
+        <v>-3.14</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         </is>
       </c>
       <c r="N793" t="n">
-        <v>3.49</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
@@ -47076,31 +47076,31 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>23146.15</v>
+        <v>22888.95</v>
       </c>
       <c r="D104" t="n">
         <v>22888.95</v>
       </c>
       <c r="E104" t="n">
-        <v>257.2</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>23149.85</v>
+        <v>23175.25</v>
       </c>
       <c r="G104" t="n">
         <v>23094.46</v>
       </c>
       <c r="H104" t="n">
-        <v>55.39</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>22913.8</v>
+        <v>22845</v>
       </c>
       <c r="J104" t="n">
         <v>22764.21</v>
       </c>
       <c r="K104" t="n">
-        <v>149.59</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -47128,31 +47128,31 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>55844</v>
+        <v>55488.1</v>
       </c>
       <c r="D105" t="n">
         <v>55488.1</v>
       </c>
       <c r="E105" t="n">
-        <v>355.9</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>55989.55</v>
+        <v>55883.7</v>
       </c>
       <c r="G105" t="n">
         <v>55804.16</v>
       </c>
       <c r="H105" t="n">
-        <v>185.39</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>55526.3</v>
+        <v>55331.1</v>
       </c>
       <c r="J105" t="n">
         <v>55251.56</v>
       </c>
       <c r="K105" t="n">
-        <v>274.74</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88242,31 +88242,31 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>116.3</v>
+        <v>121.9</v>
       </c>
       <c r="D790" t="n">
-        <v>127.32</v>
+        <v>118.6</v>
       </c>
       <c r="E790" t="n">
-        <v>-11.02</v>
+        <v>3.3</v>
       </c>
       <c r="F790" t="n">
-        <v>116.4</v>
+        <v>125.22</v>
       </c>
       <c r="G790" t="n">
-        <v>124.96</v>
+        <v>124.62</v>
       </c>
       <c r="H790" t="n">
-        <v>-8.56</v>
+        <v>0.6</v>
       </c>
       <c r="I790" t="n">
-        <v>114.1</v>
+        <v>120</v>
       </c>
       <c r="J790" t="n">
-        <v>118.66</v>
+        <v>119.48</v>
       </c>
       <c r="K790" t="n">
-        <v>-4.56</v>
+        <v>0.52</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -88275,11 +88275,11 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N790" t="n">
-        <v>8.66</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="791">
@@ -88294,31 +88294,31 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293</v>
+        <v>293.65</v>
       </c>
       <c r="D791" t="n">
-        <v>307.98</v>
+        <v>292.92</v>
       </c>
       <c r="E791" t="n">
-        <v>-14.98</v>
+        <v>0.73</v>
       </c>
       <c r="F791" t="n">
-        <v>295.2</v>
+        <v>295.4</v>
       </c>
       <c r="G791" t="n">
-        <v>298.76</v>
+        <v>297.95</v>
       </c>
       <c r="H791" t="n">
-        <v>-3.56</v>
+        <v>-2.55</v>
       </c>
       <c r="I791" t="n">
-        <v>290.1</v>
+        <v>291.05</v>
       </c>
       <c r="J791" t="n">
-        <v>287.55</v>
+        <v>289.53</v>
       </c>
       <c r="K791" t="n">
-        <v>2.55</v>
+        <v>1.52</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -88327,11 +88327,11 @@
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N791" t="n">
-        <v>4.86</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="792">
@@ -88346,31 +88346,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5741</v>
+        <v>5690</v>
       </c>
       <c r="D792" t="n">
-        <v>5849.28</v>
+        <v>6032.09</v>
       </c>
       <c r="E792" t="n">
-        <v>-108.28</v>
+        <v>-342.09</v>
       </c>
       <c r="F792" t="n">
-        <v>5755</v>
+        <v>5909</v>
       </c>
       <c r="G792" t="n">
-        <v>5872.27</v>
+        <v>5856.32</v>
       </c>
       <c r="H792" t="n">
-        <v>-117.27</v>
+        <v>52.68</v>
       </c>
       <c r="I792" t="n">
-        <v>5492</v>
+        <v>5635</v>
       </c>
       <c r="J792" t="n">
-        <v>5508.81</v>
+        <v>5546.88</v>
       </c>
       <c r="K792" t="n">
-        <v>-16.81</v>
+        <v>88.12</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -88379,11 +88379,11 @@
       </c>
       <c r="M792" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N792" t="n">
-        <v>1.85</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="793">
@@ -88401,28 +88401,28 @@
         <v>2500</v>
       </c>
       <c r="D793" t="n">
-        <v>2673.2</v>
+        <v>2509.78</v>
       </c>
       <c r="E793" t="n">
-        <v>-173.2</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="F793" t="n">
-        <v>2521.7</v>
+        <v>2515.8</v>
       </c>
       <c r="G793" t="n">
-        <v>2572.42</v>
+        <v>2565.44</v>
       </c>
       <c r="H793" t="n">
-        <v>-50.72</v>
+        <v>-49.64</v>
       </c>
       <c r="I793" t="n">
-        <v>2455.1</v>
+        <v>2453</v>
       </c>
       <c r="J793" t="n">
-        <v>2426.16</v>
+        <v>2442.93</v>
       </c>
       <c r="K793" t="n">
-        <v>28.94</v>
+        <v>10.07</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -88431,11 +88431,11 @@
       </c>
       <c r="M793" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N793" t="n">
-        <v>6.48</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N793"/>
+  <dimension ref="A1:N797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41672,6 +41672,214 @@
       </c>
       <c r="N793" t="n">
         <v>2.79</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>295</v>
+      </c>
+      <c r="D794" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="E794" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="F794" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="G794" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="H794" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="I794" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="J794" t="n">
+        <v>292.51</v>
+      </c>
+      <c r="K794" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N794" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>2575</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2668.12</v>
+      </c>
+      <c r="E795" t="n">
+        <v>-93.12</v>
+      </c>
+      <c r="F795" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G795" t="n">
+        <v>2668.12</v>
+      </c>
+      <c r="H795" t="n">
+        <v>-88.12</v>
+      </c>
+      <c r="I795" t="n">
+        <v>2491</v>
+      </c>
+      <c r="J795" t="n">
+        <v>2566.89</v>
+      </c>
+      <c r="K795" t="n">
+        <v>-75.89</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N795" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D796" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="E796" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="F796" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="G796" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="H796" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="I796" t="n">
+        <v>121.38</v>
+      </c>
+      <c r="J796" t="n">
+        <v>119.28</v>
+      </c>
+      <c r="K796" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N796" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>5858.5</v>
+      </c>
+      <c r="D797" t="n">
+        <v>5766.3</v>
+      </c>
+      <c r="E797" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F797" t="n">
+        <v>5868</v>
+      </c>
+      <c r="G797" t="n">
+        <v>5830.86</v>
+      </c>
+      <c r="H797" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="I797" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J797" t="n">
+        <v>5673.85</v>
+      </c>
+      <c r="K797" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N797" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -41685,7 +41893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47165,6 +47373,110 @@
         </is>
       </c>
       <c r="N105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="D106" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>23120.9</v>
+      </c>
+      <c r="G106" t="n">
+        <v>23071.54</v>
+      </c>
+      <c r="H106" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="I106" t="n">
+        <v>22649.9</v>
+      </c>
+      <c r="J106" t="n">
+        <v>22600.54</v>
+      </c>
+      <c r="K106" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>54976.9</v>
+      </c>
+      <c r="D107" t="n">
+        <v>54976.9</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>55867.45</v>
+      </c>
+      <c r="G107" t="n">
+        <v>55664.09</v>
+      </c>
+      <c r="H107" t="n">
+        <v>203.36</v>
+      </c>
+      <c r="I107" t="n">
+        <v>54696.45</v>
+      </c>
+      <c r="J107" t="n">
+        <v>54493.09</v>
+      </c>
+      <c r="K107" t="n">
+        <v>203.36</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -47179,7 +47491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N793"/>
+  <dimension ref="A1:N797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88438,6 +88750,214 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D794" t="n">
+        <v>134.47</v>
+      </c>
+      <c r="E794" t="n">
+        <v>-11.97</v>
+      </c>
+      <c r="F794" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="G794" t="n">
+        <v>127.31</v>
+      </c>
+      <c r="H794" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="I794" t="n">
+        <v>121.38</v>
+      </c>
+      <c r="J794" t="n">
+        <v>120.56</v>
+      </c>
+      <c r="K794" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N794" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>295</v>
+      </c>
+      <c r="D795" t="n">
+        <v>309.73</v>
+      </c>
+      <c r="E795" t="n">
+        <v>-14.73</v>
+      </c>
+      <c r="F795" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="G795" t="n">
+        <v>303.16</v>
+      </c>
+      <c r="H795" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="I795" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="J795" t="n">
+        <v>292.92</v>
+      </c>
+      <c r="K795" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N795" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>2575</v>
+      </c>
+      <c r="D796" t="n">
+        <v>2752.28</v>
+      </c>
+      <c r="E796" t="n">
+        <v>-177.28</v>
+      </c>
+      <c r="F796" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G796" t="n">
+        <v>2678.18</v>
+      </c>
+      <c r="H796" t="n">
+        <v>-98.18000000000001</v>
+      </c>
+      <c r="I796" t="n">
+        <v>2491</v>
+      </c>
+      <c r="J796" t="n">
+        <v>2532.56</v>
+      </c>
+      <c r="K796" t="n">
+        <v>-41.56</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N796" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>5858.5</v>
+      </c>
+      <c r="D797" t="n">
+        <v>5977.04</v>
+      </c>
+      <c r="E797" t="n">
+        <v>-118.54</v>
+      </c>
+      <c r="F797" t="n">
+        <v>5868</v>
+      </c>
+      <c r="G797" t="n">
+        <v>6121.66</v>
+      </c>
+      <c r="H797" t="n">
+        <v>-253.66</v>
+      </c>
+      <c r="I797" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J797" t="n">
+        <v>5740.44</v>
+      </c>
+      <c r="K797" t="n">
+        <v>-50.44</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N797" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41686,31 +41686,31 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>295</v>
+        <v>293.65</v>
       </c>
       <c r="D794" t="n">
         <v>304.03</v>
       </c>
       <c r="E794" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.38</v>
       </c>
       <c r="F794" t="n">
-        <v>299.2</v>
+        <v>295.4</v>
       </c>
       <c r="G794" t="n">
         <v>304.03</v>
       </c>
       <c r="H794" t="n">
-        <v>-4.83</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="I794" t="n">
-        <v>294.1</v>
+        <v>291.05</v>
       </c>
       <c r="J794" t="n">
         <v>292.51</v>
       </c>
       <c r="K794" t="n">
-        <v>1.59</v>
+        <v>-1.46</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="795">
@@ -41738,31 +41738,31 @@
         </is>
       </c>
       <c r="C795" t="n">
-        <v>2575</v>
+        <v>2500</v>
       </c>
       <c r="D795" t="n">
         <v>2668.12</v>
       </c>
       <c r="E795" t="n">
-        <v>-93.12</v>
+        <v>-168.12</v>
       </c>
       <c r="F795" t="n">
-        <v>2580</v>
+        <v>2515.8</v>
       </c>
       <c r="G795" t="n">
         <v>2668.12</v>
       </c>
       <c r="H795" t="n">
-        <v>-88.12</v>
+        <v>-152.32</v>
       </c>
       <c r="I795" t="n">
-        <v>2491</v>
+        <v>2453</v>
       </c>
       <c r="J795" t="n">
         <v>2566.89</v>
       </c>
       <c r="K795" t="n">
-        <v>-75.89</v>
+        <v>-113.89</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         </is>
       </c>
       <c r="N795" t="n">
-        <v>3.49</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="796">
@@ -41790,31 +41790,31 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>122.5</v>
+        <v>121.9</v>
       </c>
       <c r="D796" t="n">
         <v>130.46</v>
       </c>
       <c r="E796" t="n">
-        <v>-7.96</v>
+        <v>-8.56</v>
       </c>
       <c r="F796" t="n">
-        <v>124.2</v>
+        <v>125.22</v>
       </c>
       <c r="G796" t="n">
         <v>130.46</v>
       </c>
       <c r="H796" t="n">
-        <v>-6.26</v>
+        <v>-5.24</v>
       </c>
       <c r="I796" t="n">
-        <v>121.38</v>
+        <v>120</v>
       </c>
       <c r="J796" t="n">
         <v>119.28</v>
       </c>
       <c r="K796" t="n">
-        <v>2.1</v>
+        <v>0.72</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         </is>
       </c>
       <c r="N796" t="n">
-        <v>6.1</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="797">
@@ -41842,31 +41842,31 @@
         </is>
       </c>
       <c r="C797" t="n">
-        <v>5858.5</v>
+        <v>5690</v>
       </c>
       <c r="D797" t="n">
         <v>5766.3</v>
       </c>
       <c r="E797" t="n">
-        <v>92.2</v>
+        <v>-76.3</v>
       </c>
       <c r="F797" t="n">
-        <v>5868</v>
+        <v>5909</v>
       </c>
       <c r="G797" t="n">
         <v>5830.86</v>
       </c>
       <c r="H797" t="n">
-        <v>37.14</v>
+        <v>78.14</v>
       </c>
       <c r="I797" t="n">
-        <v>5690</v>
+        <v>5635</v>
       </c>
       <c r="J797" t="n">
         <v>5673.85</v>
       </c>
       <c r="K797" t="n">
-        <v>16.15</v>
+        <v>-38.85</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         </is>
       </c>
       <c r="N797" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
@@ -47388,31 +47388,31 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>22811.35</v>
+        <v>22888.95</v>
       </c>
       <c r="D106" t="n">
         <v>22811.35</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>23120.9</v>
+        <v>23175.25</v>
       </c>
       <c r="G106" t="n">
         <v>23071.54</v>
       </c>
       <c r="H106" t="n">
-        <v>49.36</v>
+        <v>103.71</v>
       </c>
       <c r="I106" t="n">
-        <v>22649.9</v>
+        <v>22845</v>
       </c>
       <c r="J106" t="n">
         <v>22600.54</v>
       </c>
       <c r="K106" t="n">
-        <v>49.36</v>
+        <v>244.46</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="107">
@@ -47440,31 +47440,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>54976.9</v>
+        <v>55488.1</v>
       </c>
       <c r="D107" t="n">
         <v>54976.9</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>511.2</v>
       </c>
       <c r="F107" t="n">
-        <v>55867.45</v>
+        <v>55883.7</v>
       </c>
       <c r="G107" t="n">
         <v>55664.09</v>
       </c>
       <c r="H107" t="n">
-        <v>203.36</v>
+        <v>219.61</v>
       </c>
       <c r="I107" t="n">
-        <v>54696.45</v>
+        <v>55331.1</v>
       </c>
       <c r="J107" t="n">
         <v>54493.09</v>
       </c>
       <c r="K107" t="n">
-        <v>203.36</v>
+        <v>838.01</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -88762,31 +88762,31 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>122.5</v>
+        <v>121.9</v>
       </c>
       <c r="D794" t="n">
         <v>134.47</v>
       </c>
       <c r="E794" t="n">
-        <v>-11.97</v>
+        <v>-12.57</v>
       </c>
       <c r="F794" t="n">
-        <v>124.2</v>
+        <v>125.22</v>
       </c>
       <c r="G794" t="n">
         <v>127.31</v>
       </c>
       <c r="H794" t="n">
-        <v>-3.11</v>
+        <v>-2.09</v>
       </c>
       <c r="I794" t="n">
-        <v>121.38</v>
+        <v>120</v>
       </c>
       <c r="J794" t="n">
         <v>120.56</v>
       </c>
       <c r="K794" t="n">
-        <v>0.82</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
@@ -88799,7 +88799,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>8.9</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="795">
@@ -88814,31 +88814,31 @@
         </is>
       </c>
       <c r="C795" t="n">
-        <v>295</v>
+        <v>293.65</v>
       </c>
       <c r="D795" t="n">
         <v>309.73</v>
       </c>
       <c r="E795" t="n">
-        <v>-14.73</v>
+        <v>-16.08</v>
       </c>
       <c r="F795" t="n">
-        <v>299.2</v>
+        <v>295.4</v>
       </c>
       <c r="G795" t="n">
         <v>303.16</v>
       </c>
       <c r="H795" t="n">
-        <v>-3.96</v>
+        <v>-7.76</v>
       </c>
       <c r="I795" t="n">
-        <v>294.1</v>
+        <v>291.05</v>
       </c>
       <c r="J795" t="n">
         <v>292.92</v>
       </c>
       <c r="K795" t="n">
-        <v>1.18</v>
+        <v>-1.87</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
@@ -88851,7 +88851,7 @@
         </is>
       </c>
       <c r="N795" t="n">
-        <v>4.76</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="796">
@@ -88866,31 +88866,31 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>2575</v>
+        <v>2500</v>
       </c>
       <c r="D796" t="n">
         <v>2752.28</v>
       </c>
       <c r="E796" t="n">
-        <v>-177.28</v>
+        <v>-252.28</v>
       </c>
       <c r="F796" t="n">
-        <v>2580</v>
+        <v>2515.8</v>
       </c>
       <c r="G796" t="n">
         <v>2678.18</v>
       </c>
       <c r="H796" t="n">
-        <v>-98.18000000000001</v>
+        <v>-162.38</v>
       </c>
       <c r="I796" t="n">
-        <v>2491</v>
+        <v>2453</v>
       </c>
       <c r="J796" t="n">
         <v>2532.56</v>
       </c>
       <c r="K796" t="n">
-        <v>-41.56</v>
+        <v>-79.56</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
@@ -88903,7 +88903,7 @@
         </is>
       </c>
       <c r="N796" t="n">
-        <v>6.44</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="797">
@@ -88918,31 +88918,31 @@
         </is>
       </c>
       <c r="C797" t="n">
-        <v>5858.5</v>
+        <v>5690</v>
       </c>
       <c r="D797" t="n">
         <v>5977.04</v>
       </c>
       <c r="E797" t="n">
-        <v>-118.54</v>
+        <v>-287.04</v>
       </c>
       <c r="F797" t="n">
-        <v>5868</v>
+        <v>5909</v>
       </c>
       <c r="G797" t="n">
         <v>6121.66</v>
       </c>
       <c r="H797" t="n">
-        <v>-253.66</v>
+        <v>-212.66</v>
       </c>
       <c r="I797" t="n">
-        <v>5690</v>
+        <v>5635</v>
       </c>
       <c r="J797" t="n">
         <v>5740.44</v>
       </c>
       <c r="K797" t="n">
-        <v>-50.44</v>
+        <v>-105.44</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>
@@ -88951,11 +88951,11 @@
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N797" t="n">
-        <v>1.98</v>
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N797"/>
+  <dimension ref="A1:N802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41880,6 +41880,266 @@
       </c>
       <c r="N797" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="D798" t="n">
+        <v>282.73</v>
+      </c>
+      <c r="E798" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="F798" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="G798" t="n">
+        <v>284.13</v>
+      </c>
+      <c r="H798" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="I798" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="J798" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="K798" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N798" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>11293</v>
+      </c>
+      <c r="D799" t="n">
+        <v>10933.7</v>
+      </c>
+      <c r="E799" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="F799" t="n">
+        <v>11420</v>
+      </c>
+      <c r="G799" t="n">
+        <v>10933.7</v>
+      </c>
+      <c r="H799" t="n">
+        <v>486.3</v>
+      </c>
+      <c r="I799" t="n">
+        <v>10834</v>
+      </c>
+      <c r="J799" t="n">
+        <v>10899.86</v>
+      </c>
+      <c r="K799" t="n">
+        <v>-65.86</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N799" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D800" t="n">
+        <v>5709.87</v>
+      </c>
+      <c r="E800" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="F800" t="n">
+        <v>5906.5</v>
+      </c>
+      <c r="G800" t="n">
+        <v>5709.87</v>
+      </c>
+      <c r="H800" t="n">
+        <v>196.63</v>
+      </c>
+      <c r="I800" t="n">
+        <v>5733.5</v>
+      </c>
+      <c r="J800" t="n">
+        <v>5464.94</v>
+      </c>
+      <c r="K800" t="n">
+        <v>268.56</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N800" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D801" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="E801" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F801" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G801" t="n">
+        <v>120.13</v>
+      </c>
+      <c r="H801" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I801" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="J801" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="K801" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N801" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2360.75</v>
+      </c>
+      <c r="E802" t="n">
+        <v>138.75</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2601.4</v>
+      </c>
+      <c r="G802" t="n">
+        <v>2423.86</v>
+      </c>
+      <c r="H802" t="n">
+        <v>177.54</v>
+      </c>
+      <c r="I802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="J802" t="n">
+        <v>2390.22</v>
+      </c>
+      <c r="K802" t="n">
+        <v>109.28</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N802" t="n">
+        <v>5.88</v>
       </c>
     </row>
   </sheetData>
@@ -41893,7 +42153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N107"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47478,6 +47738,110 @@
       </c>
       <c r="N107" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="D108" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>22784.7</v>
+      </c>
+      <c r="G108" t="n">
+        <v>22796.61</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="I108" t="n">
+        <v>22554.85</v>
+      </c>
+      <c r="J108" t="n">
+        <v>22566.76</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>54925.7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>54925.7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>55134.45</v>
+      </c>
+      <c r="G109" t="n">
+        <v>55220.31</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-85.86</v>
+      </c>
+      <c r="I109" t="n">
+        <v>54459.35</v>
+      </c>
+      <c r="J109" t="n">
+        <v>54545.21</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-85.86</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -47491,7 +47855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N797"/>
+  <dimension ref="A1:N802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88958,6 +89322,266 @@
         <v>4.8</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="D798" t="n">
+        <v>287.88</v>
+      </c>
+      <c r="E798" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F798" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="G798" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="H798" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I798" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="J798" t="n">
+        <v>283.82</v>
+      </c>
+      <c r="K798" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N798" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>11293</v>
+      </c>
+      <c r="D799" t="n">
+        <v>11190.09</v>
+      </c>
+      <c r="E799" t="n">
+        <v>102.91</v>
+      </c>
+      <c r="F799" t="n">
+        <v>11420</v>
+      </c>
+      <c r="G799" t="n">
+        <v>11345.44</v>
+      </c>
+      <c r="H799" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="I799" t="n">
+        <v>10834</v>
+      </c>
+      <c r="J799" t="n">
+        <v>10994.12</v>
+      </c>
+      <c r="K799" t="n">
+        <v>-160.12</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N799" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D800" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="E800" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F800" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G800" t="n">
+        <v>123.84</v>
+      </c>
+      <c r="H800" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="I800" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="J800" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="K800" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N800" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D801" t="n">
+        <v>5922.02</v>
+      </c>
+      <c r="E801" t="n">
+        <v>-181.52</v>
+      </c>
+      <c r="F801" t="n">
+        <v>5906.5</v>
+      </c>
+      <c r="G801" t="n">
+        <v>5841.39</v>
+      </c>
+      <c r="H801" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="I801" t="n">
+        <v>5733.5</v>
+      </c>
+      <c r="J801" t="n">
+        <v>5531.8</v>
+      </c>
+      <c r="K801" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N801" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2437.95</v>
+      </c>
+      <c r="E802" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2601.4</v>
+      </c>
+      <c r="G802" t="n">
+        <v>2532.94</v>
+      </c>
+      <c r="H802" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="I802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="J802" t="n">
+        <v>2416.65</v>
+      </c>
+      <c r="K802" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N802" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -41894,31 +41894,31 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>290.4</v>
+        <v>295</v>
       </c>
       <c r="D798" t="n">
         <v>282.73</v>
       </c>
       <c r="E798" t="n">
-        <v>7.67</v>
+        <v>12.27</v>
       </c>
       <c r="F798" t="n">
-        <v>293.1</v>
+        <v>299.2</v>
       </c>
       <c r="G798" t="n">
         <v>284.13</v>
       </c>
       <c r="H798" t="n">
-        <v>8.970000000000001</v>
+        <v>15.07</v>
       </c>
       <c r="I798" t="n">
-        <v>288.5</v>
+        <v>294.1</v>
       </c>
       <c r="J798" t="n">
         <v>281.75</v>
       </c>
       <c r="K798" t="n">
-        <v>6.75</v>
+        <v>12.35</v>
       </c>
       <c r="L798" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="N798" t="n">
-        <v>2.71</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="799">
@@ -41946,31 +41946,31 @@
         </is>
       </c>
       <c r="C799" t="n">
-        <v>11293</v>
+        <v>10975</v>
       </c>
       <c r="D799" t="n">
         <v>10933.7</v>
       </c>
       <c r="E799" t="n">
-        <v>359.3</v>
+        <v>41.3</v>
       </c>
       <c r="F799" t="n">
-        <v>11420</v>
+        <v>11255</v>
       </c>
       <c r="G799" t="n">
         <v>10933.7</v>
       </c>
       <c r="H799" t="n">
-        <v>486.3</v>
+        <v>321.3</v>
       </c>
       <c r="I799" t="n">
-        <v>10834</v>
+        <v>10924</v>
       </c>
       <c r="J799" t="n">
         <v>10899.86</v>
       </c>
       <c r="K799" t="n">
-        <v>-65.86</v>
+        <v>24.14</v>
       </c>
       <c r="L799" t="inlineStr">
         <is>
@@ -41979,11 +41979,11 @@
       </c>
       <c r="M799" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N799" t="n">
-        <v>3.29</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="800">
@@ -41998,31 +41998,31 @@
         </is>
       </c>
       <c r="C800" t="n">
-        <v>5740.5</v>
+        <v>5858.5</v>
       </c>
       <c r="D800" t="n">
         <v>5709.87</v>
       </c>
       <c r="E800" t="n">
-        <v>30.63</v>
+        <v>148.63</v>
       </c>
       <c r="F800" t="n">
-        <v>5906.5</v>
+        <v>5868</v>
       </c>
       <c r="G800" t="n">
         <v>5709.87</v>
       </c>
       <c r="H800" t="n">
-        <v>196.63</v>
+        <v>158.13</v>
       </c>
       <c r="I800" t="n">
-        <v>5733.5</v>
+        <v>5690</v>
       </c>
       <c r="J800" t="n">
         <v>5464.94</v>
       </c>
       <c r="K800" t="n">
-        <v>268.56</v>
+        <v>225.06</v>
       </c>
       <c r="L800" t="inlineStr">
         <is>
@@ -42031,11 +42031,11 @@
       </c>
       <c r="M800" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N800" t="n">
-        <v>0.54</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="801">
@@ -42059,22 +42059,22 @@
         <v>7.12</v>
       </c>
       <c r="F801" t="n">
-        <v>122.5</v>
+        <v>124.2</v>
       </c>
       <c r="G801" t="n">
         <v>120.13</v>
       </c>
       <c r="H801" t="n">
-        <v>2.37</v>
+        <v>4.07</v>
       </c>
       <c r="I801" t="n">
-        <v>120.55</v>
+        <v>121.38</v>
       </c>
       <c r="J801" t="n">
         <v>118.25</v>
       </c>
       <c r="K801" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="L801" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N801" t="n">
@@ -42102,31 +42102,31 @@
         </is>
       </c>
       <c r="C802" t="n">
-        <v>2499.5</v>
+        <v>2575</v>
       </c>
       <c r="D802" t="n">
         <v>2360.75</v>
       </c>
       <c r="E802" t="n">
-        <v>138.75</v>
+        <v>214.25</v>
       </c>
       <c r="F802" t="n">
-        <v>2601.4</v>
+        <v>2580</v>
       </c>
       <c r="G802" t="n">
         <v>2423.86</v>
       </c>
       <c r="H802" t="n">
-        <v>177.54</v>
+        <v>156.14</v>
       </c>
       <c r="I802" t="n">
-        <v>2499.5</v>
+        <v>2491</v>
       </c>
       <c r="J802" t="n">
         <v>2390.22</v>
       </c>
       <c r="K802" t="n">
-        <v>109.28</v>
+        <v>100.78</v>
       </c>
       <c r="L802" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         </is>
       </c>
       <c r="N802" t="n">
-        <v>5.88</v>
+        <v>9.08</v>
       </c>
     </row>
   </sheetData>
@@ -47752,31 +47752,31 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>22687.65</v>
+        <v>22811.35</v>
       </c>
       <c r="D108" t="n">
         <v>22687.65</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>123.7</v>
       </c>
       <c r="F108" t="n">
-        <v>22784.7</v>
+        <v>23120.9</v>
       </c>
       <c r="G108" t="n">
         <v>22796.61</v>
       </c>
       <c r="H108" t="n">
-        <v>-11.91</v>
+        <v>324.29</v>
       </c>
       <c r="I108" t="n">
-        <v>22554.85</v>
+        <v>22649.9</v>
       </c>
       <c r="J108" t="n">
         <v>22566.76</v>
       </c>
       <c r="K108" t="n">
-        <v>-11.91</v>
+        <v>83.14</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="109">
@@ -47804,31 +47804,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>54925.7</v>
+        <v>54976.9</v>
       </c>
       <c r="D109" t="n">
         <v>54925.7</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="F109" t="n">
-        <v>55134.45</v>
+        <v>55867.45</v>
       </c>
       <c r="G109" t="n">
         <v>55220.31</v>
       </c>
       <c r="H109" t="n">
-        <v>-85.86</v>
+        <v>647.14</v>
       </c>
       <c r="I109" t="n">
-        <v>54459.35</v>
+        <v>54696.45</v>
       </c>
       <c r="J109" t="n">
         <v>54545.21</v>
       </c>
       <c r="K109" t="n">
-        <v>-85.86</v>
+        <v>151.24</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -89334,31 +89334,31 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>290.4</v>
+        <v>295</v>
       </c>
       <c r="D798" t="n">
         <v>287.88</v>
       </c>
       <c r="E798" t="n">
-        <v>2.52</v>
+        <v>7.12</v>
       </c>
       <c r="F798" t="n">
-        <v>293.1</v>
+        <v>299.2</v>
       </c>
       <c r="G798" t="n">
         <v>290.32</v>
       </c>
       <c r="H798" t="n">
-        <v>2.78</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="I798" t="n">
-        <v>288.5</v>
+        <v>294.1</v>
       </c>
       <c r="J798" t="n">
         <v>283.82</v>
       </c>
       <c r="K798" t="n">
-        <v>4.68</v>
+        <v>10.28</v>
       </c>
       <c r="L798" t="inlineStr">
         <is>
@@ -89371,7 +89371,7 @@
         </is>
       </c>
       <c r="N798" t="n">
-        <v>0.88</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="799">
@@ -89386,31 +89386,31 @@
         </is>
       </c>
       <c r="C799" t="n">
-        <v>11293</v>
+        <v>10975</v>
       </c>
       <c r="D799" t="n">
         <v>11190.09</v>
       </c>
       <c r="E799" t="n">
-        <v>102.91</v>
+        <v>-215.09</v>
       </c>
       <c r="F799" t="n">
-        <v>11420</v>
+        <v>11255</v>
       </c>
       <c r="G799" t="n">
         <v>11345.44</v>
       </c>
       <c r="H799" t="n">
-        <v>74.56</v>
+        <v>-90.44</v>
       </c>
       <c r="I799" t="n">
-        <v>10834</v>
+        <v>10924</v>
       </c>
       <c r="J799" t="n">
         <v>10994.12</v>
       </c>
       <c r="K799" t="n">
-        <v>-160.12</v>
+        <v>-70.12</v>
       </c>
       <c r="L799" t="inlineStr">
         <is>
@@ -89423,7 +89423,7 @@
         </is>
       </c>
       <c r="N799" t="n">
-        <v>0.92</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="800">
@@ -89447,22 +89447,22 @@
         <v>3.65</v>
       </c>
       <c r="F800" t="n">
-        <v>122.5</v>
+        <v>124.2</v>
       </c>
       <c r="G800" t="n">
         <v>123.84</v>
       </c>
       <c r="H800" t="n">
-        <v>-1.34</v>
+        <v>0.36</v>
       </c>
       <c r="I800" t="n">
-        <v>120.55</v>
+        <v>121.38</v>
       </c>
       <c r="J800" t="n">
         <v>118.67</v>
       </c>
       <c r="K800" t="n">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="L800" t="inlineStr">
         <is>
@@ -89490,31 +89490,31 @@
         </is>
       </c>
       <c r="C801" t="n">
-        <v>5740.5</v>
+        <v>5858.5</v>
       </c>
       <c r="D801" t="n">
         <v>5922.02</v>
       </c>
       <c r="E801" t="n">
-        <v>-181.52</v>
+        <v>-63.52</v>
       </c>
       <c r="F801" t="n">
-        <v>5906.5</v>
+        <v>5868</v>
       </c>
       <c r="G801" t="n">
         <v>5841.39</v>
       </c>
       <c r="H801" t="n">
-        <v>65.11</v>
+        <v>26.61</v>
       </c>
       <c r="I801" t="n">
-        <v>5733.5</v>
+        <v>5690</v>
       </c>
       <c r="J801" t="n">
         <v>5531.8</v>
       </c>
       <c r="K801" t="n">
-        <v>201.7</v>
+        <v>158.2</v>
       </c>
       <c r="L801" t="inlineStr">
         <is>
@@ -89527,7 +89527,7 @@
         </is>
       </c>
       <c r="N801" t="n">
-        <v>3.07</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="802">
@@ -89542,31 +89542,31 @@
         </is>
       </c>
       <c r="C802" t="n">
-        <v>2499.5</v>
+        <v>2575</v>
       </c>
       <c r="D802" t="n">
         <v>2437.95</v>
       </c>
       <c r="E802" t="n">
-        <v>61.55</v>
+        <v>137.05</v>
       </c>
       <c r="F802" t="n">
-        <v>2601.4</v>
+        <v>2580</v>
       </c>
       <c r="G802" t="n">
         <v>2532.94</v>
       </c>
       <c r="H802" t="n">
-        <v>68.45999999999999</v>
+        <v>47.06</v>
       </c>
       <c r="I802" t="n">
-        <v>2499.5</v>
+        <v>2491</v>
       </c>
       <c r="J802" t="n">
         <v>2416.65</v>
       </c>
       <c r="K802" t="n">
-        <v>82.84999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L802" t="inlineStr">
         <is>
@@ -89579,7 +89579,7 @@
         </is>
       </c>
       <c r="N802" t="n">
-        <v>2.52</v>
+        <v>5.62</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N802"/>
+  <dimension ref="A1:N806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42140,6 +42140,214 @@
       </c>
       <c r="N802" t="n">
         <v>9.08</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>5727.5</v>
+      </c>
+      <c r="D803" t="n">
+        <v>5923.6</v>
+      </c>
+      <c r="E803" t="n">
+        <v>-196.1</v>
+      </c>
+      <c r="F803" t="n">
+        <v>5914.5</v>
+      </c>
+      <c r="G803" t="n">
+        <v>5923.6</v>
+      </c>
+      <c r="H803" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="I803" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="J803" t="n">
+        <v>5591.1</v>
+      </c>
+      <c r="K803" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N803" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>11175</v>
+      </c>
+      <c r="D804" t="n">
+        <v>11306.98</v>
+      </c>
+      <c r="E804" t="n">
+        <v>-131.98</v>
+      </c>
+      <c r="F804" t="n">
+        <v>11299</v>
+      </c>
+      <c r="G804" t="n">
+        <v>11306.98</v>
+      </c>
+      <c r="H804" t="n">
+        <v>-7.98</v>
+      </c>
+      <c r="I804" t="n">
+        <v>11029</v>
+      </c>
+      <c r="J804" t="n">
+        <v>11013.61</v>
+      </c>
+      <c r="K804" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N804" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D805" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="E805" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="F805" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="G805" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="H805" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="I805" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="J805" t="n">
+        <v>118.26</v>
+      </c>
+      <c r="K805" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N805" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>2480</v>
+      </c>
+      <c r="D806" t="n">
+        <v>2726.73</v>
+      </c>
+      <c r="E806" t="n">
+        <v>-246.73</v>
+      </c>
+      <c r="F806" t="n">
+        <v>2585.6</v>
+      </c>
+      <c r="G806" t="n">
+        <v>2726.73</v>
+      </c>
+      <c r="H806" t="n">
+        <v>-141.13</v>
+      </c>
+      <c r="I806" t="n">
+        <v>2470.1</v>
+      </c>
+      <c r="J806" t="n">
+        <v>2429.48</v>
+      </c>
+      <c r="K806" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N806" t="n">
+        <v>9.050000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -42153,7 +42361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47842,6 +48050,110 @@
       </c>
       <c r="N109" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>22600</v>
+      </c>
+      <c r="D110" t="n">
+        <v>22600</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>22787.25</v>
+      </c>
+      <c r="G110" t="n">
+        <v>22800.84</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-13.59</v>
+      </c>
+      <c r="I110" t="n">
+        <v>22372</v>
+      </c>
+      <c r="J110" t="n">
+        <v>22385.59</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-13.59</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>54287.35</v>
+      </c>
+      <c r="D111" t="n">
+        <v>54287.35</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>54990.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>54871.11</v>
+      </c>
+      <c r="H111" t="n">
+        <v>119.39</v>
+      </c>
+      <c r="I111" t="n">
+        <v>53942.35</v>
+      </c>
+      <c r="J111" t="n">
+        <v>53822.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>119.39</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -47855,7 +48167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N802"/>
+  <dimension ref="A1:N806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89582,6 +89894,214 @@
         <v>5.62</v>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D803" t="n">
+        <v>132.65</v>
+      </c>
+      <c r="E803" t="n">
+        <v>-12.28</v>
+      </c>
+      <c r="F803" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="G803" t="n">
+        <v>126.39</v>
+      </c>
+      <c r="H803" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="I803" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="J803" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="K803" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N803" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>5727.5</v>
+      </c>
+      <c r="D804" t="n">
+        <v>6137.72</v>
+      </c>
+      <c r="E804" t="n">
+        <v>-410.22</v>
+      </c>
+      <c r="F804" t="n">
+        <v>5914.5</v>
+      </c>
+      <c r="G804" t="n">
+        <v>6050.02</v>
+      </c>
+      <c r="H804" t="n">
+        <v>-135.52</v>
+      </c>
+      <c r="I804" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="J804" t="n">
+        <v>5657.35</v>
+      </c>
+      <c r="K804" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N804" t="n">
+        <v>6.68</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>2480</v>
+      </c>
+      <c r="D805" t="n">
+        <v>2815.78</v>
+      </c>
+      <c r="E805" t="n">
+        <v>-335.78</v>
+      </c>
+      <c r="F805" t="n">
+        <v>2585.6</v>
+      </c>
+      <c r="G805" t="n">
+        <v>2611.17</v>
+      </c>
+      <c r="H805" t="n">
+        <v>-25.57</v>
+      </c>
+      <c r="I805" t="n">
+        <v>2470.1</v>
+      </c>
+      <c r="J805" t="n">
+        <v>2456.02</v>
+      </c>
+      <c r="K805" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N805" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>11175</v>
+      </c>
+      <c r="D806" t="n">
+        <v>11608.2</v>
+      </c>
+      <c r="E806" t="n">
+        <v>-433.2</v>
+      </c>
+      <c r="F806" t="n">
+        <v>11299</v>
+      </c>
+      <c r="G806" t="n">
+        <v>11700.14</v>
+      </c>
+      <c r="H806" t="n">
+        <v>-401.14</v>
+      </c>
+      <c r="I806" t="n">
+        <v>11029</v>
+      </c>
+      <c r="J806" t="n">
+        <v>11116.67</v>
+      </c>
+      <c r="K806" t="n">
+        <v>-87.67</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N806" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -42154,31 +42154,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>5727.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D803" t="n">
         <v>5923.6</v>
       </c>
       <c r="E803" t="n">
-        <v>-196.1</v>
+        <v>-183.1</v>
       </c>
       <c r="F803" t="n">
-        <v>5914.5</v>
+        <v>5906.5</v>
       </c>
       <c r="G803" t="n">
         <v>5923.6</v>
       </c>
       <c r="H803" t="n">
-        <v>-9.1</v>
+        <v>-17.1</v>
       </c>
       <c r="I803" t="n">
-        <v>5674.5</v>
+        <v>5733.5</v>
       </c>
       <c r="J803" t="n">
         <v>5591.1</v>
       </c>
       <c r="K803" t="n">
-        <v>83.40000000000001</v>
+        <v>142.4</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         </is>
       </c>
       <c r="N803" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="804">
@@ -42206,31 +42206,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>11175</v>
+        <v>11293</v>
       </c>
       <c r="D804" t="n">
         <v>11306.98</v>
       </c>
       <c r="E804" t="n">
-        <v>-131.98</v>
+        <v>-13.98</v>
       </c>
       <c r="F804" t="n">
-        <v>11299</v>
+        <v>11420</v>
       </c>
       <c r="G804" t="n">
         <v>11306.98</v>
       </c>
       <c r="H804" t="n">
-        <v>-7.98</v>
+        <v>113.02</v>
       </c>
       <c r="I804" t="n">
-        <v>11029</v>
+        <v>10834</v>
       </c>
       <c r="J804" t="n">
         <v>11013.61</v>
       </c>
       <c r="K804" t="n">
-        <v>15.39</v>
+        <v>-179.61</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         </is>
       </c>
       <c r="N804" t="n">
-        <v>1.17</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="805">
@@ -42258,31 +42258,31 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>120.37</v>
+        <v>122.5</v>
       </c>
       <c r="D805" t="n">
         <v>128.82</v>
       </c>
       <c r="E805" t="n">
-        <v>-8.449999999999999</v>
+        <v>-6.32</v>
       </c>
       <c r="F805" t="n">
-        <v>122.3</v>
+        <v>122.5</v>
       </c>
       <c r="G805" t="n">
         <v>128.82</v>
       </c>
       <c r="H805" t="n">
-        <v>-6.52</v>
+        <v>-6.32</v>
       </c>
       <c r="I805" t="n">
-        <v>119.06</v>
+        <v>120.55</v>
       </c>
       <c r="J805" t="n">
         <v>118.26</v>
       </c>
       <c r="K805" t="n">
-        <v>0.8</v>
+        <v>2.29</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         </is>
       </c>
       <c r="N805" t="n">
-        <v>6.56</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="806">
@@ -42310,31 +42310,31 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>2480</v>
+        <v>2499.5</v>
       </c>
       <c r="D806" t="n">
         <v>2726.73</v>
       </c>
       <c r="E806" t="n">
-        <v>-246.73</v>
+        <v>-227.23</v>
       </c>
       <c r="F806" t="n">
-        <v>2585.6</v>
+        <v>2601.4</v>
       </c>
       <c r="G806" t="n">
         <v>2726.73</v>
       </c>
       <c r="H806" t="n">
-        <v>-141.13</v>
+        <v>-125.33</v>
       </c>
       <c r="I806" t="n">
-        <v>2470.1</v>
+        <v>2499.5</v>
       </c>
       <c r="J806" t="n">
         <v>2429.48</v>
       </c>
       <c r="K806" t="n">
-        <v>40.62</v>
+        <v>70.02</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         </is>
       </c>
       <c r="N806" t="n">
-        <v>9.050000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>
@@ -48064,31 +48064,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>22600</v>
+        <v>22687.65</v>
       </c>
       <c r="D110" t="n">
         <v>22600</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>22787.25</v>
+        <v>22785</v>
       </c>
       <c r="G110" t="n">
         <v>22800.84</v>
       </c>
       <c r="H110" t="n">
-        <v>-13.59</v>
+        <v>-15.84</v>
       </c>
       <c r="I110" t="n">
-        <v>22372</v>
+        <v>22554.85</v>
       </c>
       <c r="J110" t="n">
         <v>22385.59</v>
       </c>
       <c r="K110" t="n">
-        <v>-13.59</v>
+        <v>169.26</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="111">
@@ -48116,31 +48116,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>54287.35</v>
+        <v>54925.7</v>
       </c>
       <c r="D111" t="n">
         <v>54287.35</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>638.35</v>
       </c>
       <c r="F111" t="n">
-        <v>54990.5</v>
+        <v>55134.45</v>
       </c>
       <c r="G111" t="n">
         <v>54871.11</v>
       </c>
       <c r="H111" t="n">
-        <v>119.39</v>
+        <v>263.34</v>
       </c>
       <c r="I111" t="n">
-        <v>53942.35</v>
+        <v>54459.35</v>
       </c>
       <c r="J111" t="n">
         <v>53822.96</v>
       </c>
       <c r="K111" t="n">
-        <v>119.39</v>
+        <v>636.39</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>
@@ -89906,31 +89906,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>120.37</v>
+        <v>122.5</v>
       </c>
       <c r="D803" t="n">
         <v>132.65</v>
       </c>
       <c r="E803" t="n">
-        <v>-12.28</v>
+        <v>-10.15</v>
       </c>
       <c r="F803" t="n">
-        <v>122.3</v>
+        <v>122.5</v>
       </c>
       <c r="G803" t="n">
         <v>126.39</v>
       </c>
       <c r="H803" t="n">
-        <v>-4.09</v>
+        <v>-3.89</v>
       </c>
       <c r="I803" t="n">
-        <v>119.06</v>
+        <v>120.55</v>
       </c>
       <c r="J803" t="n">
         <v>119.47</v>
       </c>
       <c r="K803" t="n">
-        <v>-0.41</v>
+        <v>1.08</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -89943,7 +89943,7 @@
         </is>
       </c>
       <c r="N803" t="n">
-        <v>9.26</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="804">
@@ -89958,31 +89958,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>5727.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D804" t="n">
         <v>6137.72</v>
       </c>
       <c r="E804" t="n">
-        <v>-410.22</v>
+        <v>-397.22</v>
       </c>
       <c r="F804" t="n">
-        <v>5914.5</v>
+        <v>5906.5</v>
       </c>
       <c r="G804" t="n">
         <v>6050.02</v>
       </c>
       <c r="H804" t="n">
-        <v>-135.52</v>
+        <v>-143.52</v>
       </c>
       <c r="I804" t="n">
-        <v>5674.5</v>
+        <v>5733.5</v>
       </c>
       <c r="J804" t="n">
         <v>5657.35</v>
       </c>
       <c r="K804" t="n">
-        <v>17.15</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -89995,7 +89995,7 @@
         </is>
       </c>
       <c r="N804" t="n">
-        <v>6.68</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="805">
@@ -90010,31 +90010,31 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>2480</v>
+        <v>2499.5</v>
       </c>
       <c r="D805" t="n">
         <v>2815.78</v>
       </c>
       <c r="E805" t="n">
-        <v>-335.78</v>
+        <v>-316.28</v>
       </c>
       <c r="F805" t="n">
-        <v>2585.6</v>
+        <v>2601.4</v>
       </c>
       <c r="G805" t="n">
         <v>2611.17</v>
       </c>
       <c r="H805" t="n">
-        <v>-25.57</v>
+        <v>-9.77</v>
       </c>
       <c r="I805" t="n">
-        <v>2470.1</v>
+        <v>2499.5</v>
       </c>
       <c r="J805" t="n">
         <v>2456.02</v>
       </c>
       <c r="K805" t="n">
-        <v>14.08</v>
+        <v>43.48</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -90047,7 +90047,7 @@
         </is>
       </c>
       <c r="N805" t="n">
-        <v>11.92</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="806">
@@ -90062,31 +90062,31 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>11175</v>
+        <v>11293</v>
       </c>
       <c r="D806" t="n">
         <v>11608.2</v>
       </c>
       <c r="E806" t="n">
-        <v>-433.2</v>
+        <v>-315.2</v>
       </c>
       <c r="F806" t="n">
-        <v>11299</v>
+        <v>11420</v>
       </c>
       <c r="G806" t="n">
         <v>11700.14</v>
       </c>
       <c r="H806" t="n">
-        <v>-401.14</v>
+        <v>-280.14</v>
       </c>
       <c r="I806" t="n">
-        <v>11029</v>
+        <v>10834</v>
       </c>
       <c r="J806" t="n">
         <v>11116.67</v>
       </c>
       <c r="K806" t="n">
-        <v>-87.67</v>
+        <v>-282.67</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -90099,7 +90099,7 @@
         </is>
       </c>
       <c r="N806" t="n">
-        <v>3.73</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -42154,31 +42154,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>5740.5</v>
+        <v>5727.5</v>
       </c>
       <c r="D803" t="n">
-        <v>5923.6</v>
+        <v>5594.87</v>
       </c>
       <c r="E803" t="n">
-        <v>-183.1</v>
+        <v>132.63</v>
       </c>
       <c r="F803" t="n">
-        <v>5906.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G803" t="n">
-        <v>5923.6</v>
+        <v>5594.87</v>
       </c>
       <c r="H803" t="n">
-        <v>-17.1</v>
+        <v>319.63</v>
       </c>
       <c r="I803" t="n">
-        <v>5733.5</v>
+        <v>5674.5</v>
       </c>
       <c r="J803" t="n">
-        <v>5591.1</v>
+        <v>5477.93</v>
       </c>
       <c r="K803" t="n">
-        <v>142.4</v>
+        <v>196.57</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         </is>
       </c>
       <c r="N803" t="n">
-        <v>3.09</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="804">
@@ -42206,31 +42206,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>11293</v>
+        <v>11175</v>
       </c>
       <c r="D804" t="n">
-        <v>11306.98</v>
+        <v>11250.43</v>
       </c>
       <c r="E804" t="n">
-        <v>-13.98</v>
+        <v>-75.43000000000001</v>
       </c>
       <c r="F804" t="n">
-        <v>11420</v>
+        <v>11299</v>
       </c>
       <c r="G804" t="n">
-        <v>11306.98</v>
+        <v>11250.43</v>
       </c>
       <c r="H804" t="n">
-        <v>113.02</v>
+        <v>48.57</v>
       </c>
       <c r="I804" t="n">
-        <v>10834</v>
+        <v>11029</v>
       </c>
       <c r="J804" t="n">
-        <v>11013.61</v>
+        <v>10790.69</v>
       </c>
       <c r="K804" t="n">
-        <v>-179.61</v>
+        <v>238.31</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         </is>
       </c>
       <c r="N804" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="805">
@@ -42258,31 +42258,31 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>122.5</v>
+        <v>120.37</v>
       </c>
       <c r="D805" t="n">
-        <v>128.82</v>
+        <v>115.38</v>
       </c>
       <c r="E805" t="n">
-        <v>-6.32</v>
+        <v>4.99</v>
       </c>
       <c r="F805" t="n">
-        <v>122.5</v>
+        <v>122.3</v>
       </c>
       <c r="G805" t="n">
-        <v>128.82</v>
+        <v>118.16</v>
       </c>
       <c r="H805" t="n">
-        <v>-6.32</v>
+        <v>4.14</v>
       </c>
       <c r="I805" t="n">
-        <v>120.55</v>
+        <v>119.06</v>
       </c>
       <c r="J805" t="n">
-        <v>118.26</v>
+        <v>115.86</v>
       </c>
       <c r="K805" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -42291,11 +42291,11 @@
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N805" t="n">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="806">
@@ -42310,31 +42310,31 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>2499.5</v>
+        <v>2480</v>
       </c>
       <c r="D806" t="n">
-        <v>2726.73</v>
+        <v>2291.53</v>
       </c>
       <c r="E806" t="n">
-        <v>-227.23</v>
+        <v>188.47</v>
       </c>
       <c r="F806" t="n">
-        <v>2601.4</v>
+        <v>2585.6</v>
       </c>
       <c r="G806" t="n">
-        <v>2726.73</v>
+        <v>2426.66</v>
       </c>
       <c r="H806" t="n">
-        <v>-125.33</v>
+        <v>158.94</v>
       </c>
       <c r="I806" t="n">
-        <v>2499.5</v>
+        <v>2470.1</v>
       </c>
       <c r="J806" t="n">
-        <v>2429.48</v>
+        <v>2380.3</v>
       </c>
       <c r="K806" t="n">
-        <v>70.02</v>
+        <v>89.8</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -42343,11 +42343,11 @@
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N806" t="n">
-        <v>8.33</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -48064,31 +48064,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>22687.65</v>
+        <v>22600</v>
       </c>
       <c r="D110" t="n">
         <v>22600</v>
       </c>
       <c r="E110" t="n">
-        <v>87.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>22785</v>
+        <v>22787.25</v>
       </c>
       <c r="G110" t="n">
         <v>22800.84</v>
       </c>
       <c r="H110" t="n">
-        <v>-15.84</v>
+        <v>-13.59</v>
       </c>
       <c r="I110" t="n">
-        <v>22554.85</v>
+        <v>22372</v>
       </c>
       <c r="J110" t="n">
         <v>22385.59</v>
       </c>
       <c r="K110" t="n">
-        <v>169.26</v>
+        <v>-13.59</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -48116,31 +48116,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>54925.7</v>
+        <v>54287.35</v>
       </c>
       <c r="D111" t="n">
         <v>54287.35</v>
       </c>
       <c r="E111" t="n">
-        <v>638.35</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>55134.45</v>
+        <v>54990.5</v>
       </c>
       <c r="G111" t="n">
         <v>54871.11</v>
       </c>
       <c r="H111" t="n">
-        <v>263.34</v>
+        <v>119.39</v>
       </c>
       <c r="I111" t="n">
-        <v>54459.35</v>
+        <v>53942.35</v>
       </c>
       <c r="J111" t="n">
         <v>53822.96</v>
       </c>
       <c r="K111" t="n">
-        <v>636.39</v>
+        <v>119.39</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -89906,31 +89906,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>122.5</v>
+        <v>120.37</v>
       </c>
       <c r="D803" t="n">
-        <v>132.65</v>
+        <v>118.79</v>
       </c>
       <c r="E803" t="n">
-        <v>-10.15</v>
+        <v>1.58</v>
       </c>
       <c r="F803" t="n">
-        <v>122.5</v>
+        <v>122.3</v>
       </c>
       <c r="G803" t="n">
-        <v>126.39</v>
+        <v>122.64</v>
       </c>
       <c r="H803" t="n">
-        <v>-3.89</v>
+        <v>-0.34</v>
       </c>
       <c r="I803" t="n">
-        <v>120.55</v>
+        <v>119.06</v>
       </c>
       <c r="J803" t="n">
-        <v>119.47</v>
+        <v>117.03</v>
       </c>
       <c r="K803" t="n">
-        <v>1.08</v>
+        <v>2.03</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -89939,11 +89939,11 @@
       </c>
       <c r="M803" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N803" t="n">
-        <v>7.65</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="804">
@@ -89958,31 +89958,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>5740.5</v>
+        <v>5727.5</v>
       </c>
       <c r="D804" t="n">
-        <v>6137.72</v>
+        <v>5796.26</v>
       </c>
       <c r="E804" t="n">
-        <v>-397.22</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="F804" t="n">
-        <v>5906.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G804" t="n">
-        <v>6050.02</v>
+        <v>5870.73</v>
       </c>
       <c r="H804" t="n">
-        <v>-143.52</v>
+        <v>43.77</v>
       </c>
       <c r="I804" t="n">
-        <v>5733.5</v>
+        <v>5674.5</v>
       </c>
       <c r="J804" t="n">
-        <v>5657.35</v>
+        <v>5541.98</v>
       </c>
       <c r="K804" t="n">
-        <v>76.15000000000001</v>
+        <v>132.52</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -89991,11 +89991,11 @@
       </c>
       <c r="M804" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N804" t="n">
-        <v>6.47</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="805">
@@ -90006,35 +90006,35 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>MPHASIS (OCT-2026 FUT)</t>
+          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>2499.5</v>
+        <v>11175</v>
       </c>
       <c r="D805" t="n">
-        <v>2815.78</v>
+        <v>11548.46</v>
       </c>
       <c r="E805" t="n">
-        <v>-316.28</v>
+        <v>-373.46</v>
       </c>
       <c r="F805" t="n">
-        <v>2601.4</v>
+        <v>11299</v>
       </c>
       <c r="G805" t="n">
-        <v>2611.17</v>
+        <v>11353.39</v>
       </c>
       <c r="H805" t="n">
-        <v>-9.77</v>
+        <v>-54.39</v>
       </c>
       <c r="I805" t="n">
-        <v>2499.5</v>
+        <v>11029</v>
       </c>
       <c r="J805" t="n">
-        <v>2456.02</v>
+        <v>10889.98</v>
       </c>
       <c r="K805" t="n">
-        <v>43.48</v>
+        <v>139.02</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -90047,7 +90047,7 @@
         </is>
       </c>
       <c r="N805" t="n">
-        <v>11.23</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="806">
@@ -90058,35 +90058,35 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
+          <t>MPHASIS (OCT-2026 FUT)</t>
         </is>
       </c>
       <c r="C806" t="n">
-        <v>11293</v>
+        <v>2480</v>
       </c>
       <c r="D806" t="n">
-        <v>11608.2</v>
+        <v>2366.03</v>
       </c>
       <c r="E806" t="n">
-        <v>-315.2</v>
+        <v>113.97</v>
       </c>
       <c r="F806" t="n">
-        <v>11420</v>
+        <v>2585.6</v>
       </c>
       <c r="G806" t="n">
-        <v>11700.14</v>
+        <v>2533.79</v>
       </c>
       <c r="H806" t="n">
-        <v>-280.14</v>
+        <v>51.81</v>
       </c>
       <c r="I806" t="n">
-        <v>10834</v>
+        <v>2470.1</v>
       </c>
       <c r="J806" t="n">
-        <v>11116.67</v>
+        <v>2405.94</v>
       </c>
       <c r="K806" t="n">
-        <v>-282.67</v>
+        <v>64.16</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -90095,11 +90095,11 @@
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N806" t="n">
-        <v>2.72</v>
+        <v>4.82</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N806"/>
+  <dimension ref="A1:N814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42348,6 +42348,422 @@
       </c>
       <c r="N806" t="n">
         <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="D807" t="n">
+        <v>299.88</v>
+      </c>
+      <c r="E807" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="F807" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="G807" t="n">
+        <v>305.34</v>
+      </c>
+      <c r="H807" t="n">
+        <v>-12.59</v>
+      </c>
+      <c r="I807" t="n">
+        <v>282.05</v>
+      </c>
+      <c r="J807" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="K807" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N807" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>1310.9</v>
+      </c>
+      <c r="D808" t="n">
+        <v>1342.85</v>
+      </c>
+      <c r="E808" t="n">
+        <v>-31.95</v>
+      </c>
+      <c r="F808" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G808" t="n">
+        <v>1343.98</v>
+      </c>
+      <c r="H808" t="n">
+        <v>-24.98</v>
+      </c>
+      <c r="I808" t="n">
+        <v>1224</v>
+      </c>
+      <c r="J808" t="n">
+        <v>1295.15</v>
+      </c>
+      <c r="K808" t="n">
+        <v>-71.15000000000001</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N808" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="D809" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="E809" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="F809" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="G809" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="H809" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="I809" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="J809" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="K809" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N809" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2041.57</v>
+      </c>
+      <c r="E810" t="n">
+        <v>-48.57</v>
+      </c>
+      <c r="F810" t="n">
+        <v>1997.6</v>
+      </c>
+      <c r="G810" t="n">
+        <v>2077.29</v>
+      </c>
+      <c r="H810" t="n">
+        <v>-79.69</v>
+      </c>
+      <c r="I810" t="n">
+        <v>1812.2</v>
+      </c>
+      <c r="J810" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K810" t="n">
+        <v>-180.8</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N810" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="D811" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="E811" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="F811" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="G811" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="H811" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="I811" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="J811" t="n">
+        <v>316.72</v>
+      </c>
+      <c r="K811" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N811" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D812" t="n">
+        <v>6036.61</v>
+      </c>
+      <c r="E812" t="n">
+        <v>-186.61</v>
+      </c>
+      <c r="F812" t="n">
+        <v>5873.5</v>
+      </c>
+      <c r="G812" t="n">
+        <v>6036.61</v>
+      </c>
+      <c r="H812" t="n">
+        <v>-163.11</v>
+      </c>
+      <c r="I812" t="n">
+        <v>5600</v>
+      </c>
+      <c r="J812" t="n">
+        <v>5744.8</v>
+      </c>
+      <c r="K812" t="n">
+        <v>-144.8</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N812" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D813" t="n">
+        <v>1451.54</v>
+      </c>
+      <c r="E813" t="n">
+        <v>-34.54</v>
+      </c>
+      <c r="F813" t="n">
+        <v>1422.7</v>
+      </c>
+      <c r="G813" t="n">
+        <v>1451.54</v>
+      </c>
+      <c r="H813" t="n">
+        <v>-28.84</v>
+      </c>
+      <c r="I813" t="n">
+        <v>1386</v>
+      </c>
+      <c r="J813" t="n">
+        <v>1387.05</v>
+      </c>
+      <c r="K813" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N813" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>2557.6</v>
+      </c>
+      <c r="D814" t="n">
+        <v>2790.11</v>
+      </c>
+      <c r="E814" t="n">
+        <v>-232.51</v>
+      </c>
+      <c r="F814" t="n">
+        <v>2563.3</v>
+      </c>
+      <c r="G814" t="n">
+        <v>2790.11</v>
+      </c>
+      <c r="H814" t="n">
+        <v>-226.81</v>
+      </c>
+      <c r="I814" t="n">
+        <v>2435</v>
+      </c>
+      <c r="J814" t="n">
+        <v>2498.67</v>
+      </c>
+      <c r="K814" t="n">
+        <v>-63.67</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N814" t="n">
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>
@@ -42361,7 +42777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48153,6 +48569,110 @@
         </is>
       </c>
       <c r="N111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="G112" t="n">
+        <v>22875.15</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-121.95</v>
+      </c>
+      <c r="I112" t="n">
+        <v>22387.35</v>
+      </c>
+      <c r="J112" t="n">
+        <v>22509.3</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-121.95</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>54366.7</v>
+      </c>
+      <c r="D113" t="n">
+        <v>54366.7</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>54392.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>54580.3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-187.8</v>
+      </c>
+      <c r="I113" t="n">
+        <v>53777.5</v>
+      </c>
+      <c r="J113" t="n">
+        <v>53965.3</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-187.8</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -48167,7 +48687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N806"/>
+  <dimension ref="A1:N814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90102,6 +90622,422 @@
         <v>4.82</v>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="D807" t="n">
+        <v>304.88</v>
+      </c>
+      <c r="E807" t="n">
+        <v>-13.13</v>
+      </c>
+      <c r="F807" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="G807" t="n">
+        <v>304.09</v>
+      </c>
+      <c r="H807" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="I807" t="n">
+        <v>282.05</v>
+      </c>
+      <c r="J807" t="n">
+        <v>289.64</v>
+      </c>
+      <c r="K807" t="n">
+        <v>-7.59</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N807" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="D808" t="n">
+        <v>130.76</v>
+      </c>
+      <c r="E808" t="n">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="F808" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="G808" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="H808" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="I808" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="J808" t="n">
+        <v>119.27</v>
+      </c>
+      <c r="K808" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N808" t="n">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>DRREDDY (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>1310.9</v>
+      </c>
+      <c r="D809" t="n">
+        <v>1367.45</v>
+      </c>
+      <c r="E809" t="n">
+        <v>-56.55</v>
+      </c>
+      <c r="F809" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G809" t="n">
+        <v>1363.96</v>
+      </c>
+      <c r="H809" t="n">
+        <v>-44.96</v>
+      </c>
+      <c r="I809" t="n">
+        <v>1224</v>
+      </c>
+      <c r="J809" t="n">
+        <v>1303.2</v>
+      </c>
+      <c r="K809" t="n">
+        <v>-79.2</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N809" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>COFORGE (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2106.42</v>
+      </c>
+      <c r="E810" t="n">
+        <v>-113.42</v>
+      </c>
+      <c r="F810" t="n">
+        <v>1997.6</v>
+      </c>
+      <c r="G810" t="n">
+        <v>2099.98</v>
+      </c>
+      <c r="H810" t="n">
+        <v>-102.38</v>
+      </c>
+      <c r="I810" t="n">
+        <v>1812.2</v>
+      </c>
+      <c r="J810" t="n">
+        <v>1961.58</v>
+      </c>
+      <c r="K810" t="n">
+        <v>-149.38</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N810" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="D811" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="E811" t="n">
+        <v>-19.01</v>
+      </c>
+      <c r="F811" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="G811" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="H811" t="n">
+        <v>-15.53</v>
+      </c>
+      <c r="I811" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="J811" t="n">
+        <v>320.08</v>
+      </c>
+      <c r="K811" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N811" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D812" t="n">
+        <v>6254.38</v>
+      </c>
+      <c r="E812" t="n">
+        <v>-404.38</v>
+      </c>
+      <c r="F812" t="n">
+        <v>5873.5</v>
+      </c>
+      <c r="G812" t="n">
+        <v>6188.75</v>
+      </c>
+      <c r="H812" t="n">
+        <v>-315.25</v>
+      </c>
+      <c r="I812" t="n">
+        <v>5600</v>
+      </c>
+      <c r="J812" t="n">
+        <v>5739.26</v>
+      </c>
+      <c r="K812" t="n">
+        <v>-139.26</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N812" t="n">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>2557.6</v>
+      </c>
+      <c r="D813" t="n">
+        <v>2876.67</v>
+      </c>
+      <c r="E813" t="n">
+        <v>-319.07</v>
+      </c>
+      <c r="F813" t="n">
+        <v>2563.3</v>
+      </c>
+      <c r="G813" t="n">
+        <v>2693.02</v>
+      </c>
+      <c r="H813" t="n">
+        <v>-129.72</v>
+      </c>
+      <c r="I813" t="n">
+        <v>2435</v>
+      </c>
+      <c r="J813" t="n">
+        <v>2518.68</v>
+      </c>
+      <c r="K813" t="n">
+        <v>-83.68000000000001</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N813" t="n">
+        <v>11.09</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>HCLTECH (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D814" t="n">
+        <v>1495.3</v>
+      </c>
+      <c r="E814" t="n">
+        <v>-78.3</v>
+      </c>
+      <c r="F814" t="n">
+        <v>1422.7</v>
+      </c>
+      <c r="G814" t="n">
+        <v>1490.82</v>
+      </c>
+      <c r="H814" t="n">
+        <v>-68.12</v>
+      </c>
+      <c r="I814" t="n">
+        <v>1386</v>
+      </c>
+      <c r="J814" t="n">
+        <v>1396.35</v>
+      </c>
+      <c r="K814" t="n">
+        <v>-10.35</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N814" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -42362,31 +42362,31 @@
         </is>
       </c>
       <c r="C807" t="n">
-        <v>291.75</v>
+        <v>286.3</v>
       </c>
       <c r="D807" t="n">
         <v>299.88</v>
       </c>
       <c r="E807" t="n">
-        <v>-8.130000000000001</v>
+        <v>-13.58</v>
       </c>
       <c r="F807" t="n">
-        <v>292.75</v>
+        <v>292</v>
       </c>
       <c r="G807" t="n">
         <v>305.34</v>
       </c>
       <c r="H807" t="n">
-        <v>-12.59</v>
+        <v>-13.34</v>
       </c>
       <c r="I807" t="n">
-        <v>282.05</v>
+        <v>279.35</v>
       </c>
       <c r="J807" t="n">
         <v>291.75</v>
       </c>
       <c r="K807" t="n">
-        <v>-9.699999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="L807" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         </is>
       </c>
       <c r="N807" t="n">
-        <v>2.71</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="808">
@@ -42414,31 +42414,31 @@
         </is>
       </c>
       <c r="C808" t="n">
-        <v>1310.9</v>
+        <v>1229.5</v>
       </c>
       <c r="D808" t="n">
         <v>1342.85</v>
       </c>
       <c r="E808" t="n">
-        <v>-31.95</v>
+        <v>-113.35</v>
       </c>
       <c r="F808" t="n">
-        <v>1319</v>
+        <v>1250.6</v>
       </c>
       <c r="G808" t="n">
         <v>1343.98</v>
       </c>
       <c r="H808" t="n">
-        <v>-24.98</v>
+        <v>-93.38</v>
       </c>
       <c r="I808" t="n">
-        <v>1224</v>
+        <v>1215.6</v>
       </c>
       <c r="J808" t="n">
         <v>1295.15</v>
       </c>
       <c r="K808" t="n">
-        <v>-71.15000000000001</v>
+        <v>-79.55</v>
       </c>
       <c r="L808" t="inlineStr">
         <is>
@@ -42447,11 +42447,11 @@
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N808" t="n">
-        <v>2.38</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="809">
@@ -42466,31 +42466,31 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>120.89</v>
+        <v>120.37</v>
       </c>
       <c r="D809" t="n">
         <v>127.13</v>
       </c>
       <c r="E809" t="n">
-        <v>-6.24</v>
+        <v>-6.76</v>
       </c>
       <c r="F809" t="n">
-        <v>120.89</v>
+        <v>122.3</v>
       </c>
       <c r="G809" t="n">
         <v>127.13</v>
       </c>
       <c r="H809" t="n">
-        <v>-6.24</v>
+        <v>-4.83</v>
       </c>
       <c r="I809" t="n">
-        <v>118.2</v>
+        <v>119.06</v>
       </c>
       <c r="J809" t="n">
         <v>120.25</v>
       </c>
       <c r="K809" t="n">
-        <v>-2.05</v>
+        <v>-1.19</v>
       </c>
       <c r="L809" t="inlineStr">
         <is>
@@ -42499,11 +42499,11 @@
       </c>
       <c r="M809" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N809" t="n">
-        <v>4.91</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="810">
@@ -42518,31 +42518,31 @@
         </is>
       </c>
       <c r="C810" t="n">
-        <v>1993</v>
+        <v>1900.5</v>
       </c>
       <c r="D810" t="n">
         <v>2041.57</v>
       </c>
       <c r="E810" t="n">
-        <v>-48.57</v>
+        <v>-141.07</v>
       </c>
       <c r="F810" t="n">
-        <v>1997.6</v>
+        <v>1992.4</v>
       </c>
       <c r="G810" t="n">
         <v>2077.29</v>
       </c>
       <c r="H810" t="n">
-        <v>-79.69</v>
+        <v>-84.89</v>
       </c>
       <c r="I810" t="n">
-        <v>1812.2</v>
+        <v>1890</v>
       </c>
       <c r="J810" t="n">
         <v>1993</v>
       </c>
       <c r="K810" t="n">
-        <v>-180.8</v>
+        <v>-103</v>
       </c>
       <c r="L810" t="inlineStr">
         <is>
@@ -42551,11 +42551,11 @@
       </c>
       <c r="M810" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N810" t="n">
-        <v>2.38</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="811">
@@ -42570,31 +42570,31 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>325.55</v>
+        <v>317.4</v>
       </c>
       <c r="D811" t="n">
         <v>333.48</v>
       </c>
       <c r="E811" t="n">
-        <v>-7.93</v>
+        <v>-16.08</v>
       </c>
       <c r="F811" t="n">
-        <v>327.95</v>
+        <v>318</v>
       </c>
       <c r="G811" t="n">
         <v>333.48</v>
       </c>
       <c r="H811" t="n">
-        <v>-5.53</v>
+        <v>-15.48</v>
       </c>
       <c r="I811" t="n">
-        <v>313.65</v>
+        <v>301.75</v>
       </c>
       <c r="J811" t="n">
         <v>316.72</v>
       </c>
       <c r="K811" t="n">
-        <v>-3.07</v>
+        <v>-14.97</v>
       </c>
       <c r="L811" t="inlineStr">
         <is>
@@ -42603,11 +42603,11 @@
       </c>
       <c r="M811" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N811" t="n">
-        <v>2.38</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="812">
@@ -42622,31 +42622,31 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>5850</v>
+        <v>5727.5</v>
       </c>
       <c r="D812" t="n">
         <v>6036.61</v>
       </c>
       <c r="E812" t="n">
-        <v>-186.61</v>
+        <v>-309.11</v>
       </c>
       <c r="F812" t="n">
-        <v>5873.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G812" t="n">
         <v>6036.61</v>
       </c>
       <c r="H812" t="n">
-        <v>-163.11</v>
+        <v>-122.11</v>
       </c>
       <c r="I812" t="n">
-        <v>5600</v>
+        <v>5674.5</v>
       </c>
       <c r="J812" t="n">
         <v>5744.8</v>
       </c>
       <c r="K812" t="n">
-        <v>-144.8</v>
+        <v>-70.3</v>
       </c>
       <c r="L812" t="inlineStr">
         <is>
@@ -42655,11 +42655,11 @@
       </c>
       <c r="M812" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N812" t="n">
-        <v>3.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="813">
@@ -42674,31 +42674,31 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>1417</v>
+        <v>1422.2</v>
       </c>
       <c r="D813" t="n">
         <v>1451.54</v>
       </c>
       <c r="E813" t="n">
-        <v>-34.54</v>
+        <v>-29.34</v>
       </c>
       <c r="F813" t="n">
-        <v>1422.7</v>
+        <v>1467.5</v>
       </c>
       <c r="G813" t="n">
         <v>1451.54</v>
       </c>
       <c r="H813" t="n">
-        <v>-28.84</v>
+        <v>15.96</v>
       </c>
       <c r="I813" t="n">
-        <v>1386</v>
+        <v>1415</v>
       </c>
       <c r="J813" t="n">
         <v>1387.05</v>
       </c>
       <c r="K813" t="n">
-        <v>-1.05</v>
+        <v>27.95</v>
       </c>
       <c r="L813" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         </is>
       </c>
       <c r="N813" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="814">
@@ -42726,31 +42726,31 @@
         </is>
       </c>
       <c r="C814" t="n">
-        <v>2557.6</v>
+        <v>2480</v>
       </c>
       <c r="D814" t="n">
         <v>2790.11</v>
       </c>
       <c r="E814" t="n">
-        <v>-232.51</v>
+        <v>-310.11</v>
       </c>
       <c r="F814" t="n">
-        <v>2563.3</v>
+        <v>2585.6</v>
       </c>
       <c r="G814" t="n">
         <v>2790.11</v>
       </c>
       <c r="H814" t="n">
-        <v>-226.81</v>
+        <v>-204.51</v>
       </c>
       <c r="I814" t="n">
-        <v>2435</v>
+        <v>2470.1</v>
       </c>
       <c r="J814" t="n">
         <v>2498.67</v>
       </c>
       <c r="K814" t="n">
-        <v>-63.67</v>
+        <v>-28.57</v>
       </c>
       <c r="L814" t="inlineStr">
         <is>
@@ -42759,11 +42759,11 @@
       </c>
       <c r="M814" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N814" t="n">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
     </row>
   </sheetData>
@@ -48584,31 +48584,31 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>22753.2</v>
+        <v>22600</v>
       </c>
       <c r="D112" t="n">
         <v>22753.2</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>-153.2</v>
       </c>
       <c r="F112" t="n">
-        <v>22753.2</v>
+        <v>22787.25</v>
       </c>
       <c r="G112" t="n">
         <v>22875.15</v>
       </c>
       <c r="H112" t="n">
-        <v>-121.95</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>22387.35</v>
+        <v>22372</v>
       </c>
       <c r="J112" t="n">
         <v>22509.3</v>
       </c>
       <c r="K112" t="n">
-        <v>-121.95</v>
+        <v>-137.3</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="113">
@@ -48636,31 +48636,31 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>54366.7</v>
+        <v>54287.35</v>
       </c>
       <c r="D113" t="n">
         <v>54366.7</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>-79.34999999999999</v>
       </c>
       <c r="F113" t="n">
-        <v>54392.5</v>
+        <v>54990.5</v>
       </c>
       <c r="G113" t="n">
         <v>54580.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-187.8</v>
+        <v>410.2</v>
       </c>
       <c r="I113" t="n">
-        <v>53777.5</v>
+        <v>53942.35</v>
       </c>
       <c r="J113" t="n">
         <v>53965.3</v>
       </c>
       <c r="K113" t="n">
-        <v>-187.8</v>
+        <v>-22.95</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -48673,7 +48673,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -90634,31 +90634,31 @@
         </is>
       </c>
       <c r="C807" t="n">
-        <v>291.75</v>
+        <v>286.3</v>
       </c>
       <c r="D807" t="n">
         <v>304.88</v>
       </c>
       <c r="E807" t="n">
-        <v>-13.13</v>
+        <v>-18.58</v>
       </c>
       <c r="F807" t="n">
-        <v>292.75</v>
+        <v>292</v>
       </c>
       <c r="G807" t="n">
         <v>304.09</v>
       </c>
       <c r="H807" t="n">
-        <v>-11.34</v>
+        <v>-12.09</v>
       </c>
       <c r="I807" t="n">
-        <v>282.05</v>
+        <v>279.35</v>
       </c>
       <c r="J807" t="n">
         <v>289.64</v>
       </c>
       <c r="K807" t="n">
-        <v>-7.59</v>
+        <v>-10.29</v>
       </c>
       <c r="L807" t="inlineStr">
         <is>
@@ -90671,7 +90671,7 @@
         </is>
       </c>
       <c r="N807" t="n">
-        <v>4.31</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="808">
@@ -90686,31 +90686,31 @@
         </is>
       </c>
       <c r="C808" t="n">
-        <v>120.89</v>
+        <v>120.37</v>
       </c>
       <c r="D808" t="n">
         <v>130.76</v>
       </c>
       <c r="E808" t="n">
-        <v>-9.869999999999999</v>
+        <v>-10.39</v>
       </c>
       <c r="F808" t="n">
-        <v>120.89</v>
+        <v>122.3</v>
       </c>
       <c r="G808" t="n">
         <v>127.01</v>
       </c>
       <c r="H808" t="n">
-        <v>-6.12</v>
+        <v>-4.71</v>
       </c>
       <c r="I808" t="n">
-        <v>118.2</v>
+        <v>119.06</v>
       </c>
       <c r="J808" t="n">
         <v>119.27</v>
       </c>
       <c r="K808" t="n">
-        <v>-1.07</v>
+        <v>-0.21</v>
       </c>
       <c r="L808" t="inlineStr">
         <is>
@@ -90723,7 +90723,7 @@
         </is>
       </c>
       <c r="N808" t="n">
-        <v>7.55</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="809">
@@ -90738,31 +90738,31 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>1310.9</v>
+        <v>1229.5</v>
       </c>
       <c r="D809" t="n">
         <v>1367.45</v>
       </c>
       <c r="E809" t="n">
-        <v>-56.55</v>
+        <v>-137.95</v>
       </c>
       <c r="F809" t="n">
-        <v>1319</v>
+        <v>1250.6</v>
       </c>
       <c r="G809" t="n">
         <v>1363.96</v>
       </c>
       <c r="H809" t="n">
-        <v>-44.96</v>
+        <v>-113.36</v>
       </c>
       <c r="I809" t="n">
-        <v>1224</v>
+        <v>1215.6</v>
       </c>
       <c r="J809" t="n">
         <v>1303.2</v>
       </c>
       <c r="K809" t="n">
-        <v>-79.2</v>
+        <v>-87.59999999999999</v>
       </c>
       <c r="L809" t="inlineStr">
         <is>
@@ -90775,7 +90775,7 @@
         </is>
       </c>
       <c r="N809" t="n">
-        <v>4.14</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="810">
@@ -90790,31 +90790,31 @@
         </is>
       </c>
       <c r="C810" t="n">
-        <v>1993</v>
+        <v>1900.5</v>
       </c>
       <c r="D810" t="n">
         <v>2106.42</v>
       </c>
       <c r="E810" t="n">
-        <v>-113.42</v>
+        <v>-205.92</v>
       </c>
       <c r="F810" t="n">
-        <v>1997.6</v>
+        <v>1992.4</v>
       </c>
       <c r="G810" t="n">
         <v>2099.98</v>
       </c>
       <c r="H810" t="n">
-        <v>-102.38</v>
+        <v>-107.58</v>
       </c>
       <c r="I810" t="n">
-        <v>1812.2</v>
+        <v>1890</v>
       </c>
       <c r="J810" t="n">
         <v>1961.58</v>
       </c>
       <c r="K810" t="n">
-        <v>-149.38</v>
+        <v>-71.58</v>
       </c>
       <c r="L810" t="inlineStr">
         <is>
@@ -90827,7 +90827,7 @@
         </is>
       </c>
       <c r="N810" t="n">
-        <v>5.38</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="811">
@@ -90842,31 +90842,31 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>325.55</v>
+        <v>317.4</v>
       </c>
       <c r="D811" t="n">
         <v>344.56</v>
       </c>
       <c r="E811" t="n">
-        <v>-19.01</v>
+        <v>-27.16</v>
       </c>
       <c r="F811" t="n">
-        <v>327.95</v>
+        <v>318</v>
       </c>
       <c r="G811" t="n">
         <v>343.48</v>
       </c>
       <c r="H811" t="n">
-        <v>-15.53</v>
+        <v>-25.48</v>
       </c>
       <c r="I811" t="n">
-        <v>313.65</v>
+        <v>301.75</v>
       </c>
       <c r="J811" t="n">
         <v>320.08</v>
       </c>
       <c r="K811" t="n">
-        <v>-6.43</v>
+        <v>-18.33</v>
       </c>
       <c r="L811" t="inlineStr">
         <is>
@@ -90879,7 +90879,7 @@
         </is>
       </c>
       <c r="N811" t="n">
-        <v>5.52</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="812">
@@ -90894,31 +90894,31 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>5850</v>
+        <v>5727.5</v>
       </c>
       <c r="D812" t="n">
         <v>6254.38</v>
       </c>
       <c r="E812" t="n">
-        <v>-404.38</v>
+        <v>-526.88</v>
       </c>
       <c r="F812" t="n">
-        <v>5873.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G812" t="n">
         <v>6188.75</v>
       </c>
       <c r="H812" t="n">
-        <v>-315.25</v>
+        <v>-274.25</v>
       </c>
       <c r="I812" t="n">
-        <v>5600</v>
+        <v>5674.5</v>
       </c>
       <c r="J812" t="n">
         <v>5739.26</v>
       </c>
       <c r="K812" t="n">
-        <v>-139.26</v>
+        <v>-64.76000000000001</v>
       </c>
       <c r="L812" t="inlineStr">
         <is>
@@ -90931,7 +90931,7 @@
         </is>
       </c>
       <c r="N812" t="n">
-        <v>6.47</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="813">
@@ -90946,31 +90946,31 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>2557.6</v>
+        <v>2480</v>
       </c>
       <c r="D813" t="n">
         <v>2876.67</v>
       </c>
       <c r="E813" t="n">
-        <v>-319.07</v>
+        <v>-396.67</v>
       </c>
       <c r="F813" t="n">
-        <v>2563.3</v>
+        <v>2585.6</v>
       </c>
       <c r="G813" t="n">
         <v>2693.02</v>
       </c>
       <c r="H813" t="n">
-        <v>-129.72</v>
+        <v>-107.42</v>
       </c>
       <c r="I813" t="n">
-        <v>2435</v>
+        <v>2470.1</v>
       </c>
       <c r="J813" t="n">
         <v>2518.68</v>
       </c>
       <c r="K813" t="n">
-        <v>-83.68000000000001</v>
+        <v>-48.58</v>
       </c>
       <c r="L813" t="inlineStr">
         <is>
@@ -90983,7 +90983,7 @@
         </is>
       </c>
       <c r="N813" t="n">
-        <v>11.09</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="814">
@@ -90998,31 +90998,31 @@
         </is>
       </c>
       <c r="C814" t="n">
-        <v>1417</v>
+        <v>1422.2</v>
       </c>
       <c r="D814" t="n">
         <v>1495.3</v>
       </c>
       <c r="E814" t="n">
-        <v>-78.3</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="F814" t="n">
-        <v>1422.7</v>
+        <v>1467.5</v>
       </c>
       <c r="G814" t="n">
         <v>1490.82</v>
       </c>
       <c r="H814" t="n">
-        <v>-68.12</v>
+        <v>-23.32</v>
       </c>
       <c r="I814" t="n">
-        <v>1386</v>
+        <v>1415</v>
       </c>
       <c r="J814" t="n">
         <v>1396.35</v>
       </c>
       <c r="K814" t="n">
-        <v>-10.35</v>
+        <v>18.65</v>
       </c>
       <c r="L814" t="inlineStr">
         <is>
@@ -91035,7 +91035,7 @@
         </is>
       </c>
       <c r="N814" t="n">
-        <v>5.24</v>
+        <v>4.89</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N814"/>
+  <dimension ref="A1:N824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42764,6 +42764,526 @@
       </c>
       <c r="N814" t="n">
         <v>11.11</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>671</v>
+      </c>
+      <c r="D815" t="n">
+        <v>635.33</v>
+      </c>
+      <c r="E815" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="F815" t="n">
+        <v>673</v>
+      </c>
+      <c r="G815" t="n">
+        <v>643.85</v>
+      </c>
+      <c r="H815" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="I815" t="n">
+        <v>659</v>
+      </c>
+      <c r="J815" t="n">
+        <v>640.04</v>
+      </c>
+      <c r="K815" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N815" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="D816" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="E816" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="F816" t="n">
+        <v>122.34</v>
+      </c>
+      <c r="G816" t="n">
+        <v>118.22</v>
+      </c>
+      <c r="H816" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I816" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="J816" t="n">
+        <v>116.94</v>
+      </c>
+      <c r="K816" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N816" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>296</v>
+      </c>
+      <c r="D817" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="E817" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="F817" t="n">
+        <v>296</v>
+      </c>
+      <c r="G817" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="H817" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="I817" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>288.95</v>
+      </c>
+      <c r="K817" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N817" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2123.74</v>
+      </c>
+      <c r="E818" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="G818" t="n">
+        <v>2209.51</v>
+      </c>
+      <c r="H818" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I818" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J818" t="n">
+        <v>2188.64</v>
+      </c>
+      <c r="K818" t="n">
+        <v>-88.64</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N818" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D819" t="n">
+        <v>1402.43</v>
+      </c>
+      <c r="E819" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="F819" t="n">
+        <v>1420</v>
+      </c>
+      <c r="G819" t="n">
+        <v>1402.43</v>
+      </c>
+      <c r="H819" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="I819" t="n">
+        <v>1391</v>
+      </c>
+      <c r="J819" t="n">
+        <v>1367.03</v>
+      </c>
+      <c r="K819" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N819" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="D820" t="n">
+        <v>2345.99</v>
+      </c>
+      <c r="E820" t="n">
+        <v>272.41</v>
+      </c>
+      <c r="F820" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="G820" t="n">
+        <v>2500.03</v>
+      </c>
+      <c r="H820" t="n">
+        <v>118.37</v>
+      </c>
+      <c r="I820" t="n">
+        <v>2498.7</v>
+      </c>
+      <c r="J820" t="n">
+        <v>2476.32</v>
+      </c>
+      <c r="K820" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N820" t="n">
+        <v>11.61</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D821" t="n">
+        <v>1873.88</v>
+      </c>
+      <c r="E821" t="n">
+        <v>123.12</v>
+      </c>
+      <c r="F821" t="n">
+        <v>2008.8</v>
+      </c>
+      <c r="G821" t="n">
+        <v>1934.19</v>
+      </c>
+      <c r="H821" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="I821" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J821" t="n">
+        <v>1912.91</v>
+      </c>
+      <c r="K821" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N821" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>331</v>
+      </c>
+      <c r="D822" t="n">
+        <v>317.56</v>
+      </c>
+      <c r="E822" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="F822" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="G822" t="n">
+        <v>317.56</v>
+      </c>
+      <c r="H822" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="I822" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="J822" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="K822" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N822" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D823" t="n">
+        <v>5578.09</v>
+      </c>
+      <c r="E823" t="n">
+        <v>254.41</v>
+      </c>
+      <c r="F823" t="n">
+        <v>5861</v>
+      </c>
+      <c r="G823" t="n">
+        <v>5618.54</v>
+      </c>
+      <c r="H823" t="n">
+        <v>242.46</v>
+      </c>
+      <c r="I823" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J823" t="n">
+        <v>5555.6</v>
+      </c>
+      <c r="K823" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N823" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D824" t="n">
+        <v>1209.02</v>
+      </c>
+      <c r="E824" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="F824" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="G824" t="n">
+        <v>1227.88</v>
+      </c>
+      <c r="H824" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="I824" t="n">
+        <v>1299.4</v>
+      </c>
+      <c r="J824" t="n">
+        <v>1248.15</v>
+      </c>
+      <c r="K824" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N824" t="n">
+        <v>8.35</v>
       </c>
     </row>
   </sheetData>
@@ -42777,7 +43297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48674,6 +49194,110 @@
       </c>
       <c r="N113" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="D114" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>22829.75</v>
+      </c>
+      <c r="G114" t="n">
+        <v>22840.71</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="I114" t="n">
+        <v>22636.85</v>
+      </c>
+      <c r="J114" t="n">
+        <v>22647.81</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>53974.9</v>
+      </c>
+      <c r="D115" t="n">
+        <v>53974.9</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>54654.05</v>
+      </c>
+      <c r="G115" t="n">
+        <v>54435.56</v>
+      </c>
+      <c r="H115" t="n">
+        <v>218.49</v>
+      </c>
+      <c r="I115" t="n">
+        <v>53951.2</v>
+      </c>
+      <c r="J115" t="n">
+        <v>53732.71</v>
+      </c>
+      <c r="K115" t="n">
+        <v>218.49</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48687,7 +49311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N814"/>
+  <dimension ref="A1:N824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91038,6 +91662,526 @@
         <v>4.89</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>671</v>
+      </c>
+      <c r="D815" t="n">
+        <v>649.49</v>
+      </c>
+      <c r="E815" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="F815" t="n">
+        <v>673</v>
+      </c>
+      <c r="G815" t="n">
+        <v>662.28</v>
+      </c>
+      <c r="H815" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="I815" t="n">
+        <v>659</v>
+      </c>
+      <c r="J815" t="n">
+        <v>644.95</v>
+      </c>
+      <c r="K815" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N815" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="D816" t="n">
+        <v>118.91</v>
+      </c>
+      <c r="E816" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F816" t="n">
+        <v>122.34</v>
+      </c>
+      <c r="G816" t="n">
+        <v>120.27</v>
+      </c>
+      <c r="H816" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I816" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="J816" t="n">
+        <v>116.12</v>
+      </c>
+      <c r="K816" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N816" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>296</v>
+      </c>
+      <c r="D817" t="n">
+        <v>290.62</v>
+      </c>
+      <c r="E817" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F817" t="n">
+        <v>296</v>
+      </c>
+      <c r="G817" t="n">
+        <v>291.59</v>
+      </c>
+      <c r="H817" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I817" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>284.93</v>
+      </c>
+      <c r="K817" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N817" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2150.46</v>
+      </c>
+      <c r="E818" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="G818" t="n">
+        <v>2192.54</v>
+      </c>
+      <c r="H818" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="I818" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J818" t="n">
+        <v>2122.25</v>
+      </c>
+      <c r="K818" t="n">
+        <v>-22.25</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N818" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="D819" t="n">
+        <v>2418.33</v>
+      </c>
+      <c r="E819" t="n">
+        <v>200.07</v>
+      </c>
+      <c r="F819" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="G819" t="n">
+        <v>2605.2</v>
+      </c>
+      <c r="H819" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I819" t="n">
+        <v>2498.7</v>
+      </c>
+      <c r="J819" t="n">
+        <v>2500.74</v>
+      </c>
+      <c r="K819" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N819" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>COFORGE (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D820" t="n">
+        <v>1940.55</v>
+      </c>
+      <c r="E820" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="F820" t="n">
+        <v>2008.8</v>
+      </c>
+      <c r="G820" t="n">
+        <v>1995.72</v>
+      </c>
+      <c r="H820" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I820" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J820" t="n">
+        <v>1900.51</v>
+      </c>
+      <c r="K820" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N820" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>331</v>
+      </c>
+      <c r="D821" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="E821" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F821" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="G821" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="H821" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I821" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="J821" t="n">
+        <v>315.79</v>
+      </c>
+      <c r="K821" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N821" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>HCLTECH (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D822" t="n">
+        <v>1443.2</v>
+      </c>
+      <c r="E822" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="F822" t="n">
+        <v>1420</v>
+      </c>
+      <c r="G822" t="n">
+        <v>1410.51</v>
+      </c>
+      <c r="H822" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="I822" t="n">
+        <v>1391</v>
+      </c>
+      <c r="J822" t="n">
+        <v>1357.98</v>
+      </c>
+      <c r="K822" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N822" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D823" t="n">
+        <v>5780.96</v>
+      </c>
+      <c r="E823" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="F823" t="n">
+        <v>5861</v>
+      </c>
+      <c r="G823" t="n">
+        <v>5833.03</v>
+      </c>
+      <c r="H823" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="I823" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J823" t="n">
+        <v>5547.43</v>
+      </c>
+      <c r="K823" t="n">
+        <v>142.57</v>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N823" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>DRREDDY (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D824" t="n">
+        <v>1237.34</v>
+      </c>
+      <c r="E824" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="F824" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="G824" t="n">
+        <v>1294.38</v>
+      </c>
+      <c r="H824" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="I824" t="n">
+        <v>1299.4</v>
+      </c>
+      <c r="J824" t="n">
+        <v>1258.07</v>
+      </c>
+      <c r="K824" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N824" t="n">
+        <v>5.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -42778,31 +42778,31 @@
         </is>
       </c>
       <c r="C815" t="n">
-        <v>671</v>
+        <v>662.3</v>
       </c>
       <c r="D815" t="n">
         <v>635.33</v>
       </c>
       <c r="E815" t="n">
-        <v>35.67</v>
+        <v>26.97</v>
       </c>
       <c r="F815" t="n">
-        <v>673</v>
+        <v>664.9</v>
       </c>
       <c r="G815" t="n">
         <v>643.85</v>
       </c>
       <c r="H815" t="n">
-        <v>29.15</v>
+        <v>21.05</v>
       </c>
       <c r="I815" t="n">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="J815" t="n">
         <v>640.04</v>
       </c>
       <c r="K815" t="n">
-        <v>18.96</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L815" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         </is>
       </c>
       <c r="N815" t="n">
-        <v>5.61</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="816">
@@ -42830,31 +42830,31 @@
         </is>
       </c>
       <c r="C816" t="n">
-        <v>121.27</v>
+        <v>120.89</v>
       </c>
       <c r="D816" t="n">
         <v>115.74</v>
       </c>
       <c r="E816" t="n">
-        <v>5.53</v>
+        <v>5.15</v>
       </c>
       <c r="F816" t="n">
-        <v>122.34</v>
+        <v>120.89</v>
       </c>
       <c r="G816" t="n">
         <v>118.22</v>
       </c>
       <c r="H816" t="n">
-        <v>4.12</v>
+        <v>2.67</v>
       </c>
       <c r="I816" t="n">
-        <v>120.2</v>
+        <v>118.2</v>
       </c>
       <c r="J816" t="n">
         <v>116.94</v>
       </c>
       <c r="K816" t="n">
-        <v>3.26</v>
+        <v>1.26</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
@@ -42863,11 +42863,11 @@
       </c>
       <c r="M816" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N816" t="n">
-        <v>4.78</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="817">
@@ -42882,31 +42882,31 @@
         </is>
       </c>
       <c r="C817" t="n">
-        <v>296</v>
+        <v>291.75</v>
       </c>
       <c r="D817" t="n">
         <v>285.03</v>
       </c>
       <c r="E817" t="n">
-        <v>10.97</v>
+        <v>6.72</v>
       </c>
       <c r="F817" t="n">
-        <v>296</v>
+        <v>292.75</v>
       </c>
       <c r="G817" t="n">
         <v>291.98</v>
       </c>
       <c r="H817" t="n">
-        <v>4.02</v>
+        <v>0.77</v>
       </c>
       <c r="I817" t="n">
-        <v>288.1</v>
+        <v>282.05</v>
       </c>
       <c r="J817" t="n">
         <v>288.95</v>
       </c>
       <c r="K817" t="n">
-        <v>-0.85</v>
+        <v>-6.9</v>
       </c>
       <c r="L817" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         </is>
       </c>
       <c r="N817" t="n">
-        <v>3.85</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="818">
@@ -42934,31 +42934,31 @@
         </is>
       </c>
       <c r="C818" t="n">
-        <v>2213.9</v>
+        <v>2077.9</v>
       </c>
       <c r="D818" t="n">
         <v>2123.74</v>
       </c>
       <c r="E818" t="n">
-        <v>90.16</v>
+        <v>-45.84</v>
       </c>
       <c r="F818" t="n">
-        <v>2213.9</v>
+        <v>2084.9</v>
       </c>
       <c r="G818" t="n">
         <v>2209.51</v>
       </c>
       <c r="H818" t="n">
-        <v>4.39</v>
+        <v>-124.61</v>
       </c>
       <c r="I818" t="n">
-        <v>2100</v>
+        <v>2025.1</v>
       </c>
       <c r="J818" t="n">
         <v>2188.64</v>
       </c>
       <c r="K818" t="n">
-        <v>-88.64</v>
+        <v>-163.54</v>
       </c>
       <c r="L818" t="inlineStr">
         <is>
@@ -42967,11 +42967,11 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N818" t="n">
-        <v>4.25</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="819">
@@ -42986,31 +42986,31 @@
         </is>
       </c>
       <c r="C819" t="n">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="D819" t="n">
         <v>1402.43</v>
       </c>
       <c r="E819" t="n">
-        <v>17.57</v>
+        <v>14.57</v>
       </c>
       <c r="F819" t="n">
-        <v>1420</v>
+        <v>1422.7</v>
       </c>
       <c r="G819" t="n">
         <v>1402.43</v>
       </c>
       <c r="H819" t="n">
-        <v>17.57</v>
+        <v>20.27</v>
       </c>
       <c r="I819" t="n">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="J819" t="n">
         <v>1367.03</v>
       </c>
       <c r="K819" t="n">
-        <v>23.97</v>
+        <v>18.97</v>
       </c>
       <c r="L819" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         </is>
       </c>
       <c r="N819" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="820">
@@ -43038,31 +43038,31 @@
         </is>
       </c>
       <c r="C820" t="n">
-        <v>2618.4</v>
+        <v>2557.6</v>
       </c>
       <c r="D820" t="n">
         <v>2345.99</v>
       </c>
       <c r="E820" t="n">
-        <v>272.41</v>
+        <v>211.61</v>
       </c>
       <c r="F820" t="n">
-        <v>2618.4</v>
+        <v>2563.3</v>
       </c>
       <c r="G820" t="n">
         <v>2500.03</v>
       </c>
       <c r="H820" t="n">
-        <v>118.37</v>
+        <v>63.27</v>
       </c>
       <c r="I820" t="n">
-        <v>2498.7</v>
+        <v>2435</v>
       </c>
       <c r="J820" t="n">
         <v>2476.32</v>
       </c>
       <c r="K820" t="n">
-        <v>22.38</v>
+        <v>-41.32</v>
       </c>
       <c r="L820" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         </is>
       </c>
       <c r="N820" t="n">
-        <v>11.61</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="821">
@@ -43090,31 +43090,31 @@
         </is>
       </c>
       <c r="C821" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D821" t="n">
         <v>1873.88</v>
       </c>
       <c r="E821" t="n">
-        <v>123.12</v>
+        <v>119.12</v>
       </c>
       <c r="F821" t="n">
-        <v>2008.8</v>
+        <v>1997.6</v>
       </c>
       <c r="G821" t="n">
         <v>1934.19</v>
       </c>
       <c r="H821" t="n">
-        <v>74.61</v>
+        <v>63.41</v>
       </c>
       <c r="I821" t="n">
-        <v>1953</v>
+        <v>1812.2</v>
       </c>
       <c r="J821" t="n">
         <v>1912.91</v>
       </c>
       <c r="K821" t="n">
-        <v>40.09</v>
+        <v>-100.71</v>
       </c>
       <c r="L821" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         </is>
       </c>
       <c r="N821" t="n">
-        <v>6.57</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="822">
@@ -43142,31 +43142,31 @@
         </is>
       </c>
       <c r="C822" t="n">
-        <v>331</v>
+        <v>325.55</v>
       </c>
       <c r="D822" t="n">
         <v>317.56</v>
       </c>
       <c r="E822" t="n">
-        <v>13.44</v>
+        <v>7.99</v>
       </c>
       <c r="F822" t="n">
-        <v>331.45</v>
+        <v>327.95</v>
       </c>
       <c r="G822" t="n">
         <v>317.56</v>
       </c>
       <c r="H822" t="n">
-        <v>13.89</v>
+        <v>10.39</v>
       </c>
       <c r="I822" t="n">
-        <v>323.35</v>
+        <v>313.65</v>
       </c>
       <c r="J822" t="n">
         <v>312.6</v>
       </c>
       <c r="K822" t="n">
-        <v>10.75</v>
+        <v>1.05</v>
       </c>
       <c r="L822" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         </is>
       </c>
       <c r="N822" t="n">
-        <v>4.23</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="823">
@@ -43194,31 +43194,31 @@
         </is>
       </c>
       <c r="C823" t="n">
-        <v>5832.5</v>
+        <v>5850</v>
       </c>
       <c r="D823" t="n">
         <v>5578.09</v>
       </c>
       <c r="E823" t="n">
-        <v>254.41</v>
+        <v>271.91</v>
       </c>
       <c r="F823" t="n">
-        <v>5861</v>
+        <v>5873.5</v>
       </c>
       <c r="G823" t="n">
         <v>5618.54</v>
       </c>
       <c r="H823" t="n">
-        <v>242.46</v>
+        <v>254.96</v>
       </c>
       <c r="I823" t="n">
-        <v>5690</v>
+        <v>5600</v>
       </c>
       <c r="J823" t="n">
         <v>5555.6</v>
       </c>
       <c r="K823" t="n">
-        <v>134.4</v>
+        <v>44.4</v>
       </c>
       <c r="L823" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         </is>
       </c>
       <c r="N823" t="n">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="824">
@@ -43246,31 +43246,31 @@
         </is>
       </c>
       <c r="C824" t="n">
-        <v>1310</v>
+        <v>1310.9</v>
       </c>
       <c r="D824" t="n">
         <v>1209.02</v>
       </c>
       <c r="E824" t="n">
-        <v>100.98</v>
+        <v>101.88</v>
       </c>
       <c r="F824" t="n">
-        <v>1323.7</v>
+        <v>1319</v>
       </c>
       <c r="G824" t="n">
         <v>1227.88</v>
       </c>
       <c r="H824" t="n">
-        <v>95.81999999999999</v>
+        <v>91.12</v>
       </c>
       <c r="I824" t="n">
-        <v>1299.4</v>
+        <v>1224</v>
       </c>
       <c r="J824" t="n">
         <v>1248.15</v>
       </c>
       <c r="K824" t="n">
-        <v>51.25</v>
+        <v>-24.15</v>
       </c>
       <c r="L824" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         </is>
       </c>
       <c r="N824" t="n">
-        <v>8.35</v>
+        <v>8.43</v>
       </c>
     </row>
   </sheetData>
@@ -49208,31 +49208,31 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>22749.75</v>
+        <v>22753.2</v>
       </c>
       <c r="D114" t="n">
         <v>22749.75</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="F114" t="n">
-        <v>22829.75</v>
+        <v>22753.2</v>
       </c>
       <c r="G114" t="n">
         <v>22840.71</v>
       </c>
       <c r="H114" t="n">
-        <v>-10.96</v>
+        <v>-87.51000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>22636.85</v>
+        <v>22387.35</v>
       </c>
       <c r="J114" t="n">
         <v>22647.81</v>
       </c>
       <c r="K114" t="n">
-        <v>-10.96</v>
+        <v>-260.46</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="115">
@@ -49260,31 +49260,31 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>53974.9</v>
+        <v>54366.7</v>
       </c>
       <c r="D115" t="n">
         <v>53974.9</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>391.8</v>
       </c>
       <c r="F115" t="n">
-        <v>54654.05</v>
+        <v>54392.5</v>
       </c>
       <c r="G115" t="n">
         <v>54435.56</v>
       </c>
       <c r="H115" t="n">
-        <v>218.49</v>
+        <v>-43.06</v>
       </c>
       <c r="I115" t="n">
-        <v>53951.2</v>
+        <v>53777.5</v>
       </c>
       <c r="J115" t="n">
         <v>53732.71</v>
       </c>
       <c r="K115" t="n">
-        <v>218.49</v>
+        <v>44.79</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -91674,31 +91674,31 @@
         </is>
       </c>
       <c r="C815" t="n">
-        <v>671</v>
+        <v>662.3</v>
       </c>
       <c r="D815" t="n">
         <v>649.49</v>
       </c>
       <c r="E815" t="n">
-        <v>21.51</v>
+        <v>12.81</v>
       </c>
       <c r="F815" t="n">
-        <v>673</v>
+        <v>664.9</v>
       </c>
       <c r="G815" t="n">
         <v>662.28</v>
       </c>
       <c r="H815" t="n">
-        <v>10.72</v>
+        <v>2.62</v>
       </c>
       <c r="I815" t="n">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="J815" t="n">
         <v>644.95</v>
       </c>
       <c r="K815" t="n">
-        <v>14.05</v>
+        <v>5.05</v>
       </c>
       <c r="L815" t="inlineStr">
         <is>
@@ -91711,7 +91711,7 @@
         </is>
       </c>
       <c r="N815" t="n">
-        <v>3.31</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="816">
@@ -91726,31 +91726,31 @@
         </is>
       </c>
       <c r="C816" t="n">
-        <v>121.27</v>
+        <v>120.89</v>
       </c>
       <c r="D816" t="n">
         <v>118.91</v>
       </c>
       <c r="E816" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="F816" t="n">
-        <v>122.34</v>
+        <v>120.89</v>
       </c>
       <c r="G816" t="n">
         <v>120.27</v>
       </c>
       <c r="H816" t="n">
-        <v>2.07</v>
+        <v>0.62</v>
       </c>
       <c r="I816" t="n">
-        <v>120.2</v>
+        <v>118.2</v>
       </c>
       <c r="J816" t="n">
         <v>116.12</v>
       </c>
       <c r="K816" t="n">
-        <v>4.08</v>
+        <v>2.08</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
@@ -91763,7 +91763,7 @@
         </is>
       </c>
       <c r="N816" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="817">
@@ -91778,31 +91778,31 @@
         </is>
       </c>
       <c r="C817" t="n">
-        <v>296</v>
+        <v>291.75</v>
       </c>
       <c r="D817" t="n">
         <v>290.62</v>
       </c>
       <c r="E817" t="n">
-        <v>5.38</v>
+        <v>1.13</v>
       </c>
       <c r="F817" t="n">
-        <v>296</v>
+        <v>292.75</v>
       </c>
       <c r="G817" t="n">
         <v>291.59</v>
       </c>
       <c r="H817" t="n">
-        <v>4.41</v>
+        <v>1.16</v>
       </c>
       <c r="I817" t="n">
-        <v>288.1</v>
+        <v>282.05</v>
       </c>
       <c r="J817" t="n">
         <v>284.93</v>
       </c>
       <c r="K817" t="n">
-        <v>3.17</v>
+        <v>-2.88</v>
       </c>
       <c r="L817" t="inlineStr">
         <is>
@@ -91815,7 +91815,7 @@
         </is>
       </c>
       <c r="N817" t="n">
-        <v>1.85</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="818">
@@ -91830,31 +91830,31 @@
         </is>
       </c>
       <c r="C818" t="n">
-        <v>2213.9</v>
+        <v>2077.9</v>
       </c>
       <c r="D818" t="n">
         <v>2150.46</v>
       </c>
       <c r="E818" t="n">
-        <v>63.44</v>
+        <v>-72.56</v>
       </c>
       <c r="F818" t="n">
-        <v>2213.9</v>
+        <v>2084.9</v>
       </c>
       <c r="G818" t="n">
         <v>2192.54</v>
       </c>
       <c r="H818" t="n">
-        <v>21.36</v>
+        <v>-107.64</v>
       </c>
       <c r="I818" t="n">
-        <v>2100</v>
+        <v>2025.1</v>
       </c>
       <c r="J818" t="n">
         <v>2122.25</v>
       </c>
       <c r="K818" t="n">
-        <v>-22.25</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="L818" t="inlineStr">
         <is>
@@ -91863,11 +91863,11 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N818" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="819">
@@ -91882,31 +91882,31 @@
         </is>
       </c>
       <c r="C819" t="n">
-        <v>2618.4</v>
+        <v>2557.6</v>
       </c>
       <c r="D819" t="n">
         <v>2418.33</v>
       </c>
       <c r="E819" t="n">
-        <v>200.07</v>
+        <v>139.27</v>
       </c>
       <c r="F819" t="n">
-        <v>2618.4</v>
+        <v>2563.3</v>
       </c>
       <c r="G819" t="n">
         <v>2605.2</v>
       </c>
       <c r="H819" t="n">
-        <v>13.2</v>
+        <v>-41.9</v>
       </c>
       <c r="I819" t="n">
-        <v>2498.7</v>
+        <v>2435</v>
       </c>
       <c r="J819" t="n">
         <v>2500.74</v>
       </c>
       <c r="K819" t="n">
-        <v>-2.04</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="L819" t="inlineStr">
         <is>
@@ -91919,7 +91919,7 @@
         </is>
       </c>
       <c r="N819" t="n">
-        <v>8.27</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="820">
@@ -91934,31 +91934,31 @@
         </is>
       </c>
       <c r="C820" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D820" t="n">
         <v>1940.55</v>
       </c>
       <c r="E820" t="n">
-        <v>56.45</v>
+        <v>52.45</v>
       </c>
       <c r="F820" t="n">
-        <v>2008.8</v>
+        <v>1997.6</v>
       </c>
       <c r="G820" t="n">
         <v>1995.72</v>
       </c>
       <c r="H820" t="n">
-        <v>13.08</v>
+        <v>1.88</v>
       </c>
       <c r="I820" t="n">
-        <v>1953</v>
+        <v>1812.2</v>
       </c>
       <c r="J820" t="n">
         <v>1900.51</v>
       </c>
       <c r="K820" t="n">
-        <v>52.49</v>
+        <v>-88.31</v>
       </c>
       <c r="L820" t="inlineStr">
         <is>
@@ -91971,7 +91971,7 @@
         </is>
       </c>
       <c r="N820" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="821">
@@ -91986,31 +91986,31 @@
         </is>
       </c>
       <c r="C821" t="n">
-        <v>331</v>
+        <v>325.55</v>
       </c>
       <c r="D821" t="n">
         <v>327.8</v>
       </c>
       <c r="E821" t="n">
-        <v>3.2</v>
+        <v>-2.25</v>
       </c>
       <c r="F821" t="n">
-        <v>331.45</v>
+        <v>327.95</v>
       </c>
       <c r="G821" t="n">
         <v>329.77</v>
       </c>
       <c r="H821" t="n">
-        <v>1.68</v>
+        <v>-1.82</v>
       </c>
       <c r="I821" t="n">
-        <v>323.35</v>
+        <v>313.65</v>
       </c>
       <c r="J821" t="n">
         <v>315.79</v>
       </c>
       <c r="K821" t="n">
-        <v>7.56</v>
+        <v>-2.14</v>
       </c>
       <c r="L821" t="inlineStr">
         <is>
@@ -92023,7 +92023,7 @@
         </is>
       </c>
       <c r="N821" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="822">
@@ -92038,31 +92038,31 @@
         </is>
       </c>
       <c r="C822" t="n">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="D822" t="n">
         <v>1443.2</v>
       </c>
       <c r="E822" t="n">
-        <v>-23.2</v>
+        <v>-26.2</v>
       </c>
       <c r="F822" t="n">
-        <v>1420</v>
+        <v>1422.7</v>
       </c>
       <c r="G822" t="n">
         <v>1410.51</v>
       </c>
       <c r="H822" t="n">
-        <v>9.49</v>
+        <v>12.19</v>
       </c>
       <c r="I822" t="n">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="J822" t="n">
         <v>1357.98</v>
       </c>
       <c r="K822" t="n">
-        <v>33.02</v>
+        <v>28.02</v>
       </c>
       <c r="L822" t="inlineStr">
         <is>
@@ -92075,7 +92075,7 @@
         </is>
       </c>
       <c r="N822" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="823">
@@ -92090,31 +92090,31 @@
         </is>
       </c>
       <c r="C823" t="n">
-        <v>5832.5</v>
+        <v>5850</v>
       </c>
       <c r="D823" t="n">
         <v>5780.96</v>
       </c>
       <c r="E823" t="n">
-        <v>51.54</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F823" t="n">
-        <v>5861</v>
+        <v>5873.5</v>
       </c>
       <c r="G823" t="n">
         <v>5833.03</v>
       </c>
       <c r="H823" t="n">
-        <v>27.97</v>
+        <v>40.47</v>
       </c>
       <c r="I823" t="n">
-        <v>5690</v>
+        <v>5600</v>
       </c>
       <c r="J823" t="n">
         <v>5547.43</v>
       </c>
       <c r="K823" t="n">
-        <v>142.57</v>
+        <v>52.57</v>
       </c>
       <c r="L823" t="inlineStr">
         <is>
@@ -92127,7 +92127,7 @@
         </is>
       </c>
       <c r="N823" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="824">
@@ -92142,31 +92142,31 @@
         </is>
       </c>
       <c r="C824" t="n">
-        <v>1310</v>
+        <v>1310.9</v>
       </c>
       <c r="D824" t="n">
         <v>1237.34</v>
       </c>
       <c r="E824" t="n">
-        <v>72.66</v>
+        <v>73.56</v>
       </c>
       <c r="F824" t="n">
-        <v>1323.7</v>
+        <v>1319</v>
       </c>
       <c r="G824" t="n">
         <v>1294.38</v>
       </c>
       <c r="H824" t="n">
-        <v>29.32</v>
+        <v>24.62</v>
       </c>
       <c r="I824" t="n">
-        <v>1299.4</v>
+        <v>1224</v>
       </c>
       <c r="J824" t="n">
         <v>1258.07</v>
       </c>
       <c r="K824" t="n">
-        <v>41.33</v>
+        <v>-34.07</v>
       </c>
       <c r="L824" t="inlineStr">
         <is>
@@ -92179,7 +92179,7 @@
         </is>
       </c>
       <c r="N824" t="n">
-        <v>5.87</v>
+        <v>5.95</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N824"/>
+  <dimension ref="A1:N833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43284,6 +43284,474 @@
       </c>
       <c r="N824" t="n">
         <v>8.43</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>1335.4</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1459.51</v>
+      </c>
+      <c r="E825" t="n">
+        <v>-124.11</v>
+      </c>
+      <c r="F825" t="n">
+        <v>1338.2</v>
+      </c>
+      <c r="G825" t="n">
+        <v>1459.51</v>
+      </c>
+      <c r="H825" t="n">
+        <v>-121.31</v>
+      </c>
+      <c r="I825" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J825" t="n">
+        <v>1305.41</v>
+      </c>
+      <c r="K825" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N825" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>120.31</v>
+      </c>
+      <c r="D826" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="E826" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="F826" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G826" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="H826" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="I826" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="J826" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="K826" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N826" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>666.3</v>
+      </c>
+      <c r="D827" t="n">
+        <v>700.14</v>
+      </c>
+      <c r="E827" t="n">
+        <v>-33.84</v>
+      </c>
+      <c r="F827" t="n">
+        <v>671.4</v>
+      </c>
+      <c r="G827" t="n">
+        <v>700.14</v>
+      </c>
+      <c r="H827" t="n">
+        <v>-28.74</v>
+      </c>
+      <c r="I827" t="n">
+        <v>663.95</v>
+      </c>
+      <c r="J827" t="n">
+        <v>647.64</v>
+      </c>
+      <c r="K827" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N827" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>5848</v>
+      </c>
+      <c r="D828" t="n">
+        <v>6182.15</v>
+      </c>
+      <c r="E828" t="n">
+        <v>-334.15</v>
+      </c>
+      <c r="F828" t="n">
+        <v>5872.5</v>
+      </c>
+      <c r="G828" t="n">
+        <v>6182.15</v>
+      </c>
+      <c r="H828" t="n">
+        <v>-309.65</v>
+      </c>
+      <c r="I828" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J828" t="n">
+        <v>5614.44</v>
+      </c>
+      <c r="K828" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N828" t="n">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>2165.3</v>
+      </c>
+      <c r="D829" t="n">
+        <v>2135.52</v>
+      </c>
+      <c r="E829" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="F829" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G829" t="n">
+        <v>2135.52</v>
+      </c>
+      <c r="H829" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="I829" t="n">
+        <v>2156.3</v>
+      </c>
+      <c r="J829" t="n">
+        <v>2089.74</v>
+      </c>
+      <c r="K829" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N829" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>1961.9</v>
+      </c>
+      <c r="D830" t="n">
+        <v>2103.32</v>
+      </c>
+      <c r="E830" t="n">
+        <v>-141.42</v>
+      </c>
+      <c r="F830" t="n">
+        <v>1977.8</v>
+      </c>
+      <c r="G830" t="n">
+        <v>2103.32</v>
+      </c>
+      <c r="H830" t="n">
+        <v>-125.52</v>
+      </c>
+      <c r="I830" t="n">
+        <v>1903.8</v>
+      </c>
+      <c r="J830" t="n">
+        <v>1887.63</v>
+      </c>
+      <c r="K830" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N830" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>1400.5</v>
+      </c>
+      <c r="D831" t="n">
+        <v>1426.37</v>
+      </c>
+      <c r="E831" t="n">
+        <v>-25.87</v>
+      </c>
+      <c r="F831" t="n">
+        <v>1401.4</v>
+      </c>
+      <c r="G831" t="n">
+        <v>1427.07</v>
+      </c>
+      <c r="H831" t="n">
+        <v>-25.67</v>
+      </c>
+      <c r="I831" t="n">
+        <v>1364</v>
+      </c>
+      <c r="J831" t="n">
+        <v>1363.3</v>
+      </c>
+      <c r="K831" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N831" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>2518</v>
+      </c>
+      <c r="D832" t="n">
+        <v>2767.08</v>
+      </c>
+      <c r="E832" t="n">
+        <v>-249.08</v>
+      </c>
+      <c r="F832" t="n">
+        <v>2563.9</v>
+      </c>
+      <c r="G832" t="n">
+        <v>2767.08</v>
+      </c>
+      <c r="H832" t="n">
+        <v>-203.18</v>
+      </c>
+      <c r="I832" t="n">
+        <v>2455.2</v>
+      </c>
+      <c r="J832" t="n">
+        <v>2417.66</v>
+      </c>
+      <c r="K832" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N832" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D833" t="n">
+        <v>2550.72</v>
+      </c>
+      <c r="E833" t="n">
+        <v>-90.72</v>
+      </c>
+      <c r="F833" t="n">
+        <v>2461.3</v>
+      </c>
+      <c r="G833" t="n">
+        <v>2550.72</v>
+      </c>
+      <c r="H833" t="n">
+        <v>-89.42</v>
+      </c>
+      <c r="I833" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="J833" t="n">
+        <v>2362.5</v>
+      </c>
+      <c r="K833" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N833" t="n">
+        <v>3.56</v>
       </c>
     </row>
   </sheetData>
@@ -43297,7 +43765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49298,6 +49766,110 @@
       </c>
       <c r="N115" t="n">
         <v>0.73</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="D116" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>22778.05</v>
+      </c>
+      <c r="G116" t="n">
+        <v>22818.7</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="I116" t="n">
+        <v>22497.7</v>
+      </c>
+      <c r="J116" t="n">
+        <v>22538.35</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>54267.4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>54267.4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>54440.25</v>
+      </c>
+      <c r="G117" t="n">
+        <v>54596.39</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-156.14</v>
+      </c>
+      <c r="I117" t="n">
+        <v>53626.15</v>
+      </c>
+      <c r="J117" t="n">
+        <v>53782.29</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-156.14</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -49311,7 +49883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N824"/>
+  <dimension ref="A1:N833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92182,6 +92754,474 @@
         <v>5.95</v>
       </c>
     </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>DRREDDY (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>1335.4</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1493.47</v>
+      </c>
+      <c r="E825" t="n">
+        <v>-158.07</v>
+      </c>
+      <c r="F825" t="n">
+        <v>1338.2</v>
+      </c>
+      <c r="G825" t="n">
+        <v>1392.5</v>
+      </c>
+      <c r="H825" t="n">
+        <v>-54.3</v>
+      </c>
+      <c r="I825" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J825" t="n">
+        <v>1307.84</v>
+      </c>
+      <c r="K825" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N825" t="n">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>120.31</v>
+      </c>
+      <c r="D826" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="E826" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F826" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G826" t="n">
+        <v>126</v>
+      </c>
+      <c r="H826" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I826" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="J826" t="n">
+        <v>117.43</v>
+      </c>
+      <c r="K826" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N826" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>666.3</v>
+      </c>
+      <c r="D827" t="n">
+        <v>716.22</v>
+      </c>
+      <c r="E827" t="n">
+        <v>-49.92</v>
+      </c>
+      <c r="F827" t="n">
+        <v>671.4</v>
+      </c>
+      <c r="G827" t="n">
+        <v>694.59</v>
+      </c>
+      <c r="H827" t="n">
+        <v>-23.19</v>
+      </c>
+      <c r="I827" t="n">
+        <v>663.95</v>
+      </c>
+      <c r="J827" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="K827" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N827" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>5848</v>
+      </c>
+      <c r="D828" t="n">
+        <v>6413.84</v>
+      </c>
+      <c r="E828" t="n">
+        <v>-565.84</v>
+      </c>
+      <c r="F828" t="n">
+        <v>5872.5</v>
+      </c>
+      <c r="G828" t="n">
+        <v>6179.45</v>
+      </c>
+      <c r="H828" t="n">
+        <v>-306.95</v>
+      </c>
+      <c r="I828" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J828" t="n">
+        <v>5666.9</v>
+      </c>
+      <c r="K828" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N828" t="n">
+        <v>8.82</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>COFORGE (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>1961.9</v>
+      </c>
+      <c r="D829" t="n">
+        <v>2180.21</v>
+      </c>
+      <c r="E829" t="n">
+        <v>-218.31</v>
+      </c>
+      <c r="F829" t="n">
+        <v>1977.8</v>
+      </c>
+      <c r="G829" t="n">
+        <v>2071.34</v>
+      </c>
+      <c r="H829" t="n">
+        <v>-93.54000000000001</v>
+      </c>
+      <c r="I829" t="n">
+        <v>1903.8</v>
+      </c>
+      <c r="J829" t="n">
+        <v>1902.46</v>
+      </c>
+      <c r="K829" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N829" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>2518</v>
+      </c>
+      <c r="D830" t="n">
+        <v>2864.38</v>
+      </c>
+      <c r="E830" t="n">
+        <v>-346.38</v>
+      </c>
+      <c r="F830" t="n">
+        <v>2563.9</v>
+      </c>
+      <c r="G830" t="n">
+        <v>2655</v>
+      </c>
+      <c r="H830" t="n">
+        <v>-91.09999999999999</v>
+      </c>
+      <c r="I830" t="n">
+        <v>2455.2</v>
+      </c>
+      <c r="J830" t="n">
+        <v>2444.26</v>
+      </c>
+      <c r="K830" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N830" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>2165.3</v>
+      </c>
+      <c r="D831" t="n">
+        <v>2199.7</v>
+      </c>
+      <c r="E831" t="n">
+        <v>-34.4</v>
+      </c>
+      <c r="F831" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G831" t="n">
+        <v>2272.28</v>
+      </c>
+      <c r="H831" t="n">
+        <v>-53.28</v>
+      </c>
+      <c r="I831" t="n">
+        <v>2156.3</v>
+      </c>
+      <c r="J831" t="n">
+        <v>2109.94</v>
+      </c>
+      <c r="K831" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N831" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>HCLTECH (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>1400.5</v>
+      </c>
+      <c r="D832" t="n">
+        <v>1469.33</v>
+      </c>
+      <c r="E832" t="n">
+        <v>-68.83</v>
+      </c>
+      <c r="F832" t="n">
+        <v>1401.4</v>
+      </c>
+      <c r="G832" t="n">
+        <v>1469.78</v>
+      </c>
+      <c r="H832" t="n">
+        <v>-68.38</v>
+      </c>
+      <c r="I832" t="n">
+        <v>1364</v>
+      </c>
+      <c r="J832" t="n">
+        <v>1364.62</v>
+      </c>
+      <c r="K832" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N832" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>TCS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D833" t="n">
+        <v>2639.85</v>
+      </c>
+      <c r="E833" t="n">
+        <v>-179.85</v>
+      </c>
+      <c r="F833" t="n">
+        <v>2461.3</v>
+      </c>
+      <c r="G833" t="n">
+        <v>2593.31</v>
+      </c>
+      <c r="H833" t="n">
+        <v>-132.01</v>
+      </c>
+      <c r="I833" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="J833" t="n">
+        <v>2388.36</v>
+      </c>
+      <c r="K833" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N833" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -43298,31 +43298,31 @@
         </is>
       </c>
       <c r="C825" t="n">
-        <v>1335.4</v>
+        <v>1310</v>
       </c>
       <c r="D825" t="n">
         <v>1459.51</v>
       </c>
       <c r="E825" t="n">
-        <v>-124.11</v>
+        <v>-149.51</v>
       </c>
       <c r="F825" t="n">
-        <v>1338.2</v>
+        <v>1323.7</v>
       </c>
       <c r="G825" t="n">
         <v>1459.51</v>
       </c>
       <c r="H825" t="n">
-        <v>-121.31</v>
+        <v>-135.81</v>
       </c>
       <c r="I825" t="n">
-        <v>1301</v>
+        <v>1299.4</v>
       </c>
       <c r="J825" t="n">
         <v>1305.41</v>
       </c>
       <c r="K825" t="n">
-        <v>-4.41</v>
+        <v>-6.01</v>
       </c>
       <c r="L825" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         </is>
       </c>
       <c r="N825" t="n">
-        <v>8.5</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="826">
@@ -43350,31 +43350,31 @@
         </is>
       </c>
       <c r="C826" t="n">
-        <v>120.31</v>
+        <v>121.27</v>
       </c>
       <c r="D826" t="n">
         <v>126.67</v>
       </c>
       <c r="E826" t="n">
-        <v>-6.36</v>
+        <v>-5.4</v>
       </c>
       <c r="F826" t="n">
-        <v>121.5</v>
+        <v>122.34</v>
       </c>
       <c r="G826" t="n">
         <v>126.67</v>
       </c>
       <c r="H826" t="n">
-        <v>-5.17</v>
+        <v>-4.33</v>
       </c>
       <c r="I826" t="n">
-        <v>119.42</v>
+        <v>120.2</v>
       </c>
       <c r="J826" t="n">
         <v>118.87</v>
       </c>
       <c r="K826" t="n">
-        <v>0.55</v>
+        <v>1.33</v>
       </c>
       <c r="L826" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         </is>
       </c>
       <c r="N826" t="n">
-        <v>5.02</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="827">
@@ -43402,31 +43402,31 @@
         </is>
       </c>
       <c r="C827" t="n">
-        <v>666.3</v>
+        <v>671</v>
       </c>
       <c r="D827" t="n">
         <v>700.14</v>
       </c>
       <c r="E827" t="n">
-        <v>-33.84</v>
+        <v>-29.14</v>
       </c>
       <c r="F827" t="n">
-        <v>671.4</v>
+        <v>673</v>
       </c>
       <c r="G827" t="n">
         <v>700.14</v>
       </c>
       <c r="H827" t="n">
-        <v>-28.74</v>
+        <v>-27.14</v>
       </c>
       <c r="I827" t="n">
-        <v>663.95</v>
+        <v>659</v>
       </c>
       <c r="J827" t="n">
         <v>647.64</v>
       </c>
       <c r="K827" t="n">
-        <v>16.31</v>
+        <v>11.36</v>
       </c>
       <c r="L827" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         </is>
       </c>
       <c r="N827" t="n">
-        <v>4.83</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="828">
@@ -43454,31 +43454,31 @@
         </is>
       </c>
       <c r="C828" t="n">
-        <v>5848</v>
+        <v>5832.5</v>
       </c>
       <c r="D828" t="n">
         <v>6182.15</v>
       </c>
       <c r="E828" t="n">
-        <v>-334.15</v>
+        <v>-349.65</v>
       </c>
       <c r="F828" t="n">
-        <v>5872.5</v>
+        <v>5861</v>
       </c>
       <c r="G828" t="n">
         <v>6182.15</v>
       </c>
       <c r="H828" t="n">
-        <v>-309.65</v>
+        <v>-321.15</v>
       </c>
       <c r="I828" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="J828" t="n">
         <v>5614.44</v>
       </c>
       <c r="K828" t="n">
-        <v>35.56</v>
+        <v>75.56</v>
       </c>
       <c r="L828" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         </is>
       </c>
       <c r="N828" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="829">
@@ -43506,31 +43506,31 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>2165.3</v>
+        <v>2213.9</v>
       </c>
       <c r="D829" t="n">
         <v>2135.52</v>
       </c>
       <c r="E829" t="n">
-        <v>29.78</v>
+        <v>78.38</v>
       </c>
       <c r="F829" t="n">
-        <v>2219</v>
+        <v>2213.9</v>
       </c>
       <c r="G829" t="n">
         <v>2135.52</v>
       </c>
       <c r="H829" t="n">
-        <v>83.48</v>
+        <v>78.38</v>
       </c>
       <c r="I829" t="n">
-        <v>2156.3</v>
+        <v>2100</v>
       </c>
       <c r="J829" t="n">
         <v>2089.74</v>
       </c>
       <c r="K829" t="n">
-        <v>66.56</v>
+        <v>10.26</v>
       </c>
       <c r="L829" t="inlineStr">
         <is>
@@ -43539,11 +43539,11 @@
       </c>
       <c r="M829" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N829" t="n">
-        <v>1.39</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="830">
@@ -43558,31 +43558,31 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>1961.9</v>
+        <v>1997</v>
       </c>
       <c r="D830" t="n">
         <v>2103.32</v>
       </c>
       <c r="E830" t="n">
-        <v>-141.42</v>
+        <v>-106.32</v>
       </c>
       <c r="F830" t="n">
-        <v>1977.8</v>
+        <v>2008.8</v>
       </c>
       <c r="G830" t="n">
         <v>2103.32</v>
       </c>
       <c r="H830" t="n">
-        <v>-125.52</v>
+        <v>-94.52</v>
       </c>
       <c r="I830" t="n">
-        <v>1903.8</v>
+        <v>1953</v>
       </c>
       <c r="J830" t="n">
         <v>1887.63</v>
       </c>
       <c r="K830" t="n">
-        <v>16.17</v>
+        <v>65.37</v>
       </c>
       <c r="L830" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         </is>
       </c>
       <c r="N830" t="n">
-        <v>6.72</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="831">
@@ -43610,31 +43610,31 @@
         </is>
       </c>
       <c r="C831" t="n">
-        <v>1400.5</v>
+        <v>1420</v>
       </c>
       <c r="D831" t="n">
         <v>1426.37</v>
       </c>
       <c r="E831" t="n">
-        <v>-25.87</v>
+        <v>-6.37</v>
       </c>
       <c r="F831" t="n">
-        <v>1401.4</v>
+        <v>1420</v>
       </c>
       <c r="G831" t="n">
         <v>1427.07</v>
       </c>
       <c r="H831" t="n">
-        <v>-25.67</v>
+        <v>-7.07</v>
       </c>
       <c r="I831" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="J831" t="n">
         <v>1363.3</v>
       </c>
       <c r="K831" t="n">
-        <v>0.7</v>
+        <v>27.7</v>
       </c>
       <c r="L831" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         </is>
       </c>
       <c r="N831" t="n">
-        <v>1.81</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="832">
@@ -43662,31 +43662,31 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>2518</v>
+        <v>2618.4</v>
       </c>
       <c r="D832" t="n">
         <v>2767.08</v>
       </c>
       <c r="E832" t="n">
-        <v>-249.08</v>
+        <v>-148.68</v>
       </c>
       <c r="F832" t="n">
-        <v>2563.9</v>
+        <v>2618.4</v>
       </c>
       <c r="G832" t="n">
         <v>2767.08</v>
       </c>
       <c r="H832" t="n">
-        <v>-203.18</v>
+        <v>-148.68</v>
       </c>
       <c r="I832" t="n">
-        <v>2455.2</v>
+        <v>2498.7</v>
       </c>
       <c r="J832" t="n">
         <v>2417.66</v>
       </c>
       <c r="K832" t="n">
-        <v>37.54</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="L832" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         </is>
       </c>
       <c r="N832" t="n">
-        <v>9</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="833">
@@ -43714,31 +43714,31 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>2460</v>
+        <v>2496.9</v>
       </c>
       <c r="D833" t="n">
         <v>2550.72</v>
       </c>
       <c r="E833" t="n">
-        <v>-90.72</v>
+        <v>-53.82</v>
       </c>
       <c r="F833" t="n">
-        <v>2461.3</v>
+        <v>2534.9</v>
       </c>
       <c r="G833" t="n">
         <v>2550.72</v>
       </c>
       <c r="H833" t="n">
-        <v>-89.42</v>
+        <v>-15.82</v>
       </c>
       <c r="I833" t="n">
-        <v>2408.2</v>
+        <v>2465.4</v>
       </c>
       <c r="J833" t="n">
         <v>2362.5</v>
       </c>
       <c r="K833" t="n">
-        <v>45.7</v>
+        <v>102.9</v>
       </c>
       <c r="L833" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         </is>
       </c>
       <c r="N833" t="n">
-        <v>3.56</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -49780,31 +49780,31 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>22698.85</v>
+        <v>22749.75</v>
       </c>
       <c r="D116" t="n">
         <v>22698.85</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>50.9</v>
       </c>
       <c r="F116" t="n">
-        <v>22778.05</v>
+        <v>22829.75</v>
       </c>
       <c r="G116" t="n">
         <v>22818.7</v>
       </c>
       <c r="H116" t="n">
-        <v>-40.65</v>
+        <v>11.05</v>
       </c>
       <c r="I116" t="n">
-        <v>22497.7</v>
+        <v>22636.85</v>
       </c>
       <c r="J116" t="n">
         <v>22538.35</v>
       </c>
       <c r="K116" t="n">
-        <v>-40.65</v>
+        <v>98.5</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -49817,7 +49817,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="117">
@@ -49832,31 +49832,31 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>54267.4</v>
+        <v>53974.9</v>
       </c>
       <c r="D117" t="n">
         <v>54267.4</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>-292.5</v>
       </c>
       <c r="F117" t="n">
-        <v>54440.25</v>
+        <v>54654.05</v>
       </c>
       <c r="G117" t="n">
         <v>54596.39</v>
       </c>
       <c r="H117" t="n">
-        <v>-156.14</v>
+        <v>57.66</v>
       </c>
       <c r="I117" t="n">
-        <v>53626.15</v>
+        <v>53951.2</v>
       </c>
       <c r="J117" t="n">
         <v>53782.29</v>
       </c>
       <c r="K117" t="n">
-        <v>-156.14</v>
+        <v>168.91</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -92766,31 +92766,31 @@
         </is>
       </c>
       <c r="C825" t="n">
-        <v>1335.4</v>
+        <v>1310</v>
       </c>
       <c r="D825" t="n">
         <v>1493.47</v>
       </c>
       <c r="E825" t="n">
-        <v>-158.07</v>
+        <v>-183.47</v>
       </c>
       <c r="F825" t="n">
-        <v>1338.2</v>
+        <v>1323.7</v>
       </c>
       <c r="G825" t="n">
         <v>1392.5</v>
       </c>
       <c r="H825" t="n">
-        <v>-54.3</v>
+        <v>-68.8</v>
       </c>
       <c r="I825" t="n">
-        <v>1301</v>
+        <v>1299.4</v>
       </c>
       <c r="J825" t="n">
         <v>1307.84</v>
       </c>
       <c r="K825" t="n">
-        <v>-6.84</v>
+        <v>-8.44</v>
       </c>
       <c r="L825" t="inlineStr">
         <is>
@@ -92803,7 +92803,7 @@
         </is>
       </c>
       <c r="N825" t="n">
-        <v>10.58</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="826">
@@ -92818,31 +92818,31 @@
         </is>
       </c>
       <c r="C826" t="n">
-        <v>120.31</v>
+        <v>121.27</v>
       </c>
       <c r="D826" t="n">
         <v>130.21</v>
       </c>
       <c r="E826" t="n">
-        <v>-9.9</v>
+        <v>-8.94</v>
       </c>
       <c r="F826" t="n">
-        <v>121.5</v>
+        <v>122.34</v>
       </c>
       <c r="G826" t="n">
         <v>126</v>
       </c>
       <c r="H826" t="n">
-        <v>-4.5</v>
+        <v>-3.66</v>
       </c>
       <c r="I826" t="n">
-        <v>119.42</v>
+        <v>120.2</v>
       </c>
       <c r="J826" t="n">
         <v>117.43</v>
       </c>
       <c r="K826" t="n">
-        <v>1.99</v>
+        <v>2.77</v>
       </c>
       <c r="L826" t="inlineStr">
         <is>
@@ -92855,7 +92855,7 @@
         </is>
       </c>
       <c r="N826" t="n">
-        <v>7.6</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="827">
@@ -92870,31 +92870,31 @@
         </is>
       </c>
       <c r="C827" t="n">
-        <v>666.3</v>
+        <v>671</v>
       </c>
       <c r="D827" t="n">
         <v>716.22</v>
       </c>
       <c r="E827" t="n">
-        <v>-49.92</v>
+        <v>-45.22</v>
       </c>
       <c r="F827" t="n">
-        <v>671.4</v>
+        <v>673</v>
       </c>
       <c r="G827" t="n">
         <v>694.59</v>
       </c>
       <c r="H827" t="n">
-        <v>-23.19</v>
+        <v>-21.59</v>
       </c>
       <c r="I827" t="n">
-        <v>663.95</v>
+        <v>659</v>
       </c>
       <c r="J827" t="n">
         <v>652.7</v>
       </c>
       <c r="K827" t="n">
-        <v>11.25</v>
+        <v>6.3</v>
       </c>
       <c r="L827" t="inlineStr">
         <is>
@@ -92907,7 +92907,7 @@
         </is>
       </c>
       <c r="N827" t="n">
-        <v>6.97</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="828">
@@ -92922,31 +92922,31 @@
         </is>
       </c>
       <c r="C828" t="n">
-        <v>5848</v>
+        <v>5832.5</v>
       </c>
       <c r="D828" t="n">
         <v>6413.84</v>
       </c>
       <c r="E828" t="n">
-        <v>-565.84</v>
+        <v>-581.34</v>
       </c>
       <c r="F828" t="n">
-        <v>5872.5</v>
+        <v>5861</v>
       </c>
       <c r="G828" t="n">
         <v>6179.45</v>
       </c>
       <c r="H828" t="n">
-        <v>-306.95</v>
+        <v>-318.45</v>
       </c>
       <c r="I828" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="J828" t="n">
         <v>5666.9</v>
       </c>
       <c r="K828" t="n">
-        <v>-16.9</v>
+        <v>23.1</v>
       </c>
       <c r="L828" t="inlineStr">
         <is>
@@ -92959,7 +92959,7 @@
         </is>
       </c>
       <c r="N828" t="n">
-        <v>8.82</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="829">
@@ -92974,31 +92974,31 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>1961.9</v>
+        <v>1997</v>
       </c>
       <c r="D829" t="n">
         <v>2180.21</v>
       </c>
       <c r="E829" t="n">
-        <v>-218.31</v>
+        <v>-183.21</v>
       </c>
       <c r="F829" t="n">
-        <v>1977.8</v>
+        <v>2008.8</v>
       </c>
       <c r="G829" t="n">
         <v>2071.34</v>
       </c>
       <c r="H829" t="n">
-        <v>-93.54000000000001</v>
+        <v>-62.54</v>
       </c>
       <c r="I829" t="n">
-        <v>1903.8</v>
+        <v>1953</v>
       </c>
       <c r="J829" t="n">
         <v>1902.46</v>
       </c>
       <c r="K829" t="n">
-        <v>1.34</v>
+        <v>50.54</v>
       </c>
       <c r="L829" t="inlineStr">
         <is>
@@ -93011,7 +93011,7 @@
         </is>
       </c>
       <c r="N829" t="n">
-        <v>10.01</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="830">
@@ -93026,31 +93026,31 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>2518</v>
+        <v>2618.4</v>
       </c>
       <c r="D830" t="n">
         <v>2864.38</v>
       </c>
       <c r="E830" t="n">
-        <v>-346.38</v>
+        <v>-245.98</v>
       </c>
       <c r="F830" t="n">
-        <v>2563.9</v>
+        <v>2618.4</v>
       </c>
       <c r="G830" t="n">
         <v>2655</v>
       </c>
       <c r="H830" t="n">
-        <v>-91.09999999999999</v>
+        <v>-36.6</v>
       </c>
       <c r="I830" t="n">
-        <v>2455.2</v>
+        <v>2498.7</v>
       </c>
       <c r="J830" t="n">
         <v>2444.26</v>
       </c>
       <c r="K830" t="n">
-        <v>10.94</v>
+        <v>54.44</v>
       </c>
       <c r="L830" t="inlineStr">
         <is>
@@ -93063,7 +93063,7 @@
         </is>
       </c>
       <c r="N830" t="n">
-        <v>12.09</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="831">
@@ -93078,31 +93078,31 @@
         </is>
       </c>
       <c r="C831" t="n">
-        <v>2165.3</v>
+        <v>2213.9</v>
       </c>
       <c r="D831" t="n">
         <v>2199.7</v>
       </c>
       <c r="E831" t="n">
-        <v>-34.4</v>
+        <v>14.2</v>
       </c>
       <c r="F831" t="n">
-        <v>2219</v>
+        <v>2213.9</v>
       </c>
       <c r="G831" t="n">
         <v>2272.28</v>
       </c>
       <c r="H831" t="n">
-        <v>-53.28</v>
+        <v>-58.38</v>
       </c>
       <c r="I831" t="n">
-        <v>2156.3</v>
+        <v>2100</v>
       </c>
       <c r="J831" t="n">
         <v>2109.94</v>
       </c>
       <c r="K831" t="n">
-        <v>46.36</v>
+        <v>-9.94</v>
       </c>
       <c r="L831" t="inlineStr">
         <is>
@@ -93115,7 +93115,7 @@
         </is>
       </c>
       <c r="N831" t="n">
-        <v>1.56</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="832">
@@ -93130,31 +93130,31 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>1400.5</v>
+        <v>1420</v>
       </c>
       <c r="D832" t="n">
         <v>1469.33</v>
       </c>
       <c r="E832" t="n">
-        <v>-68.83</v>
+        <v>-49.33</v>
       </c>
       <c r="F832" t="n">
-        <v>1401.4</v>
+        <v>1420</v>
       </c>
       <c r="G832" t="n">
         <v>1469.78</v>
       </c>
       <c r="H832" t="n">
-        <v>-68.38</v>
+        <v>-49.78</v>
       </c>
       <c r="I832" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="J832" t="n">
         <v>1364.62</v>
       </c>
       <c r="K832" t="n">
-        <v>-0.62</v>
+        <v>26.38</v>
       </c>
       <c r="L832" t="inlineStr">
         <is>
@@ -93167,7 +93167,7 @@
         </is>
       </c>
       <c r="N832" t="n">
-        <v>4.68</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="833">
@@ -93182,31 +93182,31 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>2460</v>
+        <v>2496.9</v>
       </c>
       <c r="D833" t="n">
         <v>2639.85</v>
       </c>
       <c r="E833" t="n">
-        <v>-179.85</v>
+        <v>-142.95</v>
       </c>
       <c r="F833" t="n">
-        <v>2461.3</v>
+        <v>2534.9</v>
       </c>
       <c r="G833" t="n">
         <v>2593.31</v>
       </c>
       <c r="H833" t="n">
-        <v>-132.01</v>
+        <v>-58.41</v>
       </c>
       <c r="I833" t="n">
-        <v>2408.2</v>
+        <v>2465.4</v>
       </c>
       <c r="J833" t="n">
         <v>2388.36</v>
       </c>
       <c r="K833" t="n">
-        <v>19.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="L833" t="inlineStr">
         <is>
@@ -93219,7 +93219,7 @@
         </is>
       </c>
       <c r="N833" t="n">
-        <v>6.81</v>
+        <v>5.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N833"/>
+  <dimension ref="A1:N842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43752,6 +43752,474 @@
       </c>
       <c r="N833" t="n">
         <v>2.11</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D834" t="n">
+        <v>119.72</v>
+      </c>
+      <c r="E834" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="G834" t="n">
+        <v>123.39</v>
+      </c>
+      <c r="H834" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I834" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="J834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="K834" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N834" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="D835" t="n">
+        <v>670.77</v>
+      </c>
+      <c r="E835" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="F835" t="n">
+        <v>696</v>
+      </c>
+      <c r="G835" t="n">
+        <v>686.61</v>
+      </c>
+      <c r="H835" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="I835" t="n">
+        <v>665</v>
+      </c>
+      <c r="J835" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="K835" t="n">
+        <v>-29.35</v>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N835" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>1403.9</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1408.8</v>
+      </c>
+      <c r="E836" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="F836" t="n">
+        <v>1421.9</v>
+      </c>
+      <c r="G836" t="n">
+        <v>1408.8</v>
+      </c>
+      <c r="H836" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I836" t="n">
+        <v>1391.1</v>
+      </c>
+      <c r="J836" t="n">
+        <v>1368.32</v>
+      </c>
+      <c r="K836" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N836" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>1345</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1216.88</v>
+      </c>
+      <c r="E837" t="n">
+        <v>128.12</v>
+      </c>
+      <c r="F837" t="n">
+        <v>1352.8</v>
+      </c>
+      <c r="G837" t="n">
+        <v>1306.39</v>
+      </c>
+      <c r="H837" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I837" t="n">
+        <v>1336.1</v>
+      </c>
+      <c r="J837" t="n">
+        <v>1321.6</v>
+      </c>
+      <c r="K837" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N837" t="n">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D838" t="n">
+        <v>1877.73</v>
+      </c>
+      <c r="E838" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="F838" t="n">
+        <v>1978.5</v>
+      </c>
+      <c r="G838" t="n">
+        <v>1924.25</v>
+      </c>
+      <c r="H838" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="I838" t="n">
+        <v>1939</v>
+      </c>
+      <c r="J838" t="n">
+        <v>1945.66</v>
+      </c>
+      <c r="K838" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N838" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D839" t="n">
+        <v>5591.81</v>
+      </c>
+      <c r="E839" t="n">
+        <v>288.19</v>
+      </c>
+      <c r="F839" t="n">
+        <v>5905.5</v>
+      </c>
+      <c r="G839" t="n">
+        <v>5749.84</v>
+      </c>
+      <c r="H839" t="n">
+        <v>155.66</v>
+      </c>
+      <c r="I839" t="n">
+        <v>5800</v>
+      </c>
+      <c r="J839" t="n">
+        <v>5813.2</v>
+      </c>
+      <c r="K839" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N839" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D840" t="n">
+        <v>2293.76</v>
+      </c>
+      <c r="E840" t="n">
+        <v>-98.76000000000001</v>
+      </c>
+      <c r="F840" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G840" t="n">
+        <v>2293.76</v>
+      </c>
+      <c r="H840" t="n">
+        <v>-54.76</v>
+      </c>
+      <c r="I840" t="n">
+        <v>2158.9</v>
+      </c>
+      <c r="J840" t="n">
+        <v>2152.56</v>
+      </c>
+      <c r="K840" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N840" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>2561.3</v>
+      </c>
+      <c r="D841" t="n">
+        <v>2443.07</v>
+      </c>
+      <c r="E841" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="F841" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G841" t="n">
+        <v>2443.07</v>
+      </c>
+      <c r="H841" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="I841" t="n">
+        <v>2501.7</v>
+      </c>
+      <c r="J841" t="n">
+        <v>2478.79</v>
+      </c>
+      <c r="K841" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N841" t="n">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>2478</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2445.12</v>
+      </c>
+      <c r="E842" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="F842" t="n">
+        <v>2509.5</v>
+      </c>
+      <c r="G842" t="n">
+        <v>2445.12</v>
+      </c>
+      <c r="H842" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="I842" t="n">
+        <v>2464</v>
+      </c>
+      <c r="J842" t="n">
+        <v>2402.59</v>
+      </c>
+      <c r="K842" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N842" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
@@ -43765,7 +44233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49870,6 +50338,110 @@
       </c>
       <c r="N117" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="D118" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>22961.95</v>
+      </c>
+      <c r="G118" t="n">
+        <v>23046.89</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-84.94</v>
+      </c>
+      <c r="I118" t="n">
+        <v>22656.75</v>
+      </c>
+      <c r="J118" t="n">
+        <v>22741.69</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-84.94</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>54909.65</v>
+      </c>
+      <c r="D119" t="n">
+        <v>54909.65</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>54980.15</v>
+      </c>
+      <c r="G119" t="n">
+        <v>55243.9</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-263.75</v>
+      </c>
+      <c r="I119" t="n">
+        <v>54047.9</v>
+      </c>
+      <c r="J119" t="n">
+        <v>54311.65</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-263.75</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -49883,7 +50455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N833"/>
+  <dimension ref="A1:N842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93222,6 +93794,474 @@
         <v>5.42</v>
       </c>
     </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>PNB (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D834" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="E834" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="G834" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="H834" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I834" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="J834" t="n">
+        <v>123.07</v>
+      </c>
+      <c r="K834" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N834" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>DLF (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="D835" t="n">
+        <v>687.39</v>
+      </c>
+      <c r="E835" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="F835" t="n">
+        <v>696</v>
+      </c>
+      <c r="G835" t="n">
+        <v>693.16</v>
+      </c>
+      <c r="H835" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I835" t="n">
+        <v>665</v>
+      </c>
+      <c r="J835" t="n">
+        <v>691.78</v>
+      </c>
+      <c r="K835" t="n">
+        <v>-26.78</v>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N835" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>DRREDDY (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>1345</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1250.18</v>
+      </c>
+      <c r="E836" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="F836" t="n">
+        <v>1352.8</v>
+      </c>
+      <c r="G836" t="n">
+        <v>1345.97</v>
+      </c>
+      <c r="H836" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I836" t="n">
+        <v>1336.1</v>
+      </c>
+      <c r="J836" t="n">
+        <v>1337.46</v>
+      </c>
+      <c r="K836" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N836" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>COFORGE (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1958.54</v>
+      </c>
+      <c r="E837" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F837" t="n">
+        <v>1978.5</v>
+      </c>
+      <c r="G837" t="n">
+        <v>1992.21</v>
+      </c>
+      <c r="H837" t="n">
+        <v>-13.71</v>
+      </c>
+      <c r="I837" t="n">
+        <v>1939</v>
+      </c>
+      <c r="J837" t="n">
+        <v>1928.41</v>
+      </c>
+      <c r="K837" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N837" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>PERSISTENT (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D838" t="n">
+        <v>5833.67</v>
+      </c>
+      <c r="E838" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="F838" t="n">
+        <v>5905.5</v>
+      </c>
+      <c r="G838" t="n">
+        <v>5971.68</v>
+      </c>
+      <c r="H838" t="n">
+        <v>-66.18000000000001</v>
+      </c>
+      <c r="I838" t="n">
+        <v>5800</v>
+      </c>
+      <c r="J838" t="n">
+        <v>5778.4</v>
+      </c>
+      <c r="K838" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N838" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D839" t="n">
+        <v>2372.43</v>
+      </c>
+      <c r="E839" t="n">
+        <v>-177.43</v>
+      </c>
+      <c r="F839" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G839" t="n">
+        <v>2210.82</v>
+      </c>
+      <c r="H839" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="I839" t="n">
+        <v>2158.9</v>
+      </c>
+      <c r="J839" t="n">
+        <v>2171.54</v>
+      </c>
+      <c r="K839" t="n">
+        <v>-12.64</v>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N839" t="n">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>MPHASIS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>2561.3</v>
+      </c>
+      <c r="D840" t="n">
+        <v>2546.87</v>
+      </c>
+      <c r="E840" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="F840" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G840" t="n">
+        <v>2599.4</v>
+      </c>
+      <c r="H840" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="I840" t="n">
+        <v>2501.7</v>
+      </c>
+      <c r="J840" t="n">
+        <v>2518.49</v>
+      </c>
+      <c r="K840" t="n">
+        <v>-16.79</v>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N840" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>HCLTECH (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>1403.9</v>
+      </c>
+      <c r="D841" t="n">
+        <v>1458.79</v>
+      </c>
+      <c r="E841" t="n">
+        <v>-54.89</v>
+      </c>
+      <c r="F841" t="n">
+        <v>1421.9</v>
+      </c>
+      <c r="G841" t="n">
+        <v>1415.58</v>
+      </c>
+      <c r="H841" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I841" t="n">
+        <v>1391.1</v>
+      </c>
+      <c r="J841" t="n">
+        <v>1387.66</v>
+      </c>
+      <c r="K841" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N841" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>TCS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>2478</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2544.55</v>
+      </c>
+      <c r="E842" t="n">
+        <v>-66.55</v>
+      </c>
+      <c r="F842" t="n">
+        <v>2509.5</v>
+      </c>
+      <c r="G842" t="n">
+        <v>2510.64</v>
+      </c>
+      <c r="H842" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="I842" t="n">
+        <v>2464</v>
+      </c>
+      <c r="J842" t="n">
+        <v>2439.89</v>
+      </c>
+      <c r="K842" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N842" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -43766,31 +43766,31 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>123.9</v>
+        <v>120.31</v>
       </c>
       <c r="D834" t="n">
         <v>119.72</v>
       </c>
       <c r="E834" t="n">
-        <v>4.18</v>
+        <v>0.59</v>
       </c>
       <c r="F834" t="n">
-        <v>123.9</v>
+        <v>121.5</v>
       </c>
       <c r="G834" t="n">
         <v>123.39</v>
       </c>
       <c r="H834" t="n">
-        <v>0.51</v>
+        <v>-1.89</v>
       </c>
       <c r="I834" t="n">
-        <v>119.62</v>
+        <v>119.42</v>
       </c>
       <c r="J834" t="n">
         <v>123.9</v>
       </c>
       <c r="K834" t="n">
-        <v>-4.28</v>
+        <v>-4.48</v>
       </c>
       <c r="L834" t="inlineStr">
         <is>
@@ -43799,11 +43799,11 @@
       </c>
       <c r="M834" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N834" t="n">
-        <v>3.49</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="835">
@@ -43818,31 +43818,31 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>694.35</v>
+        <v>666.3</v>
       </c>
       <c r="D835" t="n">
         <v>670.77</v>
       </c>
       <c r="E835" t="n">
-        <v>23.58</v>
+        <v>-4.47</v>
       </c>
       <c r="F835" t="n">
-        <v>696</v>
+        <v>671.4</v>
       </c>
       <c r="G835" t="n">
         <v>686.61</v>
       </c>
       <c r="H835" t="n">
-        <v>9.390000000000001</v>
+        <v>-15.21</v>
       </c>
       <c r="I835" t="n">
-        <v>665</v>
+        <v>663.95</v>
       </c>
       <c r="J835" t="n">
         <v>694.35</v>
       </c>
       <c r="K835" t="n">
-        <v>-29.35</v>
+        <v>-30.4</v>
       </c>
       <c r="L835" t="inlineStr">
         <is>
@@ -43851,11 +43851,11 @@
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N835" t="n">
-        <v>3.52</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="836">
@@ -43870,31 +43870,31 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>1403.9</v>
+        <v>1400.5</v>
       </c>
       <c r="D836" t="n">
         <v>1408.8</v>
       </c>
       <c r="E836" t="n">
-        <v>-4.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F836" t="n">
-        <v>1421.9</v>
+        <v>1401.4</v>
       </c>
       <c r="G836" t="n">
         <v>1408.8</v>
       </c>
       <c r="H836" t="n">
-        <v>13.1</v>
+        <v>-7.4</v>
       </c>
       <c r="I836" t="n">
-        <v>1391.1</v>
+        <v>1364</v>
       </c>
       <c r="J836" t="n">
         <v>1368.32</v>
       </c>
       <c r="K836" t="n">
-        <v>22.78</v>
+        <v>-4.32</v>
       </c>
       <c r="L836" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         </is>
       </c>
       <c r="N836" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="837">
@@ -43922,31 +43922,31 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>1345</v>
+        <v>1335.4</v>
       </c>
       <c r="D837" t="n">
         <v>1216.88</v>
       </c>
       <c r="E837" t="n">
-        <v>128.12</v>
+        <v>118.52</v>
       </c>
       <c r="F837" t="n">
-        <v>1352.8</v>
+        <v>1338.2</v>
       </c>
       <c r="G837" t="n">
         <v>1306.39</v>
       </c>
       <c r="H837" t="n">
-        <v>46.41</v>
+        <v>31.81</v>
       </c>
       <c r="I837" t="n">
-        <v>1336.1</v>
+        <v>1301</v>
       </c>
       <c r="J837" t="n">
         <v>1321.6</v>
       </c>
       <c r="K837" t="n">
-        <v>14.5</v>
+        <v>-20.6</v>
       </c>
       <c r="L837" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         </is>
       </c>
       <c r="N837" t="n">
-        <v>10.53</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="838">
@@ -43974,31 +43974,31 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>1962</v>
+        <v>1961.9</v>
       </c>
       <c r="D838" t="n">
         <v>1877.73</v>
       </c>
       <c r="E838" t="n">
-        <v>84.27</v>
+        <v>84.17</v>
       </c>
       <c r="F838" t="n">
-        <v>1978.5</v>
+        <v>1977.8</v>
       </c>
       <c r="G838" t="n">
         <v>1924.25</v>
       </c>
       <c r="H838" t="n">
-        <v>54.25</v>
+        <v>53.55</v>
       </c>
       <c r="I838" t="n">
-        <v>1939</v>
+        <v>1903.8</v>
       </c>
       <c r="J838" t="n">
         <v>1945.66</v>
       </c>
       <c r="K838" t="n">
-        <v>-6.66</v>
+        <v>-41.86</v>
       </c>
       <c r="L838" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         </is>
       </c>
       <c r="N838" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="839">
@@ -44026,31 +44026,31 @@
         </is>
       </c>
       <c r="C839" t="n">
-        <v>5880</v>
+        <v>5848</v>
       </c>
       <c r="D839" t="n">
         <v>5591.81</v>
       </c>
       <c r="E839" t="n">
-        <v>288.19</v>
+        <v>256.19</v>
       </c>
       <c r="F839" t="n">
-        <v>5905.5</v>
+        <v>5872.5</v>
       </c>
       <c r="G839" t="n">
         <v>5749.84</v>
       </c>
       <c r="H839" t="n">
-        <v>155.66</v>
+        <v>122.66</v>
       </c>
       <c r="I839" t="n">
-        <v>5800</v>
+        <v>5650</v>
       </c>
       <c r="J839" t="n">
         <v>5813.2</v>
       </c>
       <c r="K839" t="n">
-        <v>-13.2</v>
+        <v>-163.2</v>
       </c>
       <c r="L839" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="N839" t="n">
-        <v>5.15</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="840">
@@ -44078,31 +44078,31 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>2195</v>
+        <v>2165.3</v>
       </c>
       <c r="D840" t="n">
         <v>2293.76</v>
       </c>
       <c r="E840" t="n">
-        <v>-98.76000000000001</v>
+        <v>-128.46</v>
       </c>
       <c r="F840" t="n">
-        <v>2239</v>
+        <v>2219</v>
       </c>
       <c r="G840" t="n">
         <v>2293.76</v>
       </c>
       <c r="H840" t="n">
-        <v>-54.76</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="I840" t="n">
-        <v>2158.9</v>
+        <v>2156.3</v>
       </c>
       <c r="J840" t="n">
         <v>2152.56</v>
       </c>
       <c r="K840" t="n">
-        <v>6.34</v>
+        <v>3.74</v>
       </c>
       <c r="L840" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         </is>
       </c>
       <c r="N840" t="n">
-        <v>4.31</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="841">
@@ -44130,31 +44130,31 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>2561.3</v>
+        <v>2518</v>
       </c>
       <c r="D841" t="n">
         <v>2443.07</v>
       </c>
       <c r="E841" t="n">
-        <v>118.23</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="F841" t="n">
-        <v>2562</v>
+        <v>2563.9</v>
       </c>
       <c r="G841" t="n">
         <v>2443.07</v>
       </c>
       <c r="H841" t="n">
-        <v>118.93</v>
+        <v>120.83</v>
       </c>
       <c r="I841" t="n">
-        <v>2501.7</v>
+        <v>2455.2</v>
       </c>
       <c r="J841" t="n">
         <v>2478.79</v>
       </c>
       <c r="K841" t="n">
-        <v>22.91</v>
+        <v>-23.59</v>
       </c>
       <c r="L841" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         </is>
       </c>
       <c r="N841" t="n">
-        <v>4.84</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="842">
@@ -44182,31 +44182,31 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>2478</v>
+        <v>2460</v>
       </c>
       <c r="D842" t="n">
         <v>2445.12</v>
       </c>
       <c r="E842" t="n">
-        <v>32.88</v>
+        <v>14.88</v>
       </c>
       <c r="F842" t="n">
-        <v>2509.5</v>
+        <v>2461.3</v>
       </c>
       <c r="G842" t="n">
         <v>2445.12</v>
       </c>
       <c r="H842" t="n">
-        <v>64.38</v>
+        <v>16.18</v>
       </c>
       <c r="I842" t="n">
-        <v>2464</v>
+        <v>2408.2</v>
       </c>
       <c r="J842" t="n">
         <v>2402.59</v>
       </c>
       <c r="K842" t="n">
-        <v>61.41</v>
+        <v>5.61</v>
       </c>
       <c r="L842" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         </is>
       </c>
       <c r="N842" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -50352,31 +50352,31 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>22936.75</v>
+        <v>22698.85</v>
       </c>
       <c r="D118" t="n">
         <v>22936.75</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>-237.9</v>
       </c>
       <c r="F118" t="n">
-        <v>22961.95</v>
+        <v>22778.05</v>
       </c>
       <c r="G118" t="n">
         <v>23046.89</v>
       </c>
       <c r="H118" t="n">
-        <v>-84.94</v>
+        <v>-268.84</v>
       </c>
       <c r="I118" t="n">
-        <v>22656.75</v>
+        <v>22497.7</v>
       </c>
       <c r="J118" t="n">
         <v>22741.69</v>
       </c>
       <c r="K118" t="n">
-        <v>-84.94</v>
+        <v>-243.99</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="119">
@@ -50404,31 +50404,31 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>54909.65</v>
+        <v>54267.4</v>
       </c>
       <c r="D119" t="n">
         <v>54909.65</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>-642.25</v>
       </c>
       <c r="F119" t="n">
-        <v>54980.15</v>
+        <v>54440.25</v>
       </c>
       <c r="G119" t="n">
         <v>55243.9</v>
       </c>
       <c r="H119" t="n">
-        <v>-263.75</v>
+        <v>-803.65</v>
       </c>
       <c r="I119" t="n">
-        <v>54047.9</v>
+        <v>53626.15</v>
       </c>
       <c r="J119" t="n">
         <v>54311.65</v>
       </c>
       <c r="K119" t="n">
-        <v>-263.75</v>
+        <v>-685.5</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
@@ -93806,31 +93806,31 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>123.9</v>
+        <v>120.31</v>
       </c>
       <c r="D834" t="n">
         <v>123.03</v>
       </c>
       <c r="E834" t="n">
-        <v>0.87</v>
+        <v>-2.72</v>
       </c>
       <c r="F834" t="n">
-        <v>123.9</v>
+        <v>121.5</v>
       </c>
       <c r="G834" t="n">
         <v>124.18</v>
       </c>
       <c r="H834" t="n">
-        <v>-0.28</v>
+        <v>-2.68</v>
       </c>
       <c r="I834" t="n">
-        <v>119.62</v>
+        <v>119.42</v>
       </c>
       <c r="J834" t="n">
         <v>123.07</v>
       </c>
       <c r="K834" t="n">
-        <v>-3.45</v>
+        <v>-3.65</v>
       </c>
       <c r="L834" t="inlineStr">
         <is>
@@ -93843,7 +93843,7 @@
         </is>
       </c>
       <c r="N834" t="n">
-        <v>0.71</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="835">
@@ -93858,31 +93858,31 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>694.35</v>
+        <v>666.3</v>
       </c>
       <c r="D835" t="n">
         <v>687.39</v>
       </c>
       <c r="E835" t="n">
-        <v>6.96</v>
+        <v>-21.09</v>
       </c>
       <c r="F835" t="n">
-        <v>696</v>
+        <v>671.4</v>
       </c>
       <c r="G835" t="n">
         <v>693.16</v>
       </c>
       <c r="H835" t="n">
-        <v>2.84</v>
+        <v>-21.76</v>
       </c>
       <c r="I835" t="n">
-        <v>665</v>
+        <v>663.95</v>
       </c>
       <c r="J835" t="n">
         <v>691.78</v>
       </c>
       <c r="K835" t="n">
-        <v>-26.78</v>
+        <v>-27.83</v>
       </c>
       <c r="L835" t="inlineStr">
         <is>
@@ -93891,11 +93891,11 @@
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N835" t="n">
-        <v>1.01</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="836">
@@ -93910,31 +93910,31 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>1345</v>
+        <v>1335.4</v>
       </c>
       <c r="D836" t="n">
         <v>1250.18</v>
       </c>
       <c r="E836" t="n">
-        <v>94.81999999999999</v>
+        <v>85.22</v>
       </c>
       <c r="F836" t="n">
-        <v>1352.8</v>
+        <v>1338.2</v>
       </c>
       <c r="G836" t="n">
         <v>1345.97</v>
       </c>
       <c r="H836" t="n">
-        <v>6.83</v>
+        <v>-7.77</v>
       </c>
       <c r="I836" t="n">
-        <v>1336.1</v>
+        <v>1301</v>
       </c>
       <c r="J836" t="n">
         <v>1337.46</v>
       </c>
       <c r="K836" t="n">
-        <v>-1.36</v>
+        <v>-36.46</v>
       </c>
       <c r="L836" t="inlineStr">
         <is>
@@ -93947,7 +93947,7 @@
         </is>
       </c>
       <c r="N836" t="n">
-        <v>7.58</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="837">
@@ -93962,31 +93962,31 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>1962</v>
+        <v>1961.9</v>
       </c>
       <c r="D837" t="n">
         <v>1958.54</v>
       </c>
       <c r="E837" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="F837" t="n">
-        <v>1978.5</v>
+        <v>1977.8</v>
       </c>
       <c r="G837" t="n">
         <v>1992.21</v>
       </c>
       <c r="H837" t="n">
-        <v>-13.71</v>
+        <v>-14.41</v>
       </c>
       <c r="I837" t="n">
-        <v>1939</v>
+        <v>1903.8</v>
       </c>
       <c r="J837" t="n">
         <v>1928.41</v>
       </c>
       <c r="K837" t="n">
-        <v>10.59</v>
+        <v>-24.61</v>
       </c>
       <c r="L837" t="inlineStr">
         <is>
@@ -93999,7 +93999,7 @@
         </is>
       </c>
       <c r="N837" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="838">
@@ -94014,31 +94014,31 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>5880</v>
+        <v>5848</v>
       </c>
       <c r="D838" t="n">
         <v>5833.67</v>
       </c>
       <c r="E838" t="n">
-        <v>46.33</v>
+        <v>14.33</v>
       </c>
       <c r="F838" t="n">
-        <v>5905.5</v>
+        <v>5872.5</v>
       </c>
       <c r="G838" t="n">
         <v>5971.68</v>
       </c>
       <c r="H838" t="n">
-        <v>-66.18000000000001</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="I838" t="n">
-        <v>5800</v>
+        <v>5650</v>
       </c>
       <c r="J838" t="n">
         <v>5778.4</v>
       </c>
       <c r="K838" t="n">
-        <v>21.6</v>
+        <v>-128.4</v>
       </c>
       <c r="L838" t="inlineStr">
         <is>
@@ -94051,7 +94051,7 @@
         </is>
       </c>
       <c r="N838" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="839">
@@ -94066,31 +94066,31 @@
         </is>
       </c>
       <c r="C839" t="n">
-        <v>2195</v>
+        <v>2165.3</v>
       </c>
       <c r="D839" t="n">
         <v>2372.43</v>
       </c>
       <c r="E839" t="n">
-        <v>-177.43</v>
+        <v>-207.13</v>
       </c>
       <c r="F839" t="n">
-        <v>2239</v>
+        <v>2219</v>
       </c>
       <c r="G839" t="n">
         <v>2210.82</v>
       </c>
       <c r="H839" t="n">
-        <v>28.18</v>
+        <v>8.18</v>
       </c>
       <c r="I839" t="n">
-        <v>2158.9</v>
+        <v>2156.3</v>
       </c>
       <c r="J839" t="n">
         <v>2171.54</v>
       </c>
       <c r="K839" t="n">
-        <v>-12.64</v>
+        <v>-15.24</v>
       </c>
       <c r="L839" t="inlineStr">
         <is>
@@ -94103,7 +94103,7 @@
         </is>
       </c>
       <c r="N839" t="n">
-        <v>7.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="840">
@@ -94118,31 +94118,31 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>2561.3</v>
+        <v>2518</v>
       </c>
       <c r="D840" t="n">
         <v>2546.87</v>
       </c>
       <c r="E840" t="n">
-        <v>14.43</v>
+        <v>-28.87</v>
       </c>
       <c r="F840" t="n">
-        <v>2562</v>
+        <v>2563.9</v>
       </c>
       <c r="G840" t="n">
         <v>2599.4</v>
       </c>
       <c r="H840" t="n">
-        <v>-37.4</v>
+        <v>-35.5</v>
       </c>
       <c r="I840" t="n">
-        <v>2501.7</v>
+        <v>2455.2</v>
       </c>
       <c r="J840" t="n">
         <v>2518.49</v>
       </c>
       <c r="K840" t="n">
-        <v>-16.79</v>
+        <v>-63.29</v>
       </c>
       <c r="L840" t="inlineStr">
         <is>
@@ -94155,7 +94155,7 @@
         </is>
       </c>
       <c r="N840" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="841">
@@ -94170,31 +94170,31 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>1403.9</v>
+        <v>1400.5</v>
       </c>
       <c r="D841" t="n">
         <v>1458.79</v>
       </c>
       <c r="E841" t="n">
-        <v>-54.89</v>
+        <v>-58.29</v>
       </c>
       <c r="F841" t="n">
-        <v>1421.9</v>
+        <v>1401.4</v>
       </c>
       <c r="G841" t="n">
         <v>1415.58</v>
       </c>
       <c r="H841" t="n">
-        <v>6.32</v>
+        <v>-14.18</v>
       </c>
       <c r="I841" t="n">
-        <v>1391.1</v>
+        <v>1364</v>
       </c>
       <c r="J841" t="n">
         <v>1387.66</v>
       </c>
       <c r="K841" t="n">
-        <v>3.44</v>
+        <v>-23.66</v>
       </c>
       <c r="L841" t="inlineStr">
         <is>
@@ -94207,7 +94207,7 @@
         </is>
       </c>
       <c r="N841" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
     </row>
     <row r="842">
@@ -94222,31 +94222,31 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>2478</v>
+        <v>2460</v>
       </c>
       <c r="D842" t="n">
         <v>2544.55</v>
       </c>
       <c r="E842" t="n">
-        <v>-66.55</v>
+        <v>-84.55</v>
       </c>
       <c r="F842" t="n">
-        <v>2509.5</v>
+        <v>2461.3</v>
       </c>
       <c r="G842" t="n">
         <v>2510.64</v>
       </c>
       <c r="H842" t="n">
-        <v>-1.14</v>
+        <v>-49.34</v>
       </c>
       <c r="I842" t="n">
-        <v>2464</v>
+        <v>2408.2</v>
       </c>
       <c r="J842" t="n">
         <v>2439.89</v>
       </c>
       <c r="K842" t="n">
-        <v>24.11</v>
+        <v>-31.69</v>
       </c>
       <c r="L842" t="inlineStr">
         <is>
@@ -94259,7 +94259,7 @@
         </is>
       </c>
       <c r="N842" t="n">
-        <v>2.62</v>
+        <v>3.32</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N842"/>
+  <dimension ref="A1:N851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44220,6 +44220,474 @@
       </c>
       <c r="N842" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1495.56</v>
+      </c>
+      <c r="E843" t="n">
+        <v>-143.56</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1495.56</v>
+      </c>
+      <c r="H843" t="n">
+        <v>-131.86</v>
+      </c>
+      <c r="I843" t="n">
+        <v>1345</v>
+      </c>
+      <c r="J843" t="n">
+        <v>1294.83</v>
+      </c>
+      <c r="K843" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N843" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>186</v>
+      </c>
+      <c r="D844" t="n">
+        <v>188.55</v>
+      </c>
+      <c r="E844" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="F844" t="n">
+        <v>187.74</v>
+      </c>
+      <c r="G844" t="n">
+        <v>189.84</v>
+      </c>
+      <c r="H844" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I844" t="n">
+        <v>184.82</v>
+      </c>
+      <c r="J844" t="n">
+        <v>181.02</v>
+      </c>
+      <c r="K844" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N844" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="D845" t="n">
+        <v>1431.04</v>
+      </c>
+      <c r="E845" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="F845" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G845" t="n">
+        <v>1431.04</v>
+      </c>
+      <c r="H845" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="I845" t="n">
+        <v>1410</v>
+      </c>
+      <c r="J845" t="n">
+        <v>1355.96</v>
+      </c>
+      <c r="K845" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N845" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>691.55</v>
+      </c>
+      <c r="D846" t="n">
+        <v>692.4400000000001</v>
+      </c>
+      <c r="E846" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F846" t="n">
+        <v>699.6</v>
+      </c>
+      <c r="G846" t="n">
+        <v>692.4400000000001</v>
+      </c>
+      <c r="H846" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="I846" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="J846" t="n">
+        <v>662.24</v>
+      </c>
+      <c r="K846" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N846" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D847" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="E847" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F847" t="n">
+        <v>125.09</v>
+      </c>
+      <c r="G847" t="n">
+        <v>124.88</v>
+      </c>
+      <c r="H847" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I847" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="J847" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="K847" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N847" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>6048</v>
+      </c>
+      <c r="D848" t="n">
+        <v>6375.72</v>
+      </c>
+      <c r="E848" t="n">
+        <v>-327.72</v>
+      </c>
+      <c r="F848" t="n">
+        <v>6048.5</v>
+      </c>
+      <c r="G848" t="n">
+        <v>6375.72</v>
+      </c>
+      <c r="H848" t="n">
+        <v>-327.22</v>
+      </c>
+      <c r="I848" t="n">
+        <v>5884</v>
+      </c>
+      <c r="J848" t="n">
+        <v>5900.42</v>
+      </c>
+      <c r="K848" t="n">
+        <v>-16.42</v>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N848" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>2502.6</v>
+      </c>
+      <c r="D849" t="n">
+        <v>2537.98</v>
+      </c>
+      <c r="E849" t="n">
+        <v>-35.38</v>
+      </c>
+      <c r="F849" t="n">
+        <v>2527.7</v>
+      </c>
+      <c r="G849" t="n">
+        <v>2537.98</v>
+      </c>
+      <c r="H849" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="I849" t="n">
+        <v>2494.2</v>
+      </c>
+      <c r="J849" t="n">
+        <v>2365.36</v>
+      </c>
+      <c r="K849" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N849" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>2525.6</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2623.88</v>
+      </c>
+      <c r="E850" t="n">
+        <v>-98.28</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2591.3</v>
+      </c>
+      <c r="G850" t="n">
+        <v>2623.88</v>
+      </c>
+      <c r="H850" t="n">
+        <v>-32.58</v>
+      </c>
+      <c r="I850" t="n">
+        <v>2516.6</v>
+      </c>
+      <c r="J850" t="n">
+        <v>2378.75</v>
+      </c>
+      <c r="K850" t="n">
+        <v>137.85</v>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N850" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="D851" t="n">
+        <v>2060.2</v>
+      </c>
+      <c r="E851" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="F851" t="n">
+        <v>2215.8</v>
+      </c>
+      <c r="G851" t="n">
+        <v>2197.59</v>
+      </c>
+      <c r="H851" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="I851" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="J851" t="n">
+        <v>2095.04</v>
+      </c>
+      <c r="K851" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N851" t="n">
+        <v>5.09</v>
       </c>
     </row>
   </sheetData>
@@ -44233,7 +44701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50442,6 +50910,110 @@
       </c>
       <c r="N119" t="n">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>23118.1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>23145.76</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-27.66</v>
+      </c>
+      <c r="I120" t="n">
+        <v>22905.1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>22932.76</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-27.66</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>54686.95</v>
+      </c>
+      <c r="D121" t="n">
+        <v>54686.95</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>55068.5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>54976.71</v>
+      </c>
+      <c r="H121" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="I121" t="n">
+        <v>54580.75</v>
+      </c>
+      <c r="J121" t="n">
+        <v>54488.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -50455,7 +51027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N842"/>
+  <dimension ref="A1:N851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94262,6 +94834,474 @@
         <v>3.32</v>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>DRREDDY (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1534.14</v>
+      </c>
+      <c r="E843" t="n">
+        <v>-182.14</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1394.74</v>
+      </c>
+      <c r="H843" t="n">
+        <v>-31.04</v>
+      </c>
+      <c r="I843" t="n">
+        <v>1345</v>
+      </c>
+      <c r="J843" t="n">
+        <v>1309.69</v>
+      </c>
+      <c r="K843" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N843" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>PERSISTENT (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>6048</v>
+      </c>
+      <c r="D844" t="n">
+        <v>6633.44</v>
+      </c>
+      <c r="E844" t="n">
+        <v>-585.4400000000001</v>
+      </c>
+      <c r="F844" t="n">
+        <v>6048.5</v>
+      </c>
+      <c r="G844" t="n">
+        <v>6324.62</v>
+      </c>
+      <c r="H844" t="n">
+        <v>-276.12</v>
+      </c>
+      <c r="I844" t="n">
+        <v>5884</v>
+      </c>
+      <c r="J844" t="n">
+        <v>5795.47</v>
+      </c>
+      <c r="K844" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N844" t="n">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>UNIONBANK (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>186</v>
+      </c>
+      <c r="D845" t="n">
+        <v>194.45</v>
+      </c>
+      <c r="E845" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="F845" t="n">
+        <v>187.74</v>
+      </c>
+      <c r="G845" t="n">
+        <v>192.87</v>
+      </c>
+      <c r="H845" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="I845" t="n">
+        <v>184.82</v>
+      </c>
+      <c r="J845" t="n">
+        <v>179.45</v>
+      </c>
+      <c r="K845" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N845" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>HCLTECH (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="D846" t="n">
+        <v>1480.33</v>
+      </c>
+      <c r="E846" t="n">
+        <v>-52.23</v>
+      </c>
+      <c r="F846" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G846" t="n">
+        <v>1485.16</v>
+      </c>
+      <c r="H846" t="n">
+        <v>-33.16</v>
+      </c>
+      <c r="I846" t="n">
+        <v>1410</v>
+      </c>
+      <c r="J846" t="n">
+        <v>1374.6</v>
+      </c>
+      <c r="K846" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N846" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>DLF (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>691.55</v>
+      </c>
+      <c r="D847" t="n">
+        <v>710.37</v>
+      </c>
+      <c r="E847" t="n">
+        <v>-18.82</v>
+      </c>
+      <c r="F847" t="n">
+        <v>699.6</v>
+      </c>
+      <c r="G847" t="n">
+        <v>713.47</v>
+      </c>
+      <c r="H847" t="n">
+        <v>-13.87</v>
+      </c>
+      <c r="I847" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="J847" t="n">
+        <v>669.86</v>
+      </c>
+      <c r="K847" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N847" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>PNB (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D848" t="n">
+        <v>128.11</v>
+      </c>
+      <c r="E848" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="F848" t="n">
+        <v>125.09</v>
+      </c>
+      <c r="G848" t="n">
+        <v>127.16</v>
+      </c>
+      <c r="H848" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="I848" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="J848" t="n">
+        <v>118.68</v>
+      </c>
+      <c r="K848" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N848" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TCS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>2502.6</v>
+      </c>
+      <c r="D849" t="n">
+        <v>2636.85</v>
+      </c>
+      <c r="E849" t="n">
+        <v>-134.25</v>
+      </c>
+      <c r="F849" t="n">
+        <v>2527.7</v>
+      </c>
+      <c r="G849" t="n">
+        <v>2613.52</v>
+      </c>
+      <c r="H849" t="n">
+        <v>-85.81999999999999</v>
+      </c>
+      <c r="I849" t="n">
+        <v>2494.2</v>
+      </c>
+      <c r="J849" t="n">
+        <v>2400.73</v>
+      </c>
+      <c r="K849" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N849" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2130.38</v>
+      </c>
+      <c r="E850" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2215.8</v>
+      </c>
+      <c r="G850" t="n">
+        <v>2250.83</v>
+      </c>
+      <c r="H850" t="n">
+        <v>-35.03</v>
+      </c>
+      <c r="I850" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="J850" t="n">
+        <v>2084.55</v>
+      </c>
+      <c r="K850" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N850" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>MPHASIS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>2525.6</v>
+      </c>
+      <c r="D851" t="n">
+        <v>2735.2</v>
+      </c>
+      <c r="E851" t="n">
+        <v>-209.6</v>
+      </c>
+      <c r="F851" t="n">
+        <v>2591.3</v>
+      </c>
+      <c r="G851" t="n">
+        <v>2646.01</v>
+      </c>
+      <c r="H851" t="n">
+        <v>-54.71</v>
+      </c>
+      <c r="I851" t="n">
+        <v>2516.6</v>
+      </c>
+      <c r="J851" t="n">
+        <v>2416.52</v>
+      </c>
+      <c r="K851" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N851" t="n">
+        <v>7.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -44234,31 +44234,31 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="D843" t="n">
         <v>1495.56</v>
       </c>
       <c r="E843" t="n">
-        <v>-143.56</v>
+        <v>-150.56</v>
       </c>
       <c r="F843" t="n">
-        <v>1363.7</v>
+        <v>1352.8</v>
       </c>
       <c r="G843" t="n">
         <v>1495.56</v>
       </c>
       <c r="H843" t="n">
-        <v>-131.86</v>
+        <v>-142.76</v>
       </c>
       <c r="I843" t="n">
-        <v>1345</v>
+        <v>1336.1</v>
       </c>
       <c r="J843" t="n">
         <v>1294.83</v>
       </c>
       <c r="K843" t="n">
-        <v>50.17</v>
+        <v>41.27</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         </is>
       </c>
       <c r="N843" t="n">
-        <v>9.6</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="844">
@@ -44286,31 +44286,31 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>186</v>
+        <v>186.5</v>
       </c>
       <c r="D844" t="n">
         <v>188.55</v>
       </c>
       <c r="E844" t="n">
-        <v>-2.55</v>
+        <v>-2.05</v>
       </c>
       <c r="F844" t="n">
-        <v>187.74</v>
+        <v>187.5</v>
       </c>
       <c r="G844" t="n">
         <v>189.84</v>
       </c>
       <c r="H844" t="n">
-        <v>-2.1</v>
+        <v>-2.34</v>
       </c>
       <c r="I844" t="n">
-        <v>184.82</v>
+        <v>182.55</v>
       </c>
       <c r="J844" t="n">
         <v>181.02</v>
       </c>
       <c r="K844" t="n">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         </is>
       </c>
       <c r="N844" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="845">
@@ -44338,31 +44338,31 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>1428.1</v>
+        <v>1403.9</v>
       </c>
       <c r="D845" t="n">
         <v>1431.04</v>
       </c>
       <c r="E845" t="n">
-        <v>-2.94</v>
+        <v>-27.14</v>
       </c>
       <c r="F845" t="n">
-        <v>1452</v>
+        <v>1421.9</v>
       </c>
       <c r="G845" t="n">
         <v>1431.04</v>
       </c>
       <c r="H845" t="n">
-        <v>20.96</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="I845" t="n">
-        <v>1410</v>
+        <v>1391.1</v>
       </c>
       <c r="J845" t="n">
         <v>1355.96</v>
       </c>
       <c r="K845" t="n">
-        <v>54.04</v>
+        <v>35.14</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>0.21</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="846">
@@ -44390,31 +44390,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>691.55</v>
+        <v>694.35</v>
       </c>
       <c r="D846" t="n">
         <v>692.4400000000001</v>
       </c>
       <c r="E846" t="n">
-        <v>-0.89</v>
+        <v>1.91</v>
       </c>
       <c r="F846" t="n">
-        <v>699.6</v>
+        <v>696</v>
       </c>
       <c r="G846" t="n">
         <v>692.4400000000001</v>
       </c>
       <c r="H846" t="n">
-        <v>7.16</v>
+        <v>3.56</v>
       </c>
       <c r="I846" t="n">
-        <v>686.5</v>
+        <v>665</v>
       </c>
       <c r="J846" t="n">
         <v>662.24</v>
       </c>
       <c r="K846" t="n">
-        <v>24.26</v>
+        <v>2.76</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         </is>
       </c>
       <c r="N846" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="847">
@@ -44442,31 +44442,31 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>122.85</v>
+        <v>123.9</v>
       </c>
       <c r="D847" t="n">
         <v>124.44</v>
       </c>
       <c r="E847" t="n">
-        <v>-1.59</v>
+        <v>-0.54</v>
       </c>
       <c r="F847" t="n">
-        <v>125.09</v>
+        <v>123.9</v>
       </c>
       <c r="G847" t="n">
         <v>124.88</v>
       </c>
       <c r="H847" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
       <c r="I847" t="n">
-        <v>122.48</v>
+        <v>119.62</v>
       </c>
       <c r="J847" t="n">
         <v>119.06</v>
       </c>
       <c r="K847" t="n">
-        <v>3.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         </is>
       </c>
       <c r="N847" t="n">
-        <v>1.28</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="848">
@@ -44494,31 +44494,31 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>6048</v>
+        <v>5880</v>
       </c>
       <c r="D848" t="n">
         <v>6375.72</v>
       </c>
       <c r="E848" t="n">
-        <v>-327.72</v>
+        <v>-495.72</v>
       </c>
       <c r="F848" t="n">
-        <v>6048.5</v>
+        <v>5905.5</v>
       </c>
       <c r="G848" t="n">
         <v>6375.72</v>
       </c>
       <c r="H848" t="n">
-        <v>-327.22</v>
+        <v>-470.22</v>
       </c>
       <c r="I848" t="n">
-        <v>5884</v>
+        <v>5800</v>
       </c>
       <c r="J848" t="n">
         <v>5900.42</v>
       </c>
       <c r="K848" t="n">
-        <v>-16.42</v>
+        <v>-100.42</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -44527,11 +44527,11 @@
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N848" t="n">
-        <v>5.14</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="849">
@@ -44546,31 +44546,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2502.6</v>
+        <v>2478</v>
       </c>
       <c r="D849" t="n">
         <v>2537.98</v>
       </c>
       <c r="E849" t="n">
-        <v>-35.38</v>
+        <v>-59.98</v>
       </c>
       <c r="F849" t="n">
-        <v>2527.7</v>
+        <v>2509.5</v>
       </c>
       <c r="G849" t="n">
         <v>2537.98</v>
       </c>
       <c r="H849" t="n">
-        <v>-10.28</v>
+        <v>-28.48</v>
       </c>
       <c r="I849" t="n">
-        <v>2494.2</v>
+        <v>2464</v>
       </c>
       <c r="J849" t="n">
         <v>2365.36</v>
       </c>
       <c r="K849" t="n">
-        <v>128.84</v>
+        <v>98.64</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         </is>
       </c>
       <c r="N849" t="n">
-        <v>1.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="850">
@@ -44598,31 +44598,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2525.6</v>
+        <v>2561.3</v>
       </c>
       <c r="D850" t="n">
         <v>2623.88</v>
       </c>
       <c r="E850" t="n">
-        <v>-98.28</v>
+        <v>-62.58</v>
       </c>
       <c r="F850" t="n">
-        <v>2591.3</v>
+        <v>2562</v>
       </c>
       <c r="G850" t="n">
         <v>2623.88</v>
       </c>
       <c r="H850" t="n">
-        <v>-32.58</v>
+        <v>-61.88</v>
       </c>
       <c r="I850" t="n">
-        <v>2516.6</v>
+        <v>2501.7</v>
       </c>
       <c r="J850" t="n">
         <v>2378.75</v>
       </c>
       <c r="K850" t="n">
-        <v>137.85</v>
+        <v>122.95</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         </is>
       </c>
       <c r="N850" t="n">
-        <v>3.75</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="851">
@@ -44650,31 +44650,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2165.1</v>
+        <v>2195</v>
       </c>
       <c r="D851" t="n">
         <v>2060.2</v>
       </c>
       <c r="E851" t="n">
-        <v>104.9</v>
+        <v>134.8</v>
       </c>
       <c r="F851" t="n">
-        <v>2215.8</v>
+        <v>2239</v>
       </c>
       <c r="G851" t="n">
         <v>2197.59</v>
       </c>
       <c r="H851" t="n">
-        <v>18.21</v>
+        <v>41.41</v>
       </c>
       <c r="I851" t="n">
-        <v>2165.1</v>
+        <v>2158.9</v>
       </c>
       <c r="J851" t="n">
         <v>2095.04</v>
       </c>
       <c r="K851" t="n">
-        <v>70.06</v>
+        <v>63.86</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         </is>
       </c>
       <c r="N851" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
   </sheetData>
@@ -50924,31 +50924,31 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>23053.1</v>
+        <v>22936.75</v>
       </c>
       <c r="D120" t="n">
         <v>23053.1</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>-116.35</v>
       </c>
       <c r="F120" t="n">
-        <v>23118.1</v>
+        <v>22961.95</v>
       </c>
       <c r="G120" t="n">
         <v>23145.76</v>
       </c>
       <c r="H120" t="n">
-        <v>-27.66</v>
+        <v>-183.81</v>
       </c>
       <c r="I120" t="n">
-        <v>22905.1</v>
+        <v>22656.75</v>
       </c>
       <c r="J120" t="n">
         <v>22932.76</v>
       </c>
       <c r="K120" t="n">
-        <v>-27.66</v>
+        <v>-276.01</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="121">
@@ -50976,31 +50976,31 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>54686.95</v>
+        <v>54909.65</v>
       </c>
       <c r="D121" t="n">
         <v>54686.95</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>222.7</v>
       </c>
       <c r="F121" t="n">
-        <v>55068.5</v>
+        <v>54980.15</v>
       </c>
       <c r="G121" t="n">
         <v>54976.71</v>
       </c>
       <c r="H121" t="n">
-        <v>91.79000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="I121" t="n">
-        <v>54580.75</v>
+        <v>54047.9</v>
       </c>
       <c r="J121" t="n">
         <v>54488.96</v>
       </c>
       <c r="K121" t="n">
-        <v>91.79000000000001</v>
+        <v>-441.06</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -94846,31 +94846,31 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="D843" t="n">
         <v>1534.14</v>
       </c>
       <c r="E843" t="n">
-        <v>-182.14</v>
+        <v>-189.14</v>
       </c>
       <c r="F843" t="n">
-        <v>1363.7</v>
+        <v>1352.8</v>
       </c>
       <c r="G843" t="n">
         <v>1394.74</v>
       </c>
       <c r="H843" t="n">
-        <v>-31.04</v>
+        <v>-41.94</v>
       </c>
       <c r="I843" t="n">
-        <v>1345</v>
+        <v>1336.1</v>
       </c>
       <c r="J843" t="n">
         <v>1309.69</v>
       </c>
       <c r="K843" t="n">
-        <v>35.31</v>
+        <v>26.41</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -94883,7 +94883,7 @@
         </is>
       </c>
       <c r="N843" t="n">
-        <v>11.87</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="844">
@@ -94898,31 +94898,31 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>6048</v>
+        <v>5880</v>
       </c>
       <c r="D844" t="n">
         <v>6633.44</v>
       </c>
       <c r="E844" t="n">
-        <v>-585.4400000000001</v>
+        <v>-753.4400000000001</v>
       </c>
       <c r="F844" t="n">
-        <v>6048.5</v>
+        <v>5905.5</v>
       </c>
       <c r="G844" t="n">
         <v>6324.62</v>
       </c>
       <c r="H844" t="n">
-        <v>-276.12</v>
+        <v>-419.12</v>
       </c>
       <c r="I844" t="n">
-        <v>5884</v>
+        <v>5800</v>
       </c>
       <c r="J844" t="n">
         <v>5795.47</v>
       </c>
       <c r="K844" t="n">
-        <v>88.53</v>
+        <v>4.53</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
@@ -94935,7 +94935,7 @@
         </is>
       </c>
       <c r="N844" t="n">
-        <v>8.83</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="845">
@@ -94950,31 +94950,31 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>186</v>
+        <v>186.5</v>
       </c>
       <c r="D845" t="n">
         <v>194.45</v>
       </c>
       <c r="E845" t="n">
-        <v>-8.449999999999999</v>
+        <v>-7.95</v>
       </c>
       <c r="F845" t="n">
-        <v>187.74</v>
+        <v>187.5</v>
       </c>
       <c r="G845" t="n">
         <v>192.87</v>
       </c>
       <c r="H845" t="n">
-        <v>-5.13</v>
+        <v>-5.37</v>
       </c>
       <c r="I845" t="n">
-        <v>184.82</v>
+        <v>182.55</v>
       </c>
       <c r="J845" t="n">
         <v>179.45</v>
       </c>
       <c r="K845" t="n">
-        <v>5.37</v>
+        <v>3.1</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -94987,7 +94987,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>4.35</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="846">
@@ -95002,31 +95002,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>1428.1</v>
+        <v>1403.9</v>
       </c>
       <c r="D846" t="n">
         <v>1480.33</v>
       </c>
       <c r="E846" t="n">
-        <v>-52.23</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="F846" t="n">
-        <v>1452</v>
+        <v>1421.9</v>
       </c>
       <c r="G846" t="n">
         <v>1485.16</v>
       </c>
       <c r="H846" t="n">
-        <v>-33.16</v>
+        <v>-63.26</v>
       </c>
       <c r="I846" t="n">
-        <v>1410</v>
+        <v>1391.1</v>
       </c>
       <c r="J846" t="n">
         <v>1374.6</v>
       </c>
       <c r="K846" t="n">
-        <v>35.4</v>
+        <v>16.5</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -95039,7 +95039,7 @@
         </is>
       </c>
       <c r="N846" t="n">
-        <v>3.53</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="847">
@@ -95054,31 +95054,31 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>691.55</v>
+        <v>694.35</v>
       </c>
       <c r="D847" t="n">
         <v>710.37</v>
       </c>
       <c r="E847" t="n">
-        <v>-18.82</v>
+        <v>-16.02</v>
       </c>
       <c r="F847" t="n">
-        <v>699.6</v>
+        <v>696</v>
       </c>
       <c r="G847" t="n">
         <v>713.47</v>
       </c>
       <c r="H847" t="n">
-        <v>-13.87</v>
+        <v>-17.47</v>
       </c>
       <c r="I847" t="n">
-        <v>686.5</v>
+        <v>665</v>
       </c>
       <c r="J847" t="n">
         <v>669.86</v>
       </c>
       <c r="K847" t="n">
-        <v>16.64</v>
+        <v>-4.86</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -95087,11 +95087,11 @@
       </c>
       <c r="M847" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N847" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="848">
@@ -95106,31 +95106,31 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>122.85</v>
+        <v>123.9</v>
       </c>
       <c r="D848" t="n">
         <v>128.11</v>
       </c>
       <c r="E848" t="n">
-        <v>-5.26</v>
+        <v>-4.21</v>
       </c>
       <c r="F848" t="n">
-        <v>125.09</v>
+        <v>123.9</v>
       </c>
       <c r="G848" t="n">
         <v>127.16</v>
       </c>
       <c r="H848" t="n">
-        <v>-2.07</v>
+        <v>-3.26</v>
       </c>
       <c r="I848" t="n">
-        <v>122.48</v>
+        <v>119.62</v>
       </c>
       <c r="J848" t="n">
         <v>118.68</v>
       </c>
       <c r="K848" t="n">
-        <v>3.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -95143,7 +95143,7 @@
         </is>
       </c>
       <c r="N848" t="n">
-        <v>4.11</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="849">
@@ -95158,31 +95158,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2502.6</v>
+        <v>2478</v>
       </c>
       <c r="D849" t="n">
         <v>2636.85</v>
       </c>
       <c r="E849" t="n">
-        <v>-134.25</v>
+        <v>-158.85</v>
       </c>
       <c r="F849" t="n">
-        <v>2527.7</v>
+        <v>2509.5</v>
       </c>
       <c r="G849" t="n">
         <v>2613.52</v>
       </c>
       <c r="H849" t="n">
-        <v>-85.81999999999999</v>
+        <v>-104.02</v>
       </c>
       <c r="I849" t="n">
-        <v>2494.2</v>
+        <v>2464</v>
       </c>
       <c r="J849" t="n">
         <v>2400.73</v>
       </c>
       <c r="K849" t="n">
-        <v>93.47</v>
+        <v>63.27</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -95195,7 +95195,7 @@
         </is>
       </c>
       <c r="N849" t="n">
-        <v>5.09</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="850">
@@ -95210,31 +95210,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2165.1</v>
+        <v>2195</v>
       </c>
       <c r="D850" t="n">
         <v>2130.38</v>
       </c>
       <c r="E850" t="n">
-        <v>34.72</v>
+        <v>64.62</v>
       </c>
       <c r="F850" t="n">
-        <v>2215.8</v>
+        <v>2239</v>
       </c>
       <c r="G850" t="n">
         <v>2250.83</v>
       </c>
       <c r="H850" t="n">
-        <v>-35.03</v>
+        <v>-11.83</v>
       </c>
       <c r="I850" t="n">
-        <v>2165.1</v>
+        <v>2158.9</v>
       </c>
       <c r="J850" t="n">
         <v>2084.55</v>
       </c>
       <c r="K850" t="n">
-        <v>80.55</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -95247,7 +95247,7 @@
         </is>
       </c>
       <c r="N850" t="n">
-        <v>1.63</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="851">
@@ -95262,31 +95262,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2525.6</v>
+        <v>2561.3</v>
       </c>
       <c r="D851" t="n">
         <v>2735.2</v>
       </c>
       <c r="E851" t="n">
-        <v>-209.6</v>
+        <v>-173.9</v>
       </c>
       <c r="F851" t="n">
-        <v>2591.3</v>
+        <v>2562</v>
       </c>
       <c r="G851" t="n">
         <v>2646.01</v>
       </c>
       <c r="H851" t="n">
-        <v>-54.71</v>
+        <v>-84.01000000000001</v>
       </c>
       <c r="I851" t="n">
-        <v>2516.6</v>
+        <v>2501.7</v>
       </c>
       <c r="J851" t="n">
         <v>2416.52</v>
       </c>
       <c r="K851" t="n">
-        <v>100.08</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -95299,7 +95299,7 @@
         </is>
       </c>
       <c r="N851" t="n">
-        <v>7.66</v>
+        <v>6.36</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Accuracy_Report.xlsx
+++ b/Post_Market_Accuracy_Report.xlsx
@@ -44234,31 +44234,31 @@
         </is>
       </c>
       <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1225.62</v>
+      </c>
+      <c r="E843" t="n">
+        <v>126.38</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1328.8</v>
+      </c>
+      <c r="H843" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="I843" t="n">
         <v>1345</v>
       </c>
-      <c r="D843" t="n">
-        <v>1495.56</v>
-      </c>
-      <c r="E843" t="n">
-        <v>-150.56</v>
-      </c>
-      <c r="F843" t="n">
-        <v>1352.8</v>
-      </c>
-      <c r="G843" t="n">
-        <v>1495.56</v>
-      </c>
-      <c r="H843" t="n">
-        <v>-142.76</v>
-      </c>
-      <c r="I843" t="n">
-        <v>1336.1</v>
-      </c>
       <c r="J843" t="n">
-        <v>1294.83</v>
+        <v>1334.32</v>
       </c>
       <c r="K843" t="n">
-        <v>41.27</v>
+        <v>10.68</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -44267,11 +44267,11 @@
       </c>
       <c r="M843" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N843" t="n">
-        <v>10.07</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="844">
@@ -44286,31 +44286,31 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>186.5</v>
+        <v>186</v>
       </c>
       <c r="D844" t="n">
-        <v>188.55</v>
+        <v>185.45</v>
       </c>
       <c r="E844" t="n">
-        <v>-2.05</v>
+        <v>0.55</v>
       </c>
       <c r="F844" t="n">
-        <v>187.5</v>
+        <v>187.74</v>
       </c>
       <c r="G844" t="n">
-        <v>189.84</v>
+        <v>186.74</v>
       </c>
       <c r="H844" t="n">
-        <v>-2.34</v>
+        <v>1</v>
       </c>
       <c r="I844" t="n">
-        <v>182.55</v>
+        <v>184.82</v>
       </c>
       <c r="J844" t="n">
-        <v>181.02</v>
+        <v>186</v>
       </c>
       <c r="K844" t="n">
-        <v>1.53</v>
+        <v>-1.18</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         </is>
       </c>
       <c r="N844" t="n">
-        <v>1.09</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="845">
@@ -44334,35 +44334,35 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C845" t="n">
-        <v>1403.9</v>
+        <v>122.85</v>
       </c>
       <c r="D845" t="n">
-        <v>1431.04</v>
+        <v>123.29</v>
       </c>
       <c r="E845" t="n">
-        <v>-27.14</v>
+        <v>-0.44</v>
       </c>
       <c r="F845" t="n">
-        <v>1421.9</v>
+        <v>125.09</v>
       </c>
       <c r="G845" t="n">
-        <v>1431.04</v>
+        <v>123.29</v>
       </c>
       <c r="H845" t="n">
-        <v>-9.140000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="I845" t="n">
-        <v>1391.1</v>
+        <v>122.48</v>
       </c>
       <c r="J845" t="n">
-        <v>1355.96</v>
+        <v>122.7</v>
       </c>
       <c r="K845" t="n">
-        <v>35.14</v>
+        <v>-0.22</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>1.9</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="846">
@@ -44390,31 +44390,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>694.35</v>
+        <v>691.55</v>
       </c>
       <c r="D846" t="n">
-        <v>692.4400000000001</v>
+        <v>699</v>
       </c>
       <c r="E846" t="n">
-        <v>1.91</v>
+        <v>-7.45</v>
       </c>
       <c r="F846" t="n">
-        <v>696</v>
+        <v>699.6</v>
       </c>
       <c r="G846" t="n">
-        <v>692.4400000000001</v>
+        <v>699</v>
       </c>
       <c r="H846" t="n">
-        <v>3.56</v>
+        <v>0.6</v>
       </c>
       <c r="I846" t="n">
-        <v>665</v>
+        <v>686.5</v>
       </c>
       <c r="J846" t="n">
-        <v>662.24</v>
+        <v>682.4400000000001</v>
       </c>
       <c r="K846" t="n">
-        <v>2.76</v>
+        <v>4.06</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         </is>
       </c>
       <c r="N846" t="n">
-        <v>0.28</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="847">
@@ -44438,35 +44438,35 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>123.9</v>
+        <v>1428.1</v>
       </c>
       <c r="D847" t="n">
-        <v>124.44</v>
+        <v>1412.21</v>
       </c>
       <c r="E847" t="n">
-        <v>-0.54</v>
+        <v>15.89</v>
       </c>
       <c r="F847" t="n">
-        <v>123.9</v>
+        <v>1452</v>
       </c>
       <c r="G847" t="n">
-        <v>124.88</v>
+        <v>1412.21</v>
       </c>
       <c r="H847" t="n">
-        <v>-0.98</v>
+        <v>39.79</v>
       </c>
       <c r="I847" t="n">
-        <v>119.62</v>
+        <v>1410</v>
       </c>
       <c r="J847" t="n">
-        <v>119.06</v>
+        <v>1397.31</v>
       </c>
       <c r="K847" t="n">
-        <v>0.5600000000000001</v>
+        <v>12.69</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         </is>
       </c>
       <c r="N847" t="n">
-        <v>0.43</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="848">
@@ -44494,31 +44494,31 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>5880</v>
+        <v>6048</v>
       </c>
       <c r="D848" t="n">
-        <v>6375.72</v>
+        <v>5622.39</v>
       </c>
       <c r="E848" t="n">
-        <v>-495.72</v>
+        <v>425.61</v>
       </c>
       <c r="F848" t="n">
-        <v>5905.5</v>
+        <v>6048.5</v>
       </c>
       <c r="G848" t="n">
-        <v>6375.72</v>
+        <v>6086.5</v>
       </c>
       <c r="H848" t="n">
-        <v>-470.22</v>
+        <v>-38</v>
       </c>
       <c r="I848" t="n">
-        <v>5800</v>
+        <v>5884</v>
       </c>
       <c r="J848" t="n">
-        <v>5900.42</v>
+        <v>6048</v>
       </c>
       <c r="K848" t="n">
-        <v>-100.42</v>
+        <v>-164</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         </is>
       </c>
       <c r="N848" t="n">
-        <v>7.78</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="849">
@@ -44546,31 +44546,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2478</v>
+        <v>2502.6</v>
       </c>
       <c r="D849" t="n">
-        <v>2537.98</v>
+        <v>2463.01</v>
       </c>
       <c r="E849" t="n">
-        <v>-59.98</v>
+        <v>39.59</v>
       </c>
       <c r="F849" t="n">
-        <v>2509.5</v>
+        <v>2527.7</v>
       </c>
       <c r="G849" t="n">
-        <v>2537.98</v>
+        <v>2463.01</v>
       </c>
       <c r="H849" t="n">
-        <v>-28.48</v>
+        <v>64.69</v>
       </c>
       <c r="I849" t="n">
-        <v>2464</v>
+        <v>2494.2</v>
       </c>
       <c r="J849" t="n">
-        <v>2365.36</v>
+        <v>2437.51</v>
       </c>
       <c r="K849" t="n">
-        <v>98.64</v>
+        <v>56.69</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         </is>
       </c>
       <c r="N849" t="n">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="850">
@@ -44598,31 +44598,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2561.3</v>
+        <v>2525.6</v>
       </c>
       <c r="D850" t="n">
-        <v>2623.88</v>
+        <v>2485.08</v>
       </c>
       <c r="E850" t="n">
-        <v>-62.58</v>
+        <v>40.52</v>
       </c>
       <c r="F850" t="n">
-        <v>2562</v>
+        <v>2591.3</v>
       </c>
       <c r="G850" t="n">
-        <v>2623.88</v>
+        <v>2485.08</v>
       </c>
       <c r="H850" t="n">
-        <v>-61.88</v>
+        <v>106.22</v>
       </c>
       <c r="I850" t="n">
-        <v>2501.7</v>
+        <v>2516.6</v>
       </c>
       <c r="J850" t="n">
-        <v>2378.75</v>
+        <v>2451.31</v>
       </c>
       <c r="K850" t="n">
-        <v>122.95</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         </is>
       </c>
       <c r="N850" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="851">
@@ -44650,31 +44650,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2195</v>
+        <v>2165.1</v>
       </c>
       <c r="D851" t="n">
-        <v>2060.2</v>
+        <v>2325.22</v>
       </c>
       <c r="E851" t="n">
-        <v>134.8</v>
+        <v>-160.12</v>
       </c>
       <c r="F851" t="n">
-        <v>2239</v>
+        <v>2215.8</v>
       </c>
       <c r="G851" t="n">
-        <v>2197.59</v>
+        <v>2325.22</v>
       </c>
       <c r="H851" t="n">
-        <v>41.41</v>
+        <v>-109.42</v>
       </c>
       <c r="I851" t="n">
-        <v>2158.9</v>
+        <v>2165.1</v>
       </c>
       <c r="J851" t="n">
-        <v>2095.04</v>
+        <v>2158.94</v>
       </c>
       <c r="K851" t="n">
-        <v>63.86</v>
+        <v>6.16</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         </is>
       </c>
       <c r="N851" t="n">
-        <v>6.54</v>
+        <v>6.89</v>
       </c>
     </row>
   </sheetData>
@@ -50924,31 +50924,31 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>22936.75</v>
+        <v>23053.1</v>
       </c>
       <c r="D120" t="n">
         <v>23053.1</v>
       </c>
       <c r="E120" t="n">
-        <v>-116.35</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>22961.95</v>
+        <v>23118.1</v>
       </c>
       <c r="G120" t="n">
         <v>23145.76</v>
       </c>
       <c r="H120" t="n">
-        <v>-183.81</v>
+        <v>-27.66</v>
       </c>
       <c r="I120" t="n">
-        <v>22656.75</v>
+        <v>22905.1</v>
       </c>
       <c r="J120" t="n">
         <v>22932.76</v>
       </c>
       <c r="K120" t="n">
-        <v>-276.01</v>
+        <v>-27.66</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -50976,31 +50976,31 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>54909.65</v>
+        <v>54686.95</v>
       </c>
       <c r="D121" t="n">
         <v>54686.95</v>
       </c>
       <c r="E121" t="n">
-        <v>222.7</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>54980.15</v>
+        <v>55068.5</v>
       </c>
       <c r="G121" t="n">
         <v>54976.71</v>
       </c>
       <c r="H121" t="n">
-        <v>3.44</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>54047.9</v>
+        <v>54580.75</v>
       </c>
       <c r="J121" t="n">
         <v>54488.96</v>
       </c>
       <c r="K121" t="n">
-        <v>-441.06</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -94846,31 +94846,31 @@
         </is>
       </c>
       <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1257.06</v>
+      </c>
+      <c r="E843" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1371.76</v>
+      </c>
+      <c r="H843" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="I843" t="n">
         <v>1345</v>
       </c>
-      <c r="D843" t="n">
-        <v>1534.14</v>
-      </c>
-      <c r="E843" t="n">
-        <v>-189.14</v>
-      </c>
-      <c r="F843" t="n">
-        <v>1352.8</v>
-      </c>
-      <c r="G843" t="n">
-        <v>1394.74</v>
-      </c>
-      <c r="H843" t="n">
-        <v>-41.94</v>
-      </c>
-      <c r="I843" t="n">
-        <v>1336.1</v>
-      </c>
       <c r="J843" t="n">
-        <v>1309.69</v>
+        <v>1349.43</v>
       </c>
       <c r="K843" t="n">
-        <v>26.41</v>
+        <v>-4.43</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -94879,11 +94879,11 @@
       </c>
       <c r="M843" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N843" t="n">
-        <v>12.33</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="844">
@@ -94898,44 +94898,44 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>5880</v>
+        <v>6048</v>
       </c>
       <c r="D844" t="n">
-        <v>6633.44</v>
+        <v>5848.82</v>
       </c>
       <c r="E844" t="n">
-        <v>-753.4400000000001</v>
+        <v>199.18</v>
       </c>
       <c r="F844" t="n">
-        <v>5905.5</v>
+        <v>6048.5</v>
       </c>
       <c r="G844" t="n">
-        <v>6324.62</v>
+        <v>6220.46</v>
       </c>
       <c r="H844" t="n">
-        <v>-419.12</v>
+        <v>-171.96</v>
       </c>
       <c r="I844" t="n">
-        <v>5800</v>
+        <v>5884</v>
       </c>
       <c r="J844" t="n">
-        <v>5795.47</v>
+        <v>5971.32</v>
       </c>
       <c r="K844" t="n">
-        <v>4.53</v>
+        <v>-87.31999999999999</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N844" t="n">
-        <v>11.36</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="845">
@@ -94950,31 +94950,31 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>186.5</v>
+        <v>186</v>
       </c>
       <c r="D845" t="n">
-        <v>194.45</v>
+        <v>191.22</v>
       </c>
       <c r="E845" t="n">
-        <v>-7.95</v>
+        <v>-5.22</v>
       </c>
       <c r="F845" t="n">
-        <v>187.5</v>
+        <v>187.74</v>
       </c>
       <c r="G845" t="n">
-        <v>192.87</v>
+        <v>189.69</v>
       </c>
       <c r="H845" t="n">
-        <v>-5.37</v>
+        <v>-1.95</v>
       </c>
       <c r="I845" t="n">
-        <v>182.55</v>
+        <v>184.82</v>
       </c>
       <c r="J845" t="n">
-        <v>179.45</v>
+        <v>184.89</v>
       </c>
       <c r="K845" t="n">
-        <v>3.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -94987,7 +94987,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>4.09</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="846">
@@ -95002,31 +95002,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>1403.9</v>
+        <v>1428.1</v>
       </c>
       <c r="D846" t="n">
-        <v>1480.33</v>
+        <v>1460.64</v>
       </c>
       <c r="E846" t="n">
-        <v>-76.43000000000001</v>
+        <v>-32.54</v>
       </c>
       <c r="F846" t="n">
-        <v>1421.9</v>
+        <v>1452</v>
       </c>
       <c r="G846" t="n">
-        <v>1485.16</v>
+        <v>1460.69</v>
       </c>
       <c r="H846" t="n">
-        <v>-63.26</v>
+        <v>-8.69</v>
       </c>
       <c r="I846" t="n">
-        <v>1391.1</v>
+        <v>1410</v>
       </c>
       <c r="J846" t="n">
-        <v>1374.6</v>
+        <v>1416.3</v>
       </c>
       <c r="K846" t="n">
-        <v>16.5</v>
+        <v>-6.3</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -95035,11 +95035,11 @@
       </c>
       <c r="M846" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N846" t="n">
-        <v>5.16</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="847">
@@ -95050,35 +95050,35 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>DLF (NOV-2026 FUT)</t>
+          <t>PNB (NOV-2026 FUT)</t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>694.35</v>
+        <v>122.85</v>
       </c>
       <c r="D847" t="n">
-        <v>710.37</v>
+        <v>126.91</v>
       </c>
       <c r="E847" t="n">
-        <v>-16.02</v>
+        <v>-4.06</v>
       </c>
       <c r="F847" t="n">
-        <v>696</v>
+        <v>125.09</v>
       </c>
       <c r="G847" t="n">
-        <v>713.47</v>
+        <v>125.07</v>
       </c>
       <c r="H847" t="n">
-        <v>-17.47</v>
+        <v>0.02</v>
       </c>
       <c r="I847" t="n">
-        <v>665</v>
+        <v>122.48</v>
       </c>
       <c r="J847" t="n">
-        <v>669.86</v>
+        <v>122.28</v>
       </c>
       <c r="K847" t="n">
-        <v>-4.86</v>
+        <v>0.2</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -95087,11 +95087,11 @@
       </c>
       <c r="M847" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N847" t="n">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="848">
@@ -95102,35 +95102,35 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>PNB (NOV-2026 FUT)</t>
+          <t>DLF (NOV-2026 FUT)</t>
         </is>
       </c>
       <c r="C848" t="n">
-        <v>123.9</v>
+        <v>691.55</v>
       </c>
       <c r="D848" t="n">
-        <v>128.11</v>
+        <v>717</v>
       </c>
       <c r="E848" t="n">
-        <v>-4.21</v>
+        <v>-25.45</v>
       </c>
       <c r="F848" t="n">
-        <v>123.9</v>
+        <v>699.6</v>
       </c>
       <c r="G848" t="n">
-        <v>127.16</v>
+        <v>701.72</v>
       </c>
       <c r="H848" t="n">
-        <v>-3.26</v>
+        <v>-2.12</v>
       </c>
       <c r="I848" t="n">
-        <v>119.62</v>
+        <v>686.5</v>
       </c>
       <c r="J848" t="n">
-        <v>118.68</v>
+        <v>690.1900000000001</v>
       </c>
       <c r="K848" t="n">
-        <v>0.9399999999999999</v>
+        <v>-3.69</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -95143,7 +95143,7 @@
         </is>
       </c>
       <c r="N848" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="849">
@@ -95158,31 +95158,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2478</v>
+        <v>2502.6</v>
       </c>
       <c r="D849" t="n">
-        <v>2636.85</v>
+        <v>2558.61</v>
       </c>
       <c r="E849" t="n">
-        <v>-158.85</v>
+        <v>-56.01</v>
       </c>
       <c r="F849" t="n">
-        <v>2509.5</v>
+        <v>2527.7</v>
       </c>
       <c r="G849" t="n">
-        <v>2613.52</v>
+        <v>2570.49</v>
       </c>
       <c r="H849" t="n">
-        <v>-104.02</v>
+        <v>-42.79</v>
       </c>
       <c r="I849" t="n">
-        <v>2464</v>
+        <v>2494.2</v>
       </c>
       <c r="J849" t="n">
-        <v>2400.73</v>
+        <v>2473.57</v>
       </c>
       <c r="K849" t="n">
-        <v>63.27</v>
+        <v>20.63</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -95191,11 +95191,11 @@
       </c>
       <c r="M849" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N849" t="n">
-        <v>6.02</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="850">
@@ -95210,31 +95210,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2195</v>
+        <v>2165.1</v>
       </c>
       <c r="D850" t="n">
-        <v>2130.38</v>
+        <v>2404.07</v>
       </c>
       <c r="E850" t="n">
-        <v>64.62</v>
+        <v>-238.97</v>
       </c>
       <c r="F850" t="n">
-        <v>2239</v>
+        <v>2215.8</v>
       </c>
       <c r="G850" t="n">
-        <v>2250.83</v>
+        <v>2213.75</v>
       </c>
       <c r="H850" t="n">
-        <v>-11.83</v>
+        <v>2.05</v>
       </c>
       <c r="I850" t="n">
-        <v>2158.9</v>
+        <v>2165.1</v>
       </c>
       <c r="J850" t="n">
-        <v>2084.55</v>
+        <v>2147.8</v>
       </c>
       <c r="K850" t="n">
-        <v>74.34999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -95243,11 +95243,11 @@
       </c>
       <c r="M850" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N850" t="n">
-        <v>3.03</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="851">
@@ -95262,31 +95262,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2561.3</v>
+        <v>2525.6</v>
       </c>
       <c r="D851" t="n">
-        <v>2735.2</v>
+        <v>2590.15</v>
       </c>
       <c r="E851" t="n">
-        <v>-173.9</v>
+        <v>-64.55</v>
       </c>
       <c r="F851" t="n">
-        <v>2562</v>
+        <v>2591.3</v>
       </c>
       <c r="G851" t="n">
-        <v>2646.01</v>
+        <v>2602.43</v>
       </c>
       <c r="H851" t="n">
-        <v>-84.01000000000001</v>
+        <v>-11.13</v>
       </c>
       <c r="I851" t="n">
-        <v>2501.7</v>
+        <v>2516.6</v>
       </c>
       <c r="J851" t="n">
-        <v>2416.52</v>
+        <v>2489.84</v>
       </c>
       <c r="K851" t="n">
-        <v>85.18000000000001</v>
+        <v>26.76</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -95295,11 +95295,11 @@
       </c>
       <c r="M851" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N851" t="n">
-        <v>6.36</v>
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>
